--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="627">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1184,6 +1184,9 @@
   </si>
   <si>
     <t>21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42</t>
+  </si>
+  <si>
+    <t>0_60|1_30|2_10</t>
   </si>
   <si>
     <t>概率在第1轴改出vs1符号</t>
@@ -8874,7 +8877,7 @@
         <v>341</v>
       </c>
       <c r="I188" s="14" t="s">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="K188" s="86"/>
     </row>
@@ -8886,10 +8889,10 @@
         <v>102000</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>56</v>
@@ -8898,13 +8901,13 @@
         <v>133</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K189" s="64"/>
     </row>
@@ -8916,10 +8919,10 @@
         <v>102000</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>193</v>
@@ -8928,13 +8931,13 @@
         <v>133</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K190" s="64"/>
     </row>
@@ -8946,10 +8949,10 @@
         <v>102000</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>195</v>
@@ -8958,13 +8961,13 @@
         <v>133</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K191" s="64"/>
     </row>
@@ -8976,10 +8979,10 @@
         <v>102000</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>196</v>
@@ -8988,13 +8991,13 @@
         <v>133</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K192" s="64"/>
     </row>
@@ -9006,10 +9009,10 @@
         <v>102000</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>205</v>
@@ -9018,13 +9021,13 @@
         <v>133</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K193" s="64"/>
     </row>
@@ -9036,10 +9039,10 @@
         <v>102000</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>205</v>
@@ -9048,13 +9051,13 @@
         <v>133</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K194" s="64"/>
     </row>
@@ -9066,10 +9069,10 @@
         <v>102000</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>205</v>
@@ -9078,7 +9081,7 @@
         <v>133</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>341</v>
@@ -9096,10 +9099,10 @@
         <v>102000</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>205</v>
@@ -9108,7 +9111,7 @@
         <v>133</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>341</v>
@@ -9126,10 +9129,10 @@
         <v>102000</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>205</v>
@@ -9138,7 +9141,7 @@
         <v>133</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>341</v>
@@ -9156,19 +9159,19 @@
         <v>102000</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F198" s="97" t="s">
         <v>133</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I198" s="2" t="s">
         <v>39</v>
@@ -9183,19 +9186,19 @@
         <v>102000</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F199" s="97" t="s">
         <v>133</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I199" s="2" t="s">
         <v>39</v>
@@ -9210,19 +9213,19 @@
         <v>102000</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F200" s="97" t="s">
         <v>133</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I200" s="2" t="s">
         <v>39</v>
@@ -9237,19 +9240,19 @@
         <v>102000</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F201" s="97" t="s">
         <v>133</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I201" s="2" t="s">
         <v>39</v>
@@ -9264,19 +9267,19 @@
         <v>102000</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F202" s="97" t="s">
         <v>133</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>341</v>
@@ -9294,13 +9297,13 @@
         <v>102000</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F203" s="98" t="s">
         <v>133</v>
@@ -9324,10 +9327,10 @@
         <v>102000</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>197</v>
@@ -9336,13 +9339,13 @@
         <v>133</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H204" s="7" t="s">
         <v>341</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K204" s="43"/>
     </row>
@@ -9354,25 +9357,25 @@
         <v>102000</v>
       </c>
       <c r="C205" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D205" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D205" s="7" t="s">
-        <v>372</v>
-      </c>
       <c r="E205" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F205" s="98" t="s">
         <v>133</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H205" s="7" t="s">
         <v>341</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K205" s="43"/>
     </row>
@@ -9384,10 +9387,10 @@
         <v>102000</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>61</v>
@@ -9396,13 +9399,13 @@
         <v>133</v>
       </c>
       <c r="G206" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H206" s="7" t="s">
         <v>341</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K206" s="43"/>
     </row>
@@ -9414,25 +9417,25 @@
         <v>102000</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F207" s="98" t="s">
         <v>133</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H207" s="7" t="s">
         <v>341</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K207" s="43"/>
     </row>
@@ -9444,19 +9447,19 @@
         <v>102000</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F208" s="98" t="s">
         <v>133</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>39</v>
@@ -9471,19 +9474,19 @@
         <v>102000</v>
       </c>
       <c r="C209" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E209" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="D209" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="E209" s="7" t="s">
-        <v>379</v>
-      </c>
       <c r="F209" s="98" t="s">
         <v>133</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>39</v>
@@ -9498,19 +9501,19 @@
         <v>102000</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F210" s="98" t="s">
         <v>133</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>39</v>
@@ -9525,19 +9528,19 @@
         <v>102000</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F211" s="98" t="s">
         <v>133</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I211" s="7" t="s">
         <v>39</v>
@@ -9552,13 +9555,13 @@
         <v>102000</v>
       </c>
       <c r="C212" s="20" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D212" s="20" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E212" s="20" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F212" s="99" t="s">
         <v>133</v>
@@ -9582,10 +9585,10 @@
         <v>102000</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D213" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E213" s="21" t="s">
         <v>77</v>
@@ -9594,13 +9597,13 @@
         <v>133</v>
       </c>
       <c r="G213" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H213" s="21" t="s">
         <v>341</v>
       </c>
       <c r="I213" s="21" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K213" s="101"/>
     </row>
@@ -9612,10 +9615,10 @@
         <v>102000</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D214" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E214" s="21" t="s">
         <v>199</v>
@@ -9624,13 +9627,13 @@
         <v>133</v>
       </c>
       <c r="G214" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H214" s="21" t="s">
         <v>341</v>
       </c>
       <c r="I214" s="21" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K214" s="101"/>
     </row>
@@ -9642,10 +9645,10 @@
         <v>102000</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D215" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E215" s="21" t="s">
         <v>202</v>
@@ -9654,13 +9657,13 @@
         <v>133</v>
       </c>
       <c r="G215" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H215" s="21" t="s">
         <v>341</v>
       </c>
       <c r="I215" s="21" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K215" s="101"/>
     </row>
@@ -9672,10 +9675,10 @@
         <v>102000</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D216" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E216" s="21" t="s">
         <v>203</v>
@@ -9684,13 +9687,13 @@
         <v>133</v>
       </c>
       <c r="G216" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H216" s="21" t="s">
         <v>341</v>
       </c>
       <c r="I216" s="21" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="K216" s="101"/>
     </row>
@@ -9702,19 +9705,19 @@
         <v>102000</v>
       </c>
       <c r="C217" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D217" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="D217" s="21" t="s">
-        <v>386</v>
-      </c>
       <c r="E217" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F217" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G217" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I217" s="21" t="s">
         <v>39</v>
@@ -9729,19 +9732,19 @@
         <v>102000</v>
       </c>
       <c r="C218" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="D218" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="E218" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="D218" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="E218" s="21" t="s">
-        <v>388</v>
-      </c>
       <c r="F218" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G218" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I218" s="21" t="s">
         <v>39</v>
@@ -9756,19 +9759,19 @@
         <v>102000</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D219" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F219" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G219" s="21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I219" s="21" t="s">
         <v>39</v>
@@ -9783,19 +9786,19 @@
         <v>102000</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D220" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F220" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G220" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I220" s="21" t="s">
         <v>39</v>
@@ -9813,7 +9816,7 @@
         <v>292</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E221" s="22" t="s">
         <v>136</v>
@@ -9825,10 +9828,10 @@
         <v>103</v>
       </c>
       <c r="H221" s="22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I221" s="22" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K221" s="103"/>
     </row>
@@ -9840,10 +9843,10 @@
         <v>103800</v>
       </c>
       <c r="C222" s="22" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E222" s="22" t="s">
         <v>31</v>
@@ -9855,7 +9858,7 @@
         <v>103</v>
       </c>
       <c r="H222" s="22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I222" s="22" t="s">
         <v>39</v>
@@ -9870,10 +9873,10 @@
         <v>103800</v>
       </c>
       <c r="C223" s="22" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E223" s="22" t="s">
         <v>23</v>
@@ -9885,7 +9888,7 @@
         <v>103</v>
       </c>
       <c r="H223" s="22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I223" s="22" t="s">
         <v>39</v>
@@ -9900,10 +9903,10 @@
         <v>103800</v>
       </c>
       <c r="C224" s="22" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E224" s="22" t="s">
         <v>140</v>
@@ -9912,16 +9915,16 @@
         <v>133</v>
       </c>
       <c r="G224" s="22" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H224" s="22" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I224" s="22" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J224" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K224" s="103" t="s">
         <v>29</v>
@@ -9947,10 +9950,10 @@
         <v>133</v>
       </c>
       <c r="G225" s="22" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H225" s="22" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I225" s="22" t="s">
         <v>39</v>
@@ -9965,10 +9968,10 @@
         <v>103800</v>
       </c>
       <c r="C226" s="22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E226" s="22" t="s">
         <v>140</v>
@@ -9977,16 +9980,16 @@
         <v>133</v>
       </c>
       <c r="G226" s="22" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H226" s="22" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I226" s="22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J226" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K226" s="103" t="s">
         <v>29</v>
@@ -10018,7 +10021,7 @@
         <v>10</v>
       </c>
       <c r="I227" s="23" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K227" s="104"/>
     </row>
@@ -10030,10 +10033,10 @@
         <v>102700</v>
       </c>
       <c r="C228" s="23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D228" s="23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E228" s="23" t="s">
         <v>114</v>
@@ -10045,10 +10048,10 @@
         <v>232</v>
       </c>
       <c r="H228" s="23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I228" s="23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K228" s="104"/>
     </row>
@@ -10060,10 +10063,10 @@
         <v>102700</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D229" s="23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E229" s="23" t="s">
         <v>114</v>
@@ -10075,7 +10078,7 @@
         <v>232</v>
       </c>
       <c r="H229" s="23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I229" s="23" t="s">
         <v>72</v>
@@ -10090,7 +10093,7 @@
         <v>102700</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D230" s="23" t="s">
         <v>325</v>
@@ -10105,7 +10108,7 @@
         <v>232</v>
       </c>
       <c r="H230" s="23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I230" s="23" t="s">
         <v>287</v>
@@ -10120,13 +10123,13 @@
         <v>102700</v>
       </c>
       <c r="C231" s="23" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D231" s="23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F231" s="87" t="s">
         <v>133</v>
@@ -10135,7 +10138,7 @@
         <v>252</v>
       </c>
       <c r="H231" s="23" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I231" s="23" t="s">
         <v>39</v>
@@ -10153,7 +10156,7 @@
         <v>226</v>
       </c>
       <c r="D232" s="23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E232" s="23" t="s">
         <v>114</v>
@@ -10183,7 +10186,7 @@
         <v>292</v>
       </c>
       <c r="D233" s="24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E233" s="24" t="s">
         <v>293</v>
@@ -10195,7 +10198,7 @@
         <v>297</v>
       </c>
       <c r="H233" s="24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I233" s="24" t="s">
         <v>304</v>
@@ -10213,7 +10216,7 @@
         <v>292</v>
       </c>
       <c r="D234" s="24" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E234" s="24" t="s">
         <v>293</v>
@@ -10225,10 +10228,10 @@
         <v>48</v>
       </c>
       <c r="H234" s="24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I234" s="24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K234" s="106"/>
     </row>
@@ -10264,10 +10267,10 @@
         <v>103100</v>
       </c>
       <c r="C236" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D236" s="25" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E236" s="25" t="s">
         <v>136</v>
@@ -10276,7 +10279,7 @@
         <v>133</v>
       </c>
       <c r="G236" s="25" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H236" s="25">
         <v>12</v>
@@ -10294,10 +10297,10 @@
         <v>103100</v>
       </c>
       <c r="C237" s="25" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D237" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E237" s="25" t="s">
         <v>23</v>
@@ -10309,7 +10312,7 @@
         <v>174</v>
       </c>
       <c r="H237" s="25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I237" s="25" t="s">
         <v>39</v>
@@ -10324,10 +10327,10 @@
         <v>103100</v>
       </c>
       <c r="C238" s="25" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E238" s="25" t="s">
         <v>23</v>
@@ -10339,7 +10342,7 @@
         <v>176</v>
       </c>
       <c r="H238" s="25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I238" s="25" t="s">
         <v>39</v>
@@ -10354,10 +10357,10 @@
         <v>103100</v>
       </c>
       <c r="C239" s="25" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E239" s="25" t="s">
         <v>23</v>
@@ -10369,7 +10372,7 @@
         <v>178</v>
       </c>
       <c r="H239" s="25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I239" s="25" t="s">
         <v>39</v>
@@ -10384,10 +10387,10 @@
         <v>103100</v>
       </c>
       <c r="C240" s="25" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E240" s="25" t="s">
         <v>136</v>
@@ -10399,7 +10402,7 @@
         <v>176</v>
       </c>
       <c r="H240" s="25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I240" s="25" t="s">
         <v>107</v>
@@ -10414,10 +10417,10 @@
         <v>103100</v>
       </c>
       <c r="C241" s="25" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E241" s="25" t="s">
         <v>136</v>
@@ -10429,7 +10432,7 @@
         <v>263</v>
       </c>
       <c r="H241" s="25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I241" s="25" t="s">
         <v>157</v>
@@ -10447,7 +10450,7 @@
         <v>244</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E242" s="25" t="s">
         <v>140</v>
@@ -10459,10 +10462,10 @@
         <v>232</v>
       </c>
       <c r="H242" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I242" s="25" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K242" s="107"/>
     </row>
@@ -10474,7 +10477,7 @@
         <v>103100</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D243" s="25" t="s">
         <v>21</v>
@@ -10489,10 +10492,10 @@
         <v>232</v>
       </c>
       <c r="H243" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I243" s="25" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K243" s="107"/>
     </row>
@@ -10519,10 +10522,10 @@
         <v>232</v>
       </c>
       <c r="H244" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I244" s="25" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K244" s="107"/>
     </row>
@@ -10534,7 +10537,7 @@
         <v>103100</v>
       </c>
       <c r="C245" s="25" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D245" s="25" t="s">
         <v>21</v>
@@ -10549,7 +10552,7 @@
         <v>237</v>
       </c>
       <c r="H245" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I245" s="25" t="s">
         <v>106</v>
@@ -10564,10 +10567,10 @@
         <v>103100</v>
       </c>
       <c r="C246" s="25" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D246" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E246" s="25" t="s">
         <v>143</v>
@@ -10576,10 +10579,10 @@
         <v>133</v>
       </c>
       <c r="G246" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H246" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I246" s="25" t="s">
         <v>278</v>
@@ -10594,7 +10597,7 @@
         <v>103100</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D247" s="25" t="s">
         <v>21</v>
@@ -10606,10 +10609,10 @@
         <v>133</v>
       </c>
       <c r="G247" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H247" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I247" s="25" t="s">
         <v>39</v>
@@ -10624,7 +10627,7 @@
         <v>103100</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D248" s="25" t="s">
         <v>21</v>
@@ -10639,7 +10642,7 @@
         <v>252</v>
       </c>
       <c r="H248" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I248" s="25" t="s">
         <v>39</v>
@@ -10654,7 +10657,7 @@
         <v>103100</v>
       </c>
       <c r="C249" s="25" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D249" s="25" t="s">
         <v>21</v>
@@ -10669,7 +10672,7 @@
         <v>252</v>
       </c>
       <c r="H249" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I249" s="25" t="s">
         <v>39</v>
@@ -10684,7 +10687,7 @@
         <v>103100</v>
       </c>
       <c r="C250" s="25" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D250" s="25" t="s">
         <v>325</v>
@@ -10696,10 +10699,10 @@
         <v>133</v>
       </c>
       <c r="G250" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H250" s="25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I250" s="25" t="s">
         <v>138</v>
@@ -10714,7 +10717,7 @@
         <v>103100</v>
       </c>
       <c r="C251" s="25" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D251" s="25" t="s">
         <v>325</v>
@@ -10729,7 +10732,7 @@
         <v>263</v>
       </c>
       <c r="H251" s="25" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I251" s="25" t="s">
         <v>291</v>
@@ -10759,7 +10762,7 @@
         <v>232</v>
       </c>
       <c r="H252" s="26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I252" s="26" t="s">
         <v>274</v>
@@ -10789,10 +10792,10 @@
         <v>232</v>
       </c>
       <c r="H253" s="26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I253" s="26" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K253" s="108"/>
     </row>
@@ -10804,7 +10807,7 @@
         <v>104000</v>
       </c>
       <c r="C254" s="26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D254" s="26" t="s">
         <v>21</v>
@@ -10819,7 +10822,7 @@
         <v>174</v>
       </c>
       <c r="H254" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I254" s="26" t="s">
         <v>39</v>
@@ -10834,7 +10837,7 @@
         <v>104000</v>
       </c>
       <c r="C255" s="26" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D255" s="26" t="s">
         <v>21</v>
@@ -10849,7 +10852,7 @@
         <v>176</v>
       </c>
       <c r="H255" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I255" s="26" t="s">
         <v>39</v>
@@ -10864,7 +10867,7 @@
         <v>104000</v>
       </c>
       <c r="C256" s="26" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D256" s="26" t="s">
         <v>21</v>
@@ -10879,7 +10882,7 @@
         <v>178</v>
       </c>
       <c r="H256" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I256" s="26" t="s">
         <v>39</v>
@@ -10894,10 +10897,10 @@
         <v>104000</v>
       </c>
       <c r="C257" s="26" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D257" s="26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E257" s="26" t="s">
         <v>140</v>
@@ -10909,7 +10912,7 @@
         <v>174</v>
       </c>
       <c r="H257" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I257" s="26" t="s">
         <v>130</v>
@@ -10924,10 +10927,10 @@
         <v>104000</v>
       </c>
       <c r="C258" s="26" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D258" s="26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E258" s="26" t="s">
         <v>140</v>
@@ -10939,7 +10942,7 @@
         <v>176</v>
       </c>
       <c r="H258" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I258" s="26" t="s">
         <v>130</v>
@@ -10954,7 +10957,7 @@
         <v>104000</v>
       </c>
       <c r="C259" s="26" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D259" s="26" t="s">
         <v>325</v>
@@ -10969,7 +10972,7 @@
         <v>178</v>
       </c>
       <c r="H259" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I259" s="26" t="s">
         <v>130</v>
@@ -10984,7 +10987,7 @@
         <v>104000</v>
       </c>
       <c r="C260" s="26" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D260" s="26" t="s">
         <v>21</v>
@@ -10999,7 +11002,7 @@
         <v>252</v>
       </c>
       <c r="H260" s="26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I260" s="26" t="s">
         <v>39</v>
@@ -11017,7 +11020,7 @@
         <v>292</v>
       </c>
       <c r="D261" s="27" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E261" s="27" t="s">
         <v>157</v>
@@ -11029,7 +11032,7 @@
         <v>159</v>
       </c>
       <c r="H261" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I261" s="27" t="s">
         <v>274</v>
@@ -11044,10 +11047,10 @@
         <v>103900</v>
       </c>
       <c r="C262" s="27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D262" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E262" s="27" t="s">
         <v>157</v>
@@ -11059,7 +11062,7 @@
         <v>159</v>
       </c>
       <c r="H262" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I262" s="27" t="s">
         <v>39</v>
@@ -11074,7 +11077,7 @@
         <v>103900</v>
       </c>
       <c r="C263" s="27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D263" s="27" t="s">
         <v>21</v>
@@ -11089,7 +11092,7 @@
         <v>232</v>
       </c>
       <c r="H263" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I263" s="27" t="s">
         <v>284</v>
@@ -11119,7 +11122,7 @@
         <v>232</v>
       </c>
       <c r="H264" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I264" s="27" t="s">
         <v>246</v>
@@ -11149,7 +11152,7 @@
         <v>232</v>
       </c>
       <c r="H265" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I265" s="27" t="s">
         <v>106</v>
@@ -11170,7 +11173,7 @@
         <v>21</v>
       </c>
       <c r="E266" s="27" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F266" s="27" t="s">
         <v>133</v>
@@ -11179,7 +11182,7 @@
         <v>252</v>
       </c>
       <c r="H266" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I266" s="27" t="s">
         <v>39</v>
@@ -11197,7 +11200,7 @@
         <v>292</v>
       </c>
       <c r="D267" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E267" s="25" t="s">
         <v>140</v>
@@ -11206,10 +11209,10 @@
         <v>133</v>
       </c>
       <c r="G267" s="25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H267" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I267" s="25" t="s">
         <v>319</v>
@@ -11236,10 +11239,10 @@
         <v>133</v>
       </c>
       <c r="G268" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="H268" s="25" t="s">
         <v>453</v>
-      </c>
-      <c r="H268" s="25" t="s">
-        <v>452</v>
       </c>
       <c r="I268" s="25" t="s">
         <v>322</v>
@@ -11266,10 +11269,10 @@
         <v>133</v>
       </c>
       <c r="G269" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="H269" s="25" t="s">
         <v>453</v>
-      </c>
-      <c r="H269" s="25" t="s">
-        <v>452</v>
       </c>
       <c r="I269" s="25" t="s">
         <v>324</v>
@@ -11299,7 +11302,7 @@
         <v>321</v>
       </c>
       <c r="H270" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I270" s="25" t="s">
         <v>107</v>
@@ -11317,19 +11320,19 @@
         <v>327</v>
       </c>
       <c r="D271" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E271" s="25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F271" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G271" s="25" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H271" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I271" s="25" t="s">
         <v>330</v>
@@ -11347,19 +11350,19 @@
         <v>331</v>
       </c>
       <c r="D272" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E272" s="25" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F272" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G272" s="25" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H272" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I272" s="25" t="s">
         <v>330</v>
@@ -11377,19 +11380,19 @@
         <v>334</v>
       </c>
       <c r="D273" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E273" s="25" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F273" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G273" s="25" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H273" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I273" s="25" t="s">
         <v>246</v>
@@ -11404,7 +11407,7 @@
         <v>101600</v>
       </c>
       <c r="C274" s="25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D274" s="25" t="s">
         <v>325</v>
@@ -11416,13 +11419,13 @@
         <v>133</v>
       </c>
       <c r="G274" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="H274" s="25" t="s">
         <v>453</v>
       </c>
-      <c r="H274" s="25" t="s">
-        <v>452</v>
-      </c>
       <c r="I274" s="25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K274" s="107"/>
     </row>
@@ -11446,10 +11449,10 @@
         <v>133</v>
       </c>
       <c r="G275" s="25" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H275" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I275" s="25" t="s">
         <v>39</v>
@@ -11464,22 +11467,22 @@
         <v>101600</v>
       </c>
       <c r="C276" s="25" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D276" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E276" s="25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F276" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G276" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H276" s="25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I276" s="25" t="s">
         <v>39</v>
@@ -11494,22 +11497,22 @@
         <v>101600</v>
       </c>
       <c r="C277" s="25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D277" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E277" s="25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F277" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G277" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H277" s="25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I277" s="25" t="s">
         <v>39</v>
@@ -11524,22 +11527,22 @@
         <v>101600</v>
       </c>
       <c r="C278" s="25" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D278" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E278" s="25" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F278" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G278" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H278" s="25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I278" s="25" t="s">
         <v>39</v>
@@ -11554,22 +11557,22 @@
         <v>101600</v>
       </c>
       <c r="C279" s="25" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D279" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E279" s="25" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F279" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G279" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H279" s="25" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I279" s="25" t="s">
         <v>39</v>
@@ -11584,22 +11587,22 @@
         <v>101600</v>
       </c>
       <c r="C280" s="25" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D280" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E280" s="25" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F280" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G280" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H280" s="25" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I280" s="25" t="s">
         <v>39</v>
@@ -11614,22 +11617,22 @@
         <v>101600</v>
       </c>
       <c r="C281" s="25" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D281" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E281" s="25" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F281" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G281" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H281" s="25" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I281" s="25" t="s">
         <v>39</v>
@@ -11644,22 +11647,22 @@
         <v>101600</v>
       </c>
       <c r="C282" s="25" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D282" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E282" s="25" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F282" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G282" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H282" s="25" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I282" s="25" t="s">
         <v>39</v>
@@ -11674,22 +11677,22 @@
         <v>101600</v>
       </c>
       <c r="C283" s="25" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D283" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E283" s="25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F283" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G283" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H283" s="25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I283" s="25" t="s">
         <v>39</v>
@@ -11704,22 +11707,22 @@
         <v>101600</v>
       </c>
       <c r="C284" s="25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D284" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E284" s="25" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F284" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G284" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H284" s="25" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I284" s="25" t="s">
         <v>39</v>
@@ -11734,22 +11737,22 @@
         <v>101600</v>
       </c>
       <c r="C285" s="25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D285" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E285" s="25" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F285" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G285" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H285" s="25" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I285" s="25" t="s">
         <v>39</v>
@@ -11764,22 +11767,22 @@
         <v>101600</v>
       </c>
       <c r="C286" s="25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D286" s="25" t="s">
         <v>325</v>
       </c>
       <c r="E286" s="25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F286" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G286" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H286" s="25" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I286" s="25" t="s">
         <v>39</v>
@@ -11794,10 +11797,10 @@
         <v>101500</v>
       </c>
       <c r="C287" s="27" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D287" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E287" s="27" t="s">
         <v>143</v>
@@ -11809,10 +11812,10 @@
         <v>232</v>
       </c>
       <c r="H287" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I287" s="27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K287" s="109"/>
     </row>
@@ -11839,7 +11842,7 @@
         <v>232</v>
       </c>
       <c r="H288" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I288" s="27" t="s">
         <v>107</v>
@@ -11869,7 +11872,7 @@
         <v>232</v>
       </c>
       <c r="H289" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I289" s="27" t="s">
         <v>106</v>
@@ -11899,10 +11902,10 @@
         <v>232</v>
       </c>
       <c r="H290" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I290" s="27" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K290" s="109"/>
     </row>
@@ -11914,7 +11917,7 @@
         <v>101500</v>
       </c>
       <c r="C291" s="27" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D291" s="27" t="s">
         <v>275</v>
@@ -11929,7 +11932,7 @@
         <v>232</v>
       </c>
       <c r="H291" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I291" s="27" t="s">
         <v>39</v>
@@ -11944,7 +11947,7 @@
         <v>101500</v>
       </c>
       <c r="C292" s="27" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D292" s="27" t="s">
         <v>275</v>
@@ -11959,7 +11962,7 @@
         <v>232</v>
       </c>
       <c r="H292" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I292" s="27" t="s">
         <v>39</v>
@@ -11974,7 +11977,7 @@
         <v>101500</v>
       </c>
       <c r="C293" s="27" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D293" s="27" t="s">
         <v>275</v>
@@ -11989,7 +11992,7 @@
         <v>232</v>
       </c>
       <c r="H293" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I293" s="27" t="s">
         <v>39</v>
@@ -12010,7 +12013,7 @@
         <v>275</v>
       </c>
       <c r="E294" s="27" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F294" s="27" t="s">
         <v>133</v>
@@ -12019,7 +12022,7 @@
         <v>252</v>
       </c>
       <c r="H294" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I294" s="27" t="s">
         <v>39</v>
@@ -12034,10 +12037,10 @@
         <v>101500</v>
       </c>
       <c r="C295" s="27" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D295" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E295" s="27" t="s">
         <v>143</v>
@@ -12046,10 +12049,10 @@
         <v>133</v>
       </c>
       <c r="G295" s="27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H295" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I295" s="27" t="s">
         <v>107</v>
@@ -12064,10 +12067,10 @@
         <v>101500</v>
       </c>
       <c r="C296" s="27" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D296" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E296" s="27" t="s">
         <v>143</v>
@@ -12079,7 +12082,7 @@
         <v>174</v>
       </c>
       <c r="H296" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I296" s="27" t="s">
         <v>107</v>
@@ -12094,10 +12097,10 @@
         <v>101500</v>
       </c>
       <c r="C297" s="27" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D297" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E297" s="27" t="s">
         <v>143</v>
@@ -12109,7 +12112,7 @@
         <v>176</v>
       </c>
       <c r="H297" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I297" s="27" t="s">
         <v>107</v>
@@ -12124,10 +12127,10 @@
         <v>101500</v>
       </c>
       <c r="C298" s="27" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D298" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E298" s="27" t="s">
         <v>143</v>
@@ -12139,7 +12142,7 @@
         <v>178</v>
       </c>
       <c r="H298" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I298" s="27" t="s">
         <v>107</v>
@@ -12154,10 +12157,10 @@
         <v>101500</v>
       </c>
       <c r="C299" s="27" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D299" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E299" s="27" t="s">
         <v>143</v>
@@ -12169,7 +12172,7 @@
         <v>252</v>
       </c>
       <c r="H299" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I299" s="27" t="s">
         <v>107</v>
@@ -12184,7 +12187,7 @@
         <v>101500</v>
       </c>
       <c r="C300" s="27" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D300" s="27" t="s">
         <v>21</v>
@@ -12196,10 +12199,10 @@
         <v>133</v>
       </c>
       <c r="G300" s="27" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H300" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I300" s="27" t="s">
         <v>89</v>
@@ -12214,7 +12217,7 @@
         <v>101500</v>
       </c>
       <c r="C301" s="27" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D301" s="27" t="s">
         <v>21</v>
@@ -12226,10 +12229,10 @@
         <v>133</v>
       </c>
       <c r="G301" s="27" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H301" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I301" s="27" t="s">
         <v>89</v>
@@ -12244,7 +12247,7 @@
         <v>101500</v>
       </c>
       <c r="C302" s="27" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D302" s="27" t="s">
         <v>21</v>
@@ -12256,10 +12259,10 @@
         <v>133</v>
       </c>
       <c r="G302" s="27" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H302" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I302" s="27" t="s">
         <v>89</v>
@@ -12274,7 +12277,7 @@
         <v>101500</v>
       </c>
       <c r="C303" s="27" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D303" s="27" t="s">
         <v>21</v>
@@ -12286,10 +12289,10 @@
         <v>133</v>
       </c>
       <c r="G303" s="27" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H303" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I303" s="27" t="s">
         <v>89</v>
@@ -12304,7 +12307,7 @@
         <v>101500</v>
       </c>
       <c r="C304" s="27" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D304" s="27" t="s">
         <v>21</v>
@@ -12316,10 +12319,10 @@
         <v>133</v>
       </c>
       <c r="G304" s="27" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H304" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I304" s="27" t="s">
         <v>89</v>
@@ -12334,7 +12337,7 @@
         <v>101500</v>
       </c>
       <c r="C305" s="27" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D305" s="27" t="s">
         <v>21</v>
@@ -12346,10 +12349,10 @@
         <v>133</v>
       </c>
       <c r="G305" s="27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H305" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I305" s="27" t="s">
         <v>89</v>
@@ -12364,7 +12367,7 @@
         <v>101500</v>
       </c>
       <c r="C306" s="27" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D306" s="27" t="s">
         <v>21</v>
@@ -12376,10 +12379,10 @@
         <v>133</v>
       </c>
       <c r="G306" s="27" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H306" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I306" s="27" t="s">
         <v>89</v>
@@ -12394,7 +12397,7 @@
         <v>101500</v>
       </c>
       <c r="C307" s="27" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D307" s="27" t="s">
         <v>21</v>
@@ -12406,10 +12409,10 @@
         <v>133</v>
       </c>
       <c r="G307" s="27" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H307" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I307" s="27" t="s">
         <v>89</v>
@@ -12424,7 +12427,7 @@
         <v>101500</v>
       </c>
       <c r="C308" s="27" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D308" s="27" t="s">
         <v>21</v>
@@ -12436,10 +12439,10 @@
         <v>133</v>
       </c>
       <c r="G308" s="27" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H308" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I308" s="27" t="s">
         <v>89</v>
@@ -12454,7 +12457,7 @@
         <v>101500</v>
       </c>
       <c r="C309" s="27" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D309" s="27" t="s">
         <v>21</v>
@@ -12466,10 +12469,10 @@
         <v>133</v>
       </c>
       <c r="G309" s="27" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H309" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I309" s="27" t="s">
         <v>89</v>
@@ -12484,7 +12487,7 @@
         <v>101500</v>
       </c>
       <c r="C310" s="27" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D310" s="27" t="s">
         <v>21</v>
@@ -12499,7 +12502,7 @@
         <v>294</v>
       </c>
       <c r="H310" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I310" s="27" t="s">
         <v>157</v>
@@ -12514,7 +12517,7 @@
         <v>101500</v>
       </c>
       <c r="C311" s="27" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D311" s="27" t="s">
         <v>21</v>
@@ -12526,10 +12529,10 @@
         <v>133</v>
       </c>
       <c r="G311" s="27" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H311" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I311" s="27" t="s">
         <v>157</v>
@@ -12544,7 +12547,7 @@
         <v>101500</v>
       </c>
       <c r="C312" s="27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D312" s="27" t="s">
         <v>21</v>
@@ -12556,10 +12559,10 @@
         <v>133</v>
       </c>
       <c r="G312" s="27" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H312" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I312" s="27" t="s">
         <v>157</v>
@@ -12574,7 +12577,7 @@
         <v>101500</v>
       </c>
       <c r="C313" s="27" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D313" s="27" t="s">
         <v>21</v>
@@ -12586,10 +12589,10 @@
         <v>133</v>
       </c>
       <c r="G313" s="27" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H313" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I313" s="27" t="s">
         <v>157</v>
@@ -12604,7 +12607,7 @@
         <v>101500</v>
       </c>
       <c r="C314" s="27" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D314" s="27" t="s">
         <v>21</v>
@@ -12616,10 +12619,10 @@
         <v>133</v>
       </c>
       <c r="G314" s="27" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H314" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I314" s="27" t="s">
         <v>157</v>
@@ -12634,7 +12637,7 @@
         <v>101500</v>
       </c>
       <c r="C315" s="27" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D315" s="27" t="s">
         <v>21</v>
@@ -12646,10 +12649,10 @@
         <v>133</v>
       </c>
       <c r="G315" s="27" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H315" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I315" s="27" t="s">
         <v>157</v>
@@ -12664,7 +12667,7 @@
         <v>101500</v>
       </c>
       <c r="C316" s="27" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D316" s="27" t="s">
         <v>325</v>
@@ -12679,10 +12682,10 @@
         <v>232</v>
       </c>
       <c r="H316" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I316" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K316" s="109"/>
     </row>
@@ -12694,10 +12697,10 @@
         <v>102600</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D317" s="28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E317" s="28" t="s">
         <v>140</v>
@@ -12706,13 +12709,13 @@
         <v>133</v>
       </c>
       <c r="G317" s="28" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H317" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I317" s="28" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K317" s="110"/>
     </row>
@@ -12727,7 +12730,7 @@
         <v>320</v>
       </c>
       <c r="D318" s="28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E318" s="28" t="s">
         <v>143</v>
@@ -12736,10 +12739,10 @@
         <v>133</v>
       </c>
       <c r="G318" s="28" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H318" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I318" s="28" t="s">
         <v>322</v>
@@ -12769,7 +12772,7 @@
         <v>340</v>
       </c>
       <c r="H319" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I319" s="28" t="s">
         <v>107</v>
@@ -12787,7 +12790,7 @@
         <v>323</v>
       </c>
       <c r="D320" s="28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E320" s="28" t="s">
         <v>143</v>
@@ -12796,10 +12799,10 @@
         <v>133</v>
       </c>
       <c r="G320" s="28" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H320" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I320" s="28" t="s">
         <v>324</v>
@@ -12817,7 +12820,7 @@
         <v>327</v>
       </c>
       <c r="D321" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E321" s="28" t="s">
         <v>328</v>
@@ -12829,7 +12832,7 @@
         <v>329</v>
       </c>
       <c r="H321" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I321" s="28" t="s">
         <v>330</v>
@@ -12847,7 +12850,7 @@
         <v>331</v>
       </c>
       <c r="D322" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E322" s="28" t="s">
         <v>332</v>
@@ -12859,7 +12862,7 @@
         <v>333</v>
       </c>
       <c r="H322" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I322" s="28" t="s">
         <v>330</v>
@@ -12877,7 +12880,7 @@
         <v>334</v>
       </c>
       <c r="D323" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E323" s="28" t="s">
         <v>335</v>
@@ -12889,7 +12892,7 @@
         <v>336</v>
       </c>
       <c r="H323" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I323" s="28" t="s">
         <v>246</v>
@@ -12919,7 +12922,7 @@
         <v>337</v>
       </c>
       <c r="H324" s="28" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I324" s="28" t="s">
         <v>39</v>
@@ -12946,10 +12949,10 @@
         <v>133</v>
       </c>
       <c r="G325" s="28" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H325" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I325" s="28" t="s">
         <v>287</v>
@@ -12964,10 +12967,10 @@
         <v>105000</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D326" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E326" s="21" t="s">
         <v>140</v>
@@ -12976,13 +12979,13 @@
         <v>133</v>
       </c>
       <c r="G326" s="21" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H326" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I326" s="21" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="327" s="21" customFormat="1" ht="16.5" spans="1:11">
@@ -12993,10 +12996,10 @@
         <v>105000</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D327" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E327" s="21" t="s">
         <v>143</v>
@@ -13005,10 +13008,10 @@
         <v>133</v>
       </c>
       <c r="G327" s="21" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H327" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I327" s="21" t="s">
         <v>322</v>
@@ -13022,10 +13025,10 @@
         <v>105000</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D328" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E328" s="21" t="s">
         <v>143</v>
@@ -13037,7 +13040,7 @@
         <v>340</v>
       </c>
       <c r="H328" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I328" s="21" t="s">
         <v>107</v>
@@ -13051,10 +13054,10 @@
         <v>105000</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D329" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E329" s="21" t="s">
         <v>143</v>
@@ -13063,10 +13066,10 @@
         <v>133</v>
       </c>
       <c r="G329" s="21" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H329" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I329" s="21" t="s">
         <v>324</v>
@@ -13083,10 +13086,10 @@
         <v>327</v>
       </c>
       <c r="D330" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F330" s="21" t="s">
         <v>133</v>
@@ -13095,7 +13098,7 @@
         <v>329</v>
       </c>
       <c r="H330" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I330" s="21" t="s">
         <v>330</v>
@@ -13112,10 +13115,10 @@
         <v>331</v>
       </c>
       <c r="D331" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F331" s="21" t="s">
         <v>133</v>
@@ -13124,7 +13127,7 @@
         <v>333</v>
       </c>
       <c r="H331" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I331" s="21" t="s">
         <v>330</v>
@@ -13141,10 +13144,10 @@
         <v>334</v>
       </c>
       <c r="D332" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F332" s="21" t="s">
         <v>133</v>
@@ -13153,7 +13156,7 @@
         <v>336</v>
       </c>
       <c r="H332" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I332" s="21" t="s">
         <v>246</v>
@@ -13170,7 +13173,7 @@
         <v>250</v>
       </c>
       <c r="D333" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E333" s="21" t="s">
         <v>272</v>
@@ -13182,7 +13185,7 @@
         <v>337</v>
       </c>
       <c r="H333" s="21" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I333" s="21" t="s">
         <v>39</v>
@@ -13199,7 +13202,7 @@
         <v>285</v>
       </c>
       <c r="D334" s="21" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E334" s="21" t="s">
         <v>143</v>
@@ -13208,10 +13211,10 @@
         <v>133</v>
       </c>
       <c r="G334" s="21" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H334" s="21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I334" s="21" t="s">
         <v>287</v>
@@ -13225,10 +13228,10 @@
         <v>105100</v>
       </c>
       <c r="C335" s="29" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D335" s="29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E335" s="29" t="s">
         <v>195</v>
@@ -13237,7 +13240,7 @@
         <v>133</v>
       </c>
       <c r="G335" s="29" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I335" s="29" t="s">
         <v>46</v>
@@ -13252,10 +13255,10 @@
         <v>105100</v>
       </c>
       <c r="C336" s="29" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D336" s="29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E336" s="29" t="s">
         <v>195</v>
@@ -13264,7 +13267,7 @@
         <v>133</v>
       </c>
       <c r="G336" s="29" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I336" s="29" t="s">
         <v>136</v>
@@ -13279,10 +13282,10 @@
         <v>105100</v>
       </c>
       <c r="C337" s="29" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D337" s="29" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E337" s="29" t="s">
         <v>41</v>
@@ -13291,13 +13294,13 @@
         <v>133</v>
       </c>
       <c r="G337" s="29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H337" s="29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I337" s="29" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K337" s="76"/>
     </row>
@@ -13309,10 +13312,10 @@
         <v>105100</v>
       </c>
       <c r="C338" s="29" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D338" s="29" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E338" s="29" t="s">
         <v>36</v>
@@ -13321,13 +13324,13 @@
         <v>133</v>
       </c>
       <c r="G338" s="29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H338" s="29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I338" s="29" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K338" s="76"/>
     </row>
@@ -13339,10 +13342,10 @@
         <v>105100</v>
       </c>
       <c r="C339" s="29" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D339" s="29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E339" s="29" t="s">
         <v>31</v>
@@ -13351,13 +13354,13 @@
         <v>133</v>
       </c>
       <c r="G339" s="29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H339" s="29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I339" s="29" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K339" s="76"/>
     </row>
@@ -13369,10 +13372,10 @@
         <v>105100</v>
       </c>
       <c r="C340" s="29" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D340" s="29" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E340" s="29" t="s">
         <v>23</v>
@@ -13381,13 +13384,13 @@
         <v>133</v>
       </c>
       <c r="G340" s="29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H340" s="29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I340" s="29" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K340" s="76"/>
     </row>
@@ -13399,25 +13402,25 @@
         <v>105100</v>
       </c>
       <c r="C341" s="29" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D341" s="29" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E341" s="29" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F341" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G341" s="29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H341" s="29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I341" s="29" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K341" s="76"/>
     </row>
@@ -13439,24 +13442,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D2" t="s">
         <v>574</v>
       </c>
-      <c r="D2" t="s">
-        <v>573</v>
-      </c>
       <c r="E2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -13464,16 +13467,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -13481,16 +13484,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -13498,16 +13501,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -13515,7 +13518,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -13523,7 +13526,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -13531,7 +13534,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -13539,7 +13542,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -13547,7 +13550,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -13555,7 +13558,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -13563,7 +13566,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -13571,7 +13574,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -13579,7 +13582,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -13587,7 +13590,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -13595,7 +13598,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -13603,7 +13606,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -13611,7 +13614,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -13619,7 +13622,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -13627,7 +13630,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -13635,7 +13638,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -13643,7 +13646,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -13651,7 +13654,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -13659,7 +13662,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -13667,7 +13670,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -13675,7 +13678,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -13683,7 +13686,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -13691,7 +13694,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -13699,7 +13702,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -13707,7 +13710,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -13715,7 +13718,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -13723,7 +13726,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -13731,7 +13734,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -13739,7 +13742,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -13747,7 +13750,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -13755,7 +13758,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -13763,7 +13766,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -13771,7 +13774,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -13779,7 +13782,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -13787,7 +13790,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -13795,7 +13798,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -13803,7 +13806,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -13811,7 +13814,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -13819,7 +13822,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -13827,7 +13830,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -13835,7 +13838,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -13843,7 +13846,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -13851,7 +13854,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="634">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1261,7 +1261,7 @@
     <t>第5轴改出奖池符号</t>
   </si>
   <si>
-    <t>27_10|28_5|29_2|30_1</t>
+    <t>35_10|36_5|37_2|38_1</t>
   </si>
   <si>
     <t>改出39符号</t>
@@ -1774,19 +1774,25 @@
     <t>改出+1免费符号</t>
   </si>
   <si>
-    <t>6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|31_1_1|32_1_1|33_1_1|34_1_1</t>
-  </si>
-  <si>
     <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119</t>
   </si>
   <si>
     <t>0_70|1_20|2_9|3_1</t>
   </si>
   <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1</t>
-  </si>
-  <si>
-    <t>13_14_15_16_17</t>
+    <t>2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>11_1_1|12_1_1|17_1_1|18_1_1|23_1_1|24_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17</t>
+  </si>
+  <si>
+    <t>1_1_1|31_1_1</t>
   </si>
   <si>
     <t xml:space="preserve">概率改出wild </t>
@@ -1798,19 +1804,37 @@
     <t>改出4个或以上个数SCATTER</t>
   </si>
   <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_32_33_34_35_36</t>
+  </si>
+  <si>
     <t>改出3个scatter符号</t>
   </si>
   <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30</t>
+  </si>
+  <si>
     <t>概率改出3个或以下个数scatter符号</t>
   </si>
   <si>
     <t>18_1|19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|60_1|61_1|62_1|63_1|64_1|65_1|66_1|67_1|68_1|69_1|70_1</t>
   </si>
   <si>
+    <t>3_4_5_6_8_9_10_11_12_14_15_16_17_18_20_21_22_23_24_26_27_28_29_30_33_34_35_36</t>
+  </si>
+  <si>
     <t>32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|42_1|71_1|72_1|73_1|74_1|75_1|76_1|77_1|78_1|79_1|80_1|81_1</t>
   </si>
   <si>
+    <t>4_5_6_7_9_10_11_12_13_15_16_17_18_19_21_22_23_24_25_27_28_29_30_31_34_35_36_37</t>
+  </si>
+  <si>
     <t>45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1|54_1|55_1|56_1|82_1|83_1|84_1|85_1|86_1|87_1|88_1|89_1|90_1|91_1|92_1</t>
+  </si>
+  <si>
+    <t>5_6_7_8_10_11_12_13_14_16_17_18_19_20_22_23_24_25_26_28_29_30_31_32_35_36_37_38</t>
+  </si>
+  <si>
+    <t>32_33_34_35_36</t>
   </si>
   <si>
     <t>免费</t>
@@ -3375,7 +3399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N341"/>
+  <dimension ref="A1:N343"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -12706,13 +12730,13 @@
         <v>133</v>
       </c>
       <c r="G317" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="H317" s="28" t="s">
         <v>538</v>
       </c>
-      <c r="H317" s="28" t="s">
+      <c r="I317" s="28" t="s">
         <v>539</v>
-      </c>
-      <c r="I317" s="28" t="s">
-        <v>540</v>
       </c>
       <c r="K317" s="110"/>
     </row>
@@ -12736,10 +12760,10 @@
         <v>133</v>
       </c>
       <c r="G318" s="28" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H318" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I318" s="28" t="s">
         <v>322</v>
@@ -12766,10 +12790,10 @@
         <v>133</v>
       </c>
       <c r="G319" s="28" t="s">
-        <v>340</v>
+        <v>540</v>
       </c>
       <c r="H319" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I319" s="28" t="s">
         <v>107</v>
@@ -12796,10 +12820,10 @@
         <v>133</v>
       </c>
       <c r="G320" s="28" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H320" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I320" s="28" t="s">
         <v>324</v>
@@ -12826,10 +12850,10 @@
         <v>133</v>
       </c>
       <c r="G321" s="28" t="s">
-        <v>329</v>
+        <v>457</v>
       </c>
       <c r="H321" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I321" s="28" t="s">
         <v>330</v>
@@ -12856,10 +12880,10 @@
         <v>133</v>
       </c>
       <c r="G322" s="28" t="s">
-        <v>333</v>
+        <v>459</v>
       </c>
       <c r="H322" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I322" s="28" t="s">
         <v>330</v>
@@ -12886,10 +12910,10 @@
         <v>133</v>
       </c>
       <c r="G323" s="28" t="s">
-        <v>336</v>
+        <v>541</v>
       </c>
       <c r="H323" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I323" s="28" t="s">
         <v>246</v>
@@ -12916,10 +12940,10 @@
         <v>133</v>
       </c>
       <c r="G324" s="28" t="s">
-        <v>337</v>
+        <v>542</v>
       </c>
       <c r="H324" s="28" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I324" s="28" t="s">
         <v>39</v>
@@ -12946,48 +12970,46 @@
         <v>133</v>
       </c>
       <c r="G325" s="28" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H325" s="28" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I325" s="28" t="s">
         <v>287</v>
       </c>
       <c r="K325" s="110"/>
     </row>
-    <row r="326" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A326" s="21">
-        <v>10500001</v>
-      </c>
-      <c r="B326" s="21">
-        <v>105000</v>
-      </c>
-      <c r="C326" s="21" t="s">
-        <v>543</v>
-      </c>
-      <c r="D326" s="21" t="s">
+    <row r="326" s="28" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A326" s="28">
+        <v>10260010</v>
+      </c>
+      <c r="B326" s="28">
+        <v>102600</v>
+      </c>
+      <c r="C326" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="D326" s="28" t="s">
         <v>417</v>
       </c>
-      <c r="E326" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="F326" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G326" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="H326" s="21" t="s">
+      <c r="E326" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="F326" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G326" s="28" t="s">
         <v>544</v>
       </c>
-      <c r="I326" s="21" t="s">
-        <v>540</v>
-      </c>
+      <c r="I326" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="K326" s="110"/>
     </row>
     <row r="327" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A327" s="21">
-        <v>10500002</v>
+        <v>10500001</v>
       </c>
       <c r="B327" s="21">
         <v>105000</v>
@@ -12996,33 +13018,33 @@
         <v>545</v>
       </c>
       <c r="D327" s="21" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F327" s="21" t="s">
         <v>133</v>
       </c>
       <c r="G327" s="21" t="s">
-        <v>541</v>
+        <v>451</v>
       </c>
       <c r="H327" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I327" s="21" t="s">
-        <v>322</v>
+        <v>539</v>
       </c>
     </row>
     <row r="328" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A328" s="21">
-        <v>10500003</v>
+        <v>10500002</v>
       </c>
       <c r="B328" s="21">
         <v>105000</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D328" s="21" t="s">
         <v>420</v>
@@ -13034,24 +13056,24 @@
         <v>133</v>
       </c>
       <c r="G328" s="21" t="s">
-        <v>340</v>
+        <v>548</v>
       </c>
       <c r="H328" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I328" s="21" t="s">
-        <v>107</v>
+        <v>322</v>
       </c>
     </row>
     <row r="329" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A329" s="21">
-        <v>10500004</v>
+        <v>10500003</v>
       </c>
       <c r="B329" s="21">
         <v>105000</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D329" s="21" t="s">
         <v>420</v>
@@ -13063,68 +13085,68 @@
         <v>133</v>
       </c>
       <c r="G329" s="21" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="H329" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I329" s="21" t="s">
-        <v>324</v>
+        <v>107</v>
       </c>
     </row>
     <row r="330" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A330" s="21">
-        <v>10500005</v>
+        <v>10500004</v>
       </c>
       <c r="B330" s="21">
         <v>105000</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>327</v>
+        <v>551</v>
       </c>
       <c r="D330" s="21" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E330" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F330" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G330" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="F330" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G330" s="21" t="s">
-        <v>329</v>
-      </c>
       <c r="H330" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I330" s="21" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="331" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A331" s="21">
-        <v>10500006</v>
+        <v>10500005</v>
       </c>
       <c r="B331" s="21">
         <v>105000</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D331" s="21" t="s">
         <v>417</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F331" s="21" t="s">
         <v>133</v>
       </c>
       <c r="G331" s="21" t="s">
-        <v>333</v>
+        <v>553</v>
       </c>
       <c r="H331" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I331" s="21" t="s">
         <v>330</v>
@@ -13132,220 +13154,216 @@
     </row>
     <row r="332" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A332" s="21">
-        <v>10500007</v>
+        <v>10500006</v>
       </c>
       <c r="B332" s="21">
         <v>105000</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D332" s="21" t="s">
         <v>417</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F332" s="21" t="s">
         <v>133</v>
       </c>
       <c r="G332" s="21" t="s">
-        <v>336</v>
+        <v>555</v>
       </c>
       <c r="H332" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I332" s="21" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A333" s="21">
-        <v>10500008</v>
+        <v>10500007</v>
       </c>
       <c r="B333" s="21">
         <v>105000</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="D333" s="21" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>272</v>
+        <v>556</v>
       </c>
       <c r="F333" s="21" t="s">
         <v>133</v>
       </c>
       <c r="G333" s="21" t="s">
-        <v>337</v>
+        <v>557</v>
       </c>
       <c r="H333" s="21" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="I333" s="21" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
     </row>
     <row r="334" s="21" customFormat="1" ht="16.5" spans="1:11">
       <c r="A334" s="21">
-        <v>10500009</v>
+        <v>10500008</v>
       </c>
       <c r="B334" s="21">
         <v>105000</v>
       </c>
       <c r="C334" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D334" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="E334" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="F334" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G334" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="H334" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="I334" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="335" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A335" s="21">
+        <v>10500009</v>
+      </c>
+      <c r="B335" s="21">
+        <v>105000</v>
+      </c>
+      <c r="C335" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="D334" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="E334" s="21" t="s">
+      <c r="D335" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="E335" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="F334" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G334" s="21" t="s">
-        <v>541</v>
-      </c>
-      <c r="H334" s="21" t="s">
+      <c r="F335" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G335" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="H335" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="I335" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="336" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A336" s="21">
+        <v>10500010</v>
+      </c>
+      <c r="B336" s="21">
+        <v>105000</v>
+      </c>
+      <c r="C336" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="D336" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="E336" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="F336" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G336" s="21" t="s">
         <v>544</v>
       </c>
-      <c r="I334" s="21" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="335" s="29" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A335" s="29">
+      <c r="H336" s="21"/>
+      <c r="I336" s="21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="337" s="29" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A337" s="29">
         <v>10510001</v>
-      </c>
-      <c r="B335" s="29">
-        <v>105100</v>
-      </c>
-      <c r="C335" s="29" t="s">
-        <v>552</v>
-      </c>
-      <c r="D335" s="29" t="s">
-        <v>420</v>
-      </c>
-      <c r="E335" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="F335" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G335" s="29" t="s">
-        <v>553</v>
-      </c>
-      <c r="I335" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="K335" s="76"/>
-    </row>
-    <row r="336" s="29" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A336" s="29">
-        <v>10510002</v>
-      </c>
-      <c r="B336" s="29">
-        <v>105100</v>
-      </c>
-      <c r="C336" s="29" t="s">
-        <v>554</v>
-      </c>
-      <c r="D336" s="29" t="s">
-        <v>420</v>
-      </c>
-      <c r="E336" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="F336" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G336" s="29" t="s">
-        <v>555</v>
-      </c>
-      <c r="I336" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="K336" s="76"/>
-    </row>
-    <row r="337" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A337" s="29">
-        <v>10510005</v>
       </c>
       <c r="B337" s="29">
         <v>105100</v>
       </c>
       <c r="C337" s="29" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D337" s="29" t="s">
-        <v>557</v>
+        <v>420</v>
       </c>
       <c r="E337" s="29" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="F337" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G337" s="29" t="s">
-        <v>453</v>
-      </c>
-      <c r="H337" s="29" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I337" s="29" t="s">
-        <v>559</v>
+        <v>46</v>
       </c>
       <c r="K337" s="76"/>
     </row>
-    <row r="338" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="338" s="29" customFormat="1" ht="16.5" spans="1:11">
       <c r="A338" s="29">
-        <v>10510006</v>
+        <v>10510002</v>
       </c>
       <c r="B338" s="29">
         <v>105100</v>
       </c>
       <c r="C338" s="29" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D338" s="29" t="s">
-        <v>561</v>
+        <v>420</v>
       </c>
       <c r="E338" s="29" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="F338" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G338" s="29" t="s">
-        <v>453</v>
-      </c>
-      <c r="H338" s="29" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="I338" s="29" t="s">
-        <v>562</v>
+        <v>136</v>
       </c>
       <c r="K338" s="76"/>
     </row>
     <row r="339" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A339" s="29">
-        <v>10510007</v>
+        <v>10510005</v>
       </c>
       <c r="B339" s="29">
         <v>105100</v>
       </c>
       <c r="C339" s="29" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D339" s="29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E339" s="29" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F339" s="29" t="s">
         <v>133</v>
@@ -13354,28 +13372,28 @@
         <v>453</v>
       </c>
       <c r="H339" s="29" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="I339" s="29" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="K339" s="76"/>
     </row>
     <row r="340" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A340" s="29">
-        <v>10510008</v>
+        <v>10510006</v>
       </c>
       <c r="B340" s="29">
         <v>105100</v>
       </c>
       <c r="C340" s="29" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D340" s="29" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E340" s="29" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F340" s="29" t="s">
         <v>133</v>
@@ -13384,28 +13402,28 @@
         <v>453</v>
       </c>
       <c r="H340" s="29" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="I340" s="29" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="K340" s="76"/>
     </row>
     <row r="341" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A341" s="29">
-        <v>10510009</v>
+        <v>10510007</v>
       </c>
       <c r="B341" s="29">
         <v>105100</v>
       </c>
       <c r="C341" s="29" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D341" s="29" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E341" s="29" t="s">
-        <v>569</v>
+        <v>31</v>
       </c>
       <c r="F341" s="29" t="s">
         <v>133</v>
@@ -13414,12 +13432,72 @@
         <v>453</v>
       </c>
       <c r="H341" s="29" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="I341" s="29" t="s">
         <v>570</v>
       </c>
       <c r="K341" s="76"/>
+    </row>
+    <row r="342" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A342" s="29">
+        <v>10510008</v>
+      </c>
+      <c r="B342" s="29">
+        <v>105100</v>
+      </c>
+      <c r="C342" s="29" t="s">
+        <v>573</v>
+      </c>
+      <c r="D342" s="29" t="s">
+        <v>574</v>
+      </c>
+      <c r="E342" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F342" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G342" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="H342" s="29" t="s">
+        <v>566</v>
+      </c>
+      <c r="I342" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="K342" s="76"/>
+    </row>
+    <row r="343" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A343" s="29">
+        <v>10510009</v>
+      </c>
+      <c r="B343" s="29">
+        <v>105100</v>
+      </c>
+      <c r="C343" s="29" t="s">
+        <v>575</v>
+      </c>
+      <c r="D343" s="29" t="s">
+        <v>576</v>
+      </c>
+      <c r="E343" s="29" t="s">
+        <v>577</v>
+      </c>
+      <c r="F343" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G343" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="H343" s="29" t="s">
+        <v>566</v>
+      </c>
+      <c r="I343" s="29" t="s">
+        <v>578</v>
+      </c>
+      <c r="K343" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13439,24 +13517,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="D1" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="D2" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="E2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -13464,16 +13542,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="F3" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -13481,16 +13559,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="F4" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -13498,16 +13576,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="F5" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -13515,7 +13593,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -13523,7 +13601,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -13531,7 +13609,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -13539,7 +13617,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -13547,7 +13625,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -13555,7 +13633,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -13563,7 +13641,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -13571,7 +13649,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -13579,7 +13657,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -13587,7 +13665,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -13595,7 +13673,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -13603,7 +13681,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -13611,7 +13689,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -13619,7 +13697,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -13627,7 +13705,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -13635,7 +13713,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -13643,7 +13721,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -13651,7 +13729,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -13659,7 +13737,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -13667,7 +13745,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -13675,7 +13753,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -13683,7 +13761,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -13691,7 +13769,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -13699,7 +13777,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -13707,7 +13785,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -13715,7 +13793,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -13723,7 +13801,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -13731,7 +13809,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -13739,7 +13817,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -13747,7 +13825,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -13755,7 +13833,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -13763,7 +13841,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -13771,7 +13849,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -13779,7 +13857,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -13787,7 +13865,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -13795,7 +13873,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -13803,7 +13881,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -13811,7 +13889,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -13819,7 +13897,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -13827,7 +13905,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -13835,7 +13913,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -13843,7 +13921,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -13851,7 +13929,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CE8AC496A15EBA08D3E3745EBDBE7137E85DDBD7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90976DD8-0C9F-48E0-98F2-DF3DCC97C172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4590" yWindow="3480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2662" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="676">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -2186,6 +2186,14 @@
   </si>
   <si>
     <t>通用普通10</t>
+  </si>
+  <si>
+    <t>改出多格图标</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>32_1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2193,9 +2201,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.000_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2257,6 +2265,20 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2398,7 +2420,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2535,7 +2557,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2657,6 +2679,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2935,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N391"/>
+  <dimension ref="A1:N394"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -14389,6 +14415,86 @@
       </c>
       <c r="K391" s="114"/>
     </row>
+    <row r="392" spans="1:11" s="124" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A392" s="124">
+        <v>10550201</v>
+      </c>
+      <c r="B392" s="124">
+        <v>105502</v>
+      </c>
+      <c r="C392" s="124" t="s">
+        <v>250</v>
+      </c>
+      <c r="D392" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="E392" s="124" t="s">
+        <v>157</v>
+      </c>
+      <c r="F392" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G392" s="124" t="s">
+        <v>609</v>
+      </c>
+      <c r="I392" s="124" t="s">
+        <v>39</v>
+      </c>
+      <c r="K392" s="125"/>
+    </row>
+    <row r="393" spans="1:11" s="124" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A393" s="124">
+        <v>10550202</v>
+      </c>
+      <c r="B393" s="124">
+        <v>105502</v>
+      </c>
+      <c r="C393" s="124" t="s">
+        <v>610</v>
+      </c>
+      <c r="D393" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="E393" s="124" t="s">
+        <v>296</v>
+      </c>
+      <c r="F393" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G393" s="124" t="s">
+        <v>294</v>
+      </c>
+      <c r="I393" s="124" t="s">
+        <v>291</v>
+      </c>
+      <c r="K393" s="125"/>
+    </row>
+    <row r="394" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A394" s="124">
+        <v>10550203</v>
+      </c>
+      <c r="B394" s="124">
+        <v>105502</v>
+      </c>
+      <c r="C394" s="124" t="s">
+        <v>674</v>
+      </c>
+      <c r="D394" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="E394" s="124" t="s">
+        <v>675</v>
+      </c>
+      <c r="F394" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G394" s="124" t="s">
+        <v>294</v>
+      </c>
+      <c r="I394" s="124" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="683">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1529,6 +1529,9 @@
   </si>
   <si>
     <t>改出百搭符号</t>
+  </si>
+  <si>
+    <t>5_9_10_11_12_13_14</t>
   </si>
   <si>
     <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
@@ -11126,7 +11129,7 @@
         <v>159</v>
       </c>
       <c r="H262" s="26" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I262" s="26" t="s">
         <v>39</v>
@@ -11273,10 +11276,10 @@
         <v>133</v>
       </c>
       <c r="G267" s="24" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H267" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I267" s="24" t="s">
         <v>322</v>
@@ -11303,10 +11306,10 @@
         <v>133</v>
       </c>
       <c r="G268" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="H268" s="24" t="s">
         <v>459</v>
-      </c>
-      <c r="H268" s="24" t="s">
-        <v>458</v>
       </c>
       <c r="I268" s="24" t="s">
         <v>325</v>
@@ -11333,10 +11336,10 @@
         <v>133</v>
       </c>
       <c r="G269" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="H269" s="24" t="s">
         <v>459</v>
-      </c>
-      <c r="H269" s="24" t="s">
-        <v>458</v>
       </c>
       <c r="I269" s="24" t="s">
         <v>327</v>
@@ -11366,7 +11369,7 @@
         <v>324</v>
       </c>
       <c r="H270" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I270" s="24" t="s">
         <v>107</v>
@@ -11387,16 +11390,16 @@
         <v>438</v>
       </c>
       <c r="E271" s="24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F271" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G271" s="24" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H271" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I271" s="24" t="s">
         <v>333</v>
@@ -11417,16 +11420,16 @@
         <v>438</v>
       </c>
       <c r="E272" s="24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F272" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G272" s="24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H272" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I272" s="24" t="s">
         <v>333</v>
@@ -11447,16 +11450,16 @@
         <v>438</v>
       </c>
       <c r="E273" s="24" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F273" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G273" s="24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H273" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I273" s="24" t="s">
         <v>340</v>
@@ -11471,7 +11474,7 @@
         <v>101600</v>
       </c>
       <c r="C274" s="24" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D274" s="24" t="s">
         <v>328</v>
@@ -11483,13 +11486,13 @@
         <v>133</v>
       </c>
       <c r="G274" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="H274" s="24" t="s">
         <v>459</v>
       </c>
-      <c r="H274" s="24" t="s">
-        <v>458</v>
-      </c>
       <c r="I274" s="24" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K274" s="108"/>
     </row>
@@ -11513,10 +11516,10 @@
         <v>133</v>
       </c>
       <c r="G275" s="24" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H275" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I275" s="24" t="s">
         <v>39</v>
@@ -11531,22 +11534,22 @@
         <v>101600</v>
       </c>
       <c r="C276" s="24" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D276" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E276" s="24" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F276" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G276" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H276" s="24" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I276" s="24" t="s">
         <v>39</v>
@@ -11561,22 +11564,22 @@
         <v>101600</v>
       </c>
       <c r="C277" s="24" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D277" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E277" s="24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F277" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G277" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H277" s="24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I277" s="24" t="s">
         <v>39</v>
@@ -11591,22 +11594,22 @@
         <v>101600</v>
       </c>
       <c r="C278" s="24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D278" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E278" s="24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F278" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G278" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H278" s="24" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I278" s="24" t="s">
         <v>39</v>
@@ -11621,22 +11624,22 @@
         <v>101600</v>
       </c>
       <c r="C279" s="24" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D279" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E279" s="24" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F279" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G279" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H279" s="24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I279" s="24" t="s">
         <v>39</v>
@@ -11651,22 +11654,22 @@
         <v>101600</v>
       </c>
       <c r="C280" s="24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D280" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E280" s="24" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F280" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G280" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H280" s="24" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I280" s="24" t="s">
         <v>39</v>
@@ -11681,22 +11684,22 @@
         <v>101600</v>
       </c>
       <c r="C281" s="24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D281" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E281" s="24" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F281" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G281" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H281" s="24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I281" s="24" t="s">
         <v>39</v>
@@ -11711,22 +11714,22 @@
         <v>101600</v>
       </c>
       <c r="C282" s="24" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D282" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E282" s="24" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F282" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G282" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H282" s="24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I282" s="24" t="s">
         <v>39</v>
@@ -11741,22 +11744,22 @@
         <v>101600</v>
       </c>
       <c r="C283" s="24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D283" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E283" s="24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F283" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G283" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H283" s="24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I283" s="24" t="s">
         <v>39</v>
@@ -11771,22 +11774,22 @@
         <v>101600</v>
       </c>
       <c r="C284" s="24" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D284" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E284" s="24" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F284" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G284" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H284" s="24" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I284" s="24" t="s">
         <v>39</v>
@@ -11801,22 +11804,22 @@
         <v>101600</v>
       </c>
       <c r="C285" s="24" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D285" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E285" s="24" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F285" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G285" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H285" s="24" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I285" s="24" t="s">
         <v>39</v>
@@ -11831,22 +11834,22 @@
         <v>101600</v>
       </c>
       <c r="C286" s="24" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D286" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E286" s="24" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F286" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G286" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H286" s="24" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I286" s="24" t="s">
         <v>39</v>
@@ -11861,7 +11864,7 @@
         <v>101500</v>
       </c>
       <c r="C287" s="26" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D287" s="26" t="s">
         <v>422</v>
@@ -11876,7 +11879,7 @@
         <v>234</v>
       </c>
       <c r="H287" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I287" s="26" t="s">
         <v>435</v>
@@ -11906,7 +11909,7 @@
         <v>234</v>
       </c>
       <c r="H288" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I288" s="26" t="s">
         <v>107</v>
@@ -11936,7 +11939,7 @@
         <v>234</v>
       </c>
       <c r="H289" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I289" s="26" t="s">
         <v>106</v>
@@ -11966,7 +11969,7 @@
         <v>234</v>
       </c>
       <c r="H290" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I290" s="26" t="s">
         <v>432</v>
@@ -11981,7 +11984,7 @@
         <v>101500</v>
       </c>
       <c r="C291" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D291" s="26" t="s">
         <v>279</v>
@@ -11996,7 +11999,7 @@
         <v>234</v>
       </c>
       <c r="H291" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I291" s="26" t="s">
         <v>39</v>
@@ -12011,7 +12014,7 @@
         <v>101500</v>
       </c>
       <c r="C292" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D292" s="26" t="s">
         <v>279</v>
@@ -12026,7 +12029,7 @@
         <v>234</v>
       </c>
       <c r="H292" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I292" s="26" t="s">
         <v>39</v>
@@ -12041,7 +12044,7 @@
         <v>101500</v>
       </c>
       <c r="C293" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D293" s="26" t="s">
         <v>279</v>
@@ -12056,7 +12059,7 @@
         <v>234</v>
       </c>
       <c r="H293" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I293" s="26" t="s">
         <v>39</v>
@@ -12077,7 +12080,7 @@
         <v>279</v>
       </c>
       <c r="E294" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F294" s="26" t="s">
         <v>133</v>
@@ -12086,7 +12089,7 @@
         <v>255</v>
       </c>
       <c r="H294" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I294" s="26" t="s">
         <v>39</v>
@@ -12101,7 +12104,7 @@
         <v>101500</v>
       </c>
       <c r="C295" s="26" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D295" s="26" t="s">
         <v>422</v>
@@ -12116,7 +12119,7 @@
         <v>439</v>
       </c>
       <c r="H295" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I295" s="26" t="s">
         <v>107</v>
@@ -12131,7 +12134,7 @@
         <v>101500</v>
       </c>
       <c r="C296" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D296" s="26" t="s">
         <v>422</v>
@@ -12146,7 +12149,7 @@
         <v>174</v>
       </c>
       <c r="H296" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I296" s="26" t="s">
         <v>107</v>
@@ -12161,7 +12164,7 @@
         <v>101500</v>
       </c>
       <c r="C297" s="26" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D297" s="26" t="s">
         <v>422</v>
@@ -12176,7 +12179,7 @@
         <v>176</v>
       </c>
       <c r="H297" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I297" s="26" t="s">
         <v>107</v>
@@ -12191,7 +12194,7 @@
         <v>101500</v>
       </c>
       <c r="C298" s="26" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D298" s="26" t="s">
         <v>422</v>
@@ -12206,7 +12209,7 @@
         <v>178</v>
       </c>
       <c r="H298" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I298" s="26" t="s">
         <v>107</v>
@@ -12221,7 +12224,7 @@
         <v>101500</v>
       </c>
       <c r="C299" s="26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D299" s="26" t="s">
         <v>422</v>
@@ -12236,7 +12239,7 @@
         <v>255</v>
       </c>
       <c r="H299" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I299" s="26" t="s">
         <v>107</v>
@@ -12251,7 +12254,7 @@
         <v>101500</v>
       </c>
       <c r="C300" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D300" s="26" t="s">
         <v>21</v>
@@ -12263,10 +12266,10 @@
         <v>133</v>
       </c>
       <c r="G300" s="26" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H300" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I300" s="26" t="s">
         <v>89</v>
@@ -12281,7 +12284,7 @@
         <v>101500</v>
       </c>
       <c r="C301" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D301" s="26" t="s">
         <v>21</v>
@@ -12293,10 +12296,10 @@
         <v>133</v>
       </c>
       <c r="G301" s="26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H301" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I301" s="26" t="s">
         <v>89</v>
@@ -12311,7 +12314,7 @@
         <v>101500</v>
       </c>
       <c r="C302" s="26" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D302" s="26" t="s">
         <v>21</v>
@@ -12323,10 +12326,10 @@
         <v>133</v>
       </c>
       <c r="G302" s="26" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H302" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I302" s="26" t="s">
         <v>89</v>
@@ -12341,7 +12344,7 @@
         <v>101500</v>
       </c>
       <c r="C303" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D303" s="26" t="s">
         <v>21</v>
@@ -12353,10 +12356,10 @@
         <v>133</v>
       </c>
       <c r="G303" s="26" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H303" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I303" s="26" t="s">
         <v>89</v>
@@ -12371,7 +12374,7 @@
         <v>101500</v>
       </c>
       <c r="C304" s="26" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D304" s="26" t="s">
         <v>21</v>
@@ -12383,10 +12386,10 @@
         <v>133</v>
       </c>
       <c r="G304" s="26" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H304" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I304" s="26" t="s">
         <v>89</v>
@@ -12401,7 +12404,7 @@
         <v>101500</v>
       </c>
       <c r="C305" s="26" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D305" s="26" t="s">
         <v>21</v>
@@ -12416,7 +12419,7 @@
         <v>423</v>
       </c>
       <c r="H305" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I305" s="26" t="s">
         <v>89</v>
@@ -12431,7 +12434,7 @@
         <v>101500</v>
       </c>
       <c r="C306" s="26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D306" s="26" t="s">
         <v>21</v>
@@ -12443,10 +12446,10 @@
         <v>133</v>
       </c>
       <c r="G306" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H306" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I306" s="26" t="s">
         <v>89</v>
@@ -12461,7 +12464,7 @@
         <v>101500</v>
       </c>
       <c r="C307" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D307" s="26" t="s">
         <v>21</v>
@@ -12473,10 +12476,10 @@
         <v>133</v>
       </c>
       <c r="G307" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H307" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I307" s="26" t="s">
         <v>89</v>
@@ -12491,7 +12494,7 @@
         <v>101500</v>
       </c>
       <c r="C308" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D308" s="26" t="s">
         <v>21</v>
@@ -12503,10 +12506,10 @@
         <v>133</v>
       </c>
       <c r="G308" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H308" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I308" s="26" t="s">
         <v>89</v>
@@ -12521,7 +12524,7 @@
         <v>101500</v>
       </c>
       <c r="C309" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D309" s="26" t="s">
         <v>21</v>
@@ -12533,10 +12536,10 @@
         <v>133</v>
       </c>
       <c r="G309" s="26" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H309" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I309" s="26" t="s">
         <v>89</v>
@@ -12551,7 +12554,7 @@
         <v>101500</v>
       </c>
       <c r="C310" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D310" s="26" t="s">
         <v>21</v>
@@ -12566,7 +12569,7 @@
         <v>297</v>
       </c>
       <c r="H310" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I310" s="26" t="s">
         <v>157</v>
@@ -12581,7 +12584,7 @@
         <v>101500</v>
       </c>
       <c r="C311" s="26" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D311" s="26" t="s">
         <v>21</v>
@@ -12593,10 +12596,10 @@
         <v>133</v>
       </c>
       <c r="G311" s="26" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H311" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I311" s="26" t="s">
         <v>157</v>
@@ -12611,7 +12614,7 @@
         <v>101500</v>
       </c>
       <c r="C312" s="26" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D312" s="26" t="s">
         <v>21</v>
@@ -12623,10 +12626,10 @@
         <v>133</v>
       </c>
       <c r="G312" s="26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H312" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I312" s="26" t="s">
         <v>157</v>
@@ -12641,7 +12644,7 @@
         <v>101500</v>
       </c>
       <c r="C313" s="26" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D313" s="26" t="s">
         <v>21</v>
@@ -12653,10 +12656,10 @@
         <v>133</v>
       </c>
       <c r="G313" s="26" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H313" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I313" s="26" t="s">
         <v>157</v>
@@ -12671,7 +12674,7 @@
         <v>101500</v>
       </c>
       <c r="C314" s="26" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D314" s="26" t="s">
         <v>21</v>
@@ -12683,10 +12686,10 @@
         <v>133</v>
       </c>
       <c r="G314" s="26" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H314" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I314" s="26" t="s">
         <v>157</v>
@@ -12701,7 +12704,7 @@
         <v>101500</v>
       </c>
       <c r="C315" s="26" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D315" s="26" t="s">
         <v>21</v>
@@ -12713,10 +12716,10 @@
         <v>133</v>
       </c>
       <c r="G315" s="26" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H315" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I315" s="26" t="s">
         <v>157</v>
@@ -12731,7 +12734,7 @@
         <v>101500</v>
       </c>
       <c r="C316" s="26" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D316" s="26" t="s">
         <v>328</v>
@@ -12746,10 +12749,10 @@
         <v>234</v>
       </c>
       <c r="H316" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I316" s="26" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K316" s="110"/>
     </row>
@@ -12761,7 +12764,7 @@
         <v>102600</v>
       </c>
       <c r="C317" s="27" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D317" s="27" t="s">
         <v>422</v>
@@ -12773,13 +12776,13 @@
         <v>133</v>
       </c>
       <c r="G317" s="27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H317" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I317" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K317" s="111"/>
     </row>
@@ -12803,10 +12806,10 @@
         <v>133</v>
       </c>
       <c r="G318" s="27" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H318" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I318" s="27" t="s">
         <v>325</v>
@@ -12833,10 +12836,10 @@
         <v>133</v>
       </c>
       <c r="G319" s="27" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H319" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I319" s="27" t="s">
         <v>107</v>
@@ -12863,10 +12866,10 @@
         <v>133</v>
       </c>
       <c r="G320" s="27" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H320" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I320" s="27" t="s">
         <v>327</v>
@@ -12893,10 +12896,10 @@
         <v>133</v>
       </c>
       <c r="G321" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H321" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I321" s="27" t="s">
         <v>333</v>
@@ -12923,10 +12926,10 @@
         <v>133</v>
       </c>
       <c r="G322" s="27" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H322" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I322" s="27" t="s">
         <v>333</v>
@@ -12953,10 +12956,10 @@
         <v>133</v>
       </c>
       <c r="G323" s="27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H323" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I323" s="27" t="s">
         <v>340</v>
@@ -12983,10 +12986,10 @@
         <v>133</v>
       </c>
       <c r="G324" s="27" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H324" s="27" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I324" s="27" t="s">
         <v>39</v>
@@ -13013,10 +13016,10 @@
         <v>133</v>
       </c>
       <c r="G325" s="27" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H325" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I325" s="27" t="s">
         <v>291</v>
@@ -13043,7 +13046,7 @@
         <v>133</v>
       </c>
       <c r="G326" s="27" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I326" s="27" t="s">
         <v>106</v>
@@ -13058,7 +13061,7 @@
         <v>105000</v>
       </c>
       <c r="C327" s="20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D327" s="20" t="s">
         <v>422</v>
@@ -13070,13 +13073,13 @@
         <v>133</v>
       </c>
       <c r="G327" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H327" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I327" s="20" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="328" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13087,7 +13090,7 @@
         <v>105000</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D328" s="20" t="s">
         <v>425</v>
@@ -13099,10 +13102,10 @@
         <v>133</v>
       </c>
       <c r="G328" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H328" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I328" s="20" t="s">
         <v>325</v>
@@ -13116,7 +13119,7 @@
         <v>105000</v>
       </c>
       <c r="C329" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D329" s="20" t="s">
         <v>425</v>
@@ -13128,10 +13131,10 @@
         <v>133</v>
       </c>
       <c r="G329" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H329" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I329" s="20" t="s">
         <v>107</v>
@@ -13145,7 +13148,7 @@
         <v>105000</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D330" s="20" t="s">
         <v>425</v>
@@ -13157,10 +13160,10 @@
         <v>133</v>
       </c>
       <c r="G330" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H330" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I330" s="20" t="s">
         <v>327</v>
@@ -13180,16 +13183,16 @@
         <v>422</v>
       </c>
       <c r="E331" s="20" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F331" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G331" s="20" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H331" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I331" s="20" t="s">
         <v>333</v>
@@ -13209,16 +13212,16 @@
         <v>422</v>
       </c>
       <c r="E332" s="20" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F332" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G332" s="20" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H332" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I332" s="20" t="s">
         <v>333</v>
@@ -13238,16 +13241,16 @@
         <v>422</v>
       </c>
       <c r="E333" s="20" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G333" s="20" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H333" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I333" s="20" t="s">
         <v>340</v>
@@ -13273,10 +13276,10 @@
         <v>133</v>
       </c>
       <c r="G334" s="20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H334" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I334" s="20" t="s">
         <v>39</v>
@@ -13293,7 +13296,7 @@
         <v>289</v>
       </c>
       <c r="D335" s="20" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E335" s="20" t="s">
         <v>143</v>
@@ -13302,10 +13305,10 @@
         <v>133</v>
       </c>
       <c r="G335" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H335" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I335" s="20" t="s">
         <v>291</v>
@@ -13331,7 +13334,7 @@
         <v>133</v>
       </c>
       <c r="G336" s="20" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I336" s="20" t="s">
         <v>106</v>
@@ -13345,10 +13348,10 @@
         <v>105100</v>
       </c>
       <c r="C337" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E337" s="33" t="s">
         <v>41</v>
@@ -13360,7 +13363,7 @@
         <v>25</v>
       </c>
       <c r="H337" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I337" s="33" t="s">
         <v>39</v>
@@ -13375,10 +13378,10 @@
         <v>105100</v>
       </c>
       <c r="C338" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E338" s="33" t="s">
         <v>41</v>
@@ -13390,7 +13393,7 @@
         <v>344</v>
       </c>
       <c r="H338" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I338" s="33" t="s">
         <v>39</v>
@@ -13405,10 +13408,10 @@
         <v>105100</v>
       </c>
       <c r="C339" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D339" s="33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E339" s="33" t="s">
         <v>41</v>
@@ -13417,10 +13420,10 @@
         <v>133</v>
       </c>
       <c r="G339" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H339" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I339" s="33" t="s">
         <v>39</v>
@@ -13435,13 +13438,13 @@
         <v>105100</v>
       </c>
       <c r="C340" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E340" s="33" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F340" s="33" t="s">
         <v>133</v>
@@ -13450,7 +13453,7 @@
         <v>25</v>
       </c>
       <c r="H340" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I340" s="33" t="s">
         <v>39</v>
@@ -13465,13 +13468,13 @@
         <v>105100</v>
       </c>
       <c r="C341" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D341" s="33" t="s">
+        <v>575</v>
+      </c>
+      <c r="E341" s="33" t="s">
         <v>574</v>
-      </c>
-      <c r="E341" s="33" t="s">
-        <v>573</v>
       </c>
       <c r="F341" s="33" t="s">
         <v>133</v>
@@ -13480,7 +13483,7 @@
         <v>344</v>
       </c>
       <c r="H341" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I341" s="33" t="s">
         <v>39</v>
@@ -13495,22 +13498,22 @@
         <v>105100</v>
       </c>
       <c r="C342" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E342" s="33" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F342" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G342" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H342" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I342" s="33" t="s">
         <v>39</v>
@@ -13537,10 +13540,10 @@
         <v>133</v>
       </c>
       <c r="G343" s="27" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H343" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I343" s="27" t="s">
         <v>325</v>
@@ -13566,10 +13569,10 @@
         <v>133</v>
       </c>
       <c r="G344" s="27" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H344" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I344" s="27" t="s">
         <v>107</v>
@@ -13595,10 +13598,10 @@
         <v>133</v>
       </c>
       <c r="G345" s="27" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H345" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I345" s="27" t="s">
         <v>327</v>
@@ -13612,22 +13615,22 @@
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D346" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E346" s="27" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F346" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G346" s="27" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H346" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I346" s="27" t="s">
         <v>333</v>
@@ -13647,16 +13650,16 @@
         <v>422</v>
       </c>
       <c r="E347" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="F347" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G347" s="27" t="s">
         <v>580</v>
       </c>
-      <c r="F347" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G347" s="27" t="s">
-        <v>579</v>
-      </c>
       <c r="H347" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I347" s="27" t="s">
         <v>333</v>
@@ -13676,16 +13679,16 @@
         <v>422</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F348" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G348" s="27" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H348" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I348" s="27" t="s">
         <v>333</v>
@@ -13705,16 +13708,16 @@
         <v>422</v>
       </c>
       <c r="E349" s="27" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F349" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G349" s="27" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H349" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I349" s="27" t="s">
         <v>340</v>
@@ -13740,10 +13743,10 @@
         <v>133</v>
       </c>
       <c r="G350" s="27" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H350" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I350" s="27" t="s">
         <v>39</v>
@@ -13760,7 +13763,7 @@
         <v>289</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E351" s="27" t="s">
         <v>140</v>
@@ -13769,10 +13772,10 @@
         <v>133</v>
       </c>
       <c r="G351" s="27" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H351" s="27" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I351" s="27" t="s">
         <v>291</v>
@@ -13798,7 +13801,7 @@
         <v>133</v>
       </c>
       <c r="G352" s="27" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I352" s="27" t="s">
         <v>106</v>
@@ -13812,7 +13815,7 @@
         <v>100800</v>
       </c>
       <c r="C353" s="28" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D353" s="28" t="s">
         <v>422</v>
@@ -13824,13 +13827,13 @@
         <v>133</v>
       </c>
       <c r="G353" s="28" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H353" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I353" s="28" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K353" s="112"/>
     </row>
@@ -13854,7 +13857,7 @@
         <v>133</v>
       </c>
       <c r="G354" s="28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I354" s="28" t="s">
         <v>325</v>
@@ -13881,10 +13884,10 @@
         <v>133</v>
       </c>
       <c r="G355" s="28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H355" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I355" s="28" t="s">
         <v>107</v>
@@ -13911,10 +13914,10 @@
         <v>133</v>
       </c>
       <c r="G356" s="28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H356" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I356" s="28" t="s">
         <v>327</v>
@@ -13935,16 +13938,16 @@
         <v>438</v>
       </c>
       <c r="E357" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="F357" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G357" s="28" t="s">
+        <v>464</v>
+      </c>
+      <c r="H357" s="28" t="s">
         <v>585</v>
-      </c>
-      <c r="F357" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G357" s="28" t="s">
-        <v>463</v>
-      </c>
-      <c r="H357" s="28" t="s">
-        <v>584</v>
       </c>
       <c r="I357" s="28" t="s">
         <v>333</v>
@@ -13965,16 +13968,16 @@
         <v>438</v>
       </c>
       <c r="E358" s="28" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F358" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G358" s="28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H358" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I358" s="28" t="s">
         <v>333</v>
@@ -13995,16 +13998,16 @@
         <v>438</v>
       </c>
       <c r="E359" s="28" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F359" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G359" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H359" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I359" s="28" t="s">
         <v>340</v>
@@ -14025,7 +14028,7 @@
         <v>21</v>
       </c>
       <c r="E360" s="28" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F360" s="28" t="s">
         <v>133</v>
@@ -14034,7 +14037,7 @@
         <v>341</v>
       </c>
       <c r="H360" s="28" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I360" s="28" t="s">
         <v>39</v>
@@ -14061,10 +14064,10 @@
         <v>133</v>
       </c>
       <c r="G361" s="28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H361" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I361" s="28" t="s">
         <v>291</v>
@@ -14091,7 +14094,7 @@
         <v>133</v>
       </c>
       <c r="G362" s="28" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H362" s="28"/>
       <c r="I362" s="28" t="s">
@@ -14109,7 +14112,7 @@
         <v>105300</v>
       </c>
       <c r="C363" s="29" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D363" s="29" t="s">
         <v>21</v>
@@ -14121,10 +14124,10 @@
         <v>133</v>
       </c>
       <c r="G363" s="29" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H363" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I363" s="29" t="s">
         <v>340</v>
@@ -14139,7 +14142,7 @@
         <v>105300</v>
       </c>
       <c r="C364" s="29" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D364" s="29" t="s">
         <v>21</v>
@@ -14151,13 +14154,13 @@
         <v>133</v>
       </c>
       <c r="G364" s="29" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H364" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I364" s="29" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K364" s="113"/>
     </row>
@@ -14169,10 +14172,10 @@
         <v>105300</v>
       </c>
       <c r="C365" s="29" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D365" s="29" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E365" s="29" t="s">
         <v>136</v>
@@ -14181,13 +14184,13 @@
         <v>133</v>
       </c>
       <c r="G365" s="29" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H365" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I365" s="29" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K365" s="113"/>
     </row>
@@ -14199,22 +14202,22 @@
         <v>105300</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D366" s="29" t="s">
         <v>328</v>
       </c>
       <c r="E366" s="29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F366" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G366" s="29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H366" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I366" s="29" t="s">
         <v>294</v>
@@ -14241,7 +14244,7 @@
         <v>133</v>
       </c>
       <c r="G367" s="29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I367" s="29" t="s">
         <v>106</v>
@@ -14256,13 +14259,13 @@
         <v>105300</v>
       </c>
       <c r="C368" s="29" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D368" s="29" t="s">
         <v>328</v>
       </c>
       <c r="E368" s="29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F368" s="29" t="s">
         <v>133</v>
@@ -14271,7 +14274,7 @@
         <v>353</v>
       </c>
       <c r="H368" s="29" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I368" s="29" t="s">
         <v>109</v>
@@ -14298,13 +14301,13 @@
         <v>133</v>
       </c>
       <c r="G369" s="30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H369" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I369" s="30" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K369" s="114"/>
     </row>
@@ -14328,13 +14331,13 @@
         <v>133</v>
       </c>
       <c r="G370" s="30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H370" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I370" s="30" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K370" s="114"/>
     </row>
@@ -14346,7 +14349,7 @@
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D371" s="30" t="s">
         <v>328</v>
@@ -14358,10 +14361,10 @@
         <v>133</v>
       </c>
       <c r="G371" s="30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H371" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I371" s="30" t="s">
         <v>340</v>
@@ -14376,22 +14379,22 @@
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D372" s="30" t="s">
         <v>328</v>
       </c>
       <c r="E372" s="30" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F372" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H372" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I372" s="30" t="s">
         <v>294</v>
@@ -14412,13 +14415,13 @@
         <v>21</v>
       </c>
       <c r="E373" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F373" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G373" s="30" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H373" s="30" t="s">
         <v>455</v>
@@ -14448,7 +14451,7 @@
         <v>133</v>
       </c>
       <c r="G374" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I374" s="30" t="s">
         <v>106</v>
@@ -14475,13 +14478,13 @@
         <v>133</v>
       </c>
       <c r="G375" s="31" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H375" s="31" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I375" s="31" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K375" s="115"/>
     </row>
@@ -14505,13 +14508,13 @@
         <v>133</v>
       </c>
       <c r="G376" s="31" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H376" s="31" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I376" s="31" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K376" s="115"/>
     </row>
@@ -14523,7 +14526,7 @@
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D377" s="31" t="s">
         <v>328</v>
@@ -14535,10 +14538,10 @@
         <v>133</v>
       </c>
       <c r="G377" s="31" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H377" s="31" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I377" s="31" t="s">
         <v>340</v>
@@ -14565,10 +14568,10 @@
         <v>133</v>
       </c>
       <c r="G378" s="31" t="s">
+        <v>615</v>
+      </c>
+      <c r="H378" s="31" t="s">
         <v>614</v>
-      </c>
-      <c r="H378" s="31" t="s">
-        <v>613</v>
       </c>
       <c r="I378" s="31" t="s">
         <v>39</v>
@@ -14595,7 +14598,7 @@
         <v>133</v>
       </c>
       <c r="G379" s="32" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I379" s="32" t="s">
         <v>39</v>
@@ -14610,7 +14613,7 @@
         <v>105500</v>
       </c>
       <c r="C380" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D380" s="32" t="s">
         <v>21</v>
@@ -14637,7 +14640,7 @@
         <v>104800</v>
       </c>
       <c r="C381" s="33" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D381" s="33" t="s">
         <v>422</v>
@@ -14649,13 +14652,13 @@
         <v>133</v>
       </c>
       <c r="G381" s="33" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H381" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I381" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K381" s="82"/>
     </row>
@@ -14667,7 +14670,7 @@
         <v>104800</v>
       </c>
       <c r="C382" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D382" s="33" t="s">
         <v>328</v>
@@ -14679,10 +14682,10 @@
         <v>133</v>
       </c>
       <c r="G382" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H382" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I382" s="33" t="s">
         <v>325</v>
@@ -14697,7 +14700,7 @@
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D383" s="33" t="s">
         <v>328</v>
@@ -14709,10 +14712,10 @@
         <v>133</v>
       </c>
       <c r="G383" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H383" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I383" s="33" t="s">
         <v>327</v>
@@ -14727,7 +14730,7 @@
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D384" s="33" t="s">
         <v>21</v>
@@ -14739,10 +14742,10 @@
         <v>133</v>
       </c>
       <c r="G384" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H384" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I384" s="33" t="s">
         <v>107</v>
@@ -14769,10 +14772,10 @@
         <v>133</v>
       </c>
       <c r="G385" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H385" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I385" s="33" t="s">
         <v>291</v>
@@ -14793,16 +14796,16 @@
         <v>422</v>
       </c>
       <c r="E386" s="33" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F386" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G386" s="33" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H386" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I386" s="33" t="s">
         <v>333</v>
@@ -14823,16 +14826,16 @@
         <v>422</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F387" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G387" s="33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H387" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I387" s="33" t="s">
         <v>333</v>
@@ -14859,7 +14862,7 @@
         <v>133</v>
       </c>
       <c r="G388" s="33" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H388" s="33" t="s">
         <v>408</v>
@@ -14889,7 +14892,7 @@
         <v>133</v>
       </c>
       <c r="G389" s="32" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I389" s="32" t="s">
         <v>39</v>
@@ -14904,7 +14907,7 @@
         <v>105501</v>
       </c>
       <c r="C390" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D390" s="32" t="s">
         <v>21</v>
@@ -14931,7 +14934,7 @@
         <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
@@ -14943,7 +14946,7 @@
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>39</v>
@@ -14970,7 +14973,7 @@
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I392" s="32" t="s">
         <v>39</v>
@@ -14985,7 +14988,7 @@
         <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
@@ -15012,7 +15015,7 @@
         <v>105502</v>
       </c>
       <c r="C394" s="32" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D394" s="32" t="s">
         <v>21</v>
@@ -15056,7 +15059,7 @@
         <v>455</v>
       </c>
       <c r="I395" s="34" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K395" s="118"/>
     </row>
@@ -15068,7 +15071,7 @@
         <v>104100</v>
       </c>
       <c r="C396" s="34" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D396" s="34" t="s">
         <v>328</v>
@@ -15143,7 +15146,7 @@
         <v>255</v>
       </c>
       <c r="H398" s="34" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I398" s="34" t="s">
         <v>39</v>
@@ -15203,10 +15206,10 @@
         <v>234</v>
       </c>
       <c r="H400" s="35" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I400" s="35" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K400" s="119"/>
     </row>
@@ -15218,7 +15221,7 @@
         <v>104200</v>
       </c>
       <c r="C401" s="35" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D401" s="35" t="s">
         <v>328</v>
@@ -15233,7 +15236,7 @@
         <v>234</v>
       </c>
       <c r="H401" s="35" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I401" s="35" t="s">
         <v>107</v>
@@ -15263,7 +15266,7 @@
         <v>234</v>
       </c>
       <c r="H402" s="35" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I402" s="35" t="s">
         <v>291</v>
@@ -15293,7 +15296,7 @@
         <v>255</v>
       </c>
       <c r="H403" s="35" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I403" s="35" t="s">
         <v>39</v>
@@ -15323,7 +15326,7 @@
         <v>234</v>
       </c>
       <c r="H404" s="35" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I404" s="35" t="s">
         <v>340</v>
@@ -15348,24 +15351,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D2" t="s">
         <v>630</v>
       </c>
-      <c r="D2" t="s">
-        <v>629</v>
-      </c>
       <c r="E2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15373,16 +15376,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15390,16 +15393,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15407,16 +15410,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15424,7 +15427,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15432,7 +15435,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15440,7 +15443,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15448,7 +15451,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15456,7 +15459,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15464,7 +15467,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15472,7 +15475,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15480,7 +15483,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15488,7 +15491,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15496,7 +15499,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15504,7 +15507,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15512,7 +15515,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15520,7 +15523,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15528,7 +15531,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15536,7 +15539,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15544,7 +15547,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15552,7 +15555,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15560,7 +15563,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15568,7 +15571,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -15576,7 +15579,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -15584,7 +15587,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -15592,7 +15595,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -15600,7 +15603,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -15608,7 +15611,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -15616,7 +15619,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -15624,7 +15627,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -15632,7 +15635,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -15640,7 +15643,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -15648,7 +15651,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -15656,7 +15659,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -15664,7 +15667,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -15672,7 +15675,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -15680,7 +15683,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -15688,7 +15691,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -15696,7 +15699,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -15704,7 +15707,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -15712,7 +15715,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -15720,7 +15723,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -15728,7 +15731,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -15736,7 +15739,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15744,7 +15747,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -15752,7 +15755,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -15760,7 +15763,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="684">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1465,214 +1465,217 @@
     <t>3_90|4_10</t>
   </si>
   <si>
+    <t>0_200|1_80|2_60|3_1|4_1</t>
+  </si>
+  <si>
+    <t>前四轴改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>概率在第一轴上改出bonus</t>
+  </si>
+  <si>
+    <t>常规&amp;免费模式</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1</t>
+  </si>
+  <si>
+    <t>在第一轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>在第五轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>第五轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>概率在第五轴上改出bonus</t>
+  </si>
+  <si>
+    <t>概率在第二三四轴改出18符号</t>
+  </si>
+  <si>
+    <t>11_12_18</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>1_20|2_20|3_20|4_20|5_10|6_6|7_4</t>
+  </si>
+  <si>
+    <t>在第二轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>在第三轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>在第四轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率在第二轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率第三轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率第四轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>0_30|1_1</t>
+  </si>
+  <si>
+    <t>9_10_11_12_13_14</t>
+  </si>
+  <si>
+    <t>改出百搭符号</t>
+  </si>
+  <si>
+    <t>5_9_10_11_12_13_14</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1|65_1</t>
+  </si>
+  <si>
+    <t>8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|66_1|67_1|68_1|69_1|70_1|71_1|72_1|73_1|74_1|75_1|76_1</t>
+  </si>
+  <si>
+    <t>9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1|77_1|78_1|79_1|80_1|81_1|82_1|83_1|84_1|85_1|86_1|87_1</t>
+  </si>
+  <si>
+    <t>10_1_1|11_1_1|12_1_1|16_1_1|17_1_1|18_1_1|22_1_1|23_1_1|24_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>概率改出免费+1符号</t>
+  </si>
+  <si>
+    <t>0_9|1_1</t>
+  </si>
+  <si>
+    <t>31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>改出黄金10符号</t>
+  </si>
+  <si>
+    <t>121_1</t>
+  </si>
+  <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金J符号</t>
+  </si>
+  <si>
+    <t>122_1</t>
+  </si>
+  <si>
+    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金Q符号</t>
+  </si>
+  <si>
+    <t>123_1</t>
+  </si>
+  <si>
+    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金K符号</t>
+  </si>
+  <si>
+    <t>124_1</t>
+  </si>
+  <si>
+    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金A符号</t>
+  </si>
+  <si>
+    <t>125_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金罗纳尔多</t>
+  </si>
+  <si>
+    <t>126_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金格列兹曼</t>
+  </si>
+  <si>
+    <t>127_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金内马尔</t>
+  </si>
+  <si>
+    <t>128_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金斯特林</t>
+  </si>
+  <si>
+    <t>129_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金C罗</t>
+  </si>
+  <si>
+    <t>130_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>改出黄金梅西</t>
+  </si>
+  <si>
+    <t>131_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号</t>
+  </si>
+  <si>
+    <t>13_14_15_16_17_18_19_20_21_22</t>
+  </si>
+  <si>
     <t>0_50|1_30|2_15|3_4|4_1</t>
-  </si>
-  <si>
-    <t>前四轴改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>概率在第一轴上改出bonus</t>
-  </si>
-  <si>
-    <t>常规&amp;免费模式</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1</t>
-  </si>
-  <si>
-    <t>在第一轴改出1个bonus</t>
-  </si>
-  <si>
-    <t>在第五轴改出1个bonus</t>
-  </si>
-  <si>
-    <t>第五轴改出奖池符号</t>
-  </si>
-  <si>
-    <t>概率在第五轴上改出bonus</t>
-  </si>
-  <si>
-    <t>概率在第二三四轴改出18符号</t>
-  </si>
-  <si>
-    <t>11_12_18</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>1_20|2_20|3_20|4_20|5_10|6_6|7_4</t>
-  </si>
-  <si>
-    <t>在第二轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>在第三轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>在第四轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率在第二轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率第三轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率第四轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>0_30|1_1</t>
-  </si>
-  <si>
-    <t>9_10_11_12_13_14</t>
-  </si>
-  <si>
-    <t>改出百搭符号</t>
-  </si>
-  <si>
-    <t>5_9_10_11_12_13_14</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
-  </si>
-  <si>
-    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1|65_1</t>
-  </si>
-  <si>
-    <t>8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|66_1|67_1|68_1|69_1|70_1|71_1|72_1|73_1|74_1|75_1|76_1</t>
-  </si>
-  <si>
-    <t>9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1|77_1|78_1|79_1|80_1|81_1|82_1|83_1|84_1|85_1|86_1|87_1</t>
-  </si>
-  <si>
-    <t>10_1_1|11_1_1|12_1_1|16_1_1|17_1_1|18_1_1|22_1_1|23_1_1|24_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>概率改出免费+1符号</t>
-  </si>
-  <si>
-    <t>0_9|1_1</t>
-  </si>
-  <si>
-    <t>31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
-  </si>
-  <si>
-    <t>改出黄金10符号</t>
-  </si>
-  <si>
-    <t>121_1</t>
-  </si>
-  <si>
-    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金J符号</t>
-  </si>
-  <si>
-    <t>122_1</t>
-  </si>
-  <si>
-    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金Q符号</t>
-  </si>
-  <si>
-    <t>123_1</t>
-  </si>
-  <si>
-    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金K符号</t>
-  </si>
-  <si>
-    <t>124_1</t>
-  </si>
-  <si>
-    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金A符号</t>
-  </si>
-  <si>
-    <t>125_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金罗纳尔多</t>
-  </si>
-  <si>
-    <t>126_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金格列兹曼</t>
-  </si>
-  <si>
-    <t>127_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金内马尔</t>
-  </si>
-  <si>
-    <t>128_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金斯特林</t>
-  </si>
-  <si>
-    <t>129_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金C罗</t>
-  </si>
-  <si>
-    <t>130_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金梅西</t>
-  </si>
-  <si>
-    <t>131_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_10_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>概率改出百搭wild符号</t>
-  </si>
-  <si>
-    <t>13_14_15_16_17_18_19_20_21_22</t>
   </si>
   <si>
     <t>改出20符号</t>
@@ -11882,7 +11885,7 @@
         <v>504</v>
       </c>
       <c r="I287" s="26" t="s">
-        <v>435</v>
+        <v>505</v>
       </c>
       <c r="K287" s="110"/>
     </row>
@@ -11984,7 +11987,7 @@
         <v>101500</v>
       </c>
       <c r="C291" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D291" s="26" t="s">
         <v>279</v>
@@ -12014,7 +12017,7 @@
         <v>101500</v>
       </c>
       <c r="C292" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D292" s="26" t="s">
         <v>279</v>
@@ -12044,7 +12047,7 @@
         <v>101500</v>
       </c>
       <c r="C293" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D293" s="26" t="s">
         <v>279</v>
@@ -12080,7 +12083,7 @@
         <v>279</v>
       </c>
       <c r="E294" s="26" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F294" s="26" t="s">
         <v>133</v>
@@ -12104,7 +12107,7 @@
         <v>101500</v>
       </c>
       <c r="C295" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D295" s="26" t="s">
         <v>422</v>
@@ -12134,7 +12137,7 @@
         <v>101500</v>
       </c>
       <c r="C296" s="26" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D296" s="26" t="s">
         <v>422</v>
@@ -12164,7 +12167,7 @@
         <v>101500</v>
       </c>
       <c r="C297" s="26" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D297" s="26" t="s">
         <v>422</v>
@@ -12194,7 +12197,7 @@
         <v>101500</v>
       </c>
       <c r="C298" s="26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D298" s="26" t="s">
         <v>422</v>
@@ -12224,7 +12227,7 @@
         <v>101500</v>
       </c>
       <c r="C299" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D299" s="26" t="s">
         <v>422</v>
@@ -12254,7 +12257,7 @@
         <v>101500</v>
       </c>
       <c r="C300" s="26" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D300" s="26" t="s">
         <v>21</v>
@@ -12266,7 +12269,7 @@
         <v>133</v>
       </c>
       <c r="G300" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H300" s="26" t="s">
         <v>504</v>
@@ -12284,7 +12287,7 @@
         <v>101500</v>
       </c>
       <c r="C301" s="26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D301" s="26" t="s">
         <v>21</v>
@@ -12296,7 +12299,7 @@
         <v>133</v>
       </c>
       <c r="G301" s="26" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H301" s="26" t="s">
         <v>504</v>
@@ -12314,7 +12317,7 @@
         <v>101500</v>
       </c>
       <c r="C302" s="26" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D302" s="26" t="s">
         <v>21</v>
@@ -12326,7 +12329,7 @@
         <v>133</v>
       </c>
       <c r="G302" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H302" s="26" t="s">
         <v>504</v>
@@ -12344,7 +12347,7 @@
         <v>101500</v>
       </c>
       <c r="C303" s="26" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D303" s="26" t="s">
         <v>21</v>
@@ -12356,7 +12359,7 @@
         <v>133</v>
       </c>
       <c r="G303" s="26" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H303" s="26" t="s">
         <v>504</v>
@@ -12374,7 +12377,7 @@
         <v>101500</v>
       </c>
       <c r="C304" s="26" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D304" s="26" t="s">
         <v>21</v>
@@ -12386,7 +12389,7 @@
         <v>133</v>
       </c>
       <c r="G304" s="26" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H304" s="26" t="s">
         <v>504</v>
@@ -12404,7 +12407,7 @@
         <v>101500</v>
       </c>
       <c r="C305" s="26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D305" s="26" t="s">
         <v>21</v>
@@ -12434,7 +12437,7 @@
         <v>101500</v>
       </c>
       <c r="C306" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D306" s="26" t="s">
         <v>21</v>
@@ -12446,7 +12449,7 @@
         <v>133</v>
       </c>
       <c r="G306" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H306" s="26" t="s">
         <v>504</v>
@@ -12464,7 +12467,7 @@
         <v>101500</v>
       </c>
       <c r="C307" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D307" s="26" t="s">
         <v>21</v>
@@ -12476,7 +12479,7 @@
         <v>133</v>
       </c>
       <c r="G307" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H307" s="26" t="s">
         <v>504</v>
@@ -12494,7 +12497,7 @@
         <v>101500</v>
       </c>
       <c r="C308" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D308" s="26" t="s">
         <v>21</v>
@@ -12506,7 +12509,7 @@
         <v>133</v>
       </c>
       <c r="G308" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H308" s="26" t="s">
         <v>504</v>
@@ -12524,7 +12527,7 @@
         <v>101500</v>
       </c>
       <c r="C309" s="26" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D309" s="26" t="s">
         <v>21</v>
@@ -12536,7 +12539,7 @@
         <v>133</v>
       </c>
       <c r="G309" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H309" s="26" t="s">
         <v>504</v>
@@ -12554,7 +12557,7 @@
         <v>101500</v>
       </c>
       <c r="C310" s="26" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D310" s="26" t="s">
         <v>21</v>
@@ -12584,7 +12587,7 @@
         <v>101500</v>
       </c>
       <c r="C311" s="26" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D311" s="26" t="s">
         <v>21</v>
@@ -12596,7 +12599,7 @@
         <v>133</v>
       </c>
       <c r="G311" s="26" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H311" s="26" t="s">
         <v>504</v>
@@ -12614,7 +12617,7 @@
         <v>101500</v>
       </c>
       <c r="C312" s="26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D312" s="26" t="s">
         <v>21</v>
@@ -12626,7 +12629,7 @@
         <v>133</v>
       </c>
       <c r="G312" s="26" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H312" s="26" t="s">
         <v>504</v>
@@ -12644,7 +12647,7 @@
         <v>101500</v>
       </c>
       <c r="C313" s="26" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D313" s="26" t="s">
         <v>21</v>
@@ -12656,7 +12659,7 @@
         <v>133</v>
       </c>
       <c r="G313" s="26" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H313" s="26" t="s">
         <v>504</v>
@@ -12674,7 +12677,7 @@
         <v>101500</v>
       </c>
       <c r="C314" s="26" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D314" s="26" t="s">
         <v>21</v>
@@ -12686,7 +12689,7 @@
         <v>133</v>
       </c>
       <c r="G314" s="26" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H314" s="26" t="s">
         <v>504</v>
@@ -12704,7 +12707,7 @@
         <v>101500</v>
       </c>
       <c r="C315" s="26" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D315" s="26" t="s">
         <v>21</v>
@@ -12716,7 +12719,7 @@
         <v>133</v>
       </c>
       <c r="G315" s="26" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H315" s="26" t="s">
         <v>504</v>
@@ -12734,7 +12737,7 @@
         <v>101500</v>
       </c>
       <c r="C316" s="26" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D316" s="26" t="s">
         <v>328</v>
@@ -12779,10 +12782,10 @@
         <v>458</v>
       </c>
       <c r="H317" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I317" s="27" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K317" s="111"/>
     </row>
@@ -12806,10 +12809,10 @@
         <v>133</v>
       </c>
       <c r="G318" s="27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H318" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I318" s="27" t="s">
         <v>325</v>
@@ -12836,10 +12839,10 @@
         <v>133</v>
       </c>
       <c r="G319" s="27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H319" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I319" s="27" t="s">
         <v>107</v>
@@ -12866,10 +12869,10 @@
         <v>133</v>
       </c>
       <c r="G320" s="27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H320" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I320" s="27" t="s">
         <v>327</v>
@@ -12899,7 +12902,7 @@
         <v>464</v>
       </c>
       <c r="H321" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I321" s="27" t="s">
         <v>333</v>
@@ -12929,7 +12932,7 @@
         <v>466</v>
       </c>
       <c r="H322" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I322" s="27" t="s">
         <v>333</v>
@@ -12956,10 +12959,10 @@
         <v>133</v>
       </c>
       <c r="G323" s="27" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H323" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I323" s="27" t="s">
         <v>340</v>
@@ -12986,10 +12989,10 @@
         <v>133</v>
       </c>
       <c r="G324" s="27" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H324" s="27" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I324" s="27" t="s">
         <v>39</v>
@@ -13016,10 +13019,10 @@
         <v>133</v>
       </c>
       <c r="G325" s="27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H325" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I325" s="27" t="s">
         <v>291</v>
@@ -13046,7 +13049,7 @@
         <v>133</v>
       </c>
       <c r="G326" s="27" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I326" s="27" t="s">
         <v>106</v>
@@ -13061,7 +13064,7 @@
         <v>105000</v>
       </c>
       <c r="C327" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D327" s="20" t="s">
         <v>422</v>
@@ -13076,10 +13079,10 @@
         <v>458</v>
       </c>
       <c r="H327" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I327" s="20" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="328" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13090,7 +13093,7 @@
         <v>105000</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D328" s="20" t="s">
         <v>425</v>
@@ -13102,10 +13105,10 @@
         <v>133</v>
       </c>
       <c r="G328" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H328" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I328" s="20" t="s">
         <v>325</v>
@@ -13119,7 +13122,7 @@
         <v>105000</v>
       </c>
       <c r="C329" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D329" s="20" t="s">
         <v>425</v>
@@ -13131,10 +13134,10 @@
         <v>133</v>
       </c>
       <c r="G329" s="20" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H329" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I329" s="20" t="s">
         <v>107</v>
@@ -13148,7 +13151,7 @@
         <v>105000</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D330" s="20" t="s">
         <v>425</v>
@@ -13160,10 +13163,10 @@
         <v>133</v>
       </c>
       <c r="G330" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H330" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I330" s="20" t="s">
         <v>327</v>
@@ -13183,16 +13186,16 @@
         <v>422</v>
       </c>
       <c r="E331" s="20" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F331" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G331" s="20" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H331" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I331" s="20" t="s">
         <v>333</v>
@@ -13212,16 +13215,16 @@
         <v>422</v>
       </c>
       <c r="E332" s="20" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F332" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G332" s="20" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H332" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I332" s="20" t="s">
         <v>333</v>
@@ -13241,16 +13244,16 @@
         <v>422</v>
       </c>
       <c r="E333" s="20" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G333" s="20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H333" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I333" s="20" t="s">
         <v>340</v>
@@ -13276,10 +13279,10 @@
         <v>133</v>
       </c>
       <c r="G334" s="20" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H334" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I334" s="20" t="s">
         <v>39</v>
@@ -13296,7 +13299,7 @@
         <v>289</v>
       </c>
       <c r="D335" s="20" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E335" s="20" t="s">
         <v>143</v>
@@ -13305,10 +13308,10 @@
         <v>133</v>
       </c>
       <c r="G335" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H335" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I335" s="20" t="s">
         <v>291</v>
@@ -13334,7 +13337,7 @@
         <v>133</v>
       </c>
       <c r="G336" s="20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I336" s="20" t="s">
         <v>106</v>
@@ -13348,10 +13351,10 @@
         <v>105100</v>
       </c>
       <c r="C337" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E337" s="33" t="s">
         <v>41</v>
@@ -13363,7 +13366,7 @@
         <v>25</v>
       </c>
       <c r="H337" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I337" s="33" t="s">
         <v>39</v>
@@ -13378,10 +13381,10 @@
         <v>105100</v>
       </c>
       <c r="C338" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E338" s="33" t="s">
         <v>41</v>
@@ -13393,7 +13396,7 @@
         <v>344</v>
       </c>
       <c r="H338" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I338" s="33" t="s">
         <v>39</v>
@@ -13408,10 +13411,10 @@
         <v>105100</v>
       </c>
       <c r="C339" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D339" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E339" s="33" t="s">
         <v>41</v>
@@ -13423,7 +13426,7 @@
         <v>460</v>
       </c>
       <c r="H339" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I339" s="33" t="s">
         <v>39</v>
@@ -13438,13 +13441,13 @@
         <v>105100</v>
       </c>
       <c r="C340" s="33" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E340" s="33" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F340" s="33" t="s">
         <v>133</v>
@@ -13453,7 +13456,7 @@
         <v>25</v>
       </c>
       <c r="H340" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I340" s="33" t="s">
         <v>39</v>
@@ -13468,13 +13471,13 @@
         <v>105100</v>
       </c>
       <c r="C341" s="33" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D341" s="33" t="s">
+        <v>576</v>
+      </c>
+      <c r="E341" s="33" t="s">
         <v>575</v>
-      </c>
-      <c r="E341" s="33" t="s">
-        <v>574</v>
       </c>
       <c r="F341" s="33" t="s">
         <v>133</v>
@@ -13483,7 +13486,7 @@
         <v>344</v>
       </c>
       <c r="H341" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I341" s="33" t="s">
         <v>39</v>
@@ -13498,13 +13501,13 @@
         <v>105100</v>
       </c>
       <c r="C342" s="33" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E342" s="33" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F342" s="33" t="s">
         <v>133</v>
@@ -13513,7 +13516,7 @@
         <v>460</v>
       </c>
       <c r="H342" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I342" s="33" t="s">
         <v>39</v>
@@ -13540,10 +13543,10 @@
         <v>133</v>
       </c>
       <c r="G343" s="27" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H343" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I343" s="27" t="s">
         <v>325</v>
@@ -13569,10 +13572,10 @@
         <v>133</v>
       </c>
       <c r="G344" s="27" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H344" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I344" s="27" t="s">
         <v>107</v>
@@ -13598,10 +13601,10 @@
         <v>133</v>
       </c>
       <c r="G345" s="27" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H345" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I345" s="27" t="s">
         <v>327</v>
@@ -13615,22 +13618,22 @@
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D346" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E346" s="27" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F346" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G346" s="27" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H346" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I346" s="27" t="s">
         <v>333</v>
@@ -13650,16 +13653,16 @@
         <v>422</v>
       </c>
       <c r="E347" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="F347" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G347" s="27" t="s">
         <v>581</v>
       </c>
-      <c r="F347" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G347" s="27" t="s">
-        <v>580</v>
-      </c>
       <c r="H347" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I347" s="27" t="s">
         <v>333</v>
@@ -13679,16 +13682,16 @@
         <v>422</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F348" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G348" s="27" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H348" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I348" s="27" t="s">
         <v>333</v>
@@ -13708,16 +13711,16 @@
         <v>422</v>
       </c>
       <c r="E349" s="27" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F349" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G349" s="27" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H349" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I349" s="27" t="s">
         <v>340</v>
@@ -13743,10 +13746,10 @@
         <v>133</v>
       </c>
       <c r="G350" s="27" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H350" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I350" s="27" t="s">
         <v>39</v>
@@ -13763,7 +13766,7 @@
         <v>289</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E351" s="27" t="s">
         <v>140</v>
@@ -13772,10 +13775,10 @@
         <v>133</v>
       </c>
       <c r="G351" s="27" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H351" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I351" s="27" t="s">
         <v>291</v>
@@ -13801,7 +13804,7 @@
         <v>133</v>
       </c>
       <c r="G352" s="27" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I352" s="27" t="s">
         <v>106</v>
@@ -13830,10 +13833,10 @@
         <v>458</v>
       </c>
       <c r="H353" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I353" s="28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K353" s="112"/>
     </row>
@@ -13857,7 +13860,7 @@
         <v>133</v>
       </c>
       <c r="G354" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I354" s="28" t="s">
         <v>325</v>
@@ -13884,10 +13887,10 @@
         <v>133</v>
       </c>
       <c r="G355" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H355" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I355" s="28" t="s">
         <v>107</v>
@@ -13914,10 +13917,10 @@
         <v>133</v>
       </c>
       <c r="G356" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H356" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I356" s="28" t="s">
         <v>327</v>
@@ -13938,7 +13941,7 @@
         <v>438</v>
       </c>
       <c r="E357" s="28" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F357" s="28" t="s">
         <v>133</v>
@@ -13947,7 +13950,7 @@
         <v>464</v>
       </c>
       <c r="H357" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I357" s="28" t="s">
         <v>333</v>
@@ -13968,7 +13971,7 @@
         <v>438</v>
       </c>
       <c r="E358" s="28" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F358" s="28" t="s">
         <v>133</v>
@@ -13977,7 +13980,7 @@
         <v>466</v>
       </c>
       <c r="H358" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I358" s="28" t="s">
         <v>333</v>
@@ -13998,16 +14001,16 @@
         <v>438</v>
       </c>
       <c r="E359" s="28" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F359" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G359" s="28" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H359" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I359" s="28" t="s">
         <v>340</v>
@@ -14028,7 +14031,7 @@
         <v>21</v>
       </c>
       <c r="E360" s="28" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F360" s="28" t="s">
         <v>133</v>
@@ -14037,7 +14040,7 @@
         <v>341</v>
       </c>
       <c r="H360" s="28" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I360" s="28" t="s">
         <v>39</v>
@@ -14064,10 +14067,10 @@
         <v>133</v>
       </c>
       <c r="G361" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H361" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I361" s="28" t="s">
         <v>291</v>
@@ -14094,7 +14097,7 @@
         <v>133</v>
       </c>
       <c r="G362" s="28" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H362" s="28"/>
       <c r="I362" s="28" t="s">
@@ -14112,7 +14115,7 @@
         <v>105300</v>
       </c>
       <c r="C363" s="29" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D363" s="29" t="s">
         <v>21</v>
@@ -14124,10 +14127,10 @@
         <v>133</v>
       </c>
       <c r="G363" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H363" s="29" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I363" s="29" t="s">
         <v>340</v>
@@ -14142,7 +14145,7 @@
         <v>105300</v>
       </c>
       <c r="C364" s="29" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D364" s="29" t="s">
         <v>21</v>
@@ -14154,13 +14157,13 @@
         <v>133</v>
       </c>
       <c r="G364" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H364" s="29" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I364" s="29" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K364" s="113"/>
     </row>
@@ -14172,10 +14175,10 @@
         <v>105300</v>
       </c>
       <c r="C365" s="29" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D365" s="29" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E365" s="29" t="s">
         <v>136</v>
@@ -14184,13 +14187,13 @@
         <v>133</v>
       </c>
       <c r="G365" s="29" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H365" s="29" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I365" s="29" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K365" s="113"/>
     </row>
@@ -14202,22 +14205,22 @@
         <v>105300</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D366" s="29" t="s">
         <v>328</v>
       </c>
       <c r="E366" s="29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F366" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G366" s="29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H366" s="29" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I366" s="29" t="s">
         <v>294</v>
@@ -14244,7 +14247,7 @@
         <v>133</v>
       </c>
       <c r="G367" s="29" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I367" s="29" t="s">
         <v>106</v>
@@ -14259,13 +14262,13 @@
         <v>105300</v>
       </c>
       <c r="C368" s="29" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D368" s="29" t="s">
         <v>328</v>
       </c>
       <c r="E368" s="29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F368" s="29" t="s">
         <v>133</v>
@@ -14274,7 +14277,7 @@
         <v>353</v>
       </c>
       <c r="H368" s="29" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I368" s="29" t="s">
         <v>109</v>
@@ -14301,13 +14304,13 @@
         <v>133</v>
       </c>
       <c r="G369" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H369" s="30" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I369" s="30" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K369" s="114"/>
     </row>
@@ -14331,13 +14334,13 @@
         <v>133</v>
       </c>
       <c r="G370" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H370" s="30" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I370" s="30" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K370" s="114"/>
     </row>
@@ -14349,7 +14352,7 @@
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D371" s="30" t="s">
         <v>328</v>
@@ -14361,10 +14364,10 @@
         <v>133</v>
       </c>
       <c r="G371" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H371" s="30" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I371" s="30" t="s">
         <v>340</v>
@@ -14379,22 +14382,22 @@
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D372" s="30" t="s">
         <v>328</v>
       </c>
       <c r="E372" s="30" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F372" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H372" s="30" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I372" s="30" t="s">
         <v>294</v>
@@ -14415,13 +14418,13 @@
         <v>21</v>
       </c>
       <c r="E373" s="30" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F373" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G373" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H373" s="30" t="s">
         <v>455</v>
@@ -14451,7 +14454,7 @@
         <v>133</v>
       </c>
       <c r="G374" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I374" s="30" t="s">
         <v>106</v>
@@ -14478,13 +14481,13 @@
         <v>133</v>
       </c>
       <c r="G375" s="31" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H375" s="31" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I375" s="31" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K375" s="115"/>
     </row>
@@ -14508,13 +14511,13 @@
         <v>133</v>
       </c>
       <c r="G376" s="31" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H376" s="31" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I376" s="31" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K376" s="115"/>
     </row>
@@ -14526,7 +14529,7 @@
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D377" s="31" t="s">
         <v>328</v>
@@ -14538,10 +14541,10 @@
         <v>133</v>
       </c>
       <c r="G377" s="31" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H377" s="31" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I377" s="31" t="s">
         <v>340</v>
@@ -14568,10 +14571,10 @@
         <v>133</v>
       </c>
       <c r="G378" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="H378" s="31" t="s">
         <v>615</v>
-      </c>
-      <c r="H378" s="31" t="s">
-        <v>614</v>
       </c>
       <c r="I378" s="31" t="s">
         <v>39</v>
@@ -14598,7 +14601,7 @@
         <v>133</v>
       </c>
       <c r="G379" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I379" s="32" t="s">
         <v>39</v>
@@ -14613,7 +14616,7 @@
         <v>105500</v>
       </c>
       <c r="C380" s="32" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D380" s="32" t="s">
         <v>21</v>
@@ -14652,13 +14655,13 @@
         <v>133</v>
       </c>
       <c r="G381" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H381" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I381" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K381" s="82"/>
     </row>
@@ -14670,7 +14673,7 @@
         <v>104800</v>
       </c>
       <c r="C382" s="33" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D382" s="33" t="s">
         <v>328</v>
@@ -14685,7 +14688,7 @@
         <v>460</v>
       </c>
       <c r="H382" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I382" s="33" t="s">
         <v>325</v>
@@ -14700,7 +14703,7 @@
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D383" s="33" t="s">
         <v>328</v>
@@ -14715,7 +14718,7 @@
         <v>460</v>
       </c>
       <c r="H383" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I383" s="33" t="s">
         <v>327</v>
@@ -14730,7 +14733,7 @@
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D384" s="33" t="s">
         <v>21</v>
@@ -14745,7 +14748,7 @@
         <v>460</v>
       </c>
       <c r="H384" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I384" s="33" t="s">
         <v>107</v>
@@ -14775,7 +14778,7 @@
         <v>460</v>
       </c>
       <c r="H385" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I385" s="33" t="s">
         <v>291</v>
@@ -14796,7 +14799,7 @@
         <v>422</v>
       </c>
       <c r="E386" s="33" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F386" s="33" t="s">
         <v>133</v>
@@ -14805,7 +14808,7 @@
         <v>462</v>
       </c>
       <c r="H386" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I386" s="33" t="s">
         <v>333</v>
@@ -14826,7 +14829,7 @@
         <v>422</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F387" s="33" t="s">
         <v>133</v>
@@ -14835,7 +14838,7 @@
         <v>464</v>
       </c>
       <c r="H387" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I387" s="33" t="s">
         <v>333</v>
@@ -14892,7 +14895,7 @@
         <v>133</v>
       </c>
       <c r="G389" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I389" s="32" t="s">
         <v>39</v>
@@ -14907,7 +14910,7 @@
         <v>105501</v>
       </c>
       <c r="C390" s="32" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D390" s="32" t="s">
         <v>21</v>
@@ -14934,7 +14937,7 @@
         <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
@@ -14946,7 +14949,7 @@
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>39</v>
@@ -14973,7 +14976,7 @@
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I392" s="32" t="s">
         <v>39</v>
@@ -14988,7 +14991,7 @@
         <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
@@ -15015,7 +15018,7 @@
         <v>105502</v>
       </c>
       <c r="C394" s="32" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D394" s="32" t="s">
         <v>21</v>
@@ -15059,7 +15062,7 @@
         <v>455</v>
       </c>
       <c r="I395" s="34" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K395" s="118"/>
     </row>
@@ -15071,7 +15074,7 @@
         <v>104100</v>
       </c>
       <c r="C396" s="34" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D396" s="34" t="s">
         <v>328</v>
@@ -15146,7 +15149,7 @@
         <v>255</v>
       </c>
       <c r="H398" s="34" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I398" s="34" t="s">
         <v>39</v>
@@ -15206,10 +15209,10 @@
         <v>234</v>
       </c>
       <c r="H400" s="35" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I400" s="35" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K400" s="119"/>
     </row>
@@ -15221,7 +15224,7 @@
         <v>104200</v>
       </c>
       <c r="C401" s="35" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D401" s="35" t="s">
         <v>328</v>
@@ -15236,7 +15239,7 @@
         <v>234</v>
       </c>
       <c r="H401" s="35" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I401" s="35" t="s">
         <v>107</v>
@@ -15266,7 +15269,7 @@
         <v>234</v>
       </c>
       <c r="H402" s="35" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I402" s="35" t="s">
         <v>291</v>
@@ -15296,7 +15299,7 @@
         <v>255</v>
       </c>
       <c r="H403" s="35" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I403" s="35" t="s">
         <v>39</v>
@@ -15326,7 +15329,7 @@
         <v>234</v>
       </c>
       <c r="H404" s="35" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I404" s="35" t="s">
         <v>340</v>
@@ -15351,24 +15354,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D2" t="s">
         <v>631</v>
       </c>
-      <c r="D2" t="s">
-        <v>630</v>
-      </c>
       <c r="E2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15376,16 +15379,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15393,16 +15396,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15410,16 +15413,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15427,7 +15430,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15435,7 +15438,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15443,7 +15446,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15451,7 +15454,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15459,7 +15462,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15467,7 +15470,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15475,7 +15478,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15483,7 +15486,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15491,7 +15494,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15499,7 +15502,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15507,7 +15510,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15515,7 +15518,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15523,7 +15526,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15531,7 +15534,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15539,7 +15542,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15547,7 +15550,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15555,7 +15558,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15563,7 +15566,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15571,7 +15574,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -15579,7 +15582,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -15587,7 +15590,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -15595,7 +15598,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -15603,7 +15606,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -15611,7 +15614,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -15619,7 +15622,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -15627,7 +15630,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -15635,7 +15638,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -15643,7 +15646,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -15651,7 +15654,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -15659,7 +15662,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -15667,7 +15670,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -15675,7 +15678,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -15683,7 +15686,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -15691,7 +15694,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -15699,7 +15702,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -15707,7 +15710,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -15715,7 +15718,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -15723,7 +15726,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -15731,7 +15734,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -15739,7 +15742,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15747,7 +15750,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -15755,7 +15758,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -15763,7 +15766,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="682">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1961,9 +1961,6 @@
   </si>
   <si>
     <t>6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
-  </si>
-  <si>
-    <t>1_1_1|21_1_1</t>
   </si>
   <si>
     <t>第3轴必然出现金色符号</t>
@@ -3499,7 +3496,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N403"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -14226,73 +14223,76 @@
     </row>
     <row r="367" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A367" s="29">
-        <v>10530005</v>
+        <v>10530006</v>
       </c>
       <c r="B367" s="29">
         <v>105300</v>
       </c>
       <c r="C367" s="29" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="D367" s="29" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E367" s="29" t="s">
-        <v>257</v>
+        <v>599</v>
       </c>
       <c r="F367" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G367" s="29" t="s">
-        <v>601</v>
+        <v>353</v>
+      </c>
+      <c r="H367" s="29" t="s">
+        <v>602</v>
       </c>
       <c r="I367" s="29" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K367" s="113"/>
     </row>
-    <row r="368" s="29" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A368" s="29">
-        <v>10530006</v>
-      </c>
-      <c r="B368" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C368" s="29" t="s">
-        <v>602</v>
-      </c>
-      <c r="D368" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="E368" s="29" t="s">
-        <v>599</v>
-      </c>
-      <c r="F368" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G368" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="H368" s="29" t="s">
+    <row r="368" s="30" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A368" s="30">
+        <v>10570001</v>
+      </c>
+      <c r="B368" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C368" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D368" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="E368" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F368" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G368" s="30" t="s">
         <v>603</v>
       </c>
-      <c r="I368" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="K368" s="113"/>
+      <c r="H368" s="30" t="s">
+        <v>604</v>
+      </c>
+      <c r="I368" s="30" t="s">
+        <v>597</v>
+      </c>
+      <c r="K368" s="114"/>
     </row>
     <row r="369" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A369" s="30">
-        <v>10570001</v>
+        <v>10570002</v>
       </c>
       <c r="B369" s="30">
         <v>105700</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D369" s="30" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E369" s="30" t="s">
         <v>114</v>
@@ -14301,25 +14301,25 @@
         <v>133</v>
       </c>
       <c r="G369" s="30" t="s">
+        <v>603</v>
+      </c>
+      <c r="H369" s="30" t="s">
         <v>604</v>
       </c>
-      <c r="H369" s="30" t="s">
-        <v>605</v>
-      </c>
       <c r="I369" s="30" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="K369" s="114"/>
     </row>
     <row r="370" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A370" s="30">
-        <v>10570002</v>
+        <v>10570003</v>
       </c>
       <c r="B370" s="30">
         <v>105700</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>415</v>
+        <v>605</v>
       </c>
       <c r="D370" s="30" t="s">
         <v>328</v>
@@ -14331,19 +14331,19 @@
         <v>133</v>
       </c>
       <c r="G370" s="30" t="s">
+        <v>603</v>
+      </c>
+      <c r="H370" s="30" t="s">
         <v>604</v>
       </c>
-      <c r="H370" s="30" t="s">
-        <v>605</v>
-      </c>
       <c r="I370" s="30" t="s">
-        <v>595</v>
+        <v>340</v>
       </c>
       <c r="K370" s="114"/>
     </row>
     <row r="371" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A371" s="30">
-        <v>10570003</v>
+        <v>10570004</v>
       </c>
       <c r="B371" s="30">
         <v>105700</v>
@@ -14355,67 +14355,67 @@
         <v>328</v>
       </c>
       <c r="E371" s="30" t="s">
-        <v>114</v>
+        <v>607</v>
       </c>
       <c r="F371" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G371" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="H371" s="30" t="s">
         <v>604</v>
       </c>
-      <c r="H371" s="30" t="s">
-        <v>605</v>
-      </c>
       <c r="I371" s="30" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="K371" s="114"/>
     </row>
     <row r="372" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A372" s="30">
-        <v>10570004</v>
+        <v>10570005</v>
       </c>
       <c r="B372" s="30">
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>607</v>
+        <v>253</v>
       </c>
       <c r="D372" s="30" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E372" s="30" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F372" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H372" s="30" t="s">
-        <v>605</v>
+        <v>455</v>
       </c>
       <c r="I372" s="30" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K372" s="114"/>
     </row>
     <row r="373" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A373" s="30">
-        <v>10570005</v>
+        <v>10570006</v>
       </c>
       <c r="B373" s="30">
         <v>105700</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D373" s="30" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E373" s="30" t="s">
-        <v>610</v>
+        <v>257</v>
       </c>
       <c r="F373" s="30" t="s">
         <v>133</v>
@@ -14423,53 +14423,53 @@
       <c r="G373" s="30" t="s">
         <v>611</v>
       </c>
-      <c r="H373" s="30" t="s">
-        <v>455</v>
-      </c>
       <c r="I373" s="30" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K373" s="114"/>
     </row>
-    <row r="374" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A374" s="30">
-        <v>10570006</v>
-      </c>
-      <c r="B374" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C374" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="D374" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E374" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="F374" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G374" s="30" t="s">
+    <row r="374" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A374" s="31">
+        <v>10580001</v>
+      </c>
+      <c r="B374" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C374" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D374" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="E374" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F374" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G374" s="31" t="s">
         <v>612</v>
       </c>
-      <c r="I374" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="K374" s="114"/>
+      <c r="H374" s="31" t="s">
+        <v>613</v>
+      </c>
+      <c r="I374" s="31" t="s">
+        <v>597</v>
+      </c>
+      <c r="K374" s="115"/>
     </row>
     <row r="375" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A375" s="31">
-        <v>10580001</v>
+        <v>10580002</v>
       </c>
       <c r="B375" s="31">
         <v>105800</v>
       </c>
       <c r="C375" s="31" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="D375" s="31" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E375" s="31" t="s">
         <v>299</v>
@@ -14478,25 +14478,25 @@
         <v>133</v>
       </c>
       <c r="G375" s="31" t="s">
+        <v>612</v>
+      </c>
+      <c r="H375" s="31" t="s">
         <v>613</v>
       </c>
-      <c r="H375" s="31" t="s">
-        <v>614</v>
-      </c>
       <c r="I375" s="31" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="K375" s="115"/>
     </row>
     <row r="376" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A376" s="31">
-        <v>10580002</v>
+        <v>10580003</v>
       </c>
       <c r="B376" s="31">
         <v>105800</v>
       </c>
       <c r="C376" s="31" t="s">
-        <v>259</v>
+        <v>605</v>
       </c>
       <c r="D376" s="31" t="s">
         <v>328</v>
@@ -14508,163 +14508,163 @@
         <v>133</v>
       </c>
       <c r="G376" s="31" t="s">
+        <v>612</v>
+      </c>
+      <c r="H376" s="31" t="s">
         <v>613</v>
       </c>
-      <c r="H376" s="31" t="s">
-        <v>614</v>
-      </c>
       <c r="I376" s="31" t="s">
-        <v>595</v>
+        <v>340</v>
       </c>
       <c r="K376" s="115"/>
     </row>
     <row r="377" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A377" s="31">
-        <v>10580003</v>
+        <v>10580004</v>
       </c>
       <c r="B377" s="31">
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>606</v>
+        <v>253</v>
       </c>
       <c r="D377" s="31" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E377" s="31" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="F377" s="31" t="s">
         <v>133</v>
       </c>
       <c r="G377" s="31" t="s">
+        <v>614</v>
+      </c>
+      <c r="H377" s="31" t="s">
         <v>613</v>
       </c>
-      <c r="H377" s="31" t="s">
-        <v>614</v>
-      </c>
       <c r="I377" s="31" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K377" s="115"/>
     </row>
-    <row r="378" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A378" s="31">
-        <v>10580004</v>
-      </c>
-      <c r="B378" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C378" s="31" t="s">
+    <row r="378" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A378" s="32">
+        <v>10550001</v>
+      </c>
+      <c r="B378" s="32">
+        <v>105500</v>
+      </c>
+      <c r="C378" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D378" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E378" s="31" t="s">
+      <c r="D378" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E378" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F378" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G378" s="31" t="s">
+      <c r="F378" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G378" s="32" t="s">
         <v>615</v>
       </c>
-      <c r="H378" s="31" t="s">
-        <v>614</v>
-      </c>
-      <c r="I378" s="31" t="s">
+      <c r="I378" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K378" s="115"/>
+      <c r="K378" s="116"/>
     </row>
     <row r="379" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A379" s="32">
-        <v>10550001</v>
+        <v>10550002</v>
       </c>
       <c r="B379" s="32">
         <v>105500</v>
       </c>
       <c r="C379" s="32" t="s">
-        <v>253</v>
+        <v>616</v>
       </c>
       <c r="D379" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E379" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F379" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G379" s="32" t="s">
-        <v>616</v>
+        <v>297</v>
       </c>
       <c r="I379" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K379" s="116"/>
     </row>
-    <row r="380" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A380" s="32">
-        <v>10550002</v>
-      </c>
-      <c r="B380" s="32">
-        <v>105500</v>
-      </c>
-      <c r="C380" s="32" t="s">
+    <row r="380" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A380" s="33">
+        <v>10480001</v>
+      </c>
+      <c r="B380" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C380" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="D380" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E380" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F380" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G380" s="33" t="s">
         <v>617</v>
       </c>
-      <c r="D380" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E380" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="F380" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G380" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I380" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K380" s="116"/>
+      <c r="H380" s="33" t="s">
+        <v>618</v>
+      </c>
+      <c r="I380" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="K380" s="82"/>
     </row>
     <row r="381" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A381" s="33">
-        <v>10480001</v>
+        <v>10480002</v>
       </c>
       <c r="B381" s="33">
         <v>104800</v>
       </c>
       <c r="C381" s="33" t="s">
-        <v>503</v>
+        <v>619</v>
       </c>
       <c r="D381" s="33" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E381" s="33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F381" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G381" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="H381" s="33" t="s">
         <v>618</v>
       </c>
-      <c r="H381" s="33" t="s">
-        <v>619</v>
-      </c>
       <c r="I381" s="33" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K381" s="82"/>
     </row>
     <row r="382" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A382" s="33">
-        <v>10480002</v>
+        <v>10480003</v>
       </c>
       <c r="B382" s="33">
         <v>104800</v>
@@ -14685,16 +14685,16 @@
         <v>460</v>
       </c>
       <c r="H382" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I382" s="33" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K382" s="82"/>
     </row>
     <row r="383" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A383" s="33">
-        <v>10480003</v>
+        <v>10480004</v>
       </c>
       <c r="B383" s="33">
         <v>104800</v>
@@ -14703,7 +14703,7 @@
         <v>621</v>
       </c>
       <c r="D383" s="33" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E383" s="33" t="s">
         <v>143</v>
@@ -14715,25 +14715,25 @@
         <v>460</v>
       </c>
       <c r="H383" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I383" s="33" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="K383" s="82"/>
     </row>
     <row r="384" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A384" s="33">
-        <v>10480004</v>
+        <v>10480005</v>
       </c>
       <c r="B384" s="33">
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>622</v>
+        <v>289</v>
       </c>
       <c r="D384" s="33" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E384" s="33" t="s">
         <v>143</v>
@@ -14745,52 +14745,52 @@
         <v>460</v>
       </c>
       <c r="H384" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K384" s="82"/>
     </row>
     <row r="385" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A385" s="33">
-        <v>10480005</v>
+        <v>10480006</v>
       </c>
       <c r="B385" s="33">
         <v>104800</v>
       </c>
       <c r="C385" s="33" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="D385" s="33" t="s">
         <v>422</v>
       </c>
       <c r="E385" s="33" t="s">
-        <v>143</v>
+        <v>622</v>
       </c>
       <c r="F385" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G385" s="33" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H385" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I385" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="K385" s="82"/>
+        <v>333</v>
+      </c>
+      <c r="K385" s="117"/>
     </row>
     <row r="386" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A386" s="33">
-        <v>10480006</v>
+        <v>10480007</v>
       </c>
       <c r="B386" s="33">
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D386" s="33" t="s">
         <v>422</v>
@@ -14802,10 +14802,10 @@
         <v>133</v>
       </c>
       <c r="G386" s="33" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H386" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I386" s="33" t="s">
         <v>333</v>
@@ -14814,139 +14814,136 @@
     </row>
     <row r="387" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A387" s="33">
-        <v>10480007</v>
+        <v>10480008</v>
       </c>
       <c r="B387" s="33">
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="D387" s="33" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>624</v>
+        <v>254</v>
       </c>
       <c r="F387" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G387" s="33" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="H387" s="33" t="s">
-        <v>619</v>
+        <v>408</v>
       </c>
       <c r="I387" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K387" s="117"/>
-    </row>
-    <row r="388" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A388" s="33">
-        <v>10480008</v>
-      </c>
-      <c r="B388" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C388" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K387" s="82"/>
+    </row>
+    <row r="388" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A388" s="32">
+        <v>10550101</v>
+      </c>
+      <c r="B388" s="32">
+        <v>105501</v>
+      </c>
+      <c r="C388" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D388" s="33" t="s">
+      <c r="D388" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E388" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F388" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G388" s="33" t="s">
-        <v>469</v>
-      </c>
-      <c r="H388" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="I388" s="33" t="s">
+      <c r="E388" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F388" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G388" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="I388" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K388" s="82"/>
+      <c r="K388" s="116"/>
     </row>
     <row r="389" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A389" s="32">
-        <v>10550101</v>
+        <v>10550102</v>
       </c>
       <c r="B389" s="32">
         <v>105501</v>
       </c>
       <c r="C389" s="32" t="s">
-        <v>253</v>
+        <v>616</v>
       </c>
       <c r="D389" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E389" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F389" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G389" s="32" t="s">
-        <v>616</v>
+        <v>297</v>
       </c>
       <c r="I389" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K389" s="116"/>
     </row>
     <row r="390" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A390" s="32">
-        <v>10550102</v>
+        <v>10550103</v>
       </c>
       <c r="B390" s="32">
         <v>105501</v>
       </c>
       <c r="C390" s="32" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="D390" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E390" s="32" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="F390" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G390" s="32" t="s">
-        <v>297</v>
+        <v>615</v>
       </c>
       <c r="I390" s="32" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K390" s="116"/>
     </row>
     <row r="391" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A391" s="32">
-        <v>10550103</v>
+        <v>10550201</v>
       </c>
       <c r="B391" s="32">
-        <v>105501</v>
+        <v>105502</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>625</v>
+        <v>253</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="F391" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>39</v>
@@ -14955,46 +14952,46 @@
     </row>
     <row r="392" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A392" s="32">
-        <v>10550201</v>
+        <v>10550202</v>
       </c>
       <c r="B392" s="32">
         <v>105502</v>
       </c>
       <c r="C392" s="32" t="s">
-        <v>253</v>
+        <v>616</v>
       </c>
       <c r="D392" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F392" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>616</v>
+        <v>297</v>
       </c>
       <c r="I392" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K392" s="116"/>
     </row>
-    <row r="393" s="32" customFormat="1" ht="16.5" spans="1:11">
+    <row r="393" ht="16.5" spans="1:11">
       <c r="A393" s="32">
-        <v>10550202</v>
+        <v>10550203</v>
       </c>
       <c r="B393" s="32">
         <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="F393" s="32" t="s">
         <v>133</v>
@@ -15003,78 +15000,81 @@
         <v>297</v>
       </c>
       <c r="I393" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K393" s="116"/>
-    </row>
-    <row r="394" ht="16.5" spans="1:11">
-      <c r="A394" s="32">
-        <v>10550203</v>
-      </c>
-      <c r="B394" s="32">
-        <v>105502</v>
-      </c>
-      <c r="C394" s="32" t="s">
-        <v>626</v>
-      </c>
-      <c r="D394" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E394" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="F394" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G394" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I394" s="32" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="394" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A394" s="34">
+        <v>10410001</v>
+      </c>
+      <c r="B394" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C394" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="D394" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="E394" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="F394" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G394" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H394" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="I394" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="K394" s="118"/>
     </row>
     <row r="395" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A395" s="34">
-        <v>10410001</v>
+        <v>10410002</v>
       </c>
       <c r="B395" s="34">
         <v>104100</v>
       </c>
       <c r="C395" s="34" t="s">
-        <v>313</v>
+        <v>556</v>
       </c>
       <c r="D395" s="34" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E395" s="34" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="F395" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G395" s="34" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="H395" s="34" t="s">
         <v>455</v>
       </c>
       <c r="I395" s="34" t="s">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="K395" s="118"/>
     </row>
     <row r="396" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A396" s="34">
-        <v>10410002</v>
+        <v>10410003</v>
       </c>
       <c r="B396" s="34">
         <v>104100</v>
       </c>
       <c r="C396" s="34" t="s">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="D396" s="34" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E396" s="34" t="s">
         <v>114</v>
@@ -15089,115 +15089,115 @@
         <v>455</v>
       </c>
       <c r="I396" s="34" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K396" s="118"/>
     </row>
     <row r="397" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A397" s="34">
-        <v>10410003</v>
+        <v>10410004</v>
       </c>
       <c r="B397" s="34">
         <v>104100</v>
       </c>
       <c r="C397" s="34" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E397" s="34" t="s">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="F397" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H397" s="34" t="s">
-        <v>455</v>
+        <v>626</v>
       </c>
       <c r="I397" s="34" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K397" s="118"/>
     </row>
     <row r="398" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A398" s="34">
-        <v>10410004</v>
+        <v>10410005</v>
       </c>
       <c r="B398" s="34">
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E398" s="34" t="s">
-        <v>416</v>
+        <v>114</v>
       </c>
       <c r="F398" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G398" s="34" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H398" s="34" t="s">
-        <v>627</v>
+        <v>455</v>
       </c>
       <c r="I398" s="34" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K398" s="118"/>
     </row>
-    <row r="399" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A399" s="34">
-        <v>10410005</v>
-      </c>
-      <c r="B399" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C399" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D399" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E399" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F399" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G399" s="34" t="s">
+    <row r="399" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A399" s="35">
+        <v>10420001</v>
+      </c>
+      <c r="B399" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C399" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="D399" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="E399" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F399" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G399" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="H399" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I399" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="K399" s="118"/>
+      <c r="H399" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="I399" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="K399" s="119"/>
     </row>
     <row r="400" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A400" s="35">
-        <v>10420001</v>
+        <v>10420002</v>
       </c>
       <c r="B400" s="35">
         <v>104200</v>
       </c>
       <c r="C400" s="35" t="s">
-        <v>313</v>
+        <v>556</v>
       </c>
       <c r="D400" s="35" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E400" s="35" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F400" s="35" t="s">
         <v>133</v>
@@ -15209,22 +15209,22 @@
         <v>550</v>
       </c>
       <c r="I400" s="35" t="s">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="K400" s="119"/>
     </row>
     <row r="401" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A401" s="35">
-        <v>10420002</v>
+        <v>10420003</v>
       </c>
       <c r="B401" s="35">
         <v>104200</v>
       </c>
       <c r="C401" s="35" t="s">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="D401" s="35" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E401" s="35" t="s">
         <v>143</v>
@@ -15239,99 +15239,69 @@
         <v>550</v>
       </c>
       <c r="I401" s="35" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K401" s="119"/>
     </row>
     <row r="402" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A402" s="35">
-        <v>10420003</v>
+        <v>10420004</v>
       </c>
       <c r="B402" s="35">
         <v>104200</v>
       </c>
       <c r="C402" s="35" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E402" s="35" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F402" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G402" s="35" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H402" s="35" t="s">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="I402" s="35" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K402" s="119"/>
     </row>
     <row r="403" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A403" s="35">
-        <v>10420004</v>
+        <v>10420005</v>
       </c>
       <c r="B403" s="35">
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E403" s="35" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F403" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G403" s="35" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H403" s="35" t="s">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="I403" s="35" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K403" s="119"/>
-    </row>
-    <row r="404" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A404" s="35">
-        <v>10420005</v>
-      </c>
-      <c r="B404" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C404" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="D404" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="E404" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F404" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G404" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H404" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I404" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="K404" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15351,24 +15321,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D1" t="s">
         <v>628</v>
-      </c>
-      <c r="D1" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B2" t="s">
         <v>630</v>
       </c>
-      <c r="B2" t="s">
-        <v>631</v>
-      </c>
       <c r="D2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E2" t="s">
         <v>630</v>
-      </c>
-      <c r="E2" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15376,16 +15346,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>632</v>
+      </c>
+      <c r="F3" t="s">
         <v>633</v>
-      </c>
-      <c r="F3" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15393,16 +15363,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>635</v>
+      </c>
+      <c r="F4" t="s">
         <v>636</v>
-      </c>
-      <c r="F4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15410,16 +15380,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
+        <v>638</v>
+      </c>
+      <c r="F5" t="s">
         <v>639</v>
-      </c>
-      <c r="F5" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15435,7 +15405,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15443,7 +15413,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15451,7 +15421,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15459,7 +15429,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15467,7 +15437,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15475,7 +15445,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15483,7 +15453,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15491,7 +15461,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15499,7 +15469,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15507,7 +15477,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15515,7 +15485,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15523,7 +15493,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15531,7 +15501,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15539,7 +15509,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15547,7 +15517,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15555,7 +15525,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15563,7 +15533,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15571,7 +15541,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -15579,7 +15549,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -15587,7 +15557,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -15595,7 +15565,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -15603,7 +15573,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -15611,7 +15581,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -15619,7 +15589,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -15627,7 +15597,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -15635,7 +15605,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -15643,7 +15613,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -15651,7 +15621,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -15659,7 +15629,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -15667,7 +15637,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -15675,7 +15645,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -15683,7 +15653,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -15691,7 +15661,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -15699,7 +15669,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -15707,7 +15677,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -15715,7 +15685,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -15723,7 +15693,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -15731,7 +15701,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -15739,7 +15709,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15747,7 +15717,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -15755,7 +15725,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -15763,7 +15733,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -11213,7 +11213,7 @@
         <v>133</v>
       </c>
       <c r="G265" s="26" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H265" s="26" t="s">
         <v>455</v>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="686">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1889,6 +1889,18 @@
   </si>
   <si>
     <t>第三层常规&amp;免费</t>
+  </si>
+  <si>
+    <t>概率改出过关图标1图标</t>
+  </si>
+  <si>
+    <t>0_5|1_1</t>
+  </si>
+  <si>
+    <t>概率改出过关图标2图标</t>
+  </si>
+  <si>
+    <t>概率改出过关图标3图标</t>
   </si>
   <si>
     <t>11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89</t>
@@ -3496,7 +3508,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N403"/>
+  <dimension ref="A1:N406"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -13517,189 +13529,192 @@
       </c>
       <c r="K342" s="82"/>
     </row>
-    <row r="343" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A343" s="27">
-        <v>10540001</v>
-      </c>
-      <c r="B343" s="27">
-        <v>105400</v>
-      </c>
-      <c r="C343" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="D343" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="E343" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="F343" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G343" s="27" t="s">
-        <v>555</v>
-      </c>
-      <c r="H343" s="27" t="s">
+    <row r="343" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A343" s="33">
+        <v>10510007</v>
+      </c>
+      <c r="B343" s="33">
+        <v>105100</v>
+      </c>
+      <c r="C343" s="33" t="s">
         <v>577</v>
       </c>
-      <c r="I343" s="27" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="344" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A344" s="27">
-        <v>10540002</v>
-      </c>
-      <c r="B344" s="27">
-        <v>105400</v>
-      </c>
-      <c r="C344" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="D344" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="E344" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="F344" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G344" s="27" t="s">
-        <v>557</v>
-      </c>
-      <c r="H344" s="27" t="s">
-        <v>577</v>
-      </c>
-      <c r="I344" s="27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="345" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A345" s="27">
-        <v>10540003</v>
-      </c>
-      <c r="B345" s="27">
-        <v>105400</v>
-      </c>
-      <c r="C345" s="27" t="s">
-        <v>326</v>
-      </c>
-      <c r="D345" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="E345" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="F345" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G345" s="27" t="s">
-        <v>555</v>
-      </c>
-      <c r="H345" s="27" t="s">
-        <v>577</v>
-      </c>
-      <c r="I345" s="27" t="s">
-        <v>327</v>
-      </c>
+      <c r="D343" s="33" t="s">
+        <v>568</v>
+      </c>
+      <c r="E343" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F343" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G343" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H343" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="I343" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="K343" s="82"/>
+    </row>
+    <row r="344" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A344" s="33">
+        <v>10510008</v>
+      </c>
+      <c r="B344" s="33">
+        <v>105100</v>
+      </c>
+      <c r="C344" s="33" t="s">
+        <v>579</v>
+      </c>
+      <c r="D344" s="33" t="s">
+        <v>570</v>
+      </c>
+      <c r="E344" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F344" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G344" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="H344" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="I344" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="K344" s="82"/>
+    </row>
+    <row r="345" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A345" s="33">
+        <v>10510009</v>
+      </c>
+      <c r="B345" s="33">
+        <v>105100</v>
+      </c>
+      <c r="C345" s="33" t="s">
+        <v>580</v>
+      </c>
+      <c r="D345" s="33" t="s">
+        <v>571</v>
+      </c>
+      <c r="E345" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F345" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G345" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="H345" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="I345" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="K345" s="82"/>
     </row>
     <row r="346" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A346" s="27">
-        <v>10540004</v>
+        <v>10540001</v>
       </c>
       <c r="B346" s="27">
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>578</v>
+        <v>323</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E346" s="27" t="s">
-        <v>579</v>
+        <v>140</v>
       </c>
       <c r="F346" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G346" s="27" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="H346" s="27" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I346" s="27" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="347" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A347" s="27">
-        <v>10540005</v>
+        <v>10540002</v>
       </c>
       <c r="B347" s="27">
         <v>105400</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E347" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F347" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G347" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="H347" s="27" t="s">
         <v>581</v>
       </c>
-      <c r="F347" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G347" s="27" t="s">
-        <v>580</v>
-      </c>
-      <c r="H347" s="27" t="s">
-        <v>577</v>
-      </c>
       <c r="I347" s="27" t="s">
-        <v>333</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A348" s="27">
-        <v>10540006</v>
+        <v>10540003</v>
       </c>
       <c r="B348" s="27">
         <v>105400</v>
       </c>
       <c r="C348" s="27" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>582</v>
+        <v>140</v>
       </c>
       <c r="F348" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G348" s="27" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="H348" s="27" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I348" s="27" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="349" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A349" s="27">
-        <v>10540007</v>
+        <v>10540004</v>
       </c>
       <c r="B349" s="27">
         <v>105400</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>337</v>
+        <v>582</v>
       </c>
       <c r="D349" s="27" t="s">
         <v>422</v>
@@ -13711,59 +13726,59 @@
         <v>133</v>
       </c>
       <c r="G349" s="27" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="H349" s="27" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I349" s="27" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="350" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A350" s="27">
-        <v>10540008</v>
+        <v>10540005</v>
       </c>
       <c r="B350" s="27">
         <v>105400</v>
       </c>
       <c r="C350" s="27" t="s">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="D350" s="27" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E350" s="27" t="s">
-        <v>264</v>
+        <v>585</v>
       </c>
       <c r="F350" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G350" s="27" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="H350" s="27" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I350" s="27" t="s">
-        <v>39</v>
+        <v>333</v>
       </c>
     </row>
     <row r="351" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A351" s="27">
-        <v>10540009</v>
+        <v>10540006</v>
       </c>
       <c r="B351" s="27">
         <v>105400</v>
       </c>
       <c r="C351" s="27" t="s">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="E351" s="27" t="s">
-        <v>140</v>
+        <v>586</v>
       </c>
       <c r="F351" s="27" t="s">
         <v>133</v>
@@ -13772,968 +13787,965 @@
         <v>584</v>
       </c>
       <c r="H351" s="27" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I351" s="27" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
     </row>
     <row r="352" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A352" s="27">
-        <v>10540010</v>
+        <v>10540007</v>
       </c>
       <c r="B352" s="27">
         <v>105400</v>
       </c>
       <c r="C352" s="27" t="s">
-        <v>256</v>
+        <v>337</v>
       </c>
       <c r="D352" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E352" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="F352" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G352" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="H352" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="I352" s="27" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="353" s="27" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A353" s="27">
+        <v>10540008</v>
+      </c>
+      <c r="B353" s="27">
+        <v>105400</v>
+      </c>
+      <c r="C353" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="D353" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="E353" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="F353" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G353" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="H353" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="I353" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="354" s="27" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A354" s="27">
+        <v>10540009</v>
+      </c>
+      <c r="B354" s="27">
+        <v>105400</v>
+      </c>
+      <c r="C354" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="D354" s="27" t="s">
+        <v>566</v>
+      </c>
+      <c r="E354" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F354" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G354" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="H354" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="I354" s="27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="355" s="27" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A355" s="27">
+        <v>10540010</v>
+      </c>
+      <c r="B355" s="27">
+        <v>105400</v>
+      </c>
+      <c r="C355" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="D355" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="E355" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="F352" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G352" s="27" t="s">
+      <c r="F355" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G355" s="27" t="s">
         <v>551</v>
       </c>
-      <c r="I352" s="27" t="s">
+      <c r="I355" s="27" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="353" s="28" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A353" s="28">
-        <v>10080001</v>
-      </c>
-      <c r="B353" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C353" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="D353" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E353" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="F353" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G353" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="H353" s="28" t="s">
-        <v>585</v>
-      </c>
-      <c r="I353" s="28" t="s">
-        <v>546</v>
-      </c>
-      <c r="K353" s="112"/>
-    </row>
-    <row r="354" s="28" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A354" s="28">
-        <v>10080002</v>
-      </c>
-      <c r="B354" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C354" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="D354" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E354" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="F354" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G354" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="I354" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="K354" s="112"/>
-    </row>
-    <row r="355" s="28" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A355" s="28">
-        <v>10080003</v>
-      </c>
-      <c r="B355" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C355" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D355" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E355" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="F355" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G355" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="H355" s="28" t="s">
-        <v>585</v>
-      </c>
-      <c r="I355" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="K355" s="112"/>
     </row>
     <row r="356" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A356" s="28">
-        <v>10080004</v>
+        <v>10080001</v>
       </c>
       <c r="B356" s="28">
         <v>100800</v>
       </c>
       <c r="C356" s="28" t="s">
-        <v>326</v>
+        <v>503</v>
       </c>
       <c r="D356" s="28" t="s">
         <v>422</v>
       </c>
       <c r="E356" s="28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F356" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G356" s="28" t="s">
-        <v>547</v>
+        <v>458</v>
       </c>
       <c r="H356" s="28" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I356" s="28" t="s">
-        <v>327</v>
+        <v>546</v>
       </c>
       <c r="K356" s="112"/>
     </row>
     <row r="357" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A357" s="28">
-        <v>10080005</v>
+        <v>10080002</v>
       </c>
       <c r="B357" s="28">
         <v>100800</v>
       </c>
       <c r="C357" s="28" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D357" s="28" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E357" s="28" t="s">
-        <v>586</v>
+        <v>143</v>
       </c>
       <c r="F357" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G357" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="H357" s="28" t="s">
-        <v>585</v>
+        <v>547</v>
       </c>
       <c r="I357" s="28" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="K357" s="112"/>
     </row>
     <row r="358" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A358" s="28">
-        <v>10080006</v>
+        <v>10080003</v>
       </c>
       <c r="B358" s="28">
         <v>100800</v>
       </c>
       <c r="C358" s="28" t="s">
-        <v>334</v>
+        <v>259</v>
       </c>
       <c r="D358" s="28" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E358" s="28" t="s">
-        <v>587</v>
+        <v>143</v>
       </c>
       <c r="F358" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G358" s="28" t="s">
-        <v>466</v>
+        <v>547</v>
       </c>
       <c r="H358" s="28" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I358" s="28" t="s">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="K358" s="112"/>
     </row>
     <row r="359" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A359" s="28">
-        <v>10080007</v>
+        <v>10080004</v>
       </c>
       <c r="B359" s="28">
         <v>100800</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D359" s="28" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E359" s="28" t="s">
-        <v>588</v>
+        <v>143</v>
       </c>
       <c r="F359" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G359" s="28" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H359" s="28" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I359" s="28" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="K359" s="112"/>
     </row>
     <row r="360" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A360" s="28">
-        <v>10080008</v>
+        <v>10080005</v>
       </c>
       <c r="B360" s="28">
         <v>100800</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="D360" s="28" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E360" s="28" t="s">
+        <v>590</v>
+      </c>
+      <c r="F360" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G360" s="28" t="s">
+        <v>464</v>
+      </c>
+      <c r="H360" s="28" t="s">
         <v>589</v>
       </c>
-      <c r="F360" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G360" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="H360" s="28" t="s">
-        <v>590</v>
-      </c>
       <c r="I360" s="28" t="s">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="K360" s="112"/>
     </row>
     <row r="361" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A361" s="28">
-        <v>10080009</v>
+        <v>10080006</v>
       </c>
       <c r="B361" s="28">
         <v>100800</v>
       </c>
       <c r="C361" s="28" t="s">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="D361" s="28" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E361" s="28" t="s">
-        <v>143</v>
+        <v>591</v>
       </c>
       <c r="F361" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G361" s="28" t="s">
-        <v>547</v>
+        <v>466</v>
       </c>
       <c r="H361" s="28" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I361" s="28" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="K361" s="112"/>
     </row>
-    <row r="362" s="27" customFormat="1" ht="16.5" spans="1:12">
+    <row r="362" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A362" s="28">
-        <v>10080010</v>
+        <v>10080007</v>
       </c>
       <c r="B362" s="28">
         <v>100800</v>
       </c>
       <c r="C362" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="D362" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="E362" s="28" t="s">
+        <v>592</v>
+      </c>
+      <c r="F362" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G362" s="28" t="s">
+        <v>548</v>
+      </c>
+      <c r="H362" s="28" t="s">
+        <v>589</v>
+      </c>
+      <c r="I362" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="K362" s="112"/>
+    </row>
+    <row r="363" s="28" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A363" s="28">
+        <v>10080008</v>
+      </c>
+      <c r="B363" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C363" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="D363" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E363" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="F363" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G363" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="H363" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="I363" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="K363" s="112"/>
+    </row>
+    <row r="364" s="28" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A364" s="28">
+        <v>10080009</v>
+      </c>
+      <c r="B364" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C364" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="D364" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="E364" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F364" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G364" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="H364" s="28" t="s">
+        <v>589</v>
+      </c>
+      <c r="I364" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="K364" s="112"/>
+    </row>
+    <row r="365" s="27" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A365" s="28">
+        <v>10080010</v>
+      </c>
+      <c r="B365" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C365" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="D362" s="28" t="s">
+      <c r="D365" s="28" t="s">
         <v>422</v>
       </c>
-      <c r="E362" s="28" t="s">
+      <c r="E365" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="F362" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G362" s="28" t="s">
+      <c r="F365" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G365" s="28" t="s">
         <v>551</v>
       </c>
-      <c r="H362" s="28"/>
-      <c r="I362" s="28" t="s">
+      <c r="H365" s="28"/>
+      <c r="I365" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="J362" s="28"/>
-      <c r="K362" s="28"/>
-      <c r="L362" s="28"/>
-    </row>
-    <row r="363" s="29" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A363" s="29">
-        <v>10530001</v>
-      </c>
-      <c r="B363" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C363" s="29" t="s">
-        <v>591</v>
-      </c>
-      <c r="D363" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E363" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="F363" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G363" s="29" t="s">
-        <v>592</v>
-      </c>
-      <c r="H363" s="29" t="s">
-        <v>593</v>
-      </c>
-      <c r="I363" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="K363" s="113"/>
-    </row>
-    <row r="364" s="29" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A364" s="29">
-        <v>10530002</v>
-      </c>
-      <c r="B364" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C364" s="29" t="s">
-        <v>594</v>
-      </c>
-      <c r="D364" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E364" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="F364" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G364" s="29" t="s">
-        <v>592</v>
-      </c>
-      <c r="H364" s="29" t="s">
-        <v>593</v>
-      </c>
-      <c r="I364" s="29" t="s">
-        <v>595</v>
-      </c>
-      <c r="K364" s="113"/>
-    </row>
-    <row r="365" s="29" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A365" s="29">
-        <v>10530003</v>
-      </c>
-      <c r="B365" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C365" s="29" t="s">
-        <v>596</v>
-      </c>
-      <c r="D365" s="29" t="s">
-        <v>566</v>
-      </c>
-      <c r="E365" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="F365" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G365" s="29" t="s">
-        <v>592</v>
-      </c>
-      <c r="H365" s="29" t="s">
-        <v>593</v>
-      </c>
-      <c r="I365" s="29" t="s">
-        <v>597</v>
-      </c>
-      <c r="K365" s="113"/>
+      <c r="J365" s="28"/>
+      <c r="K365" s="28"/>
+      <c r="L365" s="28"/>
     </row>
     <row r="366" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A366" s="29">
-        <v>10530004</v>
+        <v>10530001</v>
       </c>
       <c r="B366" s="29">
         <v>105300</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D366" s="29" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E366" s="29" t="s">
-        <v>599</v>
+        <v>136</v>
       </c>
       <c r="F366" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G366" s="29" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="H366" s="29" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I366" s="29" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="K366" s="113"/>
     </row>
     <row r="367" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A367" s="29">
-        <v>10530006</v>
+        <v>10530002</v>
       </c>
       <c r="B367" s="29">
         <v>105300</v>
       </c>
       <c r="C367" s="29" t="s">
+        <v>598</v>
+      </c>
+      <c r="D367" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E367" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="F367" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G367" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="H367" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="I367" s="29" t="s">
+        <v>599</v>
+      </c>
+      <c r="K367" s="113"/>
+    </row>
+    <row r="368" s="29" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A368" s="29">
+        <v>10530003</v>
+      </c>
+      <c r="B368" s="29">
+        <v>105300</v>
+      </c>
+      <c r="C368" s="29" t="s">
+        <v>600</v>
+      </c>
+      <c r="D368" s="29" t="s">
+        <v>566</v>
+      </c>
+      <c r="E368" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="F368" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G368" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="H368" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="I368" s="29" t="s">
         <v>601</v>
       </c>
-      <c r="D367" s="29" t="s">
+      <c r="K368" s="113"/>
+    </row>
+    <row r="369" s="29" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A369" s="29">
+        <v>10530004</v>
+      </c>
+      <c r="B369" s="29">
+        <v>105300</v>
+      </c>
+      <c r="C369" s="29" t="s">
+        <v>602</v>
+      </c>
+      <c r="D369" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="E367" s="29" t="s">
-        <v>599</v>
-      </c>
-      <c r="F367" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G367" s="29" t="s">
+      <c r="E369" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="F369" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G369" s="29" t="s">
+        <v>604</v>
+      </c>
+      <c r="H369" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="I369" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="K369" s="113"/>
+    </row>
+    <row r="370" s="29" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A370" s="29">
+        <v>10530006</v>
+      </c>
+      <c r="B370" s="29">
+        <v>105300</v>
+      </c>
+      <c r="C370" s="29" t="s">
+        <v>605</v>
+      </c>
+      <c r="D370" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="E370" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="F370" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G370" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="H367" s="29" t="s">
-        <v>602</v>
-      </c>
-      <c r="I367" s="29" t="s">
+      <c r="H370" s="29" t="s">
+        <v>606</v>
+      </c>
+      <c r="I370" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="K367" s="113"/>
-    </row>
-    <row r="368" s="30" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A368" s="30">
-        <v>10570001</v>
-      </c>
-      <c r="B368" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C368" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="D368" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E368" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F368" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G368" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="H368" s="30" t="s">
-        <v>604</v>
-      </c>
-      <c r="I368" s="30" t="s">
-        <v>597</v>
-      </c>
-      <c r="K368" s="114"/>
-    </row>
-    <row r="369" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A369" s="30">
-        <v>10570002</v>
-      </c>
-      <c r="B369" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C369" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="D369" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="E369" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F369" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G369" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="H369" s="30" t="s">
-        <v>604</v>
-      </c>
-      <c r="I369" s="30" t="s">
-        <v>595</v>
-      </c>
-      <c r="K369" s="114"/>
-    </row>
-    <row r="370" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A370" s="30">
-        <v>10570003</v>
-      </c>
-      <c r="B370" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C370" s="30" t="s">
-        <v>605</v>
-      </c>
-      <c r="D370" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="E370" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F370" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G370" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="H370" s="30" t="s">
-        <v>604</v>
-      </c>
-      <c r="I370" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="K370" s="114"/>
+      <c r="K370" s="113"/>
     </row>
     <row r="371" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A371" s="30">
-        <v>10570004</v>
+        <v>10570001</v>
       </c>
       <c r="B371" s="30">
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>606</v>
+        <v>412</v>
       </c>
       <c r="D371" s="30" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E371" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F371" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G371" s="30" t="s">
         <v>607</v>
       </c>
-      <c r="F371" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G371" s="30" t="s">
+      <c r="H371" s="30" t="s">
         <v>608</v>
       </c>
-      <c r="H371" s="30" t="s">
-        <v>604</v>
-      </c>
       <c r="I371" s="30" t="s">
-        <v>294</v>
+        <v>601</v>
       </c>
       <c r="K371" s="114"/>
     </row>
     <row r="372" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A372" s="30">
-        <v>10570005</v>
+        <v>10570002</v>
       </c>
       <c r="B372" s="30">
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>253</v>
+        <v>415</v>
       </c>
       <c r="D372" s="30" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E372" s="30" t="s">
-        <v>609</v>
+        <v>114</v>
       </c>
       <c r="F372" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H372" s="30" t="s">
-        <v>455</v>
+        <v>608</v>
       </c>
       <c r="I372" s="30" t="s">
-        <v>39</v>
+        <v>599</v>
       </c>
       <c r="K372" s="114"/>
     </row>
     <row r="373" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A373" s="30">
-        <v>10570006</v>
+        <v>10570003</v>
       </c>
       <c r="B373" s="30">
         <v>105700</v>
       </c>
       <c r="C373" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="D373" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="E373" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F373" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G373" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="H373" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="I373" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="K373" s="114"/>
+    </row>
+    <row r="374" s="30" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A374" s="30">
+        <v>10570004</v>
+      </c>
+      <c r="B374" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C374" s="30" t="s">
+        <v>610</v>
+      </c>
+      <c r="D374" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="E374" s="30" t="s">
+        <v>611</v>
+      </c>
+      <c r="F374" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G374" s="30" t="s">
+        <v>612</v>
+      </c>
+      <c r="H374" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="I374" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="K374" s="114"/>
+    </row>
+    <row r="375" s="30" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A375" s="30">
+        <v>10570005</v>
+      </c>
+      <c r="B375" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C375" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D375" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E375" s="30" t="s">
+        <v>613</v>
+      </c>
+      <c r="F375" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G375" s="30" t="s">
+        <v>614</v>
+      </c>
+      <c r="H375" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="I375" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="K375" s="114"/>
+    </row>
+    <row r="376" s="30" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A376" s="30">
+        <v>10570006</v>
+      </c>
+      <c r="B376" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C376" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="D373" s="30" t="s">
+      <c r="D376" s="30" t="s">
         <v>438</v>
       </c>
-      <c r="E373" s="30" t="s">
+      <c r="E376" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="F373" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G373" s="30" t="s">
-        <v>611</v>
-      </c>
-      <c r="I373" s="30" t="s">
+      <c r="F376" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G376" s="30" t="s">
+        <v>615</v>
+      </c>
+      <c r="I376" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="K373" s="114"/>
-    </row>
-    <row r="374" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A374" s="31">
-        <v>10580001</v>
-      </c>
-      <c r="B374" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C374" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="D374" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E374" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F374" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G374" s="31" t="s">
-        <v>612</v>
-      </c>
-      <c r="H374" s="31" t="s">
-        <v>613</v>
-      </c>
-      <c r="I374" s="31" t="s">
-        <v>597</v>
-      </c>
-      <c r="K374" s="115"/>
-    </row>
-    <row r="375" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A375" s="31">
-        <v>10580002</v>
-      </c>
-      <c r="B375" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C375" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="D375" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="E375" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F375" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G375" s="31" t="s">
-        <v>612</v>
-      </c>
-      <c r="H375" s="31" t="s">
-        <v>613</v>
-      </c>
-      <c r="I375" s="31" t="s">
-        <v>595</v>
-      </c>
-      <c r="K375" s="115"/>
-    </row>
-    <row r="376" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A376" s="31">
-        <v>10580003</v>
-      </c>
-      <c r="B376" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C376" s="31" t="s">
-        <v>605</v>
-      </c>
-      <c r="D376" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="E376" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F376" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G376" s="31" t="s">
-        <v>612</v>
-      </c>
-      <c r="H376" s="31" t="s">
-        <v>613</v>
-      </c>
-      <c r="I376" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="K376" s="115"/>
+      <c r="K376" s="114"/>
     </row>
     <row r="377" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A377" s="31">
-        <v>10580004</v>
+        <v>10580001</v>
       </c>
       <c r="B377" s="31">
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D377" s="31" t="s">
         <v>422</v>
       </c>
       <c r="E377" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F377" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G377" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="H377" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="I377" s="31" t="s">
+        <v>601</v>
+      </c>
+      <c r="K377" s="115"/>
+    </row>
+    <row r="378" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A378" s="31">
+        <v>10580002</v>
+      </c>
+      <c r="B378" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C378" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="D378" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="E378" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F378" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G378" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="H378" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="I378" s="31" t="s">
+        <v>599</v>
+      </c>
+      <c r="K378" s="115"/>
+    </row>
+    <row r="379" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A379" s="31">
+        <v>10580003</v>
+      </c>
+      <c r="B379" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C379" s="31" t="s">
+        <v>609</v>
+      </c>
+      <c r="D379" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="E379" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F379" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G379" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="H379" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="I379" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="K379" s="115"/>
+    </row>
+    <row r="380" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A380" s="31">
+        <v>10580004</v>
+      </c>
+      <c r="B380" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C380" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="D380" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="E380" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="F377" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G377" s="31" t="s">
-        <v>614</v>
-      </c>
-      <c r="H377" s="31" t="s">
-        <v>613</v>
-      </c>
-      <c r="I377" s="31" t="s">
+      <c r="F380" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G380" s="31" t="s">
+        <v>618</v>
+      </c>
+      <c r="H380" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="I380" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="K377" s="115"/>
-    </row>
-    <row r="378" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A378" s="32">
+      <c r="K380" s="115"/>
+    </row>
+    <row r="381" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A381" s="32">
         <v>10550001</v>
       </c>
-      <c r="B378" s="32">
+      <c r="B381" s="32">
         <v>105500</v>
       </c>
-      <c r="C378" s="32" t="s">
+      <c r="C381" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D378" s="32" t="s">
+      <c r="D381" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E378" s="32" t="s">
+      <c r="E381" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F378" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G378" s="32" t="s">
-        <v>615</v>
-      </c>
-      <c r="I378" s="32" t="s">
+      <c r="F381" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G381" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="I381" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K378" s="116"/>
-    </row>
-    <row r="379" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A379" s="32">
+      <c r="K381" s="116"/>
+    </row>
+    <row r="382" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A382" s="32">
         <v>10550002</v>
       </c>
-      <c r="B379" s="32">
+      <c r="B382" s="32">
         <v>105500</v>
       </c>
-      <c r="C379" s="32" t="s">
-        <v>616</v>
-      </c>
-      <c r="D379" s="32" t="s">
+      <c r="C382" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="D382" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E379" s="32" t="s">
+      <c r="E382" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="F379" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G379" s="32" t="s">
+      <c r="F382" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G382" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="I379" s="32" t="s">
+      <c r="I382" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="K379" s="116"/>
-    </row>
-    <row r="380" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A380" s="33">
-        <v>10480001</v>
-      </c>
-      <c r="B380" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C380" s="33" t="s">
-        <v>503</v>
-      </c>
-      <c r="D380" s="33" t="s">
-        <v>422</v>
-      </c>
-      <c r="E380" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="F380" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G380" s="33" t="s">
-        <v>617</v>
-      </c>
-      <c r="H380" s="33" t="s">
-        <v>618</v>
-      </c>
-      <c r="I380" s="33" t="s">
-        <v>546</v>
-      </c>
-      <c r="K380" s="82"/>
-    </row>
-    <row r="381" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A381" s="33">
-        <v>10480002</v>
-      </c>
-      <c r="B381" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C381" s="33" t="s">
-        <v>619</v>
-      </c>
-      <c r="D381" s="33" t="s">
-        <v>328</v>
-      </c>
-      <c r="E381" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F381" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G381" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="H381" s="33" t="s">
-        <v>618</v>
-      </c>
-      <c r="I381" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="K381" s="82"/>
-    </row>
-    <row r="382" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A382" s="33">
-        <v>10480003</v>
-      </c>
-      <c r="B382" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C382" s="33" t="s">
-        <v>620</v>
-      </c>
-      <c r="D382" s="33" t="s">
-        <v>328</v>
-      </c>
-      <c r="E382" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F382" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G382" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="H382" s="33" t="s">
-        <v>618</v>
-      </c>
-      <c r="I382" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="K382" s="82"/>
+      <c r="K382" s="116"/>
     </row>
     <row r="383" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A383" s="33">
-        <v>10480004</v>
+        <v>10480001</v>
       </c>
       <c r="B383" s="33">
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="D383" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E383" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F383" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G383" s="33" t="s">
         <v>621</v>
       </c>
-      <c r="D383" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E383" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="F383" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G383" s="33" t="s">
-        <v>460</v>
-      </c>
       <c r="H383" s="33" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="I383" s="33" t="s">
-        <v>107</v>
+        <v>546</v>
       </c>
       <c r="K383" s="82"/>
     </row>
     <row r="384" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A384" s="33">
-        <v>10480005</v>
+        <v>10480002</v>
       </c>
       <c r="B384" s="33">
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>289</v>
+        <v>623</v>
       </c>
       <c r="D384" s="33" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E384" s="33" t="s">
         <v>143</v>
@@ -14745,190 +14757,199 @@
         <v>460</v>
       </c>
       <c r="H384" s="33" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="K384" s="82"/>
     </row>
     <row r="385" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A385" s="33">
-        <v>10480006</v>
+        <v>10480003</v>
       </c>
       <c r="B385" s="33">
         <v>104800</v>
       </c>
       <c r="C385" s="33" t="s">
-        <v>330</v>
+        <v>624</v>
       </c>
       <c r="D385" s="33" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E385" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F385" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G385" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="H385" s="33" t="s">
         <v>622</v>
       </c>
-      <c r="F385" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G385" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="H385" s="33" t="s">
-        <v>618</v>
-      </c>
       <c r="I385" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K385" s="117"/>
+        <v>327</v>
+      </c>
+      <c r="K385" s="82"/>
     </row>
     <row r="386" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A386" s="33">
-        <v>10480007</v>
+        <v>10480004</v>
       </c>
       <c r="B386" s="33">
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>334</v>
+        <v>625</v>
       </c>
       <c r="D386" s="33" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E386" s="33" t="s">
-        <v>623</v>
+        <v>143</v>
       </c>
       <c r="F386" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G386" s="33" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H386" s="33" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="I386" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K386" s="117"/>
+        <v>107</v>
+      </c>
+      <c r="K386" s="82"/>
     </row>
     <row r="387" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A387" s="33">
-        <v>10480008</v>
+        <v>10480005</v>
       </c>
       <c r="B387" s="33">
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="D387" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E387" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F387" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G387" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="H387" s="33" t="s">
+        <v>622</v>
+      </c>
+      <c r="I387" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="K387" s="82"/>
+    </row>
+    <row r="388" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A388" s="33">
+        <v>10480006</v>
+      </c>
+      <c r="B388" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C388" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D388" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E388" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="F388" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G388" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="H388" s="33" t="s">
+        <v>622</v>
+      </c>
+      <c r="I388" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="K388" s="117"/>
+    </row>
+    <row r="389" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A389" s="33">
+        <v>10480007</v>
+      </c>
+      <c r="B389" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C389" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="D389" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E389" s="33" t="s">
+        <v>627</v>
+      </c>
+      <c r="F389" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G389" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="H389" s="33" t="s">
+        <v>622</v>
+      </c>
+      <c r="I389" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="K389" s="117"/>
+    </row>
+    <row r="390" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A390" s="33">
+        <v>10480008</v>
+      </c>
+      <c r="B390" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C390" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="D387" s="33" t="s">
+      <c r="D390" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E387" s="33" t="s">
+      <c r="E390" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="F387" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G387" s="33" t="s">
+      <c r="F390" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G390" s="33" t="s">
         <v>469</v>
       </c>
-      <c r="H387" s="33" t="s">
+      <c r="H390" s="33" t="s">
         <v>408</v>
       </c>
-      <c r="I387" s="33" t="s">
+      <c r="I390" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="K387" s="82"/>
-    </row>
-    <row r="388" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A388" s="32">
-        <v>10550101</v>
-      </c>
-      <c r="B388" s="32">
-        <v>105501</v>
-      </c>
-      <c r="C388" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="D388" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E388" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="F388" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G388" s="32" t="s">
-        <v>615</v>
-      </c>
-      <c r="I388" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="K388" s="116"/>
-    </row>
-    <row r="389" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A389" s="32">
-        <v>10550102</v>
-      </c>
-      <c r="B389" s="32">
-        <v>105501</v>
-      </c>
-      <c r="C389" s="32" t="s">
-        <v>616</v>
-      </c>
-      <c r="D389" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E389" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="F389" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G389" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I389" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K389" s="116"/>
-    </row>
-    <row r="390" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A390" s="32">
-        <v>10550103</v>
-      </c>
-      <c r="B390" s="32">
-        <v>105501</v>
-      </c>
-      <c r="C390" s="32" t="s">
-        <v>624</v>
-      </c>
-      <c r="D390" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E390" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="F390" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G390" s="32" t="s">
-        <v>615</v>
-      </c>
-      <c r="I390" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="K390" s="116"/>
+      <c r="K390" s="82"/>
     </row>
     <row r="391" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A391" s="32">
-        <v>10550201</v>
+        <v>10550101</v>
       </c>
       <c r="B391" s="32">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
         <v>253</v>
@@ -14943,7 +14964,7 @@
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>39</v>
@@ -14952,13 +14973,13 @@
     </row>
     <row r="392" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A392" s="32">
-        <v>10550202</v>
+        <v>10550102</v>
       </c>
       <c r="B392" s="32">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C392" s="32" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D392" s="32" t="s">
         <v>21</v>
@@ -14977,164 +14998,155 @@
       </c>
       <c r="K392" s="116"/>
     </row>
-    <row r="393" ht="16.5" spans="1:11">
+    <row r="393" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A393" s="32">
-        <v>10550203</v>
+        <v>10550103</v>
       </c>
       <c r="B393" s="32">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="F393" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G393" s="32" t="s">
-        <v>297</v>
+        <v>619</v>
       </c>
       <c r="I393" s="32" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="394" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A394" s="34">
-        <v>10410001</v>
-      </c>
-      <c r="B394" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C394" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="D394" s="34" t="s">
-        <v>422</v>
-      </c>
-      <c r="E394" s="34" t="s">
+      <c r="K393" s="116"/>
+    </row>
+    <row r="394" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A394" s="32">
+        <v>10550201</v>
+      </c>
+      <c r="B394" s="32">
+        <v>105502</v>
+      </c>
+      <c r="C394" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D394" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E394" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F394" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G394" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="H394" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I394" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="K394" s="118"/>
-    </row>
-    <row r="395" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A395" s="34">
-        <v>10410002</v>
-      </c>
-      <c r="B395" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C395" s="34" t="s">
-        <v>556</v>
-      </c>
-      <c r="D395" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="E395" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F395" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G395" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="H395" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I395" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="K395" s="118"/>
-    </row>
-    <row r="396" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A396" s="34">
-        <v>10410003</v>
-      </c>
-      <c r="B396" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C396" s="34" t="s">
-        <v>412</v>
-      </c>
-      <c r="D396" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E396" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F396" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G396" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="H396" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I396" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="K396" s="118"/>
+      <c r="F394" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G394" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="I394" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K394" s="116"/>
+    </row>
+    <row r="395" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A395" s="32">
+        <v>10550202</v>
+      </c>
+      <c r="B395" s="32">
+        <v>105502</v>
+      </c>
+      <c r="C395" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="D395" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E395" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="F395" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G395" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="I395" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="K395" s="116"/>
+    </row>
+    <row r="396" ht="16.5" spans="1:11">
+      <c r="A396" s="32">
+        <v>10550203</v>
+      </c>
+      <c r="B396" s="32">
+        <v>105502</v>
+      </c>
+      <c r="C396" s="32" t="s">
+        <v>629</v>
+      </c>
+      <c r="D396" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E396" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F396" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G396" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="I396" s="32" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="397" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A397" s="34">
-        <v>10410004</v>
+        <v>10410001</v>
       </c>
       <c r="B397" s="34">
         <v>104100</v>
       </c>
       <c r="C397" s="34" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E397" s="34" t="s">
-        <v>416</v>
+        <v>157</v>
       </c>
       <c r="F397" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>255</v>
+        <v>159</v>
       </c>
       <c r="H397" s="34" t="s">
-        <v>626</v>
+        <v>455</v>
       </c>
       <c r="I397" s="34" t="s">
-        <v>39</v>
+        <v>546</v>
       </c>
       <c r="K397" s="118"/>
     </row>
     <row r="398" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A398" s="34">
-        <v>10410005</v>
+        <v>10410002</v>
       </c>
       <c r="B398" s="34">
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>246</v>
+        <v>556</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E398" s="34" t="s">
         <v>114</v>
@@ -15149,142 +15161,142 @@
         <v>455</v>
       </c>
       <c r="I398" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="K398" s="118"/>
+    </row>
+    <row r="399" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A399" s="34">
+        <v>10410003</v>
+      </c>
+      <c r="B399" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C399" s="34" t="s">
+        <v>412</v>
+      </c>
+      <c r="D399" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="E399" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F399" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G399" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H399" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="I399" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="K399" s="118"/>
+    </row>
+    <row r="400" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A400" s="34">
+        <v>10410004</v>
+      </c>
+      <c r="B400" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C400" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="D400" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E400" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="F400" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G400" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="H400" s="34" t="s">
+        <v>630</v>
+      </c>
+      <c r="I400" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="K400" s="118"/>
+    </row>
+    <row r="401" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A401" s="34">
+        <v>10410005</v>
+      </c>
+      <c r="B401" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C401" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="D401" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="E401" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F401" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G401" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H401" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="I401" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="K398" s="118"/>
-    </row>
-    <row r="399" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A399" s="35">
-        <v>10420001</v>
-      </c>
-      <c r="B399" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C399" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="D399" s="35" t="s">
-        <v>422</v>
-      </c>
-      <c r="E399" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="F399" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G399" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H399" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I399" s="35" t="s">
-        <v>546</v>
-      </c>
-      <c r="K399" s="119"/>
-    </row>
-    <row r="400" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A400" s="35">
-        <v>10420002</v>
-      </c>
-      <c r="B400" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C400" s="35" t="s">
-        <v>556</v>
-      </c>
-      <c r="D400" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="E400" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F400" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G400" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H400" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I400" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="K400" s="119"/>
-    </row>
-    <row r="401" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A401" s="35">
-        <v>10420003</v>
-      </c>
-      <c r="B401" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C401" s="35" t="s">
-        <v>412</v>
-      </c>
-      <c r="D401" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="E401" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F401" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G401" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H401" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I401" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="K401" s="119"/>
+      <c r="K401" s="118"/>
     </row>
     <row r="402" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A402" s="35">
-        <v>10420004</v>
+        <v>10420001</v>
       </c>
       <c r="B402" s="35">
         <v>104200</v>
       </c>
       <c r="C402" s="35" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E402" s="35" t="s">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="F402" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G402" s="35" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H402" s="35" t="s">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="I402" s="35" t="s">
-        <v>39</v>
+        <v>546</v>
       </c>
       <c r="K402" s="119"/>
     </row>
     <row r="403" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A403" s="35">
-        <v>10420005</v>
+        <v>10420002</v>
       </c>
       <c r="B403" s="35">
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>246</v>
+        <v>556</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E403" s="35" t="s">
         <v>143</v>
@@ -15299,9 +15311,99 @@
         <v>550</v>
       </c>
       <c r="I403" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="K403" s="119"/>
+    </row>
+    <row r="404" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A404" s="35">
+        <v>10420003</v>
+      </c>
+      <c r="B404" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C404" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="D404" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="E404" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="F404" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G404" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H404" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="I404" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="K404" s="119"/>
+    </row>
+    <row r="405" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A405" s="35">
+        <v>10420004</v>
+      </c>
+      <c r="B405" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C405" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="D405" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E405" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="F405" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G405" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="H405" s="35" t="s">
+        <v>594</v>
+      </c>
+      <c r="I405" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="K405" s="119"/>
+    </row>
+    <row r="406" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A406" s="35">
+        <v>10420005</v>
+      </c>
+      <c r="B406" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C406" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="D406" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="E406" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="F406" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G406" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H406" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="I406" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="K403" s="119"/>
+      <c r="K406" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15321,24 +15423,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15346,16 +15448,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15363,16 +15465,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15380,16 +15482,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15405,7 +15507,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15413,7 +15515,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15421,7 +15523,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15429,7 +15531,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15437,7 +15539,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15445,7 +15547,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15453,7 +15555,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15461,7 +15563,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15469,7 +15571,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15477,7 +15579,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15485,7 +15587,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15493,7 +15595,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15501,7 +15603,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15509,7 +15611,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15517,7 +15619,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15525,7 +15627,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15533,7 +15635,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15541,7 +15643,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -15549,7 +15651,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -15557,7 +15659,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -15565,7 +15667,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -15573,7 +15675,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -15581,7 +15683,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -15589,7 +15691,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -15597,7 +15699,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -15605,7 +15707,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -15613,7 +15715,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -15621,7 +15723,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -15629,7 +15731,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -15637,7 +15739,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -15645,7 +15747,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -15653,7 +15755,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -15661,7 +15763,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -15669,7 +15771,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -15677,7 +15779,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -15685,7 +15787,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -15693,7 +15795,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -15701,7 +15803,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -15709,7 +15811,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15717,7 +15819,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -15725,7 +15827,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -15733,7 +15835,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2758" uniqueCount="685">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1537,271 +1537,268 @@
     <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
   </si>
   <si>
-    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
   </si>
   <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
   </si>
   <si>
-    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1|65_1</t>
+    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1</t>
   </si>
   <si>
     <t>8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
   </si>
   <si>
-    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|66_1|67_1|68_1|69_1|70_1|71_1|72_1|73_1|74_1|75_1|76_1</t>
+    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1</t>
   </si>
   <si>
     <t>9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
   </si>
   <si>
-    <t>43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1|77_1|78_1|79_1|80_1|81_1|82_1|83_1|84_1|85_1|86_1|87_1</t>
+    <t>概率改出免费+1符号</t>
+  </si>
+  <si>
+    <t>0_9|1_1</t>
+  </si>
+  <si>
+    <t>31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>改出黄金10符号</t>
+  </si>
+  <si>
+    <t>87_1</t>
+  </si>
+  <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金J符号</t>
+  </si>
+  <si>
+    <t>88_1</t>
+  </si>
+  <si>
+    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金Q符号</t>
+  </si>
+  <si>
+    <t>89_1</t>
+  </si>
+  <si>
+    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金K符号</t>
+  </si>
+  <si>
+    <t>90_1</t>
+  </si>
+  <si>
+    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金A符号</t>
+  </si>
+  <si>
+    <t>91_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金罗纳尔多</t>
+  </si>
+  <si>
+    <t>92_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金格列兹曼</t>
+  </si>
+  <si>
+    <t>93_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金内马尔</t>
+  </si>
+  <si>
+    <t>94_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金斯特林</t>
+  </si>
+  <si>
+    <t>95_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金C罗</t>
+  </si>
+  <si>
+    <t>96_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金梅西</t>
+  </si>
+  <si>
+    <t>97_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号</t>
+  </si>
+  <si>
+    <t>13_14_15_16_17_18_19_20_21_22</t>
+  </si>
+  <si>
+    <t>改出20符号</t>
+  </si>
+  <si>
+    <t>改出21符号</t>
+  </si>
+  <si>
+    <t>改出22符号</t>
+  </si>
+  <si>
+    <t>16_10|17_5|18_2|19_1</t>
+  </si>
+  <si>
+    <t>第1轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第2轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第3轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第4轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第5轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第1、2轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1</t>
+  </si>
+  <si>
+    <t>第1、3轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第1、4轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第1、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第2、3轴改出6个wild</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第2、4轴改出6个wild</t>
+  </si>
+  <si>
+    <t>第2、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第3、4轴改出6个wild</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第3、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第4、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第1、2、3轴改出9个wild</t>
+  </si>
+  <si>
+    <t>第1、2、4轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第1、2、5轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第1、3、4轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第1、3、5轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第1、4、5轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出+1免费符号</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119</t>
+  </si>
+  <si>
+    <t>0_70|1_20|2_9|3_1</t>
+  </si>
+  <si>
+    <t>2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
   </si>
   <si>
     <t>10_1_1|11_1_1|12_1_1|16_1_1|17_1_1|18_1_1|22_1_1|23_1_1|24_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>概率改出免费+1符号</t>
-  </si>
-  <si>
-    <t>0_9|1_1</t>
-  </si>
-  <si>
-    <t>31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
-  </si>
-  <si>
-    <t>改出黄金10符号</t>
-  </si>
-  <si>
-    <t>121_1</t>
-  </si>
-  <si>
-    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金J符号</t>
-  </si>
-  <si>
-    <t>122_1</t>
-  </si>
-  <si>
-    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金Q符号</t>
-  </si>
-  <si>
-    <t>123_1</t>
-  </si>
-  <si>
-    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金K符号</t>
-  </si>
-  <si>
-    <t>124_1</t>
-  </si>
-  <si>
-    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金A符号</t>
-  </si>
-  <si>
-    <t>125_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金罗纳尔多</t>
-  </si>
-  <si>
-    <t>126_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金格列兹曼</t>
-  </si>
-  <si>
-    <t>127_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金内马尔</t>
-  </si>
-  <si>
-    <t>128_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金斯特林</t>
-  </si>
-  <si>
-    <t>129_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金C罗</t>
-  </si>
-  <si>
-    <t>130_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金梅西</t>
-  </si>
-  <si>
-    <t>131_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_10_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>概率改出百搭wild符号</t>
-  </si>
-  <si>
-    <t>13_14_15_16_17_18_19_20_21_22</t>
-  </si>
-  <si>
-    <t>改出20符号</t>
-  </si>
-  <si>
-    <t>改出21符号</t>
-  </si>
-  <si>
-    <t>改出22符号</t>
-  </si>
-  <si>
-    <t>16_10|17_5|18_2|19_1</t>
-  </si>
-  <si>
-    <t>第1轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第2轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第3轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第4轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第5轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第1、2轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1</t>
-  </si>
-  <si>
-    <t>第1、3轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>第1、4轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第1、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第2、3轴改出6个wild</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>第2、4轴改出6个wild</t>
-  </si>
-  <si>
-    <t>第2、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第3、4轴改出6个wild</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第3、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第4、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第1、2、3轴改出9个wild</t>
-  </si>
-  <si>
-    <t>第1、2、4轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第1、2、5轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第1、3、4轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第1、3、5轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第1、4、5轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出+1免费符号</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119</t>
-  </si>
-  <si>
-    <t>0_70|1_20|2_9|3_1</t>
-  </si>
-  <si>
-    <t>2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
   </si>
   <si>
     <t>11_1_1|12_1_1|17_1_1|18_1_1|23_1_1|24_1_1|29_1_1|30_1_1</t>
@@ -3508,7 +3505,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N406"/>
+  <dimension ref="A1:N405"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -11447,88 +11444,88 @@
     </row>
     <row r="273" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A273" s="24">
-        <v>10160007</v>
+        <v>10160008</v>
       </c>
       <c r="B273" s="24">
         <v>101600</v>
       </c>
       <c r="C273" s="24" t="s">
-        <v>337</v>
+        <v>465</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E273" s="24" t="s">
-        <v>465</v>
+        <v>146</v>
       </c>
       <c r="F273" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G273" s="24" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="H273" s="24" t="s">
         <v>459</v>
       </c>
       <c r="I273" s="24" t="s">
-        <v>340</v>
+        <v>466</v>
       </c>
       <c r="K273" s="108"/>
     </row>
     <row r="274" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A274" s="24">
-        <v>10160008</v>
+        <v>10160009</v>
       </c>
       <c r="B274" s="24">
         <v>101600</v>
       </c>
       <c r="C274" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D274" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E274" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F274" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G274" s="24" t="s">
         <v>467</v>
-      </c>
-      <c r="D274" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="E274" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F274" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G274" s="24" t="s">
-        <v>460</v>
       </c>
       <c r="H274" s="24" t="s">
         <v>459</v>
       </c>
       <c r="I274" s="24" t="s">
-        <v>468</v>
+        <v>39</v>
       </c>
       <c r="K274" s="108"/>
     </row>
     <row r="275" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A275" s="24">
-        <v>10160009</v>
+        <v>10160010</v>
       </c>
       <c r="B275" s="24">
         <v>101600</v>
       </c>
       <c r="C275" s="24" t="s">
-        <v>253</v>
+        <v>468</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E275" s="24" t="s">
-        <v>254</v>
+        <v>469</v>
       </c>
       <c r="F275" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G275" s="24" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="H275" s="24" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="I275" s="24" t="s">
         <v>39</v>
@@ -11537,19 +11534,19 @@
     </row>
     <row r="276" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A276" s="24">
-        <v>10160010</v>
+        <v>10160011</v>
       </c>
       <c r="B276" s="24">
         <v>101600</v>
       </c>
       <c r="C276" s="24" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D276" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E276" s="24" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F276" s="24" t="s">
         <v>133</v>
@@ -11558,7 +11555,7 @@
         <v>460</v>
       </c>
       <c r="H276" s="24" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I276" s="24" t="s">
         <v>39</v>
@@ -11567,19 +11564,19 @@
     </row>
     <row r="277" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A277" s="24">
-        <v>10160011</v>
+        <v>10160012</v>
       </c>
       <c r="B277" s="24">
         <v>101600</v>
       </c>
       <c r="C277" s="24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D277" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E277" s="24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F277" s="24" t="s">
         <v>133</v>
@@ -11588,7 +11585,7 @@
         <v>460</v>
       </c>
       <c r="H277" s="24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I277" s="24" t="s">
         <v>39</v>
@@ -11597,19 +11594,19 @@
     </row>
     <row r="278" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A278" s="24">
-        <v>10160012</v>
+        <v>10160013</v>
       </c>
       <c r="B278" s="24">
         <v>101600</v>
       </c>
       <c r="C278" s="24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D278" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E278" s="24" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F278" s="24" t="s">
         <v>133</v>
@@ -11618,7 +11615,7 @@
         <v>460</v>
       </c>
       <c r="H278" s="24" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I278" s="24" t="s">
         <v>39</v>
@@ -11627,19 +11624,19 @@
     </row>
     <row r="279" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A279" s="24">
-        <v>10160013</v>
+        <v>10160014</v>
       </c>
       <c r="B279" s="24">
         <v>101600</v>
       </c>
       <c r="C279" s="24" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D279" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E279" s="24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F279" s="24" t="s">
         <v>133</v>
@@ -11648,7 +11645,7 @@
         <v>460</v>
       </c>
       <c r="H279" s="24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I279" s="24" t="s">
         <v>39</v>
@@ -11657,19 +11654,19 @@
     </row>
     <row r="280" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A280" s="24">
-        <v>10160014</v>
+        <v>10160015</v>
       </c>
       <c r="B280" s="24">
         <v>101600</v>
       </c>
       <c r="C280" s="24" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D280" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E280" s="24" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F280" s="24" t="s">
         <v>133</v>
@@ -11678,7 +11675,7 @@
         <v>460</v>
       </c>
       <c r="H280" s="24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I280" s="24" t="s">
         <v>39</v>
@@ -11687,19 +11684,19 @@
     </row>
     <row r="281" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A281" s="24">
-        <v>10160015</v>
+        <v>10160016</v>
       </c>
       <c r="B281" s="24">
         <v>101600</v>
       </c>
       <c r="C281" s="24" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D281" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E281" s="24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F281" s="24" t="s">
         <v>133</v>
@@ -11708,7 +11705,7 @@
         <v>460</v>
       </c>
       <c r="H281" s="24" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I281" s="24" t="s">
         <v>39</v>
@@ -11717,19 +11714,19 @@
     </row>
     <row r="282" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A282" s="24">
-        <v>10160016</v>
+        <v>10160017</v>
       </c>
       <c r="B282" s="24">
         <v>101600</v>
       </c>
       <c r="C282" s="24" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D282" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E282" s="24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F282" s="24" t="s">
         <v>133</v>
@@ -11738,7 +11735,7 @@
         <v>460</v>
       </c>
       <c r="H282" s="24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I282" s="24" t="s">
         <v>39</v>
@@ -11747,19 +11744,19 @@
     </row>
     <row r="283" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A283" s="24">
-        <v>10160017</v>
+        <v>10160018</v>
       </c>
       <c r="B283" s="24">
         <v>101600</v>
       </c>
       <c r="C283" s="24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D283" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E283" s="24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F283" s="24" t="s">
         <v>133</v>
@@ -11768,7 +11765,7 @@
         <v>460</v>
       </c>
       <c r="H283" s="24" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I283" s="24" t="s">
         <v>39</v>
@@ -11777,19 +11774,19 @@
     </row>
     <row r="284" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A284" s="24">
-        <v>10160018</v>
+        <v>10160019</v>
       </c>
       <c r="B284" s="24">
         <v>101600</v>
       </c>
       <c r="C284" s="24" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D284" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E284" s="24" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F284" s="24" t="s">
         <v>133</v>
@@ -11798,7 +11795,7 @@
         <v>460</v>
       </c>
       <c r="H284" s="24" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I284" s="24" t="s">
         <v>39</v>
@@ -11807,19 +11804,19 @@
     </row>
     <row r="285" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A285" s="24">
-        <v>10160019</v>
+        <v>10160020</v>
       </c>
       <c r="B285" s="24">
         <v>101600</v>
       </c>
       <c r="C285" s="24" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D285" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E285" s="24" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F285" s="24" t="s">
         <v>133</v>
@@ -11828,58 +11825,58 @@
         <v>460</v>
       </c>
       <c r="H285" s="24" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I285" s="24" t="s">
         <v>39</v>
       </c>
       <c r="K285" s="108"/>
     </row>
-    <row r="286" s="24" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A286" s="24">
-        <v>10160020</v>
-      </c>
-      <c r="B286" s="24">
-        <v>101600</v>
-      </c>
-      <c r="C286" s="24" t="s">
-        <v>500</v>
-      </c>
-      <c r="D286" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="E286" s="24" t="s">
+    <row r="286" s="26" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A286" s="26">
+        <v>10150001</v>
+      </c>
+      <c r="B286" s="26">
+        <v>101500</v>
+      </c>
+      <c r="C286" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="F286" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G286" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="H286" s="24" t="s">
+      <c r="D286" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="E286" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F286" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G286" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="H286" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="I286" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="K286" s="108"/>
+      <c r="I286" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="K286" s="110"/>
     </row>
     <row r="287" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A287" s="26">
-        <v>10150001</v>
+        <v>10150002</v>
       </c>
       <c r="B287" s="26">
         <v>101500</v>
       </c>
       <c r="C287" s="26" t="s">
-        <v>503</v>
+        <v>259</v>
       </c>
       <c r="D287" s="26" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E287" s="26" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F287" s="26" t="s">
         <v>133</v>
@@ -11888,22 +11885,22 @@
         <v>234</v>
       </c>
       <c r="H287" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I287" s="26" t="s">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="K287" s="110"/>
     </row>
     <row r="288" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A288" s="26">
-        <v>10150002</v>
+        <v>10150003</v>
       </c>
       <c r="B288" s="26">
         <v>101500</v>
       </c>
       <c r="C288" s="26" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="D288" s="26" t="s">
         <v>21</v>
@@ -11918,22 +11915,22 @@
         <v>234</v>
       </c>
       <c r="H288" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I288" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K288" s="110"/>
     </row>
     <row r="289" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A289" s="26">
-        <v>10150003</v>
+        <v>10150004</v>
       </c>
       <c r="B289" s="26">
         <v>101500</v>
       </c>
       <c r="C289" s="26" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D289" s="26" t="s">
         <v>21</v>
@@ -11948,28 +11945,28 @@
         <v>234</v>
       </c>
       <c r="H289" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I289" s="26" t="s">
-        <v>106</v>
+        <v>432</v>
       </c>
       <c r="K289" s="110"/>
     </row>
     <row r="290" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A290" s="26">
-        <v>10150004</v>
+        <v>10150005</v>
       </c>
       <c r="B290" s="26">
         <v>101500</v>
       </c>
       <c r="C290" s="26" t="s">
-        <v>246</v>
+        <v>503</v>
       </c>
       <c r="D290" s="26" t="s">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="E290" s="26" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="F290" s="26" t="s">
         <v>133</v>
@@ -11978,28 +11975,28 @@
         <v>234</v>
       </c>
       <c r="H290" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I290" s="26" t="s">
-        <v>432</v>
+        <v>39</v>
       </c>
       <c r="K290" s="110"/>
     </row>
     <row r="291" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A291" s="26">
-        <v>10150005</v>
+        <v>10150006</v>
       </c>
       <c r="B291" s="26">
         <v>101500</v>
       </c>
       <c r="C291" s="26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D291" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E291" s="26" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F291" s="26" t="s">
         <v>133</v>
@@ -12008,7 +12005,7 @@
         <v>234</v>
       </c>
       <c r="H291" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I291" s="26" t="s">
         <v>39</v>
@@ -12017,19 +12014,19 @@
     </row>
     <row r="292" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A292" s="26">
-        <v>10150006</v>
+        <v>10150007</v>
       </c>
       <c r="B292" s="26">
         <v>101500</v>
       </c>
       <c r="C292" s="26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D292" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E292" s="26" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F292" s="26" t="s">
         <v>133</v>
@@ -12038,7 +12035,7 @@
         <v>234</v>
       </c>
       <c r="H292" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I292" s="26" t="s">
         <v>39</v>
@@ -12047,28 +12044,28 @@
     </row>
     <row r="293" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A293" s="26">
-        <v>10150007</v>
+        <v>10150008</v>
       </c>
       <c r="B293" s="26">
         <v>101500</v>
       </c>
       <c r="C293" s="26" t="s">
-        <v>507</v>
+        <v>253</v>
       </c>
       <c r="D293" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E293" s="26" t="s">
-        <v>56</v>
+        <v>506</v>
       </c>
       <c r="F293" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G293" s="26" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H293" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I293" s="26" t="s">
         <v>39</v>
@@ -12077,43 +12074,43 @@
     </row>
     <row r="294" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A294" s="26">
-        <v>10150008</v>
+        <v>10150009</v>
       </c>
       <c r="B294" s="26">
         <v>101500</v>
       </c>
       <c r="C294" s="26" t="s">
-        <v>253</v>
+        <v>507</v>
       </c>
       <c r="D294" s="26" t="s">
-        <v>279</v>
+        <v>422</v>
       </c>
       <c r="E294" s="26" t="s">
-        <v>508</v>
+        <v>143</v>
       </c>
       <c r="F294" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G294" s="26" t="s">
-        <v>255</v>
+        <v>439</v>
       </c>
       <c r="H294" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I294" s="26" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="K294" s="110"/>
     </row>
     <row r="295" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A295" s="26">
-        <v>10150009</v>
+        <v>10150010</v>
       </c>
       <c r="B295" s="26">
         <v>101500</v>
       </c>
       <c r="C295" s="26" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D295" s="26" t="s">
         <v>422</v>
@@ -12125,10 +12122,10 @@
         <v>133</v>
       </c>
       <c r="G295" s="26" t="s">
-        <v>439</v>
+        <v>174</v>
       </c>
       <c r="H295" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I295" s="26" t="s">
         <v>107</v>
@@ -12137,13 +12134,13 @@
     </row>
     <row r="296" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A296" s="26">
-        <v>10150010</v>
+        <v>10150011</v>
       </c>
       <c r="B296" s="26">
         <v>101500</v>
       </c>
       <c r="C296" s="26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D296" s="26" t="s">
         <v>422</v>
@@ -12155,10 +12152,10 @@
         <v>133</v>
       </c>
       <c r="G296" s="26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H296" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I296" s="26" t="s">
         <v>107</v>
@@ -12167,13 +12164,13 @@
     </row>
     <row r="297" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A297" s="26">
-        <v>10150011</v>
+        <v>10150012</v>
       </c>
       <c r="B297" s="26">
         <v>101500</v>
       </c>
       <c r="C297" s="26" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D297" s="26" t="s">
         <v>422</v>
@@ -12185,10 +12182,10 @@
         <v>133</v>
       </c>
       <c r="G297" s="26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H297" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I297" s="26" t="s">
         <v>107</v>
@@ -12197,13 +12194,13 @@
     </row>
     <row r="298" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A298" s="26">
-        <v>10150012</v>
+        <v>10150013</v>
       </c>
       <c r="B298" s="26">
         <v>101500</v>
       </c>
       <c r="C298" s="26" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D298" s="26" t="s">
         <v>422</v>
@@ -12215,10 +12212,10 @@
         <v>133</v>
       </c>
       <c r="G298" s="26" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="H298" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I298" s="26" t="s">
         <v>107</v>
@@ -12227,16 +12224,16 @@
     </row>
     <row r="299" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A299" s="26">
-        <v>10150013</v>
+        <v>10150014</v>
       </c>
       <c r="B299" s="26">
         <v>101500</v>
       </c>
       <c r="C299" s="26" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D299" s="26" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E299" s="26" t="s">
         <v>143</v>
@@ -12245,19 +12242,19 @@
         <v>133</v>
       </c>
       <c r="G299" s="26" t="s">
-        <v>255</v>
+        <v>513</v>
       </c>
       <c r="H299" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I299" s="26" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="K299" s="110"/>
     </row>
     <row r="300" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A300" s="26">
-        <v>10150014</v>
+        <v>10150015</v>
       </c>
       <c r="B300" s="26">
         <v>101500</v>
@@ -12278,7 +12275,7 @@
         <v>515</v>
       </c>
       <c r="H300" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I300" s="26" t="s">
         <v>89</v>
@@ -12287,7 +12284,7 @@
     </row>
     <row r="301" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A301" s="26">
-        <v>10150015</v>
+        <v>10150016</v>
       </c>
       <c r="B301" s="26">
         <v>101500</v>
@@ -12308,7 +12305,7 @@
         <v>517</v>
       </c>
       <c r="H301" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I301" s="26" t="s">
         <v>89</v>
@@ -12317,7 +12314,7 @@
     </row>
     <row r="302" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A302" s="26">
-        <v>10150016</v>
+        <v>10150017</v>
       </c>
       <c r="B302" s="26">
         <v>101500</v>
@@ -12338,7 +12335,7 @@
         <v>519</v>
       </c>
       <c r="H302" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I302" s="26" t="s">
         <v>89</v>
@@ -12347,7 +12344,7 @@
     </row>
     <row r="303" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A303" s="26">
-        <v>10150017</v>
+        <v>10150018</v>
       </c>
       <c r="B303" s="26">
         <v>101500</v>
@@ -12368,7 +12365,7 @@
         <v>521</v>
       </c>
       <c r="H303" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I303" s="26" t="s">
         <v>89</v>
@@ -12377,7 +12374,7 @@
     </row>
     <row r="304" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A304" s="26">
-        <v>10150018</v>
+        <v>10150019</v>
       </c>
       <c r="B304" s="26">
         <v>101500</v>
@@ -12395,10 +12392,10 @@
         <v>133</v>
       </c>
       <c r="G304" s="26" t="s">
-        <v>523</v>
+        <v>423</v>
       </c>
       <c r="H304" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I304" s="26" t="s">
         <v>89</v>
@@ -12407,13 +12404,13 @@
     </row>
     <row r="305" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A305" s="26">
-        <v>10150019</v>
+        <v>10150020</v>
       </c>
       <c r="B305" s="26">
         <v>101500</v>
       </c>
       <c r="C305" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D305" s="26" t="s">
         <v>21</v>
@@ -12425,10 +12422,10 @@
         <v>133</v>
       </c>
       <c r="G305" s="26" t="s">
-        <v>423</v>
+        <v>524</v>
       </c>
       <c r="H305" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I305" s="26" t="s">
         <v>89</v>
@@ -12437,7 +12434,7 @@
     </row>
     <row r="306" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A306" s="26">
-        <v>10150020</v>
+        <v>10150021</v>
       </c>
       <c r="B306" s="26">
         <v>101500</v>
@@ -12458,7 +12455,7 @@
         <v>526</v>
       </c>
       <c r="H306" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I306" s="26" t="s">
         <v>89</v>
@@ -12467,7 +12464,7 @@
     </row>
     <row r="307" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A307" s="26">
-        <v>10150021</v>
+        <v>10150022</v>
       </c>
       <c r="B307" s="26">
         <v>101500</v>
@@ -12488,7 +12485,7 @@
         <v>528</v>
       </c>
       <c r="H307" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I307" s="26" t="s">
         <v>89</v>
@@ -12497,7 +12494,7 @@
     </row>
     <row r="308" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A308" s="26">
-        <v>10150022</v>
+        <v>10150023</v>
       </c>
       <c r="B308" s="26">
         <v>101500</v>
@@ -12518,7 +12515,7 @@
         <v>530</v>
       </c>
       <c r="H308" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I308" s="26" t="s">
         <v>89</v>
@@ -12527,7 +12524,7 @@
     </row>
     <row r="309" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A309" s="26">
-        <v>10150023</v>
+        <v>10150024</v>
       </c>
       <c r="B309" s="26">
         <v>101500</v>
@@ -12545,25 +12542,25 @@
         <v>133</v>
       </c>
       <c r="G309" s="26" t="s">
-        <v>532</v>
+        <v>297</v>
       </c>
       <c r="H309" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I309" s="26" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="K309" s="110"/>
     </row>
     <row r="310" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A310" s="26">
-        <v>10150024</v>
+        <v>10150025</v>
       </c>
       <c r="B310" s="26">
         <v>101500</v>
       </c>
       <c r="C310" s="26" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D310" s="26" t="s">
         <v>21</v>
@@ -12575,10 +12572,10 @@
         <v>133</v>
       </c>
       <c r="G310" s="26" t="s">
-        <v>297</v>
+        <v>533</v>
       </c>
       <c r="H310" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I310" s="26" t="s">
         <v>157</v>
@@ -12587,7 +12584,7 @@
     </row>
     <row r="311" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A311" s="26">
-        <v>10150025</v>
+        <v>10150026</v>
       </c>
       <c r="B311" s="26">
         <v>101500</v>
@@ -12608,7 +12605,7 @@
         <v>535</v>
       </c>
       <c r="H311" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I311" s="26" t="s">
         <v>157</v>
@@ -12617,7 +12614,7 @@
     </row>
     <row r="312" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A312" s="26">
-        <v>10150026</v>
+        <v>10150027</v>
       </c>
       <c r="B312" s="26">
         <v>101500</v>
@@ -12638,7 +12635,7 @@
         <v>537</v>
       </c>
       <c r="H312" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I312" s="26" t="s">
         <v>157</v>
@@ -12647,7 +12644,7 @@
     </row>
     <row r="313" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A313" s="26">
-        <v>10150027</v>
+        <v>10150028</v>
       </c>
       <c r="B313" s="26">
         <v>101500</v>
@@ -12668,7 +12665,7 @@
         <v>539</v>
       </c>
       <c r="H313" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I313" s="26" t="s">
         <v>157</v>
@@ -12677,7 +12674,7 @@
     </row>
     <row r="314" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A314" s="26">
-        <v>10150028</v>
+        <v>10150029</v>
       </c>
       <c r="B314" s="26">
         <v>101500</v>
@@ -12698,7 +12695,7 @@
         <v>541</v>
       </c>
       <c r="H314" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I314" s="26" t="s">
         <v>157</v>
@@ -12707,7 +12704,7 @@
     </row>
     <row r="315" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A315" s="26">
-        <v>10150029</v>
+        <v>10150030</v>
       </c>
       <c r="B315" s="26">
         <v>101500</v>
@@ -12716,97 +12713,97 @@
         <v>542</v>
       </c>
       <c r="D315" s="26" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E315" s="26" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="F315" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G315" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="H315" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="I315" s="26" t="s">
+        <v>466</v>
+      </c>
+      <c r="K315" s="110"/>
+    </row>
+    <row r="316" s="27" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A316" s="27">
+        <v>10260001</v>
+      </c>
+      <c r="B316" s="27">
+        <v>102600</v>
+      </c>
+      <c r="C316" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="D316" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="E316" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F316" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G316" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="H316" s="27" t="s">
         <v>543</v>
       </c>
-      <c r="H315" s="26" t="s">
-        <v>504</v>
-      </c>
-      <c r="I315" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="K315" s="110"/>
-    </row>
-    <row r="316" s="26" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A316" s="26">
-        <v>10150030</v>
-      </c>
-      <c r="B316" s="26">
-        <v>101500</v>
-      </c>
-      <c r="C316" s="26" t="s">
+      <c r="I316" s="27" t="s">
         <v>544</v>
       </c>
-      <c r="D316" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="E316" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F316" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G316" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="H316" s="26" t="s">
-        <v>504</v>
-      </c>
-      <c r="I316" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="K316" s="110"/>
+      <c r="K316" s="111"/>
     </row>
     <row r="317" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A317" s="27">
-        <v>10260001</v>
+        <v>10260002</v>
       </c>
       <c r="B317" s="27">
         <v>102600</v>
       </c>
       <c r="C317" s="27" t="s">
-        <v>503</v>
+        <v>323</v>
       </c>
       <c r="D317" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E317" s="27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F317" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G317" s="27" t="s">
-        <v>458</v>
+        <v>545</v>
       </c>
       <c r="H317" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I317" s="27" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K317" s="111"/>
     </row>
     <row r="318" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A318" s="27">
-        <v>10260002</v>
+        <v>10260003</v>
       </c>
       <c r="B318" s="27">
         <v>102600</v>
       </c>
       <c r="C318" s="27" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D318" s="27" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E318" s="27" t="s">
         <v>143</v>
@@ -12815,28 +12812,28 @@
         <v>133</v>
       </c>
       <c r="G318" s="27" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H318" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I318" s="27" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="K318" s="111"/>
     </row>
     <row r="319" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A319" s="27">
-        <v>10260003</v>
+        <v>10260004</v>
       </c>
       <c r="B319" s="27">
         <v>102600</v>
       </c>
       <c r="C319" s="27" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D319" s="27" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E319" s="27" t="s">
         <v>143</v>
@@ -12845,70 +12842,70 @@
         <v>133</v>
       </c>
       <c r="G319" s="27" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H319" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I319" s="27" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="K319" s="111"/>
     </row>
     <row r="320" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A320" s="27">
-        <v>10260004</v>
+        <v>10260005</v>
       </c>
       <c r="B320" s="27">
         <v>102600</v>
       </c>
       <c r="C320" s="27" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D320" s="27" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E320" s="27" t="s">
-        <v>143</v>
+        <v>331</v>
       </c>
       <c r="F320" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G320" s="27" t="s">
-        <v>547</v>
+        <v>464</v>
       </c>
       <c r="H320" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I320" s="27" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K320" s="111"/>
     </row>
     <row r="321" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A321" s="27">
-        <v>10260005</v>
+        <v>10260006</v>
       </c>
       <c r="B321" s="27">
         <v>102600</v>
       </c>
       <c r="C321" s="27" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D321" s="27" t="s">
         <v>438</v>
       </c>
       <c r="E321" s="27" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F321" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G321" s="27" t="s">
-        <v>464</v>
+        <v>546</v>
       </c>
       <c r="H321" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I321" s="27" t="s">
         <v>333</v>
@@ -12917,49 +12914,49 @@
     </row>
     <row r="322" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A322" s="27">
-        <v>10260006</v>
+        <v>10260007</v>
       </c>
       <c r="B322" s="27">
         <v>102600</v>
       </c>
       <c r="C322" s="27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D322" s="27" t="s">
         <v>438</v>
       </c>
       <c r="E322" s="27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F322" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G322" s="27" t="s">
-        <v>466</v>
+        <v>547</v>
       </c>
       <c r="H322" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I322" s="27" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K322" s="111"/>
     </row>
     <row r="323" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A323" s="27">
-        <v>10260007</v>
+        <v>10260008</v>
       </c>
       <c r="B323" s="27">
         <v>102600</v>
       </c>
       <c r="C323" s="27" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D323" s="27" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E323" s="27" t="s">
-        <v>338</v>
+        <v>275</v>
       </c>
       <c r="F323" s="27" t="s">
         <v>133</v>
@@ -12968,138 +12965,137 @@
         <v>548</v>
       </c>
       <c r="H323" s="27" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="I323" s="27" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K323" s="111"/>
     </row>
     <row r="324" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A324" s="27">
-        <v>10260008</v>
+        <v>10260009</v>
       </c>
       <c r="B324" s="27">
         <v>102600</v>
       </c>
       <c r="C324" s="27" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E324" s="27" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F324" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G324" s="27" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H324" s="27" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="I324" s="27" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="K324" s="111"/>
     </row>
     <row r="325" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A325" s="27">
-        <v>10260009</v>
+        <v>10260010</v>
       </c>
       <c r="B325" s="27">
         <v>102600</v>
       </c>
       <c r="C325" s="27" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D325" s="27" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E325" s="27" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="F325" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G325" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="H325" s="27" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I325" s="27" t="s">
-        <v>291</v>
+        <v>106</v>
       </c>
       <c r="K325" s="111"/>
     </row>
-    <row r="326" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A326" s="27">
-        <v>10260010</v>
-      </c>
-      <c r="B326" s="27">
-        <v>102600</v>
-      </c>
-      <c r="C326" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D326" s="27" t="s">
+    <row r="326" s="20" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A326" s="20">
+        <v>10500001</v>
+      </c>
+      <c r="B326" s="20">
+        <v>105000</v>
+      </c>
+      <c r="C326" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="D326" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="E326" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="F326" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G326" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="I326" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="K326" s="111"/>
+      <c r="E326" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F326" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G326" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="H326" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="I326" s="20" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="327" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A327" s="20">
-        <v>10500001</v>
+        <v>10500002</v>
       </c>
       <c r="B327" s="20">
         <v>105000</v>
       </c>
       <c r="C327" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="D327" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="E327" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F327" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G327" s="20" t="s">
+        <v>554</v>
+      </c>
+      <c r="H327" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="D327" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="E327" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F327" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G327" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="H327" s="20" t="s">
-        <v>553</v>
-      </c>
       <c r="I327" s="20" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A328" s="20">
-        <v>10500002</v>
+        <v>10500003</v>
       </c>
       <c r="B328" s="20">
         <v>105000</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D328" s="20" t="s">
         <v>425</v>
@@ -13111,24 +13107,24 @@
         <v>133</v>
       </c>
       <c r="G328" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H328" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I328" s="20" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
     </row>
     <row r="329" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A329" s="20">
-        <v>10500003</v>
+        <v>10500004</v>
       </c>
       <c r="B329" s="20">
         <v>105000</v>
       </c>
       <c r="C329" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D329" s="20" t="s">
         <v>425</v>
@@ -13140,68 +13136,68 @@
         <v>133</v>
       </c>
       <c r="G329" s="20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H329" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I329" s="20" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A330" s="20">
-        <v>10500004</v>
+        <v>10500005</v>
       </c>
       <c r="B330" s="20">
         <v>105000</v>
       </c>
       <c r="C330" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="D330" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="E330" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="D330" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="E330" s="20" t="s">
-        <v>143</v>
-      </c>
       <c r="F330" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G330" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="H330" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I330" s="20" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="331" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A331" s="20">
-        <v>10500005</v>
+        <v>10500006</v>
       </c>
       <c r="B331" s="20">
         <v>105000</v>
       </c>
       <c r="C331" s="20" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D331" s="20" t="s">
         <v>422</v>
       </c>
       <c r="E331" s="20" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F331" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G331" s="20" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H331" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I331" s="20" t="s">
         <v>333</v>
@@ -13209,48 +13205,48 @@
     </row>
     <row r="332" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A332" s="20">
-        <v>10500006</v>
+        <v>10500007</v>
       </c>
       <c r="B332" s="20">
         <v>105000</v>
       </c>
       <c r="C332" s="20" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D332" s="20" t="s">
         <v>422</v>
       </c>
       <c r="E332" s="20" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F332" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G332" s="20" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H332" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I332" s="20" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="333" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A333" s="20">
-        <v>10500007</v>
+        <v>10500008</v>
       </c>
       <c r="B333" s="20">
         <v>105000</v>
       </c>
       <c r="C333" s="20" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D333" s="20" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E333" s="20" t="s">
-        <v>563</v>
+        <v>275</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>133</v>
@@ -13259,108 +13255,109 @@
         <v>564</v>
       </c>
       <c r="H333" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I333" s="20" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
     </row>
     <row r="334" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A334" s="20">
-        <v>10500008</v>
+        <v>10500009</v>
       </c>
       <c r="B334" s="20">
         <v>105000</v>
       </c>
       <c r="C334" s="20" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D334" s="20" t="s">
-        <v>425</v>
+        <v>565</v>
       </c>
       <c r="E334" s="20" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F334" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G334" s="20" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="H334" s="20" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I334" s="20" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
     </row>
     <row r="335" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A335" s="20">
-        <v>10500009</v>
+        <v>10500010</v>
       </c>
       <c r="B335" s="20">
         <v>105000</v>
       </c>
       <c r="C335" s="20" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D335" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="E335" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="F335" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G335" s="20" t="s">
+        <v>550</v>
+      </c>
+      <c r="I335" s="20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="336" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A336" s="33">
+        <v>10510001</v>
+      </c>
+      <c r="B336" s="33">
+        <v>105100</v>
+      </c>
+      <c r="C336" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="E335" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F335" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G335" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="H335" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="I335" s="20" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="336" s="20" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A336" s="20">
-        <v>10500010</v>
-      </c>
-      <c r="B336" s="20">
-        <v>105000</v>
-      </c>
-      <c r="C336" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="D336" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="E336" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="F336" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G336" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="I336" s="20" t="s">
-        <v>106</v>
-      </c>
+      <c r="D336" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="E336" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F336" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G336" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H336" s="33" t="s">
+        <v>568</v>
+      </c>
+      <c r="I336" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K336" s="82"/>
     </row>
     <row r="337" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A337" s="33">
-        <v>10510001</v>
+        <v>10510002</v>
       </c>
       <c r="B337" s="33">
         <v>105100</v>
       </c>
       <c r="C337" s="33" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E337" s="33" t="s">
         <v>41</v>
@@ -13369,10 +13366,10 @@
         <v>133</v>
       </c>
       <c r="G337" s="33" t="s">
-        <v>25</v>
+        <v>344</v>
       </c>
       <c r="H337" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I337" s="33" t="s">
         <v>39</v>
@@ -13381,13 +13378,13 @@
     </row>
     <row r="338" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A338" s="33">
-        <v>10510002</v>
+        <v>10510003</v>
       </c>
       <c r="B338" s="33">
         <v>105100</v>
       </c>
       <c r="C338" s="33" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D338" s="33" t="s">
         <v>570</v>
@@ -13399,10 +13396,10 @@
         <v>133</v>
       </c>
       <c r="G338" s="33" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="H338" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I338" s="33" t="s">
         <v>39</v>
@@ -13411,28 +13408,28 @@
     </row>
     <row r="339" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A339" s="33">
-        <v>10510003</v>
+        <v>10510004</v>
       </c>
       <c r="B339" s="33">
         <v>105100</v>
       </c>
       <c r="C339" s="33" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D339" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E339" s="33" t="s">
-        <v>41</v>
+        <v>573</v>
       </c>
       <c r="F339" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G339" s="33" t="s">
-        <v>460</v>
+        <v>25</v>
       </c>
       <c r="H339" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I339" s="33" t="s">
         <v>39</v>
@@ -13441,28 +13438,28 @@
     </row>
     <row r="340" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A340" s="33">
-        <v>10510004</v>
+        <v>10510005</v>
       </c>
       <c r="B340" s="33">
         <v>105100</v>
       </c>
       <c r="C340" s="33" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D340" s="33" t="s">
+        <v>574</v>
+      </c>
+      <c r="E340" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="E340" s="33" t="s">
-        <v>574</v>
-      </c>
       <c r="F340" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G340" s="33" t="s">
-        <v>25</v>
+        <v>344</v>
       </c>
       <c r="H340" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I340" s="33" t="s">
         <v>39</v>
@@ -13471,28 +13468,28 @@
     </row>
     <row r="341" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A341" s="33">
-        <v>10510005</v>
+        <v>10510006</v>
       </c>
       <c r="B341" s="33">
         <v>105100</v>
       </c>
       <c r="C341" s="33" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D341" s="33" t="s">
         <v>575</v>
       </c>
       <c r="E341" s="33" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F341" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G341" s="33" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="H341" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I341" s="33" t="s">
         <v>39</v>
@@ -13501,67 +13498,67 @@
     </row>
     <row r="342" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A342" s="33">
-        <v>10510006</v>
+        <v>10510007</v>
       </c>
       <c r="B342" s="33">
         <v>105100</v>
       </c>
       <c r="C342" s="33" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="E342" s="33" t="s">
-        <v>574</v>
+        <v>36</v>
       </c>
       <c r="F342" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G342" s="33" t="s">
-        <v>460</v>
+        <v>25</v>
       </c>
       <c r="H342" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I342" s="33" t="s">
-        <v>39</v>
+        <v>577</v>
       </c>
       <c r="K342" s="82"/>
     </row>
     <row r="343" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A343" s="33">
-        <v>10510007</v>
+        <v>10510008</v>
       </c>
       <c r="B343" s="33">
         <v>105100</v>
       </c>
       <c r="C343" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="D343" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="E343" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F343" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G343" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="H343" s="33" t="s">
+        <v>568</v>
+      </c>
+      <c r="I343" s="33" t="s">
         <v>577</v>
-      </c>
-      <c r="D343" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="E343" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F343" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G343" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="H343" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="I343" s="33" t="s">
-        <v>578</v>
       </c>
       <c r="K343" s="82"/>
     </row>
     <row r="344" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A344" s="33">
-        <v>10510008</v>
+        <v>10510009</v>
       </c>
       <c r="B344" s="33">
         <v>105100</v>
@@ -13573,61 +13570,60 @@
         <v>570</v>
       </c>
       <c r="E344" s="33" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F344" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G344" s="33" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="H344" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I344" s="33" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K344" s="82"/>
     </row>
-    <row r="345" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A345" s="33">
-        <v>10510009</v>
-      </c>
-      <c r="B345" s="33">
-        <v>105100</v>
-      </c>
-      <c r="C345" s="33" t="s">
+    <row r="345" s="27" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A345" s="27">
+        <v>10540001</v>
+      </c>
+      <c r="B345" s="27">
+        <v>105400</v>
+      </c>
+      <c r="C345" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="D345" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="E345" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F345" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G345" s="27" t="s">
+        <v>554</v>
+      </c>
+      <c r="H345" s="27" t="s">
         <v>580</v>
       </c>
-      <c r="D345" s="33" t="s">
-        <v>571</v>
-      </c>
-      <c r="E345" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="F345" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G345" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="H345" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="I345" s="33" t="s">
-        <v>578</v>
-      </c>
-      <c r="K345" s="82"/>
+      <c r="I345" s="27" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="346" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A346" s="27">
-        <v>10540001</v>
+        <v>10540002</v>
       </c>
       <c r="B346" s="27">
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D346" s="27" t="s">
         <v>425</v>
@@ -13639,24 +13635,24 @@
         <v>133</v>
       </c>
       <c r="G346" s="27" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H346" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I346" s="27" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
     </row>
     <row r="347" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A347" s="27">
-        <v>10540002</v>
+        <v>10540003</v>
       </c>
       <c r="B347" s="27">
         <v>105400</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D347" s="27" t="s">
         <v>425</v>
@@ -13668,68 +13664,68 @@
         <v>133</v>
       </c>
       <c r="G347" s="27" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H347" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I347" s="27" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
     </row>
     <row r="348" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A348" s="27">
-        <v>10540003</v>
+        <v>10540004</v>
       </c>
       <c r="B348" s="27">
         <v>105400</v>
       </c>
       <c r="C348" s="27" t="s">
-        <v>326</v>
+        <v>581</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>140</v>
+        <v>582</v>
       </c>
       <c r="F348" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G348" s="27" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="H348" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I348" s="27" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="349" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A349" s="27">
-        <v>10540004</v>
+        <v>10540005</v>
       </c>
       <c r="B349" s="27">
         <v>105400</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>582</v>
+        <v>330</v>
       </c>
       <c r="D349" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E349" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="F349" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G349" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="F349" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G349" s="27" t="s">
-        <v>584</v>
-      </c>
       <c r="H349" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I349" s="27" t="s">
         <v>333</v>
@@ -13737,13 +13733,13 @@
     </row>
     <row r="350" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A350" s="27">
-        <v>10540005</v>
+        <v>10540006</v>
       </c>
       <c r="B350" s="27">
         <v>105400</v>
       </c>
       <c r="C350" s="27" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D350" s="27" t="s">
         <v>422</v>
@@ -13755,10 +13751,10 @@
         <v>133</v>
       </c>
       <c r="G350" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H350" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I350" s="27" t="s">
         <v>333</v>
@@ -13766,13 +13762,13 @@
     </row>
     <row r="351" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A351" s="27">
-        <v>10540006</v>
+        <v>10540007</v>
       </c>
       <c r="B351" s="27">
         <v>105400</v>
       </c>
       <c r="C351" s="27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D351" s="27" t="s">
         <v>422</v>
@@ -13784,170 +13780,168 @@
         <v>133</v>
       </c>
       <c r="G351" s="27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H351" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I351" s="27" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="352" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A352" s="27">
-        <v>10540007</v>
+        <v>10540008</v>
       </c>
       <c r="B352" s="27">
         <v>105400</v>
       </c>
       <c r="C352" s="27" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E352" s="27" t="s">
-        <v>587</v>
+        <v>264</v>
       </c>
       <c r="F352" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G352" s="27" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="H352" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I352" s="27" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
     </row>
     <row r="353" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A353" s="27">
-        <v>10540008</v>
+        <v>10540009</v>
       </c>
       <c r="B353" s="27">
         <v>105400</v>
       </c>
       <c r="C353" s="27" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D353" s="27" t="s">
-        <v>425</v>
+        <v>565</v>
       </c>
       <c r="E353" s="27" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="F353" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G353" s="27" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="H353" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I353" s="27" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
     </row>
     <row r="354" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A354" s="27">
-        <v>10540009</v>
+        <v>10540010</v>
       </c>
       <c r="B354" s="27">
         <v>105400</v>
       </c>
       <c r="C354" s="27" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D354" s="27" t="s">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="E354" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="F354" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G354" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="I354" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="355" s="28" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A355" s="28">
+        <v>10080001</v>
+      </c>
+      <c r="B355" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C355" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="D355" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="E355" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="F354" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G354" s="27" t="s">
+      <c r="F355" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G355" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="H355" s="28" t="s">
         <v>588</v>
       </c>
-      <c r="H354" s="27" t="s">
-        <v>581</v>
-      </c>
-      <c r="I354" s="27" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="355" s="27" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A355" s="27">
-        <v>10540010</v>
-      </c>
-      <c r="B355" s="27">
-        <v>105400</v>
-      </c>
-      <c r="C355" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D355" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E355" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="F355" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G355" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="I355" s="27" t="s">
-        <v>106</v>
-      </c>
+      <c r="I355" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="K355" s="112"/>
     </row>
     <row r="356" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A356" s="28">
-        <v>10080001</v>
+        <v>10080002</v>
       </c>
       <c r="B356" s="28">
         <v>100800</v>
       </c>
       <c r="C356" s="28" t="s">
-        <v>503</v>
+        <v>323</v>
       </c>
       <c r="D356" s="28" t="s">
         <v>422</v>
       </c>
       <c r="E356" s="28" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F356" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G356" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="H356" s="28" t="s">
-        <v>589</v>
+        <v>545</v>
       </c>
       <c r="I356" s="28" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K356" s="112"/>
     </row>
     <row r="357" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A357" s="28">
-        <v>10080002</v>
+        <v>10080003</v>
       </c>
       <c r="B357" s="28">
         <v>100800</v>
       </c>
       <c r="C357" s="28" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D357" s="28" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E357" s="28" t="s">
         <v>143</v>
@@ -13956,25 +13950,28 @@
         <v>133</v>
       </c>
       <c r="G357" s="28" t="s">
-        <v>547</v>
+        <v>545</v>
+      </c>
+      <c r="H357" s="28" t="s">
+        <v>588</v>
       </c>
       <c r="I357" s="28" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="K357" s="112"/>
     </row>
     <row r="358" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A358" s="28">
-        <v>10080003</v>
+        <v>10080004</v>
       </c>
       <c r="B358" s="28">
         <v>100800</v>
       </c>
       <c r="C358" s="28" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D358" s="28" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E358" s="28" t="s">
         <v>143</v>
@@ -13983,55 +13980,55 @@
         <v>133</v>
       </c>
       <c r="G358" s="28" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H358" s="28" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I358" s="28" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="K358" s="112"/>
     </row>
     <row r="359" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A359" s="28">
-        <v>10080004</v>
+        <v>10080005</v>
       </c>
       <c r="B359" s="28">
         <v>100800</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D359" s="28" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E359" s="28" t="s">
-        <v>143</v>
+        <v>589</v>
       </c>
       <c r="F359" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G359" s="28" t="s">
-        <v>547</v>
+        <v>464</v>
       </c>
       <c r="H359" s="28" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I359" s="28" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K359" s="112"/>
     </row>
     <row r="360" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A360" s="28">
-        <v>10080005</v>
+        <v>10080006</v>
       </c>
       <c r="B360" s="28">
         <v>100800</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>438</v>
@@ -14043,10 +14040,10 @@
         <v>133</v>
       </c>
       <c r="G360" s="28" t="s">
-        <v>464</v>
+        <v>546</v>
       </c>
       <c r="H360" s="28" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I360" s="28" t="s">
         <v>333</v>
@@ -14055,13 +14052,13 @@
     </row>
     <row r="361" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A361" s="28">
-        <v>10080006</v>
+        <v>10080007</v>
       </c>
       <c r="B361" s="28">
         <v>100800</v>
       </c>
       <c r="C361" s="28" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D361" s="28" t="s">
         <v>438</v>
@@ -14073,28 +14070,28 @@
         <v>133</v>
       </c>
       <c r="G361" s="28" t="s">
-        <v>466</v>
+        <v>547</v>
       </c>
       <c r="H361" s="28" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I361" s="28" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K361" s="112"/>
     </row>
     <row r="362" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A362" s="28">
-        <v>10080007</v>
+        <v>10080008</v>
       </c>
       <c r="B362" s="28">
         <v>100800</v>
       </c>
       <c r="C362" s="28" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D362" s="28" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E362" s="28" t="s">
         <v>592</v>
@@ -14103,115 +14100,115 @@
         <v>133</v>
       </c>
       <c r="G362" s="28" t="s">
-        <v>548</v>
+        <v>341</v>
       </c>
       <c r="H362" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I362" s="28" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K362" s="112"/>
     </row>
     <row r="363" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A363" s="28">
-        <v>10080008</v>
+        <v>10080009</v>
       </c>
       <c r="B363" s="28">
         <v>100800</v>
       </c>
       <c r="C363" s="28" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D363" s="28" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E363" s="28" t="s">
-        <v>593</v>
+        <v>143</v>
       </c>
       <c r="F363" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G363" s="28" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="H363" s="28" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="I363" s="28" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="K363" s="112"/>
     </row>
-    <row r="364" s="28" customFormat="1" ht="16.5" spans="1:12">
+    <row r="364" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A364" s="28">
-        <v>10080009</v>
+        <v>10080010</v>
       </c>
       <c r="B364" s="28">
         <v>100800</v>
       </c>
       <c r="C364" s="28" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D364" s="28" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E364" s="28" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="F364" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G364" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="H364" s="28" t="s">
-        <v>589</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="H364" s="28"/>
       <c r="I364" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="K364" s="112"/>
-    </row>
-    <row r="365" s="27" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A365" s="28">
-        <v>10080010</v>
-      </c>
-      <c r="B365" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C365" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="D365" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E365" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F365" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G365" s="28" t="s">
-        <v>551</v>
-      </c>
-      <c r="H365" s="28"/>
-      <c r="I365" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="J365" s="28"/>
-      <c r="K365" s="28"/>
-      <c r="L365" s="28"/>
+      <c r="J364" s="28"/>
+      <c r="K364" s="28"/>
+      <c r="L364" s="28"/>
+    </row>
+    <row r="365" s="29" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A365" s="29">
+        <v>10530001</v>
+      </c>
+      <c r="B365" s="29">
+        <v>105300</v>
+      </c>
+      <c r="C365" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="D365" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E365" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="F365" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G365" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="H365" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="I365" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="K365" s="113"/>
     </row>
     <row r="366" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A366" s="29">
-        <v>10530001</v>
+        <v>10530002</v>
       </c>
       <c r="B366" s="29">
         <v>105300</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D366" s="29" t="s">
         <v>21</v>
@@ -14223,28 +14220,28 @@
         <v>133</v>
       </c>
       <c r="G366" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="H366" s="29" t="s">
         <v>596</v>
       </c>
-      <c r="H366" s="29" t="s">
-        <v>597</v>
-      </c>
       <c r="I366" s="29" t="s">
-        <v>340</v>
+        <v>598</v>
       </c>
       <c r="K366" s="113"/>
     </row>
     <row r="367" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A367" s="29">
-        <v>10530002</v>
+        <v>10530003</v>
       </c>
       <c r="B367" s="29">
         <v>105300</v>
       </c>
       <c r="C367" s="29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D367" s="29" t="s">
-        <v>21</v>
+        <v>565</v>
       </c>
       <c r="E367" s="29" t="s">
         <v>136</v>
@@ -14253,118 +14250,118 @@
         <v>133</v>
       </c>
       <c r="G367" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="H367" s="29" t="s">
         <v>596</v>
       </c>
-      <c r="H367" s="29" t="s">
-        <v>597</v>
-      </c>
       <c r="I367" s="29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K367" s="113"/>
     </row>
     <row r="368" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A368" s="29">
-        <v>10530003</v>
+        <v>10530004</v>
       </c>
       <c r="B368" s="29">
         <v>105300</v>
       </c>
       <c r="C368" s="29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D368" s="29" t="s">
-        <v>566</v>
+        <v>328</v>
       </c>
       <c r="E368" s="29" t="s">
-        <v>136</v>
+        <v>602</v>
       </c>
       <c r="F368" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G368" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="H368" s="29" t="s">
         <v>596</v>
       </c>
-      <c r="H368" s="29" t="s">
-        <v>597</v>
-      </c>
       <c r="I368" s="29" t="s">
-        <v>601</v>
+        <v>294</v>
       </c>
       <c r="K368" s="113"/>
     </row>
     <row r="369" s="29" customFormat="1" ht="16.5" spans="1:11">
       <c r="A369" s="29">
-        <v>10530004</v>
+        <v>10530006</v>
       </c>
       <c r="B369" s="29">
         <v>105300</v>
       </c>
       <c r="C369" s="29" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D369" s="29" t="s">
         <v>328</v>
       </c>
       <c r="E369" s="29" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F369" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G369" s="29" t="s">
-        <v>604</v>
+        <v>353</v>
       </c>
       <c r="H369" s="29" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="I369" s="29" t="s">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="K369" s="113"/>
     </row>
-    <row r="370" s="29" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A370" s="29">
-        <v>10530006</v>
-      </c>
-      <c r="B370" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C370" s="29" t="s">
-        <v>605</v>
-      </c>
-      <c r="D370" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="E370" s="29" t="s">
-        <v>603</v>
-      </c>
-      <c r="F370" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G370" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="H370" s="29" t="s">
+    <row r="370" s="30" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A370" s="30">
+        <v>10570001</v>
+      </c>
+      <c r="B370" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C370" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D370" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="E370" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F370" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G370" s="30" t="s">
         <v>606</v>
       </c>
-      <c r="I370" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="K370" s="113"/>
+      <c r="H370" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="I370" s="30" t="s">
+        <v>600</v>
+      </c>
+      <c r="K370" s="114"/>
     </row>
     <row r="371" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A371" s="30">
-        <v>10570001</v>
+        <v>10570002</v>
       </c>
       <c r="B371" s="30">
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D371" s="30" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E371" s="30" t="s">
         <v>114</v>
@@ -14373,25 +14370,25 @@
         <v>133</v>
       </c>
       <c r="G371" s="30" t="s">
+        <v>606</v>
+      </c>
+      <c r="H371" s="30" t="s">
         <v>607</v>
       </c>
-      <c r="H371" s="30" t="s">
-        <v>608</v>
-      </c>
       <c r="I371" s="30" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K371" s="114"/>
     </row>
     <row r="372" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A372" s="30">
-        <v>10570002</v>
+        <v>10570003</v>
       </c>
       <c r="B372" s="30">
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>415</v>
+        <v>608</v>
       </c>
       <c r="D372" s="30" t="s">
         <v>328</v>
@@ -14403,19 +14400,19 @@
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
+        <v>606</v>
+      </c>
+      <c r="H372" s="30" t="s">
         <v>607</v>
       </c>
-      <c r="H372" s="30" t="s">
-        <v>608</v>
-      </c>
       <c r="I372" s="30" t="s">
-        <v>599</v>
+        <v>340</v>
       </c>
       <c r="K372" s="114"/>
     </row>
     <row r="373" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A373" s="30">
-        <v>10570003</v>
+        <v>10570004</v>
       </c>
       <c r="B373" s="30">
         <v>105700</v>
@@ -14427,67 +14424,67 @@
         <v>328</v>
       </c>
       <c r="E373" s="30" t="s">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="F373" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G373" s="30" t="s">
+        <v>611</v>
+      </c>
+      <c r="H373" s="30" t="s">
         <v>607</v>
       </c>
-      <c r="H373" s="30" t="s">
-        <v>608</v>
-      </c>
       <c r="I373" s="30" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="K373" s="114"/>
     </row>
     <row r="374" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A374" s="30">
-        <v>10570004</v>
+        <v>10570005</v>
       </c>
       <c r="B374" s="30">
         <v>105700</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>610</v>
+        <v>253</v>
       </c>
       <c r="D374" s="30" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E374" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F374" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G374" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H374" s="30" t="s">
-        <v>608</v>
+        <v>455</v>
       </c>
       <c r="I374" s="30" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K374" s="114"/>
     </row>
     <row r="375" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A375" s="30">
-        <v>10570005</v>
+        <v>10570006</v>
       </c>
       <c r="B375" s="30">
         <v>105700</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D375" s="30" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E375" s="30" t="s">
-        <v>613</v>
+        <v>257</v>
       </c>
       <c r="F375" s="30" t="s">
         <v>133</v>
@@ -14495,53 +14492,53 @@
       <c r="G375" s="30" t="s">
         <v>614</v>
       </c>
-      <c r="H375" s="30" t="s">
-        <v>455</v>
-      </c>
       <c r="I375" s="30" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K375" s="114"/>
     </row>
-    <row r="376" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A376" s="30">
-        <v>10570006</v>
-      </c>
-      <c r="B376" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C376" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="D376" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E376" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="F376" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G376" s="30" t="s">
+    <row r="376" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A376" s="31">
+        <v>10580001</v>
+      </c>
+      <c r="B376" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C376" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D376" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="E376" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F376" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G376" s="31" t="s">
         <v>615</v>
       </c>
-      <c r="I376" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="K376" s="114"/>
+      <c r="H376" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="I376" s="31" t="s">
+        <v>600</v>
+      </c>
+      <c r="K376" s="115"/>
     </row>
     <row r="377" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A377" s="31">
-        <v>10580001</v>
+        <v>10580002</v>
       </c>
       <c r="B377" s="31">
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="D377" s="31" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E377" s="31" t="s">
         <v>299</v>
@@ -14550,25 +14547,25 @@
         <v>133</v>
       </c>
       <c r="G377" s="31" t="s">
+        <v>615</v>
+      </c>
+      <c r="H377" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="H377" s="31" t="s">
-        <v>617</v>
-      </c>
       <c r="I377" s="31" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K377" s="115"/>
     </row>
     <row r="378" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A378" s="31">
-        <v>10580002</v>
+        <v>10580003</v>
       </c>
       <c r="B378" s="31">
         <v>105800</v>
       </c>
       <c r="C378" s="31" t="s">
-        <v>259</v>
+        <v>608</v>
       </c>
       <c r="D378" s="31" t="s">
         <v>328</v>
@@ -14580,163 +14577,163 @@
         <v>133</v>
       </c>
       <c r="G378" s="31" t="s">
+        <v>615</v>
+      </c>
+      <c r="H378" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="H378" s="31" t="s">
-        <v>617</v>
-      </c>
       <c r="I378" s="31" t="s">
-        <v>599</v>
+        <v>340</v>
       </c>
       <c r="K378" s="115"/>
     </row>
     <row r="379" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A379" s="31">
-        <v>10580003</v>
+        <v>10580004</v>
       </c>
       <c r="B379" s="31">
         <v>105800</v>
       </c>
       <c r="C379" s="31" t="s">
-        <v>609</v>
+        <v>253</v>
       </c>
       <c r="D379" s="31" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E379" s="31" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="F379" s="31" t="s">
         <v>133</v>
       </c>
       <c r="G379" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="H379" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="H379" s="31" t="s">
-        <v>617</v>
-      </c>
       <c r="I379" s="31" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K379" s="115"/>
     </row>
-    <row r="380" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A380" s="31">
-        <v>10580004</v>
-      </c>
-      <c r="B380" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C380" s="31" t="s">
+    <row r="380" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A380" s="32">
+        <v>10550001</v>
+      </c>
+      <c r="B380" s="32">
+        <v>105500</v>
+      </c>
+      <c r="C380" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D380" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E380" s="31" t="s">
+      <c r="D380" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E380" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F380" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G380" s="31" t="s">
+      <c r="F380" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G380" s="32" t="s">
         <v>618</v>
       </c>
-      <c r="H380" s="31" t="s">
-        <v>617</v>
-      </c>
-      <c r="I380" s="31" t="s">
+      <c r="I380" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K380" s="115"/>
+      <c r="K380" s="116"/>
     </row>
     <row r="381" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A381" s="32">
-        <v>10550001</v>
+        <v>10550002</v>
       </c>
       <c r="B381" s="32">
         <v>105500</v>
       </c>
       <c r="C381" s="32" t="s">
-        <v>253</v>
+        <v>619</v>
       </c>
       <c r="D381" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E381" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F381" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G381" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I381" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K381" s="116"/>
     </row>
-    <row r="382" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A382" s="32">
-        <v>10550002</v>
-      </c>
-      <c r="B382" s="32">
-        <v>105500</v>
-      </c>
-      <c r="C382" s="32" t="s">
+    <row r="382" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A382" s="33">
+        <v>10480001</v>
+      </c>
+      <c r="B382" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C382" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="D382" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E382" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F382" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G382" s="33" t="s">
         <v>620</v>
       </c>
-      <c r="D382" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E382" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="F382" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G382" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I382" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K382" s="116"/>
+      <c r="H382" s="33" t="s">
+        <v>621</v>
+      </c>
+      <c r="I382" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="K382" s="82"/>
     </row>
     <row r="383" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A383" s="33">
-        <v>10480001</v>
+        <v>10480002</v>
       </c>
       <c r="B383" s="33">
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>503</v>
+        <v>622</v>
       </c>
       <c r="D383" s="33" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E383" s="33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F383" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G383" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="H383" s="33" t="s">
         <v>621</v>
       </c>
-      <c r="H383" s="33" t="s">
-        <v>622</v>
-      </c>
       <c r="I383" s="33" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K383" s="82"/>
     </row>
     <row r="384" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A384" s="33">
-        <v>10480002</v>
+        <v>10480003</v>
       </c>
       <c r="B384" s="33">
         <v>104800</v>
@@ -14757,16 +14754,16 @@
         <v>460</v>
       </c>
       <c r="H384" s="33" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K384" s="82"/>
     </row>
     <row r="385" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A385" s="33">
-        <v>10480003</v>
+        <v>10480004</v>
       </c>
       <c r="B385" s="33">
         <v>104800</v>
@@ -14775,7 +14772,7 @@
         <v>624</v>
       </c>
       <c r="D385" s="33" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E385" s="33" t="s">
         <v>143</v>
@@ -14787,25 +14784,25 @@
         <v>460</v>
       </c>
       <c r="H385" s="33" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I385" s="33" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="K385" s="82"/>
     </row>
     <row r="386" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A386" s="33">
-        <v>10480004</v>
+        <v>10480005</v>
       </c>
       <c r="B386" s="33">
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>625</v>
+        <v>289</v>
       </c>
       <c r="D386" s="33" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E386" s="33" t="s">
         <v>143</v>
@@ -14817,52 +14814,52 @@
         <v>460</v>
       </c>
       <c r="H386" s="33" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I386" s="33" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K386" s="82"/>
     </row>
     <row r="387" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A387" s="33">
-        <v>10480005</v>
+        <v>10480006</v>
       </c>
       <c r="B387" s="33">
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="D387" s="33" t="s">
         <v>422</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>143</v>
+        <v>625</v>
       </c>
       <c r="F387" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G387" s="33" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H387" s="33" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I387" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="K387" s="82"/>
+        <v>333</v>
+      </c>
+      <c r="K387" s="117"/>
     </row>
     <row r="388" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A388" s="33">
-        <v>10480006</v>
+        <v>10480007</v>
       </c>
       <c r="B388" s="33">
         <v>104800</v>
       </c>
       <c r="C388" s="33" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D388" s="33" t="s">
         <v>422</v>
@@ -14874,10 +14871,10 @@
         <v>133</v>
       </c>
       <c r="G388" s="33" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H388" s="33" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I388" s="33" t="s">
         <v>333</v>
@@ -14886,139 +14883,136 @@
     </row>
     <row r="389" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A389" s="33">
-        <v>10480007</v>
+        <v>10480008</v>
       </c>
       <c r="B389" s="33">
         <v>104800</v>
       </c>
       <c r="C389" s="33" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="D389" s="33" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E389" s="33" t="s">
-        <v>627</v>
+        <v>254</v>
       </c>
       <c r="F389" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G389" s="33" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="H389" s="33" t="s">
-        <v>622</v>
+        <v>408</v>
       </c>
       <c r="I389" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K389" s="117"/>
-    </row>
-    <row r="390" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A390" s="33">
-        <v>10480008</v>
-      </c>
-      <c r="B390" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C390" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K389" s="82"/>
+    </row>
+    <row r="390" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A390" s="32">
+        <v>10550101</v>
+      </c>
+      <c r="B390" s="32">
+        <v>105501</v>
+      </c>
+      <c r="C390" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D390" s="33" t="s">
+      <c r="D390" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E390" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F390" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G390" s="33" t="s">
-        <v>469</v>
-      </c>
-      <c r="H390" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="I390" s="33" t="s">
+      <c r="E390" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F390" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G390" s="32" t="s">
+        <v>618</v>
+      </c>
+      <c r="I390" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K390" s="82"/>
+      <c r="K390" s="116"/>
     </row>
     <row r="391" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A391" s="32">
-        <v>10550101</v>
+        <v>10550102</v>
       </c>
       <c r="B391" s="32">
         <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>253</v>
+        <v>619</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F391" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I391" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K391" s="116"/>
     </row>
     <row r="392" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A392" s="32">
-        <v>10550102</v>
+        <v>10550103</v>
       </c>
       <c r="B392" s="32">
         <v>105501</v>
       </c>
       <c r="C392" s="32" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="D392" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="F392" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>297</v>
+        <v>618</v>
       </c>
       <c r="I392" s="32" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K392" s="116"/>
     </row>
     <row r="393" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A393" s="32">
-        <v>10550103</v>
+        <v>10550201</v>
       </c>
       <c r="B393" s="32">
-        <v>105501</v>
+        <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>628</v>
+        <v>253</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="F393" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G393" s="32" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I393" s="32" t="s">
         <v>39</v>
@@ -15027,46 +15021,46 @@
     </row>
     <row r="394" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A394" s="32">
-        <v>10550201</v>
+        <v>10550202</v>
       </c>
       <c r="B394" s="32">
         <v>105502</v>
       </c>
       <c r="C394" s="32" t="s">
-        <v>253</v>
+        <v>619</v>
       </c>
       <c r="D394" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F394" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G394" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I394" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K394" s="116"/>
     </row>
-    <row r="395" s="32" customFormat="1" ht="16.5" spans="1:11">
+    <row r="395" ht="16.5" spans="1:11">
       <c r="A395" s="32">
-        <v>10550202</v>
+        <v>10550203</v>
       </c>
       <c r="B395" s="32">
         <v>105502</v>
       </c>
       <c r="C395" s="32" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="D395" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="F395" s="32" t="s">
         <v>133</v>
@@ -15075,78 +15069,81 @@
         <v>297</v>
       </c>
       <c r="I395" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K395" s="116"/>
-    </row>
-    <row r="396" ht="16.5" spans="1:11">
-      <c r="A396" s="32">
-        <v>10550203</v>
-      </c>
-      <c r="B396" s="32">
-        <v>105502</v>
-      </c>
-      <c r="C396" s="32" t="s">
-        <v>629</v>
-      </c>
-      <c r="D396" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E396" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="F396" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G396" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I396" s="32" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="396" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A396" s="34">
+        <v>10410001</v>
+      </c>
+      <c r="B396" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C396" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="D396" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="E396" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="F396" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G396" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H396" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="I396" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="K396" s="118"/>
     </row>
     <row r="397" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A397" s="34">
-        <v>10410001</v>
+        <v>10410002</v>
       </c>
       <c r="B397" s="34">
         <v>104100</v>
       </c>
       <c r="C397" s="34" t="s">
-        <v>313</v>
+        <v>555</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E397" s="34" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="F397" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="H397" s="34" t="s">
         <v>455</v>
       </c>
       <c r="I397" s="34" t="s">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="K397" s="118"/>
     </row>
     <row r="398" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A398" s="34">
-        <v>10410002</v>
+        <v>10410003</v>
       </c>
       <c r="B398" s="34">
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E398" s="34" t="s">
         <v>114</v>
@@ -15161,115 +15158,115 @@
         <v>455</v>
       </c>
       <c r="I398" s="34" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K398" s="118"/>
     </row>
     <row r="399" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A399" s="34">
-        <v>10410003</v>
+        <v>10410004</v>
       </c>
       <c r="B399" s="34">
         <v>104100</v>
       </c>
       <c r="C399" s="34" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="D399" s="34" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E399" s="34" t="s">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="F399" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G399" s="34" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H399" s="34" t="s">
-        <v>455</v>
+        <v>629</v>
       </c>
       <c r="I399" s="34" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K399" s="118"/>
     </row>
     <row r="400" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A400" s="34">
-        <v>10410004</v>
+        <v>10410005</v>
       </c>
       <c r="B400" s="34">
         <v>104100</v>
       </c>
       <c r="C400" s="34" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D400" s="34" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E400" s="34" t="s">
-        <v>416</v>
+        <v>114</v>
       </c>
       <c r="F400" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G400" s="34" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H400" s="34" t="s">
-        <v>630</v>
+        <v>455</v>
       </c>
       <c r="I400" s="34" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K400" s="118"/>
     </row>
-    <row r="401" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A401" s="34">
-        <v>10410005</v>
-      </c>
-      <c r="B401" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C401" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D401" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E401" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F401" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G401" s="34" t="s">
+    <row r="401" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A401" s="35">
+        <v>10420001</v>
+      </c>
+      <c r="B401" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C401" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="D401" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="E401" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F401" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G401" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="H401" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I401" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="K401" s="118"/>
+      <c r="H401" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="I401" s="35" t="s">
+        <v>544</v>
+      </c>
+      <c r="K401" s="119"/>
     </row>
     <row r="402" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A402" s="35">
-        <v>10420001</v>
+        <v>10420002</v>
       </c>
       <c r="B402" s="35">
         <v>104200</v>
       </c>
       <c r="C402" s="35" t="s">
-        <v>313</v>
+        <v>555</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E402" s="35" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F402" s="35" t="s">
         <v>133</v>
@@ -15278,25 +15275,25 @@
         <v>234</v>
       </c>
       <c r="H402" s="35" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I402" s="35" t="s">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="K402" s="119"/>
     </row>
     <row r="403" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A403" s="35">
-        <v>10420002</v>
+        <v>10420003</v>
       </c>
       <c r="B403" s="35">
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E403" s="35" t="s">
         <v>143</v>
@@ -15308,102 +15305,72 @@
         <v>234</v>
       </c>
       <c r="H403" s="35" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I403" s="35" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K403" s="119"/>
     </row>
     <row r="404" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A404" s="35">
-        <v>10420003</v>
+        <v>10420004</v>
       </c>
       <c r="B404" s="35">
         <v>104200</v>
       </c>
       <c r="C404" s="35" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="D404" s="35" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E404" s="35" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F404" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G404" s="35" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H404" s="35" t="s">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="I404" s="35" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K404" s="119"/>
     </row>
     <row r="405" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A405" s="35">
-        <v>10420004</v>
+        <v>10420005</v>
       </c>
       <c r="B405" s="35">
         <v>104200</v>
       </c>
       <c r="C405" s="35" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D405" s="35" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E405" s="35" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F405" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G405" s="35" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H405" s="35" t="s">
-        <v>594</v>
+        <v>549</v>
       </c>
       <c r="I405" s="35" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K405" s="119"/>
-    </row>
-    <row r="406" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A406" s="35">
-        <v>10420005</v>
-      </c>
-      <c r="B406" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C406" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="D406" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="E406" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F406" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G406" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H406" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I406" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="K406" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15423,24 +15390,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D1" t="s">
         <v>631</v>
-      </c>
-      <c r="D1" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B2" t="s">
         <v>633</v>
       </c>
-      <c r="B2" t="s">
-        <v>634</v>
-      </c>
       <c r="D2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E2" t="s">
         <v>633</v>
-      </c>
-      <c r="E2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15448,16 +15415,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F3" t="s">
         <v>636</v>
-      </c>
-      <c r="F3" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15465,16 +15432,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>638</v>
+      </c>
+      <c r="F4" t="s">
         <v>639</v>
-      </c>
-      <c r="F4" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15482,16 +15449,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
+        <v>641</v>
+      </c>
+      <c r="F5" t="s">
         <v>642</v>
-      </c>
-      <c r="F5" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15499,7 +15466,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15507,7 +15474,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15515,7 +15482,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15523,7 +15490,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15531,7 +15498,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15539,7 +15506,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15547,7 +15514,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15555,7 +15522,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15563,7 +15530,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15571,7 +15538,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15579,7 +15546,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15587,7 +15554,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15595,7 +15562,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15603,7 +15570,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15611,7 +15578,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15619,7 +15586,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15627,7 +15594,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15635,7 +15602,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15643,7 +15610,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -15651,7 +15618,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -15659,7 +15626,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -15667,7 +15634,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -15675,7 +15642,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -15683,7 +15650,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -15691,7 +15658,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -15699,7 +15666,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -15707,7 +15674,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -15715,7 +15682,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -15723,7 +15690,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -15731,7 +15698,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -15739,7 +15706,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -15747,7 +15714,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -15755,7 +15722,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -15763,7 +15730,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -15771,7 +15738,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -15779,7 +15746,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -15787,7 +15754,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -15795,7 +15762,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -15803,7 +15770,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -15811,7 +15778,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15819,7 +15786,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -15827,7 +15794,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -15835,7 +15802,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2828" uniqueCount="702">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1465,345 +1465,345 @@
     <t>3_90|4_10</t>
   </si>
   <si>
+    <t>0_2000|1_500|2_200|3_1</t>
+  </si>
+  <si>
+    <t>前四轴改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>概率在第一轴上改出bonus</t>
+  </si>
+  <si>
+    <t>常规&amp;免费模式</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1</t>
+  </si>
+  <si>
+    <t>在第一轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>在第五轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>第五轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>概率在第五轴上改出bonus</t>
+  </si>
+  <si>
+    <t>概率在第二三四轴改出18符号</t>
+  </si>
+  <si>
+    <t>11_12_18</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>1_20|2_20|3_20|4_20|5_10|6_6|7_4</t>
+  </si>
+  <si>
+    <t>在第二轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>在第三轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>在第四轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率在第二轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率第三轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率第四轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>0_30|1_1</t>
+  </si>
+  <si>
+    <t>9_10_11_12_13_14</t>
+  </si>
+  <si>
+    <t>改出百搭符号</t>
+  </si>
+  <si>
+    <t>5_9_10_11_12_13_14</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1</t>
+  </si>
+  <si>
+    <t>8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1</t>
+  </si>
+  <si>
+    <t>9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>概率改出免费+1符号</t>
+  </si>
+  <si>
+    <t>0_9|1_1</t>
+  </si>
+  <si>
+    <t>31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>改出黄金10符号</t>
+  </si>
+  <si>
+    <t>87_1</t>
+  </si>
+  <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金J符号</t>
+  </si>
+  <si>
+    <t>88_1</t>
+  </si>
+  <si>
+    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金Q符号</t>
+  </si>
+  <si>
+    <t>89_1</t>
+  </si>
+  <si>
+    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金K符号</t>
+  </si>
+  <si>
+    <t>90_1</t>
+  </si>
+  <si>
+    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金A符号</t>
+  </si>
+  <si>
+    <t>91_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金罗纳尔多</t>
+  </si>
+  <si>
+    <t>92_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金格列兹曼</t>
+  </si>
+  <si>
+    <t>93_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金内马尔</t>
+  </si>
+  <si>
+    <t>94_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金斯特林</t>
+  </si>
+  <si>
+    <t>95_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金C罗</t>
+  </si>
+  <si>
+    <t>96_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>改出黄金梅西</t>
+  </si>
+  <si>
+    <t>97_1</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号</t>
+  </si>
+  <si>
+    <t>13_14_15_16_17_18_19_20_21_22</t>
+  </si>
+  <si>
     <t>0_50|1_30|2_15|3_4|4_1</t>
   </si>
   <si>
-    <t>前四轴改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>概率在第一轴上改出bonus</t>
-  </si>
-  <si>
-    <t>常规&amp;免费模式</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1</t>
-  </si>
-  <si>
-    <t>在第一轴改出1个bonus</t>
-  </si>
-  <si>
-    <t>在第五轴改出1个bonus</t>
-  </si>
-  <si>
-    <t>第五轴改出奖池符号</t>
-  </si>
-  <si>
-    <t>概率在第五轴上改出bonus</t>
-  </si>
-  <si>
-    <t>概率在第二三四轴改出18符号</t>
-  </si>
-  <si>
-    <t>11_12_18</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>1_20|2_20|3_20|4_20|5_10|6_6|7_4</t>
-  </si>
-  <si>
-    <t>在第二轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>在第三轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>在第四轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率在第二轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率第三轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率第四轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>0_30|1_1</t>
-  </si>
-  <si>
-    <t>9_10_11_12_13_14</t>
-  </si>
-  <si>
-    <t>改出百搭符号</t>
-  </si>
-  <si>
-    <t>5_9_10_11_12_13_14</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
-  </si>
-  <si>
-    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1|65_1</t>
-  </si>
-  <si>
-    <t>8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|66_1|67_1|68_1|69_1|70_1|71_1|72_1|73_1|74_1|75_1|76_1</t>
-  </si>
-  <si>
-    <t>9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1|77_1|78_1|79_1|80_1|81_1|82_1|83_1|84_1|85_1|86_1|87_1</t>
+    <t>改出20符号</t>
+  </si>
+  <si>
+    <t>改出21符号</t>
+  </si>
+  <si>
+    <t>改出22符号</t>
+  </si>
+  <si>
+    <t>16_10|17_5|18_2|19_1</t>
+  </si>
+  <si>
+    <t>第1轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第2轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第3轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第4轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第5轴改出3个wild</t>
+  </si>
+  <si>
+    <t>第1、2轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1</t>
+  </si>
+  <si>
+    <t>第1、3轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第1、4轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第1、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第2、3轴改出6个wild</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第2、4轴改出6个wild</t>
+  </si>
+  <si>
+    <t>第2、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第3、4轴改出6个wild</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第3、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第4、5轴改出6个wild</t>
+  </si>
+  <si>
+    <t>10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第1、2、3轴改出9个wild</t>
+  </si>
+  <si>
+    <t>第1、2、4轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第1、2、5轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第1、3、4轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>第1、3、5轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>第1、4、5轴改出9个wild</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出+1免费符号</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119</t>
+  </si>
+  <si>
+    <t>0_70|1_20|2_9|3_1</t>
+  </si>
+  <si>
+    <t>2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
   </si>
   <si>
     <t>10_1_1|11_1_1|12_1_1|16_1_1|17_1_1|18_1_1|22_1_1|23_1_1|24_1_1|28_1_1|29_1_1|30_1_1</t>
   </si>
   <si>
-    <t>概率改出免费+1符号</t>
-  </si>
-  <si>
-    <t>0_9|1_1</t>
-  </si>
-  <si>
-    <t>31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
-  </si>
-  <si>
-    <t>改出黄金10符号</t>
-  </si>
-  <si>
-    <t>121_1</t>
-  </si>
-  <si>
-    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金J符号</t>
-  </si>
-  <si>
-    <t>122_1</t>
-  </si>
-  <si>
-    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金Q符号</t>
-  </si>
-  <si>
-    <t>123_1</t>
-  </si>
-  <si>
-    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金K符号</t>
-  </si>
-  <si>
-    <t>124_1</t>
-  </si>
-  <si>
-    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金A符号</t>
-  </si>
-  <si>
-    <t>125_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金罗纳尔多</t>
-  </si>
-  <si>
-    <t>126_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金格列兹曼</t>
-  </si>
-  <si>
-    <t>127_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金内马尔</t>
-  </si>
-  <si>
-    <t>128_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金斯特林</t>
-  </si>
-  <si>
-    <t>129_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_10_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金C罗</t>
-  </si>
-  <si>
-    <t>130_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_11_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>改出黄金梅西</t>
-  </si>
-  <si>
-    <t>131_1</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_10_12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121_122_123_124_125_126_127_128_129_130_131</t>
-  </si>
-  <si>
-    <t>概率改出百搭wild符号</t>
-  </si>
-  <si>
-    <t>13_14_15_16_17_18_19_20_21_22</t>
-  </si>
-  <si>
-    <t>改出20符号</t>
-  </si>
-  <si>
-    <t>改出21符号</t>
-  </si>
-  <si>
-    <t>改出22符号</t>
-  </si>
-  <si>
-    <t>16_10|17_5|18_2|19_1</t>
-  </si>
-  <si>
-    <t>第1轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第2轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第3轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第4轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第5轴改出3个wild</t>
-  </si>
-  <si>
-    <t>第1、2轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1</t>
-  </si>
-  <si>
-    <t>第1、3轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>第1、4轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第1、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第2、3轴改出6个wild</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>第2、4轴改出6个wild</t>
-  </si>
-  <si>
-    <t>第2、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第3、4轴改出6个wild</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第3、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第4、5轴改出6个wild</t>
-  </si>
-  <si>
-    <t>10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第1、2、3轴改出9个wild</t>
-  </si>
-  <si>
-    <t>第1、2、4轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第1、2、5轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第1、3、4轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>第1、3、5轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|7_1_1|8_1_1|9_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>第1、4、5轴改出9个wild</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出+1免费符号</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86_87_88_89_90_91_92_93_94_95_96_97_98_99_100_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119</t>
-  </si>
-  <si>
-    <t>0_70|1_20|2_9|3_1</t>
-  </si>
-  <si>
-    <t>2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
-  </si>
-  <si>
     <t>11_1_1|12_1_1|17_1_1|18_1_1|23_1_1|24_1_1|29_1_1|30_1_1</t>
   </si>
   <si>
@@ -2051,6 +2051,54 @@
   </si>
   <si>
     <t>10_11_12_13_14</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85</t>
+  </si>
+  <si>
+    <t>概率改出3个及以下scatter符号</t>
+  </si>
+  <si>
+    <t>常规触发奖池用</t>
+  </si>
+  <si>
+    <t>18_1|19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|42_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1</t>
+  </si>
+  <si>
+    <t>2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|53_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1</t>
+  </si>
+  <si>
+    <t>3_1_1|4_1_1|5_1_1|6_1_1|9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>改出占据2个格子白银符号</t>
+  </si>
+  <si>
+    <t>百搭赐福</t>
+  </si>
+  <si>
+    <t>42_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1</t>
+  </si>
+  <si>
+    <t>2_10|3_1</t>
+  </si>
+  <si>
+    <t>改出占据3个格子白银符号</t>
+  </si>
+  <si>
+    <t>53_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1</t>
+  </si>
+  <si>
+    <t>1_10|2_1</t>
+  </si>
+  <si>
+    <t>奖池模式</t>
+  </si>
+  <si>
+    <t>30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -3508,7 +3556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N406"/>
+  <dimension ref="A1:N419"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -11447,88 +11495,88 @@
     </row>
     <row r="273" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A273" s="24">
-        <v>10160007</v>
+        <v>10160008</v>
       </c>
       <c r="B273" s="24">
         <v>101600</v>
       </c>
       <c r="C273" s="24" t="s">
-        <v>337</v>
+        <v>465</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E273" s="24" t="s">
-        <v>465</v>
+        <v>146</v>
       </c>
       <c r="F273" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G273" s="24" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="H273" s="24" t="s">
         <v>459</v>
       </c>
       <c r="I273" s="24" t="s">
-        <v>340</v>
+        <v>466</v>
       </c>
       <c r="K273" s="108"/>
     </row>
     <row r="274" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A274" s="24">
-        <v>10160008</v>
+        <v>10160009</v>
       </c>
       <c r="B274" s="24">
         <v>101600</v>
       </c>
       <c r="C274" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D274" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E274" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F274" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G274" s="24" t="s">
         <v>467</v>
-      </c>
-      <c r="D274" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="E274" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F274" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G274" s="24" t="s">
-        <v>460</v>
       </c>
       <c r="H274" s="24" t="s">
         <v>459</v>
       </c>
       <c r="I274" s="24" t="s">
-        <v>468</v>
+        <v>39</v>
       </c>
       <c r="K274" s="108"/>
     </row>
     <row r="275" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A275" s="24">
-        <v>10160009</v>
+        <v>10160010</v>
       </c>
       <c r="B275" s="24">
         <v>101600</v>
       </c>
       <c r="C275" s="24" t="s">
-        <v>253</v>
+        <v>468</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E275" s="24" t="s">
-        <v>254</v>
+        <v>469</v>
       </c>
       <c r="F275" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G275" s="24" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="H275" s="24" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="I275" s="24" t="s">
         <v>39</v>
@@ -11537,19 +11585,19 @@
     </row>
     <row r="276" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A276" s="24">
-        <v>10160010</v>
+        <v>10160011</v>
       </c>
       <c r="B276" s="24">
         <v>101600</v>
       </c>
       <c r="C276" s="24" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D276" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E276" s="24" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F276" s="24" t="s">
         <v>133</v>
@@ -11558,7 +11606,7 @@
         <v>460</v>
       </c>
       <c r="H276" s="24" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I276" s="24" t="s">
         <v>39</v>
@@ -11567,19 +11615,19 @@
     </row>
     <row r="277" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A277" s="24">
-        <v>10160011</v>
+        <v>10160012</v>
       </c>
       <c r="B277" s="24">
         <v>101600</v>
       </c>
       <c r="C277" s="24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D277" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E277" s="24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F277" s="24" t="s">
         <v>133</v>
@@ -11588,7 +11636,7 @@
         <v>460</v>
       </c>
       <c r="H277" s="24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I277" s="24" t="s">
         <v>39</v>
@@ -11597,19 +11645,19 @@
     </row>
     <row r="278" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A278" s="24">
-        <v>10160012</v>
+        <v>10160013</v>
       </c>
       <c r="B278" s="24">
         <v>101600</v>
       </c>
       <c r="C278" s="24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D278" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E278" s="24" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F278" s="24" t="s">
         <v>133</v>
@@ -11618,7 +11666,7 @@
         <v>460</v>
       </c>
       <c r="H278" s="24" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I278" s="24" t="s">
         <v>39</v>
@@ -11627,19 +11675,19 @@
     </row>
     <row r="279" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A279" s="24">
-        <v>10160013</v>
+        <v>10160014</v>
       </c>
       <c r="B279" s="24">
         <v>101600</v>
       </c>
       <c r="C279" s="24" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D279" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E279" s="24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F279" s="24" t="s">
         <v>133</v>
@@ -11648,7 +11696,7 @@
         <v>460</v>
       </c>
       <c r="H279" s="24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I279" s="24" t="s">
         <v>39</v>
@@ -11657,19 +11705,19 @@
     </row>
     <row r="280" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A280" s="24">
-        <v>10160014</v>
+        <v>10160015</v>
       </c>
       <c r="B280" s="24">
         <v>101600</v>
       </c>
       <c r="C280" s="24" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D280" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E280" s="24" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F280" s="24" t="s">
         <v>133</v>
@@ -11678,7 +11726,7 @@
         <v>460</v>
       </c>
       <c r="H280" s="24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I280" s="24" t="s">
         <v>39</v>
@@ -11687,19 +11735,19 @@
     </row>
     <row r="281" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A281" s="24">
-        <v>10160015</v>
+        <v>10160016</v>
       </c>
       <c r="B281" s="24">
         <v>101600</v>
       </c>
       <c r="C281" s="24" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D281" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E281" s="24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F281" s="24" t="s">
         <v>133</v>
@@ -11708,7 +11756,7 @@
         <v>460</v>
       </c>
       <c r="H281" s="24" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I281" s="24" t="s">
         <v>39</v>
@@ -11717,19 +11765,19 @@
     </row>
     <row r="282" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A282" s="24">
-        <v>10160016</v>
+        <v>10160017</v>
       </c>
       <c r="B282" s="24">
         <v>101600</v>
       </c>
       <c r="C282" s="24" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D282" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E282" s="24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F282" s="24" t="s">
         <v>133</v>
@@ -11738,7 +11786,7 @@
         <v>460</v>
       </c>
       <c r="H282" s="24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I282" s="24" t="s">
         <v>39</v>
@@ -11747,19 +11795,19 @@
     </row>
     <row r="283" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A283" s="24">
-        <v>10160017</v>
+        <v>10160018</v>
       </c>
       <c r="B283" s="24">
         <v>101600</v>
       </c>
       <c r="C283" s="24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D283" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E283" s="24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F283" s="24" t="s">
         <v>133</v>
@@ -11768,7 +11816,7 @@
         <v>460</v>
       </c>
       <c r="H283" s="24" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I283" s="24" t="s">
         <v>39</v>
@@ -11777,19 +11825,19 @@
     </row>
     <row r="284" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A284" s="24">
-        <v>10160018</v>
+        <v>10160019</v>
       </c>
       <c r="B284" s="24">
         <v>101600</v>
       </c>
       <c r="C284" s="24" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D284" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E284" s="24" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F284" s="24" t="s">
         <v>133</v>
@@ -11798,7 +11846,7 @@
         <v>460</v>
       </c>
       <c r="H284" s="24" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I284" s="24" t="s">
         <v>39</v>
@@ -11807,19 +11855,19 @@
     </row>
     <row r="285" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A285" s="24">
-        <v>10160019</v>
+        <v>10160020</v>
       </c>
       <c r="B285" s="24">
         <v>101600</v>
       </c>
       <c r="C285" s="24" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D285" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E285" s="24" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F285" s="24" t="s">
         <v>133</v>
@@ -11828,58 +11876,58 @@
         <v>460</v>
       </c>
       <c r="H285" s="24" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I285" s="24" t="s">
         <v>39</v>
       </c>
       <c r="K285" s="108"/>
     </row>
-    <row r="286" s="24" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A286" s="24">
-        <v>10160020</v>
-      </c>
-      <c r="B286" s="24">
-        <v>101600</v>
-      </c>
-      <c r="C286" s="24" t="s">
-        <v>500</v>
-      </c>
-      <c r="D286" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="E286" s="24" t="s">
+    <row r="286" s="26" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A286" s="26">
+        <v>10150001</v>
+      </c>
+      <c r="B286" s="26">
+        <v>101500</v>
+      </c>
+      <c r="C286" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="F286" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G286" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="H286" s="24" t="s">
+      <c r="D286" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="E286" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F286" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G286" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="H286" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="I286" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="K286" s="108"/>
+      <c r="I286" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="K286" s="110"/>
     </row>
     <row r="287" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A287" s="26">
-        <v>10150001</v>
+        <v>10150002</v>
       </c>
       <c r="B287" s="26">
         <v>101500</v>
       </c>
       <c r="C287" s="26" t="s">
-        <v>503</v>
+        <v>259</v>
       </c>
       <c r="D287" s="26" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E287" s="26" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F287" s="26" t="s">
         <v>133</v>
@@ -11888,22 +11936,22 @@
         <v>234</v>
       </c>
       <c r="H287" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I287" s="26" t="s">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="K287" s="110"/>
     </row>
     <row r="288" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A288" s="26">
-        <v>10150002</v>
+        <v>10150003</v>
       </c>
       <c r="B288" s="26">
         <v>101500</v>
       </c>
       <c r="C288" s="26" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="D288" s="26" t="s">
         <v>21</v>
@@ -11918,22 +11966,22 @@
         <v>234</v>
       </c>
       <c r="H288" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I288" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K288" s="110"/>
     </row>
     <row r="289" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A289" s="26">
-        <v>10150003</v>
+        <v>10150004</v>
       </c>
       <c r="B289" s="26">
         <v>101500</v>
       </c>
       <c r="C289" s="26" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D289" s="26" t="s">
         <v>21</v>
@@ -11948,28 +11996,28 @@
         <v>234</v>
       </c>
       <c r="H289" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I289" s="26" t="s">
-        <v>106</v>
+        <v>432</v>
       </c>
       <c r="K289" s="110"/>
     </row>
     <row r="290" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A290" s="26">
-        <v>10150004</v>
+        <v>10150005</v>
       </c>
       <c r="B290" s="26">
         <v>101500</v>
       </c>
       <c r="C290" s="26" t="s">
-        <v>246</v>
+        <v>504</v>
       </c>
       <c r="D290" s="26" t="s">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="E290" s="26" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="F290" s="26" t="s">
         <v>133</v>
@@ -11978,16 +12026,16 @@
         <v>234</v>
       </c>
       <c r="H290" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I290" s="26" t="s">
-        <v>432</v>
+        <v>39</v>
       </c>
       <c r="K290" s="110"/>
     </row>
     <row r="291" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A291" s="26">
-        <v>10150005</v>
+        <v>10150006</v>
       </c>
       <c r="B291" s="26">
         <v>101500</v>
@@ -11999,7 +12047,7 @@
         <v>279</v>
       </c>
       <c r="E291" s="26" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F291" s="26" t="s">
         <v>133</v>
@@ -12008,7 +12056,7 @@
         <v>234</v>
       </c>
       <c r="H291" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I291" s="26" t="s">
         <v>39</v>
@@ -12017,7 +12065,7 @@
     </row>
     <row r="292" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A292" s="26">
-        <v>10150006</v>
+        <v>10150007</v>
       </c>
       <c r="B292" s="26">
         <v>101500</v>
@@ -12029,7 +12077,7 @@
         <v>279</v>
       </c>
       <c r="E292" s="26" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F292" s="26" t="s">
         <v>133</v>
@@ -12038,7 +12086,7 @@
         <v>234</v>
       </c>
       <c r="H292" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I292" s="26" t="s">
         <v>39</v>
@@ -12047,28 +12095,28 @@
     </row>
     <row r="293" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A293" s="26">
-        <v>10150007</v>
+        <v>10150008</v>
       </c>
       <c r="B293" s="26">
         <v>101500</v>
       </c>
       <c r="C293" s="26" t="s">
-        <v>507</v>
+        <v>253</v>
       </c>
       <c r="D293" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E293" s="26" t="s">
-        <v>56</v>
+        <v>507</v>
       </c>
       <c r="F293" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G293" s="26" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H293" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I293" s="26" t="s">
         <v>39</v>
@@ -12077,37 +12125,37 @@
     </row>
     <row r="294" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A294" s="26">
-        <v>10150008</v>
+        <v>10150009</v>
       </c>
       <c r="B294" s="26">
         <v>101500</v>
       </c>
       <c r="C294" s="26" t="s">
-        <v>253</v>
+        <v>508</v>
       </c>
       <c r="D294" s="26" t="s">
-        <v>279</v>
+        <v>422</v>
       </c>
       <c r="E294" s="26" t="s">
-        <v>508</v>
+        <v>143</v>
       </c>
       <c r="F294" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G294" s="26" t="s">
-        <v>255</v>
+        <v>439</v>
       </c>
       <c r="H294" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I294" s="26" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="K294" s="110"/>
     </row>
     <row r="295" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A295" s="26">
-        <v>10150009</v>
+        <v>10150010</v>
       </c>
       <c r="B295" s="26">
         <v>101500</v>
@@ -12125,10 +12173,10 @@
         <v>133</v>
       </c>
       <c r="G295" s="26" t="s">
-        <v>439</v>
+        <v>174</v>
       </c>
       <c r="H295" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I295" s="26" t="s">
         <v>107</v>
@@ -12137,7 +12185,7 @@
     </row>
     <row r="296" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A296" s="26">
-        <v>10150010</v>
+        <v>10150011</v>
       </c>
       <c r="B296" s="26">
         <v>101500</v>
@@ -12155,10 +12203,10 @@
         <v>133</v>
       </c>
       <c r="G296" s="26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H296" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I296" s="26" t="s">
         <v>107</v>
@@ -12167,7 +12215,7 @@
     </row>
     <row r="297" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A297" s="26">
-        <v>10150011</v>
+        <v>10150012</v>
       </c>
       <c r="B297" s="26">
         <v>101500</v>
@@ -12185,10 +12233,10 @@
         <v>133</v>
       </c>
       <c r="G297" s="26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H297" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I297" s="26" t="s">
         <v>107</v>
@@ -12197,7 +12245,7 @@
     </row>
     <row r="298" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A298" s="26">
-        <v>10150012</v>
+        <v>10150013</v>
       </c>
       <c r="B298" s="26">
         <v>101500</v>
@@ -12215,10 +12263,10 @@
         <v>133</v>
       </c>
       <c r="G298" s="26" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="H298" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I298" s="26" t="s">
         <v>107</v>
@@ -12227,7 +12275,7 @@
     </row>
     <row r="299" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A299" s="26">
-        <v>10150013</v>
+        <v>10150014</v>
       </c>
       <c r="B299" s="26">
         <v>101500</v>
@@ -12236,7 +12284,7 @@
         <v>513</v>
       </c>
       <c r="D299" s="26" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E299" s="26" t="s">
         <v>143</v>
@@ -12245,25 +12293,25 @@
         <v>133</v>
       </c>
       <c r="G299" s="26" t="s">
-        <v>255</v>
+        <v>514</v>
       </c>
       <c r="H299" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I299" s="26" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="K299" s="110"/>
     </row>
     <row r="300" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A300" s="26">
-        <v>10150014</v>
+        <v>10150015</v>
       </c>
       <c r="B300" s="26">
         <v>101500</v>
       </c>
       <c r="C300" s="26" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D300" s="26" t="s">
         <v>21</v>
@@ -12275,10 +12323,10 @@
         <v>133</v>
       </c>
       <c r="G300" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H300" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I300" s="26" t="s">
         <v>89</v>
@@ -12287,13 +12335,13 @@
     </row>
     <row r="301" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A301" s="26">
-        <v>10150015</v>
+        <v>10150016</v>
       </c>
       <c r="B301" s="26">
         <v>101500</v>
       </c>
       <c r="C301" s="26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D301" s="26" t="s">
         <v>21</v>
@@ -12305,10 +12353,10 @@
         <v>133</v>
       </c>
       <c r="G301" s="26" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H301" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I301" s="26" t="s">
         <v>89</v>
@@ -12317,13 +12365,13 @@
     </row>
     <row r="302" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A302" s="26">
-        <v>10150016</v>
+        <v>10150017</v>
       </c>
       <c r="B302" s="26">
         <v>101500</v>
       </c>
       <c r="C302" s="26" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D302" s="26" t="s">
         <v>21</v>
@@ -12335,10 +12383,10 @@
         <v>133</v>
       </c>
       <c r="G302" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H302" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I302" s="26" t="s">
         <v>89</v>
@@ -12347,13 +12395,13 @@
     </row>
     <row r="303" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A303" s="26">
-        <v>10150017</v>
+        <v>10150018</v>
       </c>
       <c r="B303" s="26">
         <v>101500</v>
       </c>
       <c r="C303" s="26" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D303" s="26" t="s">
         <v>21</v>
@@ -12365,10 +12413,10 @@
         <v>133</v>
       </c>
       <c r="G303" s="26" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H303" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I303" s="26" t="s">
         <v>89</v>
@@ -12377,13 +12425,13 @@
     </row>
     <row r="304" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A304" s="26">
-        <v>10150018</v>
+        <v>10150019</v>
       </c>
       <c r="B304" s="26">
         <v>101500</v>
       </c>
       <c r="C304" s="26" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D304" s="26" t="s">
         <v>21</v>
@@ -12395,10 +12443,10 @@
         <v>133</v>
       </c>
       <c r="G304" s="26" t="s">
-        <v>523</v>
+        <v>423</v>
       </c>
       <c r="H304" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I304" s="26" t="s">
         <v>89</v>
@@ -12407,7 +12455,7 @@
     </row>
     <row r="305" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A305" s="26">
-        <v>10150019</v>
+        <v>10150020</v>
       </c>
       <c r="B305" s="26">
         <v>101500</v>
@@ -12425,10 +12473,10 @@
         <v>133</v>
       </c>
       <c r="G305" s="26" t="s">
-        <v>423</v>
+        <v>525</v>
       </c>
       <c r="H305" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I305" s="26" t="s">
         <v>89</v>
@@ -12437,13 +12485,13 @@
     </row>
     <row r="306" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A306" s="26">
-        <v>10150020</v>
+        <v>10150021</v>
       </c>
       <c r="B306" s="26">
         <v>101500</v>
       </c>
       <c r="C306" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D306" s="26" t="s">
         <v>21</v>
@@ -12455,10 +12503,10 @@
         <v>133</v>
       </c>
       <c r="G306" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H306" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I306" s="26" t="s">
         <v>89</v>
@@ -12467,13 +12515,13 @@
     </row>
     <row r="307" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A307" s="26">
-        <v>10150021</v>
+        <v>10150022</v>
       </c>
       <c r="B307" s="26">
         <v>101500</v>
       </c>
       <c r="C307" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D307" s="26" t="s">
         <v>21</v>
@@ -12485,10 +12533,10 @@
         <v>133</v>
       </c>
       <c r="G307" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H307" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I307" s="26" t="s">
         <v>89</v>
@@ -12497,13 +12545,13 @@
     </row>
     <row r="308" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A308" s="26">
-        <v>10150022</v>
+        <v>10150023</v>
       </c>
       <c r="B308" s="26">
         <v>101500</v>
       </c>
       <c r="C308" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D308" s="26" t="s">
         <v>21</v>
@@ -12515,10 +12563,10 @@
         <v>133</v>
       </c>
       <c r="G308" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H308" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I308" s="26" t="s">
         <v>89</v>
@@ -12527,13 +12575,13 @@
     </row>
     <row r="309" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A309" s="26">
-        <v>10150023</v>
+        <v>10150024</v>
       </c>
       <c r="B309" s="26">
         <v>101500</v>
       </c>
       <c r="C309" s="26" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D309" s="26" t="s">
         <v>21</v>
@@ -12545,19 +12593,19 @@
         <v>133</v>
       </c>
       <c r="G309" s="26" t="s">
-        <v>532</v>
+        <v>297</v>
       </c>
       <c r="H309" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I309" s="26" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="K309" s="110"/>
     </row>
     <row r="310" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A310" s="26">
-        <v>10150024</v>
+        <v>10150025</v>
       </c>
       <c r="B310" s="26">
         <v>101500</v>
@@ -12575,10 +12623,10 @@
         <v>133</v>
       </c>
       <c r="G310" s="26" t="s">
-        <v>297</v>
+        <v>534</v>
       </c>
       <c r="H310" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I310" s="26" t="s">
         <v>157</v>
@@ -12587,13 +12635,13 @@
     </row>
     <row r="311" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A311" s="26">
-        <v>10150025</v>
+        <v>10150026</v>
       </c>
       <c r="B311" s="26">
         <v>101500</v>
       </c>
       <c r="C311" s="26" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D311" s="26" t="s">
         <v>21</v>
@@ -12605,10 +12653,10 @@
         <v>133</v>
       </c>
       <c r="G311" s="26" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H311" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I311" s="26" t="s">
         <v>157</v>
@@ -12617,13 +12665,13 @@
     </row>
     <row r="312" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A312" s="26">
-        <v>10150026</v>
+        <v>10150027</v>
       </c>
       <c r="B312" s="26">
         <v>101500</v>
       </c>
       <c r="C312" s="26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D312" s="26" t="s">
         <v>21</v>
@@ -12635,10 +12683,10 @@
         <v>133</v>
       </c>
       <c r="G312" s="26" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H312" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I312" s="26" t="s">
         <v>157</v>
@@ -12647,13 +12695,13 @@
     </row>
     <row r="313" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A313" s="26">
-        <v>10150027</v>
+        <v>10150028</v>
       </c>
       <c r="B313" s="26">
         <v>101500</v>
       </c>
       <c r="C313" s="26" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D313" s="26" t="s">
         <v>21</v>
@@ -12665,10 +12713,10 @@
         <v>133</v>
       </c>
       <c r="G313" s="26" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H313" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I313" s="26" t="s">
         <v>157</v>
@@ -12677,13 +12725,13 @@
     </row>
     <row r="314" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A314" s="26">
-        <v>10150028</v>
+        <v>10150029</v>
       </c>
       <c r="B314" s="26">
         <v>101500</v>
       </c>
       <c r="C314" s="26" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D314" s="26" t="s">
         <v>21</v>
@@ -12695,10 +12743,10 @@
         <v>133</v>
       </c>
       <c r="G314" s="26" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H314" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I314" s="26" t="s">
         <v>157</v>
@@ -12707,106 +12755,106 @@
     </row>
     <row r="315" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A315" s="26">
-        <v>10150029</v>
+        <v>10150030</v>
       </c>
       <c r="B315" s="26">
         <v>101500</v>
       </c>
       <c r="C315" s="26" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D315" s="26" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E315" s="26" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="F315" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G315" s="26" t="s">
-        <v>543</v>
+        <v>234</v>
       </c>
       <c r="H315" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I315" s="26" t="s">
-        <v>157</v>
+        <v>466</v>
       </c>
       <c r="K315" s="110"/>
     </row>
-    <row r="316" s="26" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A316" s="26">
-        <v>10150030</v>
-      </c>
-      <c r="B316" s="26">
-        <v>101500</v>
-      </c>
-      <c r="C316" s="26" t="s">
+    <row r="316" s="27" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A316" s="27">
+        <v>10260001</v>
+      </c>
+      <c r="B316" s="27">
+        <v>102600</v>
+      </c>
+      <c r="C316" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="D316" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="E316" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F316" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G316" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="H316" s="27" t="s">
         <v>544</v>
       </c>
-      <c r="D316" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="E316" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F316" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G316" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="H316" s="26" t="s">
-        <v>504</v>
-      </c>
-      <c r="I316" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="K316" s="110"/>
+      <c r="I316" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="K316" s="111"/>
     </row>
     <row r="317" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A317" s="27">
-        <v>10260001</v>
+        <v>10260002</v>
       </c>
       <c r="B317" s="27">
         <v>102600</v>
       </c>
       <c r="C317" s="27" t="s">
-        <v>503</v>
+        <v>323</v>
       </c>
       <c r="D317" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E317" s="27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F317" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G317" s="27" t="s">
-        <v>458</v>
+        <v>546</v>
       </c>
       <c r="H317" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I317" s="27" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K317" s="111"/>
     </row>
     <row r="318" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A318" s="27">
-        <v>10260002</v>
+        <v>10260003</v>
       </c>
       <c r="B318" s="27">
         <v>102600</v>
       </c>
       <c r="C318" s="27" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D318" s="27" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E318" s="27" t="s">
         <v>143</v>
@@ -12815,28 +12863,28 @@
         <v>133</v>
       </c>
       <c r="G318" s="27" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H318" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I318" s="27" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="K318" s="111"/>
     </row>
     <row r="319" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A319" s="27">
-        <v>10260003</v>
+        <v>10260004</v>
       </c>
       <c r="B319" s="27">
         <v>102600</v>
       </c>
       <c r="C319" s="27" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D319" s="27" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E319" s="27" t="s">
         <v>143</v>
@@ -12845,70 +12893,70 @@
         <v>133</v>
       </c>
       <c r="G319" s="27" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H319" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I319" s="27" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="K319" s="111"/>
     </row>
     <row r="320" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A320" s="27">
-        <v>10260004</v>
+        <v>10260005</v>
       </c>
       <c r="B320" s="27">
         <v>102600</v>
       </c>
       <c r="C320" s="27" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D320" s="27" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E320" s="27" t="s">
-        <v>143</v>
+        <v>331</v>
       </c>
       <c r="F320" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G320" s="27" t="s">
-        <v>547</v>
+        <v>464</v>
       </c>
       <c r="H320" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I320" s="27" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K320" s="111"/>
     </row>
     <row r="321" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A321" s="27">
-        <v>10260005</v>
+        <v>10260006</v>
       </c>
       <c r="B321" s="27">
         <v>102600</v>
       </c>
       <c r="C321" s="27" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D321" s="27" t="s">
         <v>438</v>
       </c>
       <c r="E321" s="27" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F321" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G321" s="27" t="s">
-        <v>464</v>
+        <v>547</v>
       </c>
       <c r="H321" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I321" s="27" t="s">
         <v>333</v>
@@ -12917,189 +12965,188 @@
     </row>
     <row r="322" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A322" s="27">
-        <v>10260006</v>
+        <v>10260007</v>
       </c>
       <c r="B322" s="27">
         <v>102600</v>
       </c>
       <c r="C322" s="27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D322" s="27" t="s">
         <v>438</v>
       </c>
       <c r="E322" s="27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F322" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G322" s="27" t="s">
-        <v>466</v>
+        <v>548</v>
       </c>
       <c r="H322" s="27" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I322" s="27" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K322" s="111"/>
     </row>
     <row r="323" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A323" s="27">
-        <v>10260007</v>
+        <v>10260008</v>
       </c>
       <c r="B323" s="27">
         <v>102600</v>
       </c>
       <c r="C323" s="27" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D323" s="27" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E323" s="27" t="s">
-        <v>338</v>
+        <v>275</v>
       </c>
       <c r="F323" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G323" s="27" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H323" s="27" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I323" s="27" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K323" s="111"/>
     </row>
     <row r="324" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A324" s="27">
-        <v>10260008</v>
+        <v>10260009</v>
       </c>
       <c r="B324" s="27">
         <v>102600</v>
       </c>
       <c r="C324" s="27" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E324" s="27" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F324" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G324" s="27" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H324" s="27" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="I324" s="27" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="K324" s="111"/>
     </row>
     <row r="325" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A325" s="27">
-        <v>10260009</v>
+        <v>10260010</v>
       </c>
       <c r="B325" s="27">
         <v>102600</v>
       </c>
       <c r="C325" s="27" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D325" s="27" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E325" s="27" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="F325" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G325" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="H325" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="I325" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="K325" s="111"/>
+    </row>
+    <row r="326" s="20" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A326" s="20">
+        <v>10500001</v>
+      </c>
+      <c r="B326" s="20">
+        <v>105000</v>
+      </c>
+      <c r="C326" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="D326" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="E326" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F326" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G326" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="H326" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="I326" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="I325" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="K325" s="111"/>
-    </row>
-    <row r="326" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A326" s="27">
-        <v>10260010</v>
-      </c>
-      <c r="B326" s="27">
-        <v>102600</v>
-      </c>
-      <c r="C326" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D326" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E326" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="F326" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G326" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="I326" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="K326" s="111"/>
     </row>
     <row r="327" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A327" s="20">
-        <v>10500001</v>
+        <v>10500002</v>
       </c>
       <c r="B327" s="20">
         <v>105000</v>
       </c>
       <c r="C327" s="20" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D327" s="20" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E327" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F327" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G327" s="20" t="s">
-        <v>458</v>
+        <v>555</v>
       </c>
       <c r="H327" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I327" s="20" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A328" s="20">
-        <v>10500002</v>
+        <v>10500003</v>
       </c>
       <c r="B328" s="20">
         <v>105000</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D328" s="20" t="s">
         <v>425</v>
@@ -13111,24 +13158,24 @@
         <v>133</v>
       </c>
       <c r="G328" s="20" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H328" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I328" s="20" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
     </row>
     <row r="329" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A329" s="20">
-        <v>10500003</v>
+        <v>10500004</v>
       </c>
       <c r="B329" s="20">
         <v>105000</v>
       </c>
       <c r="C329" s="20" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D329" s="20" t="s">
         <v>425</v>
@@ -13140,65 +13187,65 @@
         <v>133</v>
       </c>
       <c r="G329" s="20" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H329" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I329" s="20" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A330" s="20">
-        <v>10500004</v>
+        <v>10500005</v>
       </c>
       <c r="B330" s="20">
         <v>105000</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>558</v>
+        <v>330</v>
       </c>
       <c r="D330" s="20" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E330" s="20" t="s">
-        <v>143</v>
+        <v>559</v>
       </c>
       <c r="F330" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G330" s="20" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="H330" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I330" s="20" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="331" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A331" s="20">
-        <v>10500005</v>
+        <v>10500006</v>
       </c>
       <c r="B331" s="20">
         <v>105000</v>
       </c>
       <c r="C331" s="20" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D331" s="20" t="s">
         <v>422</v>
       </c>
       <c r="E331" s="20" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F331" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G331" s="20" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H331" s="20" t="s">
         <v>553</v>
@@ -13209,149 +13256,150 @@
     </row>
     <row r="332" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A332" s="20">
-        <v>10500006</v>
+        <v>10500007</v>
       </c>
       <c r="B332" s="20">
         <v>105000</v>
       </c>
       <c r="C332" s="20" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D332" s="20" t="s">
         <v>422</v>
       </c>
       <c r="E332" s="20" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F332" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G332" s="20" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H332" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I332" s="20" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="333" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A333" s="20">
-        <v>10500007</v>
+        <v>10500008</v>
       </c>
       <c r="B333" s="20">
         <v>105000</v>
       </c>
       <c r="C333" s="20" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D333" s="20" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E333" s="20" t="s">
-        <v>563</v>
+        <v>275</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G333" s="20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H333" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I333" s="20" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
     </row>
     <row r="334" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A334" s="20">
-        <v>10500008</v>
+        <v>10500009</v>
       </c>
       <c r="B334" s="20">
         <v>105000</v>
       </c>
       <c r="C334" s="20" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D334" s="20" t="s">
-        <v>425</v>
+        <v>566</v>
       </c>
       <c r="E334" s="20" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F334" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G334" s="20" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="H334" s="20" t="s">
         <v>553</v>
       </c>
       <c r="I334" s="20" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
     </row>
     <row r="335" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A335" s="20">
-        <v>10500009</v>
+        <v>10500010</v>
       </c>
       <c r="B335" s="20">
         <v>105000</v>
       </c>
       <c r="C335" s="20" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D335" s="20" t="s">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="E335" s="20" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="F335" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G335" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="H335" s="20" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I335" s="20" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="336" s="20" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A336" s="20">
-        <v>10500010</v>
-      </c>
-      <c r="B336" s="20">
-        <v>105000</v>
-      </c>
-      <c r="C336" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="D336" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="E336" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="F336" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G336" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="I336" s="20" t="s">
         <v>106</v>
       </c>
+    </row>
+    <row r="336" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A336" s="33">
+        <v>10510001</v>
+      </c>
+      <c r="B336" s="33">
+        <v>105100</v>
+      </c>
+      <c r="C336" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="D336" s="33" t="s">
+        <v>568</v>
+      </c>
+      <c r="E336" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F336" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G336" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H336" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="I336" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K336" s="82"/>
     </row>
     <row r="337" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A337" s="33">
-        <v>10510001</v>
+        <v>10510002</v>
       </c>
       <c r="B337" s="33">
         <v>105100</v>
@@ -13360,7 +13408,7 @@
         <v>567</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E337" s="33" t="s">
         <v>41</v>
@@ -13369,7 +13417,7 @@
         <v>133</v>
       </c>
       <c r="G337" s="33" t="s">
-        <v>25</v>
+        <v>344</v>
       </c>
       <c r="H337" s="33" t="s">
         <v>569</v>
@@ -13381,7 +13429,7 @@
     </row>
     <row r="338" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A338" s="33">
-        <v>10510002</v>
+        <v>10510003</v>
       </c>
       <c r="B338" s="33">
         <v>105100</v>
@@ -13390,7 +13438,7 @@
         <v>567</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E338" s="33" t="s">
         <v>41</v>
@@ -13399,7 +13447,7 @@
         <v>133</v>
       </c>
       <c r="G338" s="33" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="H338" s="33" t="s">
         <v>569</v>
@@ -13411,25 +13459,25 @@
     </row>
     <row r="339" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A339" s="33">
-        <v>10510003</v>
+        <v>10510004</v>
       </c>
       <c r="B339" s="33">
         <v>105100</v>
       </c>
       <c r="C339" s="33" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D339" s="33" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E339" s="33" t="s">
-        <v>41</v>
+        <v>574</v>
       </c>
       <c r="F339" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G339" s="33" t="s">
-        <v>460</v>
+        <v>25</v>
       </c>
       <c r="H339" s="33" t="s">
         <v>569</v>
@@ -13441,7 +13489,7 @@
     </row>
     <row r="340" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A340" s="33">
-        <v>10510004</v>
+        <v>10510005</v>
       </c>
       <c r="B340" s="33">
         <v>105100</v>
@@ -13450,7 +13498,7 @@
         <v>572</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E340" s="33" t="s">
         <v>574</v>
@@ -13459,7 +13507,7 @@
         <v>133</v>
       </c>
       <c r="G340" s="33" t="s">
-        <v>25</v>
+        <v>344</v>
       </c>
       <c r="H340" s="33" t="s">
         <v>569</v>
@@ -13471,7 +13519,7 @@
     </row>
     <row r="341" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A341" s="33">
-        <v>10510005</v>
+        <v>10510006</v>
       </c>
       <c r="B341" s="33">
         <v>105100</v>
@@ -13480,7 +13528,7 @@
         <v>572</v>
       </c>
       <c r="D341" s="33" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E341" s="33" t="s">
         <v>574</v>
@@ -13489,7 +13537,7 @@
         <v>133</v>
       </c>
       <c r="G341" s="33" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="H341" s="33" t="s">
         <v>569</v>
@@ -13501,55 +13549,55 @@
     </row>
     <row r="342" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A342" s="33">
-        <v>10510006</v>
+        <v>10510007</v>
       </c>
       <c r="B342" s="33">
         <v>105100</v>
       </c>
       <c r="C342" s="33" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="E342" s="33" t="s">
-        <v>574</v>
+        <v>36</v>
       </c>
       <c r="F342" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G342" s="33" t="s">
-        <v>460</v>
+        <v>25</v>
       </c>
       <c r="H342" s="33" t="s">
         <v>569</v>
       </c>
       <c r="I342" s="33" t="s">
-        <v>39</v>
+        <v>578</v>
       </c>
       <c r="K342" s="82"/>
     </row>
     <row r="343" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A343" s="33">
-        <v>10510007</v>
+        <v>10510008</v>
       </c>
       <c r="B343" s="33">
         <v>105100</v>
       </c>
       <c r="C343" s="33" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D343" s="33" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E343" s="33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F343" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G343" s="33" t="s">
-        <v>25</v>
+        <v>344</v>
       </c>
       <c r="H343" s="33" t="s">
         <v>569</v>
@@ -13561,25 +13609,25 @@
     </row>
     <row r="344" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A344" s="33">
-        <v>10510008</v>
+        <v>10510009</v>
       </c>
       <c r="B344" s="33">
         <v>105100</v>
       </c>
       <c r="C344" s="33" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D344" s="33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E344" s="33" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F344" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G344" s="33" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="H344" s="33" t="s">
         <v>569</v>
@@ -13589,45 +13637,44 @@
       </c>
       <c r="K344" s="82"/>
     </row>
-    <row r="345" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A345" s="33">
-        <v>10510009</v>
-      </c>
-      <c r="B345" s="33">
-        <v>105100</v>
-      </c>
-      <c r="C345" s="33" t="s">
-        <v>580</v>
-      </c>
-      <c r="D345" s="33" t="s">
-        <v>571</v>
-      </c>
-      <c r="E345" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="F345" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G345" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="H345" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="I345" s="33" t="s">
-        <v>578</v>
-      </c>
-      <c r="K345" s="82"/>
+    <row r="345" s="27" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A345" s="27">
+        <v>10540001</v>
+      </c>
+      <c r="B345" s="27">
+        <v>105400</v>
+      </c>
+      <c r="C345" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="D345" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="E345" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F345" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G345" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="H345" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="I345" s="27" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="346" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A346" s="27">
-        <v>10540001</v>
+        <v>10540002</v>
       </c>
       <c r="B346" s="27">
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D346" s="27" t="s">
         <v>425</v>
@@ -13639,24 +13686,24 @@
         <v>133</v>
       </c>
       <c r="G346" s="27" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H346" s="27" t="s">
         <v>581</v>
       </c>
       <c r="I346" s="27" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
     </row>
     <row r="347" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A347" s="27">
-        <v>10540002</v>
+        <v>10540003</v>
       </c>
       <c r="B347" s="27">
         <v>105400</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D347" s="27" t="s">
         <v>425</v>
@@ -13668,59 +13715,59 @@
         <v>133</v>
       </c>
       <c r="G347" s="27" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H347" s="27" t="s">
         <v>581</v>
       </c>
       <c r="I347" s="27" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
     </row>
     <row r="348" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A348" s="27">
-        <v>10540003</v>
+        <v>10540004</v>
       </c>
       <c r="B348" s="27">
         <v>105400</v>
       </c>
       <c r="C348" s="27" t="s">
-        <v>326</v>
+        <v>582</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>140</v>
+        <v>583</v>
       </c>
       <c r="F348" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G348" s="27" t="s">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="H348" s="27" t="s">
         <v>581</v>
       </c>
       <c r="I348" s="27" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="349" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A349" s="27">
-        <v>10540004</v>
+        <v>10540005</v>
       </c>
       <c r="B349" s="27">
         <v>105400</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>582</v>
+        <v>330</v>
       </c>
       <c r="D349" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E349" s="27" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F349" s="27" t="s">
         <v>133</v>
@@ -13737,19 +13784,19 @@
     </row>
     <row r="350" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A350" s="27">
-        <v>10540005</v>
+        <v>10540006</v>
       </c>
       <c r="B350" s="27">
         <v>105400</v>
       </c>
       <c r="C350" s="27" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D350" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E350" s="27" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F350" s="27" t="s">
         <v>133</v>
@@ -13766,19 +13813,19 @@
     </row>
     <row r="351" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A351" s="27">
-        <v>10540006</v>
+        <v>10540007</v>
       </c>
       <c r="B351" s="27">
         <v>105400</v>
       </c>
       <c r="C351" s="27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D351" s="27" t="s">
         <v>422</v>
       </c>
       <c r="E351" s="27" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F351" s="27" t="s">
         <v>133</v>
@@ -13790,164 +13837,162 @@
         <v>581</v>
       </c>
       <c r="I351" s="27" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="352" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A352" s="27">
-        <v>10540007</v>
+        <v>10540008</v>
       </c>
       <c r="B352" s="27">
         <v>105400</v>
       </c>
       <c r="C352" s="27" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E352" s="27" t="s">
-        <v>587</v>
+        <v>264</v>
       </c>
       <c r="F352" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G352" s="27" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="H352" s="27" t="s">
         <v>581</v>
       </c>
       <c r="I352" s="27" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
     </row>
     <row r="353" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A353" s="27">
-        <v>10540008</v>
+        <v>10540009</v>
       </c>
       <c r="B353" s="27">
         <v>105400</v>
       </c>
       <c r="C353" s="27" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D353" s="27" t="s">
-        <v>425</v>
+        <v>566</v>
       </c>
       <c r="E353" s="27" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="F353" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G353" s="27" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="H353" s="27" t="s">
         <v>581</v>
       </c>
       <c r="I353" s="27" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
     </row>
     <row r="354" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A354" s="27">
-        <v>10540009</v>
+        <v>10540010</v>
       </c>
       <c r="B354" s="27">
         <v>105400</v>
       </c>
       <c r="C354" s="27" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D354" s="27" t="s">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="E354" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="F354" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G354" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="I354" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="355" s="28" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A355" s="28">
+        <v>10080001</v>
+      </c>
+      <c r="B355" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C355" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="D355" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="E355" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="F354" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G354" s="27" t="s">
-        <v>588</v>
-      </c>
-      <c r="H354" s="27" t="s">
-        <v>581</v>
-      </c>
-      <c r="I354" s="27" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="355" s="27" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A355" s="27">
-        <v>10540010</v>
-      </c>
-      <c r="B355" s="27">
-        <v>105400</v>
-      </c>
-      <c r="C355" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D355" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E355" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="F355" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G355" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="I355" s="27" t="s">
-        <v>106</v>
-      </c>
+      <c r="F355" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G355" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="H355" s="28" t="s">
+        <v>589</v>
+      </c>
+      <c r="I355" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="K355" s="112"/>
     </row>
     <row r="356" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A356" s="28">
-        <v>10080001</v>
+        <v>10080002</v>
       </c>
       <c r="B356" s="28">
         <v>100800</v>
       </c>
       <c r="C356" s="28" t="s">
-        <v>503</v>
+        <v>323</v>
       </c>
       <c r="D356" s="28" t="s">
         <v>422</v>
       </c>
       <c r="E356" s="28" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F356" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G356" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="H356" s="28" t="s">
-        <v>589</v>
+        <v>546</v>
       </c>
       <c r="I356" s="28" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K356" s="112"/>
     </row>
     <row r="357" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A357" s="28">
-        <v>10080002</v>
+        <v>10080003</v>
       </c>
       <c r="B357" s="28">
         <v>100800</v>
       </c>
       <c r="C357" s="28" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D357" s="28" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E357" s="28" t="s">
         <v>143</v>
@@ -13956,25 +14001,28 @@
         <v>133</v>
       </c>
       <c r="G357" s="28" t="s">
-        <v>547</v>
+        <v>546</v>
+      </c>
+      <c r="H357" s="28" t="s">
+        <v>589</v>
       </c>
       <c r="I357" s="28" t="s">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="K357" s="112"/>
     </row>
     <row r="358" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A358" s="28">
-        <v>10080003</v>
+        <v>10080004</v>
       </c>
       <c r="B358" s="28">
         <v>100800</v>
       </c>
       <c r="C358" s="28" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D358" s="28" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E358" s="28" t="s">
         <v>143</v>
@@ -13983,67 +14031,67 @@
         <v>133</v>
       </c>
       <c r="G358" s="28" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H358" s="28" t="s">
         <v>589</v>
       </c>
       <c r="I358" s="28" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="K358" s="112"/>
     </row>
     <row r="359" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A359" s="28">
-        <v>10080004</v>
+        <v>10080005</v>
       </c>
       <c r="B359" s="28">
         <v>100800</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D359" s="28" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E359" s="28" t="s">
-        <v>143</v>
+        <v>590</v>
       </c>
       <c r="F359" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G359" s="28" t="s">
-        <v>547</v>
+        <v>464</v>
       </c>
       <c r="H359" s="28" t="s">
         <v>589</v>
       </c>
       <c r="I359" s="28" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K359" s="112"/>
     </row>
     <row r="360" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A360" s="28">
-        <v>10080005</v>
+        <v>10080006</v>
       </c>
       <c r="B360" s="28">
         <v>100800</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>438</v>
       </c>
       <c r="E360" s="28" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F360" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G360" s="28" t="s">
-        <v>464</v>
+        <v>547</v>
       </c>
       <c r="H360" s="28" t="s">
         <v>589</v>
@@ -14055,163 +14103,163 @@
     </row>
     <row r="361" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A361" s="28">
-        <v>10080006</v>
+        <v>10080007</v>
       </c>
       <c r="B361" s="28">
         <v>100800</v>
       </c>
       <c r="C361" s="28" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D361" s="28" t="s">
         <v>438</v>
       </c>
       <c r="E361" s="28" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F361" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G361" s="28" t="s">
-        <v>466</v>
+        <v>548</v>
       </c>
       <c r="H361" s="28" t="s">
         <v>589</v>
       </c>
       <c r="I361" s="28" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K361" s="112"/>
     </row>
     <row r="362" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A362" s="28">
-        <v>10080007</v>
+        <v>10080008</v>
       </c>
       <c r="B362" s="28">
         <v>100800</v>
       </c>
       <c r="C362" s="28" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="D362" s="28" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E362" s="28" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F362" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G362" s="28" t="s">
-        <v>548</v>
+        <v>341</v>
       </c>
       <c r="H362" s="28" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="I362" s="28" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K362" s="112"/>
     </row>
     <row r="363" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A363" s="28">
-        <v>10080008</v>
+        <v>10080009</v>
       </c>
       <c r="B363" s="28">
         <v>100800</v>
       </c>
       <c r="C363" s="28" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="D363" s="28" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E363" s="28" t="s">
-        <v>593</v>
+        <v>143</v>
       </c>
       <c r="F363" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G363" s="28" t="s">
-        <v>341</v>
+        <v>546</v>
       </c>
       <c r="H363" s="28" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="I363" s="28" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="K363" s="112"/>
     </row>
-    <row r="364" s="28" customFormat="1" ht="16.5" spans="1:12">
+    <row r="364" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A364" s="28">
-        <v>10080009</v>
+        <v>10080010</v>
       </c>
       <c r="B364" s="28">
         <v>100800</v>
       </c>
       <c r="C364" s="28" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D364" s="28" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E364" s="28" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="F364" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G364" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="H364" s="28" t="s">
-        <v>589</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="H364" s="28"/>
       <c r="I364" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="K364" s="112"/>
-    </row>
-    <row r="365" s="27" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A365" s="28">
-        <v>10080010</v>
-      </c>
-      <c r="B365" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C365" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="D365" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E365" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F365" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G365" s="28" t="s">
-        <v>551</v>
-      </c>
-      <c r="H365" s="28"/>
-      <c r="I365" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="J365" s="28"/>
-      <c r="K365" s="28"/>
-      <c r="L365" s="28"/>
+      <c r="J364" s="28"/>
+      <c r="K364" s="28"/>
+      <c r="L364" s="28"/>
+    </row>
+    <row r="365" s="29" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A365" s="29">
+        <v>10530001</v>
+      </c>
+      <c r="B365" s="29">
+        <v>105300</v>
+      </c>
+      <c r="C365" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="D365" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E365" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="F365" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G365" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="H365" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="I365" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="K365" s="113"/>
     </row>
     <row r="366" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A366" s="29">
-        <v>10530001</v>
+        <v>10530002</v>
       </c>
       <c r="B366" s="29">
         <v>105300</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D366" s="29" t="s">
         <v>21</v>
@@ -14229,22 +14277,22 @@
         <v>597</v>
       </c>
       <c r="I366" s="29" t="s">
-        <v>340</v>
+        <v>599</v>
       </c>
       <c r="K366" s="113"/>
     </row>
     <row r="367" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A367" s="29">
-        <v>10530002</v>
+        <v>10530003</v>
       </c>
       <c r="B367" s="29">
         <v>105300</v>
       </c>
       <c r="C367" s="29" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D367" s="29" t="s">
-        <v>21</v>
+        <v>566</v>
       </c>
       <c r="E367" s="29" t="s">
         <v>136</v>
@@ -14259,49 +14307,49 @@
         <v>597</v>
       </c>
       <c r="I367" s="29" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K367" s="113"/>
     </row>
     <row r="368" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A368" s="29">
-        <v>10530003</v>
+        <v>10530004</v>
       </c>
       <c r="B368" s="29">
         <v>105300</v>
       </c>
       <c r="C368" s="29" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D368" s="29" t="s">
-        <v>566</v>
+        <v>328</v>
       </c>
       <c r="E368" s="29" t="s">
-        <v>136</v>
+        <v>603</v>
       </c>
       <c r="F368" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G368" s="29" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="H368" s="29" t="s">
         <v>597</v>
       </c>
       <c r="I368" s="29" t="s">
-        <v>601</v>
+        <v>294</v>
       </c>
       <c r="K368" s="113"/>
     </row>
     <row r="369" s="29" customFormat="1" ht="16.5" spans="1:11">
       <c r="A369" s="29">
-        <v>10530004</v>
+        <v>10530006</v>
       </c>
       <c r="B369" s="29">
         <v>105300</v>
       </c>
       <c r="C369" s="29" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D369" s="29" t="s">
         <v>328</v>
@@ -14313,58 +14361,58 @@
         <v>133</v>
       </c>
       <c r="G369" s="29" t="s">
-        <v>604</v>
+        <v>353</v>
       </c>
       <c r="H369" s="29" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="I369" s="29" t="s">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="K369" s="113"/>
     </row>
-    <row r="370" s="29" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A370" s="29">
-        <v>10530006</v>
-      </c>
-      <c r="B370" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C370" s="29" t="s">
-        <v>605</v>
-      </c>
-      <c r="D370" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="E370" s="29" t="s">
-        <v>603</v>
-      </c>
-      <c r="F370" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G370" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="H370" s="29" t="s">
-        <v>606</v>
-      </c>
-      <c r="I370" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="K370" s="113"/>
+    <row r="370" s="30" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A370" s="30">
+        <v>10570001</v>
+      </c>
+      <c r="B370" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C370" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D370" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="E370" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F370" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G370" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="H370" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="I370" s="30" t="s">
+        <v>601</v>
+      </c>
+      <c r="K370" s="114"/>
     </row>
     <row r="371" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A371" s="30">
-        <v>10570001</v>
+        <v>10570002</v>
       </c>
       <c r="B371" s="30">
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D371" s="30" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E371" s="30" t="s">
         <v>114</v>
@@ -14379,19 +14427,19 @@
         <v>608</v>
       </c>
       <c r="I371" s="30" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="K371" s="114"/>
     </row>
     <row r="372" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A372" s="30">
-        <v>10570002</v>
+        <v>10570003</v>
       </c>
       <c r="B372" s="30">
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>415</v>
+        <v>609</v>
       </c>
       <c r="D372" s="30" t="s">
         <v>328</v>
@@ -14409,139 +14457,139 @@
         <v>608</v>
       </c>
       <c r="I372" s="30" t="s">
-        <v>599</v>
+        <v>340</v>
       </c>
       <c r="K372" s="114"/>
     </row>
     <row r="373" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A373" s="30">
-        <v>10570003</v>
+        <v>10570004</v>
       </c>
       <c r="B373" s="30">
         <v>105700</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D373" s="30" t="s">
         <v>328</v>
       </c>
       <c r="E373" s="30" t="s">
-        <v>114</v>
+        <v>611</v>
       </c>
       <c r="F373" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G373" s="30" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="H373" s="30" t="s">
         <v>608</v>
       </c>
       <c r="I373" s="30" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="K373" s="114"/>
     </row>
     <row r="374" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A374" s="30">
-        <v>10570004</v>
+        <v>10570005</v>
       </c>
       <c r="B374" s="30">
         <v>105700</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>610</v>
+        <v>253</v>
       </c>
       <c r="D374" s="30" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E374" s="30" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F374" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G374" s="30" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H374" s="30" t="s">
-        <v>608</v>
+        <v>455</v>
       </c>
       <c r="I374" s="30" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K374" s="114"/>
     </row>
     <row r="375" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A375" s="30">
-        <v>10570005</v>
+        <v>10570006</v>
       </c>
       <c r="B375" s="30">
         <v>105700</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D375" s="30" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E375" s="30" t="s">
-        <v>613</v>
+        <v>257</v>
       </c>
       <c r="F375" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G375" s="30" t="s">
-        <v>614</v>
-      </c>
-      <c r="H375" s="30" t="s">
-        <v>455</v>
+        <v>615</v>
       </c>
       <c r="I375" s="30" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="K375" s="114"/>
     </row>
-    <row r="376" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A376" s="30">
-        <v>10570006</v>
-      </c>
-      <c r="B376" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C376" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="D376" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E376" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="F376" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G376" s="30" t="s">
-        <v>615</v>
-      </c>
-      <c r="I376" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="K376" s="114"/>
+    <row r="376" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A376" s="31">
+        <v>10580001</v>
+      </c>
+      <c r="B376" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C376" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D376" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="E376" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F376" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G376" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="H376" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="I376" s="31" t="s">
+        <v>601</v>
+      </c>
+      <c r="K376" s="115"/>
     </row>
     <row r="377" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A377" s="31">
-        <v>10580001</v>
+        <v>10580002</v>
       </c>
       <c r="B377" s="31">
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="D377" s="31" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E377" s="31" t="s">
         <v>299</v>
@@ -14556,19 +14604,19 @@
         <v>617</v>
       </c>
       <c r="I377" s="31" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="K377" s="115"/>
     </row>
     <row r="378" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A378" s="31">
-        <v>10580002</v>
+        <v>10580003</v>
       </c>
       <c r="B378" s="31">
         <v>105800</v>
       </c>
       <c r="C378" s="31" t="s">
-        <v>259</v>
+        <v>609</v>
       </c>
       <c r="D378" s="31" t="s">
         <v>328</v>
@@ -14586,163 +14634,163 @@
         <v>617</v>
       </c>
       <c r="I378" s="31" t="s">
-        <v>599</v>
+        <v>340</v>
       </c>
       <c r="K378" s="115"/>
     </row>
     <row r="379" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A379" s="31">
-        <v>10580003</v>
+        <v>10580004</v>
       </c>
       <c r="B379" s="31">
         <v>105800</v>
       </c>
       <c r="C379" s="31" t="s">
-        <v>609</v>
+        <v>253</v>
       </c>
       <c r="D379" s="31" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="E379" s="31" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="F379" s="31" t="s">
         <v>133</v>
       </c>
       <c r="G379" s="31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H379" s="31" t="s">
         <v>617</v>
       </c>
       <c r="I379" s="31" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K379" s="115"/>
     </row>
-    <row r="380" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A380" s="31">
-        <v>10580004</v>
-      </c>
-      <c r="B380" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C380" s="31" t="s">
+    <row r="380" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A380" s="32">
+        <v>10550001</v>
+      </c>
+      <c r="B380" s="32">
+        <v>105500</v>
+      </c>
+      <c r="C380" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D380" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E380" s="31" t="s">
+      <c r="D380" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E380" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F380" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G380" s="31" t="s">
-        <v>618</v>
-      </c>
-      <c r="H380" s="31" t="s">
-        <v>617</v>
-      </c>
-      <c r="I380" s="31" t="s">
+      <c r="F380" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G380" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="I380" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K380" s="115"/>
+      <c r="K380" s="116"/>
     </row>
     <row r="381" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A381" s="32">
-        <v>10550001</v>
+        <v>10550002</v>
       </c>
       <c r="B381" s="32">
         <v>105500</v>
       </c>
       <c r="C381" s="32" t="s">
-        <v>253</v>
+        <v>620</v>
       </c>
       <c r="D381" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E381" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F381" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G381" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I381" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K381" s="116"/>
     </row>
-    <row r="382" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A382" s="32">
-        <v>10550002</v>
-      </c>
-      <c r="B382" s="32">
-        <v>105500</v>
-      </c>
-      <c r="C382" s="32" t="s">
-        <v>620</v>
-      </c>
-      <c r="D382" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E382" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="F382" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G382" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I382" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K382" s="116"/>
+    <row r="382" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A382" s="33">
+        <v>10480001</v>
+      </c>
+      <c r="B382" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C382" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="D382" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E382" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F382" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G382" s="33" t="s">
+        <v>621</v>
+      </c>
+      <c r="H382" s="33" t="s">
+        <v>622</v>
+      </c>
+      <c r="I382" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="K382" s="82"/>
     </row>
     <row r="383" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A383" s="33">
-        <v>10480001</v>
+        <v>10480002</v>
       </c>
       <c r="B383" s="33">
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="D383" s="33" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E383" s="33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F383" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G383" s="33" t="s">
-        <v>621</v>
+        <v>460</v>
       </c>
       <c r="H383" s="33" t="s">
         <v>622</v>
       </c>
       <c r="I383" s="33" t="s">
-        <v>546</v>
+        <v>325</v>
       </c>
       <c r="K383" s="82"/>
     </row>
     <row r="384" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A384" s="33">
-        <v>10480002</v>
+        <v>10480003</v>
       </c>
       <c r="B384" s="33">
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D384" s="33" t="s">
         <v>328</v>
@@ -14760,22 +14808,22 @@
         <v>622</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K384" s="82"/>
     </row>
     <row r="385" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A385" s="33">
-        <v>10480003</v>
+        <v>10480004</v>
       </c>
       <c r="B385" s="33">
         <v>104800</v>
       </c>
       <c r="C385" s="33" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D385" s="33" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E385" s="33" t="s">
         <v>143</v>
@@ -14790,22 +14838,22 @@
         <v>622</v>
       </c>
       <c r="I385" s="33" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="K385" s="82"/>
     </row>
     <row r="386" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A386" s="33">
-        <v>10480004</v>
+        <v>10480005</v>
       </c>
       <c r="B386" s="33">
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>625</v>
+        <v>289</v>
       </c>
       <c r="D386" s="33" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="E386" s="33" t="s">
         <v>143</v>
@@ -14820,61 +14868,61 @@
         <v>622</v>
       </c>
       <c r="I386" s="33" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K386" s="82"/>
     </row>
     <row r="387" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A387" s="33">
-        <v>10480005</v>
+        <v>10480006</v>
       </c>
       <c r="B387" s="33">
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="D387" s="33" t="s">
         <v>422</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>143</v>
+        <v>626</v>
       </c>
       <c r="F387" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G387" s="33" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H387" s="33" t="s">
         <v>622</v>
       </c>
       <c r="I387" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="K387" s="82"/>
+        <v>333</v>
+      </c>
+      <c r="K387" s="117"/>
     </row>
     <row r="388" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A388" s="33">
-        <v>10480006</v>
+        <v>10480007</v>
       </c>
       <c r="B388" s="33">
         <v>104800</v>
       </c>
       <c r="C388" s="33" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D388" s="33" t="s">
         <v>422</v>
       </c>
       <c r="E388" s="33" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F388" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G388" s="33" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H388" s="33" t="s">
         <v>622</v>
@@ -14886,133 +14934,130 @@
     </row>
     <row r="389" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A389" s="33">
-        <v>10480007</v>
+        <v>10480008</v>
       </c>
       <c r="B389" s="33">
         <v>104800</v>
       </c>
       <c r="C389" s="33" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="D389" s="33" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E389" s="33" t="s">
-        <v>627</v>
+        <v>254</v>
       </c>
       <c r="F389" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G389" s="33" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="H389" s="33" t="s">
-        <v>622</v>
+        <v>408</v>
       </c>
       <c r="I389" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K389" s="117"/>
-    </row>
-    <row r="390" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A390" s="33">
-        <v>10480008</v>
-      </c>
-      <c r="B390" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C390" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K389" s="82"/>
+    </row>
+    <row r="390" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A390" s="32">
+        <v>10550101</v>
+      </c>
+      <c r="B390" s="32">
+        <v>105501</v>
+      </c>
+      <c r="C390" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D390" s="33" t="s">
+      <c r="D390" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E390" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F390" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G390" s="33" t="s">
-        <v>469</v>
-      </c>
-      <c r="H390" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="I390" s="33" t="s">
+      <c r="E390" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F390" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G390" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="I390" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K390" s="82"/>
+      <c r="K390" s="116"/>
     </row>
     <row r="391" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A391" s="32">
-        <v>10550101</v>
+        <v>10550102</v>
       </c>
       <c r="B391" s="32">
         <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>253</v>
+        <v>620</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F391" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I391" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K391" s="116"/>
     </row>
     <row r="392" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A392" s="32">
-        <v>10550102</v>
+        <v>10550103</v>
       </c>
       <c r="B392" s="32">
         <v>105501</v>
       </c>
       <c r="C392" s="32" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="D392" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="F392" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>297</v>
+        <v>619</v>
       </c>
       <c r="I392" s="32" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K392" s="116"/>
     </row>
     <row r="393" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A393" s="32">
-        <v>10550103</v>
+        <v>10550201</v>
       </c>
       <c r="B393" s="32">
-        <v>105501</v>
+        <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>628</v>
+        <v>253</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="F393" s="32" t="s">
         <v>133</v>
@@ -15027,46 +15072,46 @@
     </row>
     <row r="394" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A394" s="32">
-        <v>10550201</v>
+        <v>10550202</v>
       </c>
       <c r="B394" s="32">
         <v>105502</v>
       </c>
       <c r="C394" s="32" t="s">
-        <v>253</v>
+        <v>620</v>
       </c>
       <c r="D394" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F394" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G394" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I394" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K394" s="116"/>
     </row>
-    <row r="395" s="32" customFormat="1" ht="16.5" spans="1:11">
+    <row r="395" ht="16.5" spans="1:11">
       <c r="A395" s="32">
-        <v>10550202</v>
+        <v>10550203</v>
       </c>
       <c r="B395" s="32">
         <v>105502</v>
       </c>
       <c r="C395" s="32" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D395" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="F395" s="32" t="s">
         <v>133</v>
@@ -15075,78 +15120,81 @@
         <v>297</v>
       </c>
       <c r="I395" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K395" s="116"/>
-    </row>
-    <row r="396" ht="16.5" spans="1:11">
-      <c r="A396" s="32">
-        <v>10550203</v>
-      </c>
-      <c r="B396" s="32">
-        <v>105502</v>
-      </c>
-      <c r="C396" s="32" t="s">
-        <v>629</v>
-      </c>
-      <c r="D396" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E396" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="F396" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G396" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I396" s="32" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="396" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A396" s="34">
+        <v>10410001</v>
+      </c>
+      <c r="B396" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C396" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="D396" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="E396" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="F396" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G396" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H396" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="I396" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="K396" s="118"/>
     </row>
     <row r="397" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A397" s="34">
-        <v>10410001</v>
+        <v>10410002</v>
       </c>
       <c r="B397" s="34">
         <v>104100</v>
       </c>
       <c r="C397" s="34" t="s">
-        <v>313</v>
+        <v>556</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E397" s="34" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="F397" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="H397" s="34" t="s">
         <v>455</v>
       </c>
       <c r="I397" s="34" t="s">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="K397" s="118"/>
     </row>
     <row r="398" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A398" s="34">
-        <v>10410002</v>
+        <v>10410003</v>
       </c>
       <c r="B398" s="34">
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E398" s="34" t="s">
         <v>114</v>
@@ -15161,115 +15209,115 @@
         <v>455</v>
       </c>
       <c r="I398" s="34" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K398" s="118"/>
     </row>
     <row r="399" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A399" s="34">
-        <v>10410003</v>
+        <v>10410004</v>
       </c>
       <c r="B399" s="34">
         <v>104100</v>
       </c>
       <c r="C399" s="34" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="D399" s="34" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E399" s="34" t="s">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="F399" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G399" s="34" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H399" s="34" t="s">
-        <v>455</v>
+        <v>630</v>
       </c>
       <c r="I399" s="34" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K399" s="118"/>
     </row>
     <row r="400" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A400" s="34">
-        <v>10410004</v>
+        <v>10410005</v>
       </c>
       <c r="B400" s="34">
         <v>104100</v>
       </c>
       <c r="C400" s="34" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D400" s="34" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="E400" s="34" t="s">
-        <v>416</v>
+        <v>114</v>
       </c>
       <c r="F400" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G400" s="34" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H400" s="34" t="s">
-        <v>630</v>
+        <v>455</v>
       </c>
       <c r="I400" s="34" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K400" s="118"/>
     </row>
-    <row r="401" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A401" s="34">
-        <v>10410005</v>
-      </c>
-      <c r="B401" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C401" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D401" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E401" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F401" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G401" s="34" t="s">
+    <row r="401" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A401" s="35">
+        <v>10420001</v>
+      </c>
+      <c r="B401" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C401" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="D401" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="E401" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F401" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G401" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="H401" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I401" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="K401" s="118"/>
+      <c r="H401" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="I401" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="K401" s="119"/>
     </row>
     <row r="402" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A402" s="35">
-        <v>10420001</v>
+        <v>10420002</v>
       </c>
       <c r="B402" s="35">
         <v>104200</v>
       </c>
       <c r="C402" s="35" t="s">
-        <v>313</v>
+        <v>556</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="E402" s="35" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F402" s="35" t="s">
         <v>133</v>
@@ -15281,22 +15329,22 @@
         <v>550</v>
       </c>
       <c r="I402" s="35" t="s">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="K402" s="119"/>
     </row>
     <row r="403" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A403" s="35">
-        <v>10420002</v>
+        <v>10420003</v>
       </c>
       <c r="B403" s="35">
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="E403" s="35" t="s">
         <v>143</v>
@@ -15311,99 +15359,403 @@
         <v>550</v>
       </c>
       <c r="I403" s="35" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K403" s="119"/>
     </row>
     <row r="404" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A404" s="35">
-        <v>10420003</v>
+        <v>10420004</v>
       </c>
       <c r="B404" s="35">
         <v>104200</v>
       </c>
       <c r="C404" s="35" t="s">
-        <v>412</v>
+        <v>253</v>
       </c>
       <c r="D404" s="35" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E404" s="35" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F404" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G404" s="35" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H404" s="35" t="s">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="I404" s="35" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K404" s="119"/>
     </row>
     <row r="405" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A405" s="35">
-        <v>10420004</v>
+        <v>10420005</v>
       </c>
       <c r="B405" s="35">
         <v>104200</v>
       </c>
       <c r="C405" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="D405" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="E405" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="F405" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G405" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H405" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="I405" s="35" t="s">
+        <v>340</v>
+      </c>
+      <c r="K405" s="119"/>
+    </row>
+    <row r="406" ht="16.5" spans="1:11">
+      <c r="A406" s="32">
+        <v>10190001</v>
+      </c>
+      <c r="B406" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C406" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D406" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="E406" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F406" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G406" s="32" t="s">
+        <v>458</v>
+      </c>
+      <c r="H406" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I406" s="32" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="407" ht="16.5" spans="1:11">
+      <c r="A407" s="32">
+        <v>10190002</v>
+      </c>
+      <c r="B407" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C407" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="D407" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="E407" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="F407" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G407" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="H407" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I407" s="32" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="408" ht="16.5" spans="1:11">
+      <c r="A408" s="32">
+        <v>10190003</v>
+      </c>
+      <c r="B408" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C408" s="32" t="s">
+        <v>632</v>
+      </c>
+      <c r="D408" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="E408" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="F408" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G408" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="H408" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I408" s="32" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="409" ht="16.5" spans="1:11">
+      <c r="A409" s="32">
+        <v>10190004</v>
+      </c>
+      <c r="B409" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C409" s="32" t="s">
+        <v>556</v>
+      </c>
+      <c r="D409" s="32" t="s">
+        <v>633</v>
+      </c>
+      <c r="E409" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="F409" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G409" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="H409" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I409" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="410" ht="16.5" spans="1:11">
+      <c r="A410" s="32">
+        <v>10190005</v>
+      </c>
+      <c r="B410" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C410" s="32" t="s">
+        <v>600</v>
+      </c>
+      <c r="D410" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="E410" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="F410" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G410" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="H410" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I410" s="32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="411" ht="16.5" spans="1:11">
+      <c r="A411" s="32">
+        <v>10190006</v>
+      </c>
+      <c r="B411" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C411" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="D411" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="E411" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="F411" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G411" s="32" t="s">
+        <v>635</v>
+      </c>
+      <c r="H411" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I411" s="32" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="412" ht="16.5" spans="1:11">
+      <c r="A412" s="32">
+        <v>10190007</v>
+      </c>
+      <c r="B412" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C412" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="D412" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="E412" s="32" t="s">
+        <v>636</v>
+      </c>
+      <c r="F412" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G412" s="32" t="s">
+        <v>637</v>
+      </c>
+      <c r="H412" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I412" s="32" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="413" ht="16.5" spans="1:11">
+      <c r="A413" s="32">
+        <v>10190008</v>
+      </c>
+      <c r="B413" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C413" s="32" t="s">
+        <v>638</v>
+      </c>
+      <c r="D413" s="32" t="s">
+        <v>639</v>
+      </c>
+      <c r="E413" s="32" t="s">
+        <v>640</v>
+      </c>
+      <c r="F413" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G413" s="32" t="s">
+        <v>635</v>
+      </c>
+      <c r="H413" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I413" s="32" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="414" ht="16.5" spans="1:11">
+      <c r="A414" s="32">
+        <v>10190009</v>
+      </c>
+      <c r="B414" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C414" s="32" t="s">
+        <v>642</v>
+      </c>
+      <c r="D414" s="32" t="s">
+        <v>639</v>
+      </c>
+      <c r="E414" s="32" t="s">
+        <v>643</v>
+      </c>
+      <c r="F414" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G414" s="32" t="s">
+        <v>637</v>
+      </c>
+      <c r="H414" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I414" s="32" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="415" ht="16.5" spans="1:11">
+      <c r="A415" s="32">
+        <v>10190010</v>
+      </c>
+      <c r="B415" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C415" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D405" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="E405" s="35" t="s">
+      <c r="D415" s="32" t="s">
+        <v>645</v>
+      </c>
+      <c r="E415" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="F405" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G405" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="H405" s="35" t="s">
-        <v>594</v>
-      </c>
-      <c r="I405" s="35" t="s">
+      <c r="F415" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G415" s="32" t="s">
+        <v>646</v>
+      </c>
+      <c r="H415" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="I415" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K405" s="119"/>
-    </row>
-    <row r="406" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A406" s="35">
-        <v>10420005</v>
-      </c>
-      <c r="B406" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C406" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="D406" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="E406" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F406" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G406" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H406" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I406" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="K406" s="119"/>
+    </row>
+    <row r="416" ht="16.5" spans="1:11">
+      <c r="A416" s="32"/>
+      <c r="B416" s="32"/>
+      <c r="C416" s="32"/>
+      <c r="D416" s="32"/>
+      <c r="E416" s="32"/>
+      <c r="F416" s="32"/>
+      <c r="G416" s="32"/>
+      <c r="H416" s="32"/>
+      <c r="I416" s="32"/>
+    </row>
+    <row r="417" ht="16.5" spans="1:9">
+      <c r="A417" s="32"/>
+      <c r="B417" s="32"/>
+      <c r="C417" s="32"/>
+      <c r="D417" s="32"/>
+      <c r="E417" s="32"/>
+      <c r="F417" s="32"/>
+      <c r="G417" s="32"/>
+      <c r="H417" s="32"/>
+      <c r="I417" s="32"/>
+    </row>
+    <row r="418" ht="16.5" spans="1:9">
+      <c r="A418" s="32"/>
+      <c r="B418" s="32"/>
+      <c r="C418" s="32"/>
+      <c r="D418" s="32"/>
+      <c r="E418" s="32"/>
+      <c r="F418" s="32"/>
+      <c r="G418" s="32"/>
+      <c r="H418" s="32"/>
+      <c r="I418" s="32"/>
+    </row>
+    <row r="419" ht="16.5" spans="1:9">
+      <c r="A419" s="32"/>
+      <c r="B419" s="32"/>
+      <c r="C419" s="32"/>
+      <c r="D419" s="32"/>
+      <c r="E419" s="32"/>
+      <c r="F419" s="32"/>
+      <c r="G419" s="32"/>
+      <c r="H419" s="32"/>
+      <c r="I419" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15423,24 +15775,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="D1" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="B2" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="D2" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="E2" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15448,16 +15800,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="F3" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15465,16 +15817,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="F4" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15482,16 +15834,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="F5" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15507,7 +15859,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15515,7 +15867,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15523,7 +15875,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15531,7 +15883,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15539,7 +15891,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15547,7 +15899,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15555,7 +15907,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15563,7 +15915,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15571,7 +15923,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15579,7 +15931,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15587,7 +15939,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15595,7 +15947,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15603,7 +15955,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15611,7 +15963,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15619,7 +15971,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15627,7 +15979,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15635,7 +15987,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15643,7 +15995,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -15651,7 +16003,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -15659,7 +16011,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -15667,7 +16019,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -15675,7 +16027,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -15683,7 +16035,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -15691,7 +16043,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -15699,7 +16051,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -15707,7 +16059,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -15715,7 +16067,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -15723,7 +16075,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -15731,7 +16083,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -15739,7 +16091,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -15747,7 +16099,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -15755,7 +16107,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -15763,7 +16115,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -15771,7 +16123,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -15779,7 +16131,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -15787,7 +16139,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -15795,7 +16147,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -15803,7 +16155,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -15811,7 +16163,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15819,7 +16171,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -15827,7 +16179,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -15835,7 +16187,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2828" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="705">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1393,13 +1393,19 @@
     <t>1_200|2_200|3_50|4_30|5_15|6_5</t>
   </si>
   <si>
+    <t>普通概率改出wild符号</t>
+  </si>
+  <si>
+    <t>9_10</t>
+  </si>
+  <si>
     <t>0_47|1_30|2_15|3_10|4_3</t>
   </si>
   <si>
     <t>概率改出scatter符号</t>
   </si>
   <si>
-    <t>9_11_12_13_14</t>
+    <t>9_10_11_12_13_14</t>
   </si>
   <si>
     <t>0_55|1_40|2_5</t>
@@ -1411,7 +1417,13 @@
     <t>11_10|12_5|13_2|14_1</t>
   </si>
   <si>
-    <t>9_10</t>
+    <t>10_11_12_13_14</t>
+  </si>
+  <si>
+    <t>免费概率改出wild符号</t>
+  </si>
+  <si>
+    <t>0_60|1_30|2_9|3_1</t>
   </si>
   <si>
     <t>7_8</t>
@@ -1525,9 +1537,6 @@
     <t>0_30|1_1</t>
   </si>
   <si>
-    <t>9_10_11_12_13_14</t>
-  </si>
-  <si>
     <t>改出百搭符号</t>
   </si>
   <si>
@@ -1543,13 +1552,16 @@
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
   </si>
   <si>
-    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1</t>
+    <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|43_2|44_2|45_2|46_2|47_2|48_2|49_2|50_2|51_2|52_2|53_2</t>
   </si>
   <si>
     <t>8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
   </si>
   <si>
-    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1</t>
+    <t>0_10|1_40|2_40|3_10</t>
+  </si>
+  <si>
+    <t>31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|41_1|54_2|55_2|56_2|57_2|58_2|59_2|60_2|61_2|62_2|63_2|64_2</t>
   </si>
   <si>
     <t>9_1_1|10_1_1|11_1_1|12_1_1|15_1_1|16_1_1|17_1_1|18_1_1|21_1_1|22_1_1|23_1_1|24_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
@@ -2048,9 +2060,6 @@
   </si>
   <si>
     <t>改出多格图标</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14</t>
   </si>
   <si>
     <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85</t>
@@ -3556,7 +3565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N419"/>
+  <dimension ref="A1:N420"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -10130,7 +10139,7 @@
         <v>295</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
       <c r="E227" s="22" t="s">
         <v>157</v>
@@ -10141,11 +10150,11 @@
       <c r="G227" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="H227" s="22">
-        <v>10</v>
+      <c r="H227" s="22" t="s">
+        <v>412</v>
       </c>
       <c r="I227" s="22" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K227" s="105"/>
     </row>
@@ -10157,7 +10166,7 @@
         <v>102700</v>
       </c>
       <c r="C228" s="22" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D228" s="22" t="s">
         <v>348</v>
@@ -10172,10 +10181,10 @@
         <v>234</v>
       </c>
       <c r="H228" s="22" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I228" s="22" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K228" s="105"/>
     </row>
@@ -10187,7 +10196,7 @@
         <v>102700</v>
       </c>
       <c r="C229" s="22" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D229" s="22" t="s">
         <v>348</v>
@@ -10202,7 +10211,7 @@
         <v>234</v>
       </c>
       <c r="H229" s="22" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I229" s="22" t="s">
         <v>72</v>
@@ -10217,7 +10226,7 @@
         <v>102700</v>
       </c>
       <c r="C230" s="22" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D230" s="22" t="s">
         <v>328</v>
@@ -10232,7 +10241,7 @@
         <v>234</v>
       </c>
       <c r="H230" s="22" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I230" s="22" t="s">
         <v>291</v>
@@ -10253,7 +10262,7 @@
         <v>348</v>
       </c>
       <c r="E231" s="22" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F231" s="14" t="s">
         <v>133</v>
@@ -10262,7 +10271,7 @@
         <v>255</v>
       </c>
       <c r="H231" s="22" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I231" s="22" t="s">
         <v>39</v>
@@ -10291,47 +10300,47 @@
       <c r="G232" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="H232" s="22">
-        <v>9</v>
+      <c r="H232" s="22" t="s">
+        <v>415</v>
       </c>
       <c r="I232" s="22" t="s">
         <v>106</v>
       </c>
       <c r="K232" s="105"/>
     </row>
-    <row r="233" s="23" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A233" s="106">
-        <v>10370001</v>
-      </c>
-      <c r="B233" s="23">
-        <v>103700</v>
-      </c>
-      <c r="C233" s="23" t="s">
+    <row r="233" s="22" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A233" s="14">
+        <v>10270007</v>
+      </c>
+      <c r="B233" s="22">
+        <v>102700</v>
+      </c>
+      <c r="C233" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="D233" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="E233" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="F233" s="106" t="s">
-        <v>133</v>
-      </c>
-      <c r="G233" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="H233" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="I233" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="K233" s="107"/>
+      <c r="D233" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="E233" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="F233" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G233" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="H233" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="I233" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="K233" s="105"/>
     </row>
     <row r="234" s="23" customFormat="1" ht="16.5" spans="1:11">
       <c r="A234" s="106">
-        <v>10370002</v>
+        <v>10370001</v>
       </c>
       <c r="B234" s="23">
         <v>103700</v>
@@ -10340,7 +10349,7 @@
         <v>295</v>
       </c>
       <c r="D234" s="23" t="s">
-        <v>419</v>
+        <v>348</v>
       </c>
       <c r="E234" s="23" t="s">
         <v>296</v>
@@ -10349,112 +10358,112 @@
         <v>133</v>
       </c>
       <c r="G234" s="23" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="H234" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I234" s="23" t="s">
-        <v>420</v>
+        <v>307</v>
       </c>
       <c r="K234" s="107"/>
     </row>
     <row r="235" s="23" customFormat="1" ht="16.5" spans="1:11">
       <c r="A235" s="106">
-        <v>10370003</v>
+        <v>10370002</v>
       </c>
       <c r="B235" s="23">
         <v>103700</v>
       </c>
       <c r="C235" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D235" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="E235" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="F235" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="G235" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H235" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="I235" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="K235" s="107"/>
+    </row>
+    <row r="236" s="23" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A236" s="106">
+        <v>10370003</v>
+      </c>
+      <c r="B236" s="23">
+        <v>103700</v>
+      </c>
+      <c r="C236" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="E235" s="23" t="s">
+      <c r="E236" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="F235" s="106" t="s">
-        <v>133</v>
-      </c>
-      <c r="G235" s="23" t="s">
+      <c r="F236" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="G236" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="I235" s="23" t="s">
+      <c r="I236" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="K235" s="107"/>
-    </row>
-    <row r="236" s="24" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A236" s="11">
-        <v>10310001</v>
-      </c>
-      <c r="B236" s="24">
-        <v>103100</v>
-      </c>
-      <c r="C236" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="D236" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="E236" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="F236" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G236" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="H236" s="24">
-        <v>12</v>
-      </c>
-      <c r="I236" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="K236" s="108"/>
+      <c r="K236" s="107"/>
     </row>
     <row r="237" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A237" s="11">
-        <v>10310002</v>
+        <v>10310001</v>
       </c>
       <c r="B237" s="24">
         <v>103100</v>
       </c>
       <c r="C237" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D237" s="24" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E237" s="24" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="F237" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G237" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H237" s="24" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="H237" s="24">
+        <v>12</v>
       </c>
       <c r="I237" s="24" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K237" s="108"/>
     </row>
     <row r="238" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A238" s="11">
-        <v>10310003</v>
+        <v>10310002</v>
       </c>
       <c r="B238" s="24">
         <v>103100</v>
       </c>
       <c r="C238" s="24" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D238" s="24" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E238" s="24" t="s">
         <v>23</v>
@@ -10463,10 +10472,10 @@
         <v>133</v>
       </c>
       <c r="G238" s="24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H238" s="24" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I238" s="24" t="s">
         <v>39</v>
@@ -10475,16 +10484,16 @@
     </row>
     <row r="239" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A239" s="11">
-        <v>10310004</v>
+        <v>10310003</v>
       </c>
       <c r="B239" s="24">
         <v>103100</v>
       </c>
       <c r="C239" s="24" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D239" s="24" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E239" s="24" t="s">
         <v>23</v>
@@ -10493,10 +10502,10 @@
         <v>133</v>
       </c>
       <c r="G239" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H239" s="24" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I239" s="24" t="s">
         <v>39</v>
@@ -10505,46 +10514,46 @@
     </row>
     <row r="240" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A240" s="11">
-        <v>10310005</v>
+        <v>10310004</v>
       </c>
       <c r="B240" s="24">
         <v>103100</v>
       </c>
       <c r="C240" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="D240" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="D240" s="24" t="s">
-        <v>425</v>
-      </c>
       <c r="E240" s="24" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="F240" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G240" s="24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H240" s="24" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I240" s="24" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="K240" s="108"/>
     </row>
     <row r="241" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A241" s="11">
-        <v>10310006</v>
+        <v>10310005</v>
       </c>
       <c r="B241" s="24">
         <v>103100</v>
       </c>
       <c r="C241" s="24" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D241" s="24" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E241" s="24" t="s">
         <v>136</v>
@@ -10553,58 +10562,58 @@
         <v>133</v>
       </c>
       <c r="G241" s="24" t="s">
-        <v>266</v>
+        <v>176</v>
       </c>
       <c r="H241" s="24" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I241" s="24" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="K241" s="108"/>
     </row>
     <row r="242" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A242" s="11">
-        <v>10310007</v>
+        <v>10310006</v>
       </c>
       <c r="B242" s="24">
         <v>103100</v>
       </c>
       <c r="C242" s="24" t="s">
-        <v>246</v>
+        <v>434</v>
       </c>
       <c r="D242" s="24" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E242" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F242" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G242" s="24" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="H242" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I242" s="24" t="s">
-        <v>432</v>
+        <v>157</v>
       </c>
       <c r="K242" s="108"/>
     </row>
     <row r="243" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A243" s="11">
-        <v>10310008</v>
+        <v>10310007</v>
       </c>
       <c r="B243" s="24">
         <v>103100</v>
       </c>
       <c r="C243" s="24" t="s">
-        <v>433</v>
+        <v>246</v>
       </c>
       <c r="D243" s="24" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="E243" s="24" t="s">
         <v>140</v>
@@ -10616,25 +10625,25 @@
         <v>234</v>
       </c>
       <c r="H243" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I243" s="24" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K243" s="108"/>
     </row>
     <row r="244" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A244" s="11">
-        <v>10310009</v>
+        <v>10310008</v>
       </c>
       <c r="B244" s="24">
         <v>103100</v>
       </c>
       <c r="C244" s="24" t="s">
-        <v>289</v>
+        <v>437</v>
       </c>
       <c r="D244" s="24" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E244" s="24" t="s">
         <v>140</v>
@@ -10646,25 +10655,25 @@
         <v>234</v>
       </c>
       <c r="H244" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I244" s="24" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K244" s="108"/>
     </row>
     <row r="245" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A245" s="11">
-        <v>10310010</v>
+        <v>10310009</v>
       </c>
       <c r="B245" s="24">
         <v>103100</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>436</v>
+        <v>289</v>
       </c>
       <c r="D245" s="24" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E245" s="24" t="s">
         <v>140</v>
@@ -10673,58 +10682,58 @@
         <v>133</v>
       </c>
       <c r="G245" s="24" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H245" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I245" s="24" t="s">
-        <v>106</v>
+        <v>439</v>
       </c>
       <c r="K245" s="108"/>
     </row>
     <row r="246" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A246" s="11">
-        <v>10310011</v>
+        <v>10310010</v>
       </c>
       <c r="B246" s="24">
         <v>103100</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D246" s="24" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E246" s="24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F246" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G246" s="24" t="s">
-        <v>439</v>
+        <v>239</v>
       </c>
       <c r="H246" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I246" s="24" t="s">
-        <v>282</v>
+        <v>106</v>
       </c>
       <c r="K246" s="108"/>
     </row>
     <row r="247" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A247" s="11">
-        <v>10310012</v>
+        <v>10310011</v>
       </c>
       <c r="B247" s="24">
         <v>103100</v>
       </c>
       <c r="C247" s="24" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D247" s="24" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E247" s="24" t="s">
         <v>143</v>
@@ -10733,25 +10742,25 @@
         <v>133</v>
       </c>
       <c r="G247" s="24" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H247" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I247" s="24" t="s">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="K247" s="108"/>
     </row>
     <row r="248" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A248" s="11">
-        <v>10310013</v>
+        <v>10310012</v>
       </c>
       <c r="B248" s="24">
         <v>103100</v>
       </c>
       <c r="C248" s="24" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D248" s="24" t="s">
         <v>21</v>
@@ -10763,10 +10772,10 @@
         <v>133</v>
       </c>
       <c r="G248" s="24" t="s">
-        <v>255</v>
+        <v>443</v>
       </c>
       <c r="H248" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I248" s="24" t="s">
         <v>39</v>
@@ -10775,19 +10784,19 @@
     </row>
     <row r="249" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A249" s="11">
-        <v>10310014</v>
+        <v>10310013</v>
       </c>
       <c r="B249" s="24">
         <v>103100</v>
       </c>
       <c r="C249" s="24" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D249" s="24" t="s">
         <v>21</v>
       </c>
       <c r="E249" s="24" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F249" s="11" t="s">
         <v>133</v>
@@ -10796,7 +10805,7 @@
         <v>255</v>
       </c>
       <c r="H249" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I249" s="24" t="s">
         <v>39</v>
@@ -10805,97 +10814,97 @@
     </row>
     <row r="250" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A250" s="11">
-        <v>10310015</v>
+        <v>10310014</v>
       </c>
       <c r="B250" s="24">
         <v>103100</v>
       </c>
       <c r="C250" s="24" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D250" s="24" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E250" s="24" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F250" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G250" s="24" t="s">
-        <v>439</v>
+        <v>255</v>
       </c>
       <c r="H250" s="24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I250" s="24" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="K250" s="108"/>
     </row>
     <row r="251" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A251" s="11">
-        <v>10310016</v>
+        <v>10310015</v>
       </c>
       <c r="B251" s="24">
         <v>103100</v>
       </c>
       <c r="C251" s="24" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D251" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E251" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="F251" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G251" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="H251" s="24" t="s">
+        <v>435</v>
+      </c>
+      <c r="I251" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="K251" s="108"/>
+    </row>
+    <row r="252" s="24" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A252" s="11">
+        <v>10310016</v>
+      </c>
+      <c r="B252" s="24">
+        <v>103100</v>
+      </c>
+      <c r="C252" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="D252" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="E252" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F251" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G251" s="24" t="s">
+      <c r="F252" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G252" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="H251" s="24" t="s">
-        <v>445</v>
-      </c>
-      <c r="I251" s="24" t="s">
+      <c r="H252" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="I252" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="K251" s="108"/>
-    </row>
-    <row r="252" s="25" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A252" s="25">
-        <v>10400001</v>
-      </c>
-      <c r="B252" s="25">
-        <v>104000</v>
-      </c>
-      <c r="C252" s="25" t="s">
-        <v>295</v>
-      </c>
-      <c r="D252" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E252" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F252" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G252" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="H252" s="25" t="s">
-        <v>446</v>
-      </c>
-      <c r="I252" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="J252" s="109"/>
+      <c r="K252" s="108"/>
     </row>
     <row r="253" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A253" s="25">
-        <v>10400002</v>
+        <v>10400001</v>
       </c>
       <c r="B253" s="25">
         <v>104000</v>
@@ -10904,7 +10913,7 @@
         <v>295</v>
       </c>
       <c r="D253" s="25" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E253" s="25" t="s">
         <v>136</v>
@@ -10916,52 +10925,52 @@
         <v>234</v>
       </c>
       <c r="H253" s="25" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I253" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="K253" s="109"/>
+        <v>277</v>
+      </c>
+      <c r="J253" s="109"/>
     </row>
     <row r="254" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A254" s="25">
-        <v>10400003</v>
+        <v>10400002</v>
       </c>
       <c r="B254" s="25">
         <v>104000</v>
       </c>
       <c r="C254" s="25" t="s">
-        <v>448</v>
+        <v>295</v>
       </c>
       <c r="D254" s="25" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E254" s="25" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F254" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G254" s="25" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="H254" s="25" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="I254" s="25" t="s">
-        <v>39</v>
+        <v>451</v>
       </c>
       <c r="K254" s="109"/>
     </row>
     <row r="255" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A255" s="25">
-        <v>10400004</v>
+        <v>10400003</v>
       </c>
       <c r="B255" s="25">
         <v>104000</v>
       </c>
       <c r="C255" s="25" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D255" s="25" t="s">
         <v>21</v>
@@ -10973,10 +10982,10 @@
         <v>133</v>
       </c>
       <c r="G255" s="25" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H255" s="25" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I255" s="25" t="s">
         <v>39</v>
@@ -10985,13 +10994,13 @@
     </row>
     <row r="256" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A256" s="25">
-        <v>10400005</v>
+        <v>10400004</v>
       </c>
       <c r="B256" s="25">
         <v>104000</v>
       </c>
       <c r="C256" s="25" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D256" s="25" t="s">
         <v>21</v>
@@ -11003,10 +11012,10 @@
         <v>133</v>
       </c>
       <c r="G256" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H256" s="25" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I256" s="25" t="s">
         <v>39</v>
@@ -11015,16 +11024,16 @@
     </row>
     <row r="257" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A257" s="25">
-        <v>10400006</v>
+        <v>10400005</v>
       </c>
       <c r="B257" s="25">
         <v>104000</v>
       </c>
       <c r="C257" s="25" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D257" s="25" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E257" s="25" t="s">
         <v>140</v>
@@ -11033,28 +11042,28 @@
         <v>133</v>
       </c>
       <c r="G257" s="25" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H257" s="25" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I257" s="25" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="K257" s="109"/>
     </row>
     <row r="258" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A258" s="25">
-        <v>10400007</v>
+        <v>10400006</v>
       </c>
       <c r="B258" s="25">
         <v>104000</v>
       </c>
       <c r="C258" s="25" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D258" s="25" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E258" s="25" t="s">
         <v>140</v>
@@ -11063,10 +11072,10 @@
         <v>133</v>
       </c>
       <c r="G258" s="25" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H258" s="25" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I258" s="25" t="s">
         <v>120</v>
@@ -11075,16 +11084,16 @@
     </row>
     <row r="259" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A259" s="25">
-        <v>10400008</v>
+        <v>10400007</v>
       </c>
       <c r="B259" s="25">
         <v>104000</v>
       </c>
       <c r="C259" s="25" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>328</v>
+        <v>442</v>
       </c>
       <c r="E259" s="25" t="s">
         <v>140</v>
@@ -11093,88 +11102,88 @@
         <v>133</v>
       </c>
       <c r="G259" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H259" s="25" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I259" s="25" t="s">
-        <v>454</v>
+        <v>120</v>
       </c>
       <c r="K259" s="109"/>
     </row>
     <row r="260" s="25" customFormat="1" ht="16.5" spans="1:11">
       <c r="A260" s="25">
-        <v>10400009</v>
+        <v>10400008</v>
       </c>
       <c r="B260" s="25">
         <v>104000</v>
       </c>
       <c r="C260" s="25" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="D260" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="E260" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F260" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G260" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="H260" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="I260" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="K260" s="109"/>
+    </row>
+    <row r="261" s="25" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A261" s="25">
+        <v>10400009</v>
+      </c>
+      <c r="B261" s="25">
+        <v>104000</v>
+      </c>
+      <c r="C261" s="25" t="s">
+        <v>446</v>
+      </c>
+      <c r="D261" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E260" s="25" t="s">
+      <c r="E261" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="F260" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G260" s="25" t="s">
+      <c r="F261" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G261" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="H260" s="25" t="s">
-        <v>446</v>
-      </c>
-      <c r="I260" s="25" t="s">
+      <c r="H261" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="I261" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="K260" s="109"/>
-    </row>
-    <row r="261" s="26" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A261" s="26">
-        <v>10390001</v>
-      </c>
-      <c r="B261" s="26">
-        <v>103900</v>
-      </c>
-      <c r="C261" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="D261" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="E261" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="F261" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G261" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="H261" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="I261" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="K261" s="110"/>
+      <c r="K261" s="109"/>
     </row>
     <row r="262" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A262" s="26">
-        <v>10390002</v>
+        <v>10390001</v>
       </c>
       <c r="B262" s="26">
         <v>103900</v>
       </c>
       <c r="C262" s="26" t="s">
-        <v>456</v>
+        <v>295</v>
       </c>
       <c r="D262" s="26" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E262" s="26" t="s">
         <v>157</v>
@@ -11186,52 +11195,52 @@
         <v>159</v>
       </c>
       <c r="H262" s="26" t="s">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="I262" s="26" t="s">
-        <v>39</v>
+        <v>277</v>
       </c>
       <c r="K262" s="110"/>
     </row>
     <row r="263" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A263" s="26">
-        <v>10390003</v>
+        <v>10390002</v>
       </c>
       <c r="B263" s="26">
         <v>103900</v>
       </c>
       <c r="C263" s="26" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="D263" s="26" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E263" s="26" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="F263" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G263" s="26" t="s">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="H263" s="26" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I263" s="26" t="s">
-        <v>288</v>
+        <v>39</v>
       </c>
       <c r="K263" s="110"/>
     </row>
     <row r="264" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A264" s="26">
-        <v>10390004</v>
+        <v>10390003</v>
       </c>
       <c r="B264" s="26">
         <v>103900</v>
       </c>
       <c r="C264" s="26" t="s">
-        <v>246</v>
+        <v>417</v>
       </c>
       <c r="D264" s="26" t="s">
         <v>21</v>
@@ -11246,22 +11255,22 @@
         <v>234</v>
       </c>
       <c r="H264" s="26" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="I264" s="26" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="K264" s="110"/>
     </row>
     <row r="265" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A265" s="26">
-        <v>10390005</v>
+        <v>10390004</v>
       </c>
       <c r="B265" s="26">
         <v>103900</v>
       </c>
       <c r="C265" s="26" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D265" s="26" t="s">
         <v>21</v>
@@ -11273,115 +11282,115 @@
         <v>133</v>
       </c>
       <c r="G265" s="26" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H265" s="26" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="I265" s="26" t="s">
-        <v>106</v>
+        <v>340</v>
       </c>
       <c r="K265" s="110"/>
     </row>
     <row r="266" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A266" s="26">
-        <v>10390006</v>
+        <v>10390005</v>
       </c>
       <c r="B266" s="26">
         <v>103900</v>
       </c>
       <c r="C266" s="26" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="D266" s="26" t="s">
         <v>21</v>
       </c>
       <c r="E266" s="26" t="s">
-        <v>416</v>
+        <v>114</v>
       </c>
       <c r="F266" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G266" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="H266" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="I266" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="K266" s="110"/>
+    </row>
+    <row r="267" s="26" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A267" s="26">
+        <v>10390006</v>
+      </c>
+      <c r="B267" s="26">
+        <v>103900</v>
+      </c>
+      <c r="C267" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D267" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E267" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="F267" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G267" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="H266" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="I266" s="26" t="s">
+      <c r="H267" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="I267" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="K266" s="110"/>
-    </row>
-    <row r="267" s="24" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A267" s="24">
-        <v>10160001</v>
-      </c>
-      <c r="B267" s="24">
-        <v>101600</v>
-      </c>
-      <c r="C267" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="D267" s="24" t="s">
-        <v>438</v>
-      </c>
-      <c r="E267" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="F267" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G267" s="24" t="s">
-        <v>458</v>
-      </c>
-      <c r="H267" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="I267" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="K267" s="108"/>
+      <c r="K267" s="110"/>
     </row>
     <row r="268" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A268" s="24">
-        <v>10160002</v>
+        <v>10160001</v>
       </c>
       <c r="B268" s="24">
         <v>101600</v>
       </c>
       <c r="C268" s="24" t="s">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="D268" s="24" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E268" s="24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F268" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G268" s="24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H268" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I268" s="24" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K268" s="108"/>
     </row>
     <row r="269" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A269" s="24">
-        <v>10160003</v>
+        <v>10160002</v>
       </c>
       <c r="B269" s="24">
         <v>101600</v>
       </c>
       <c r="C269" s="24" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D269" s="24" t="s">
         <v>21</v>
@@ -11393,25 +11402,25 @@
         <v>133</v>
       </c>
       <c r="G269" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H269" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I269" s="24" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K269" s="108"/>
     </row>
     <row r="270" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A270" s="24">
-        <v>10160004</v>
+        <v>10160003</v>
       </c>
       <c r="B270" s="24">
         <v>101600</v>
       </c>
       <c r="C270" s="24" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D270" s="24" t="s">
         <v>21</v>
@@ -11423,100 +11432,100 @@
         <v>133</v>
       </c>
       <c r="G270" s="24" t="s">
-        <v>324</v>
+        <v>463</v>
       </c>
       <c r="H270" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I270" s="24" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="K270" s="108"/>
     </row>
     <row r="271" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A271" s="24">
-        <v>10160005</v>
+        <v>10160004</v>
       </c>
       <c r="B271" s="24">
         <v>101600</v>
       </c>
       <c r="C271" s="24" t="s">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="D271" s="24" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="E271" s="24" t="s">
-        <v>461</v>
+        <v>143</v>
       </c>
       <c r="F271" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G271" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="H271" s="24" t="s">
         <v>462</v>
       </c>
-      <c r="H271" s="24" t="s">
-        <v>459</v>
-      </c>
       <c r="I271" s="24" t="s">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="K271" s="108"/>
     </row>
     <row r="272" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A272" s="24">
-        <v>10160006</v>
+        <v>10160005</v>
       </c>
       <c r="B272" s="24">
         <v>101600</v>
       </c>
       <c r="C272" s="24" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D272" s="24" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E272" s="24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F272" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G272" s="24" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H272" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I272" s="24" t="s">
-        <v>333</v>
+        <v>466</v>
       </c>
       <c r="K272" s="108"/>
     </row>
     <row r="273" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A273" s="24">
-        <v>10160008</v>
+        <v>10160006</v>
       </c>
       <c r="B273" s="24">
         <v>101600</v>
       </c>
       <c r="C273" s="24" t="s">
-        <v>465</v>
+        <v>334</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>328</v>
+        <v>442</v>
       </c>
       <c r="E273" s="24" t="s">
-        <v>146</v>
+        <v>467</v>
       </c>
       <c r="F273" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G273" s="24" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="H273" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I273" s="24" t="s">
         <v>466</v>
@@ -11525,58 +11534,58 @@
     </row>
     <row r="274" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A274" s="24">
-        <v>10160009</v>
+        <v>10160008</v>
       </c>
       <c r="B274" s="24">
         <v>101600</v>
       </c>
       <c r="C274" s="24" t="s">
-        <v>253</v>
+        <v>469</v>
       </c>
       <c r="D274" s="24" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E274" s="24" t="s">
-        <v>254</v>
+        <v>146</v>
       </c>
       <c r="F274" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G274" s="24" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H274" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I274" s="24" t="s">
-        <v>39</v>
+        <v>470</v>
       </c>
       <c r="K274" s="108"/>
     </row>
     <row r="275" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A275" s="24">
-        <v>10160010</v>
+        <v>10160009</v>
       </c>
       <c r="B275" s="24">
         <v>101600</v>
       </c>
       <c r="C275" s="24" t="s">
-        <v>468</v>
+        <v>253</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E275" s="24" t="s">
-        <v>469</v>
+        <v>254</v>
       </c>
       <c r="F275" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G275" s="24" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="H275" s="24" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="I275" s="24" t="s">
         <v>39</v>
@@ -11585,28 +11594,28 @@
     </row>
     <row r="276" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A276" s="24">
-        <v>10160011</v>
+        <v>10160010</v>
       </c>
       <c r="B276" s="24">
         <v>101600</v>
       </c>
       <c r="C276" s="24" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D276" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E276" s="24" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F276" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G276" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H276" s="24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I276" s="24" t="s">
         <v>39</v>
@@ -11615,28 +11624,28 @@
     </row>
     <row r="277" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A277" s="24">
-        <v>10160012</v>
+        <v>10160011</v>
       </c>
       <c r="B277" s="24">
         <v>101600</v>
       </c>
       <c r="C277" s="24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D277" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E277" s="24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F277" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G277" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H277" s="24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I277" s="24" t="s">
         <v>39</v>
@@ -11645,28 +11654,28 @@
     </row>
     <row r="278" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A278" s="24">
-        <v>10160013</v>
+        <v>10160012</v>
       </c>
       <c r="B278" s="24">
         <v>101600</v>
       </c>
       <c r="C278" s="24" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D278" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E278" s="24" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F278" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G278" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H278" s="24" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I278" s="24" t="s">
         <v>39</v>
@@ -11675,28 +11684,28 @@
     </row>
     <row r="279" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A279" s="24">
-        <v>10160014</v>
+        <v>10160013</v>
       </c>
       <c r="B279" s="24">
         <v>101600</v>
       </c>
       <c r="C279" s="24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D279" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E279" s="24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F279" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G279" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H279" s="24" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I279" s="24" t="s">
         <v>39</v>
@@ -11705,28 +11714,28 @@
     </row>
     <row r="280" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A280" s="24">
-        <v>10160015</v>
+        <v>10160014</v>
       </c>
       <c r="B280" s="24">
         <v>101600</v>
       </c>
       <c r="C280" s="24" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D280" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E280" s="24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F280" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G280" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H280" s="24" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I280" s="24" t="s">
         <v>39</v>
@@ -11735,28 +11744,28 @@
     </row>
     <row r="281" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A281" s="24">
-        <v>10160016</v>
+        <v>10160015</v>
       </c>
       <c r="B281" s="24">
         <v>101600</v>
       </c>
       <c r="C281" s="24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D281" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E281" s="24" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F281" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G281" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H281" s="24" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I281" s="24" t="s">
         <v>39</v>
@@ -11765,28 +11774,28 @@
     </row>
     <row r="282" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A282" s="24">
-        <v>10160017</v>
+        <v>10160016</v>
       </c>
       <c r="B282" s="24">
         <v>101600</v>
       </c>
       <c r="C282" s="24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D282" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E282" s="24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F282" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G282" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H282" s="24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I282" s="24" t="s">
         <v>39</v>
@@ -11795,28 +11804,28 @@
     </row>
     <row r="283" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A283" s="24">
-        <v>10160018</v>
+        <v>10160017</v>
       </c>
       <c r="B283" s="24">
         <v>101600</v>
       </c>
       <c r="C283" s="24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D283" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E283" s="24" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F283" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G283" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H283" s="24" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I283" s="24" t="s">
         <v>39</v>
@@ -11825,28 +11834,28 @@
     </row>
     <row r="284" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A284" s="24">
-        <v>10160019</v>
+        <v>10160018</v>
       </c>
       <c r="B284" s="24">
         <v>101600</v>
       </c>
       <c r="C284" s="24" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D284" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E284" s="24" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F284" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G284" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H284" s="24" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I284" s="24" t="s">
         <v>39</v>
@@ -11855,79 +11864,79 @@
     </row>
     <row r="285" s="24" customFormat="1" ht="16.5" spans="1:11">
       <c r="A285" s="24">
-        <v>10160020</v>
+        <v>10160019</v>
       </c>
       <c r="B285" s="24">
         <v>101600</v>
       </c>
       <c r="C285" s="24" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D285" s="24" t="s">
         <v>328</v>
       </c>
       <c r="E285" s="24" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F285" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G285" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H285" s="24" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I285" s="24" t="s">
         <v>39</v>
       </c>
       <c r="K285" s="108"/>
     </row>
-    <row r="286" s="26" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A286" s="26">
-        <v>10150001</v>
-      </c>
-      <c r="B286" s="26">
-        <v>101500</v>
-      </c>
-      <c r="C286" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="D286" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="E286" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="F286" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G286" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="H286" s="26" t="s">
+    <row r="286" s="24" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A286" s="24">
+        <v>10160020</v>
+      </c>
+      <c r="B286" s="24">
+        <v>101600</v>
+      </c>
+      <c r="C286" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="I286" s="26" t="s">
+      <c r="D286" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="E286" s="24" t="s">
         <v>503</v>
       </c>
-      <c r="K286" s="110"/>
+      <c r="F286" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G286" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="H286" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="I286" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K286" s="108"/>
     </row>
     <row r="287" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A287" s="26">
-        <v>10150002</v>
+        <v>10150001</v>
       </c>
       <c r="B287" s="26">
         <v>101500</v>
       </c>
       <c r="C287" s="26" t="s">
-        <v>259</v>
+        <v>505</v>
       </c>
       <c r="D287" s="26" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E287" s="26" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F287" s="26" t="s">
         <v>133</v>
@@ -11936,22 +11945,22 @@
         <v>234</v>
       </c>
       <c r="H287" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I287" s="26" t="s">
-        <v>107</v>
+        <v>507</v>
       </c>
       <c r="K287" s="110"/>
     </row>
     <row r="288" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A288" s="26">
-        <v>10150003</v>
+        <v>10150002</v>
       </c>
       <c r="B288" s="26">
         <v>101500</v>
       </c>
       <c r="C288" s="26" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="D288" s="26" t="s">
         <v>21</v>
@@ -11966,22 +11975,22 @@
         <v>234</v>
       </c>
       <c r="H288" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I288" s="26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K288" s="110"/>
     </row>
     <row r="289" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A289" s="26">
-        <v>10150004</v>
+        <v>10150003</v>
       </c>
       <c r="B289" s="26">
         <v>101500</v>
       </c>
       <c r="C289" s="26" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D289" s="26" t="s">
         <v>21</v>
@@ -11996,28 +12005,28 @@
         <v>234</v>
       </c>
       <c r="H289" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I289" s="26" t="s">
-        <v>432</v>
+        <v>106</v>
       </c>
       <c r="K289" s="110"/>
     </row>
     <row r="290" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A290" s="26">
-        <v>10150005</v>
+        <v>10150004</v>
       </c>
       <c r="B290" s="26">
         <v>101500</v>
       </c>
       <c r="C290" s="26" t="s">
-        <v>504</v>
+        <v>246</v>
       </c>
       <c r="D290" s="26" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="E290" s="26" t="s">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="F290" s="26" t="s">
         <v>133</v>
@@ -12026,28 +12035,28 @@
         <v>234</v>
       </c>
       <c r="H290" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I290" s="26" t="s">
-        <v>39</v>
+        <v>436</v>
       </c>
       <c r="K290" s="110"/>
     </row>
     <row r="291" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A291" s="26">
-        <v>10150006</v>
+        <v>10150005</v>
       </c>
       <c r="B291" s="26">
         <v>101500</v>
       </c>
       <c r="C291" s="26" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D291" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E291" s="26" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F291" s="26" t="s">
         <v>133</v>
@@ -12056,7 +12065,7 @@
         <v>234</v>
       </c>
       <c r="H291" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I291" s="26" t="s">
         <v>39</v>
@@ -12065,19 +12074,19 @@
     </row>
     <row r="292" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A292" s="26">
-        <v>10150007</v>
+        <v>10150006</v>
       </c>
       <c r="B292" s="26">
         <v>101500</v>
       </c>
       <c r="C292" s="26" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D292" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E292" s="26" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F292" s="26" t="s">
         <v>133</v>
@@ -12086,7 +12095,7 @@
         <v>234</v>
       </c>
       <c r="H292" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I292" s="26" t="s">
         <v>39</v>
@@ -12095,28 +12104,28 @@
     </row>
     <row r="293" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A293" s="26">
-        <v>10150008</v>
+        <v>10150007</v>
       </c>
       <c r="B293" s="26">
         <v>101500</v>
       </c>
       <c r="C293" s="26" t="s">
-        <v>253</v>
+        <v>510</v>
       </c>
       <c r="D293" s="26" t="s">
         <v>279</v>
       </c>
       <c r="E293" s="26" t="s">
-        <v>507</v>
+        <v>56</v>
       </c>
       <c r="F293" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G293" s="26" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H293" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I293" s="26" t="s">
         <v>39</v>
@@ -12125,46 +12134,46 @@
     </row>
     <row r="294" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A294" s="26">
-        <v>10150009</v>
+        <v>10150008</v>
       </c>
       <c r="B294" s="26">
         <v>101500</v>
       </c>
       <c r="C294" s="26" t="s">
-        <v>508</v>
+        <v>253</v>
       </c>
       <c r="D294" s="26" t="s">
-        <v>422</v>
+        <v>279</v>
       </c>
       <c r="E294" s="26" t="s">
-        <v>143</v>
+        <v>511</v>
       </c>
       <c r="F294" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G294" s="26" t="s">
-        <v>439</v>
+        <v>255</v>
       </c>
       <c r="H294" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I294" s="26" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="K294" s="110"/>
     </row>
     <row r="295" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A295" s="26">
-        <v>10150010</v>
+        <v>10150009</v>
       </c>
       <c r="B295" s="26">
         <v>101500</v>
       </c>
       <c r="C295" s="26" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D295" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E295" s="26" t="s">
         <v>143</v>
@@ -12173,10 +12182,10 @@
         <v>133</v>
       </c>
       <c r="G295" s="26" t="s">
-        <v>174</v>
+        <v>443</v>
       </c>
       <c r="H295" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I295" s="26" t="s">
         <v>107</v>
@@ -12185,16 +12194,16 @@
     </row>
     <row r="296" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A296" s="26">
-        <v>10150011</v>
+        <v>10150010</v>
       </c>
       <c r="B296" s="26">
         <v>101500</v>
       </c>
       <c r="C296" s="26" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D296" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E296" s="26" t="s">
         <v>143</v>
@@ -12203,10 +12212,10 @@
         <v>133</v>
       </c>
       <c r="G296" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H296" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I296" s="26" t="s">
         <v>107</v>
@@ -12215,16 +12224,16 @@
     </row>
     <row r="297" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A297" s="26">
-        <v>10150012</v>
+        <v>10150011</v>
       </c>
       <c r="B297" s="26">
         <v>101500</v>
       </c>
       <c r="C297" s="26" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D297" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E297" s="26" t="s">
         <v>143</v>
@@ -12233,10 +12242,10 @@
         <v>133</v>
       </c>
       <c r="G297" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H297" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I297" s="26" t="s">
         <v>107</v>
@@ -12245,16 +12254,16 @@
     </row>
     <row r="298" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A298" s="26">
-        <v>10150013</v>
+        <v>10150012</v>
       </c>
       <c r="B298" s="26">
         <v>101500</v>
       </c>
       <c r="C298" s="26" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D298" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E298" s="26" t="s">
         <v>143</v>
@@ -12263,10 +12272,10 @@
         <v>133</v>
       </c>
       <c r="G298" s="26" t="s">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="H298" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I298" s="26" t="s">
         <v>107</v>
@@ -12275,16 +12284,16 @@
     </row>
     <row r="299" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A299" s="26">
-        <v>10150014</v>
+        <v>10150013</v>
       </c>
       <c r="B299" s="26">
         <v>101500</v>
       </c>
       <c r="C299" s="26" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D299" s="26" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E299" s="26" t="s">
         <v>143</v>
@@ -12293,25 +12302,25 @@
         <v>133</v>
       </c>
       <c r="G299" s="26" t="s">
-        <v>514</v>
+        <v>255</v>
       </c>
       <c r="H299" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I299" s="26" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="K299" s="110"/>
     </row>
     <row r="300" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A300" s="26">
-        <v>10150015</v>
+        <v>10150014</v>
       </c>
       <c r="B300" s="26">
         <v>101500</v>
       </c>
       <c r="C300" s="26" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D300" s="26" t="s">
         <v>21</v>
@@ -12323,10 +12332,10 @@
         <v>133</v>
       </c>
       <c r="G300" s="26" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H300" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I300" s="26" t="s">
         <v>89</v>
@@ -12335,13 +12344,13 @@
     </row>
     <row r="301" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A301" s="26">
-        <v>10150016</v>
+        <v>10150015</v>
       </c>
       <c r="B301" s="26">
         <v>101500</v>
       </c>
       <c r="C301" s="26" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D301" s="26" t="s">
         <v>21</v>
@@ -12353,10 +12362,10 @@
         <v>133</v>
       </c>
       <c r="G301" s="26" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H301" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I301" s="26" t="s">
         <v>89</v>
@@ -12365,13 +12374,13 @@
     </row>
     <row r="302" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A302" s="26">
-        <v>10150017</v>
+        <v>10150016</v>
       </c>
       <c r="B302" s="26">
         <v>101500</v>
       </c>
       <c r="C302" s="26" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D302" s="26" t="s">
         <v>21</v>
@@ -12383,10 +12392,10 @@
         <v>133</v>
       </c>
       <c r="G302" s="26" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H302" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I302" s="26" t="s">
         <v>89</v>
@@ -12395,13 +12404,13 @@
     </row>
     <row r="303" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A303" s="26">
-        <v>10150018</v>
+        <v>10150017</v>
       </c>
       <c r="B303" s="26">
         <v>101500</v>
       </c>
       <c r="C303" s="26" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D303" s="26" t="s">
         <v>21</v>
@@ -12413,10 +12422,10 @@
         <v>133</v>
       </c>
       <c r="G303" s="26" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H303" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I303" s="26" t="s">
         <v>89</v>
@@ -12425,13 +12434,13 @@
     </row>
     <row r="304" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A304" s="26">
-        <v>10150019</v>
+        <v>10150018</v>
       </c>
       <c r="B304" s="26">
         <v>101500</v>
       </c>
       <c r="C304" s="26" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D304" s="26" t="s">
         <v>21</v>
@@ -12443,10 +12452,10 @@
         <v>133</v>
       </c>
       <c r="G304" s="26" t="s">
-        <v>423</v>
+        <v>526</v>
       </c>
       <c r="H304" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I304" s="26" t="s">
         <v>89</v>
@@ -12455,13 +12464,13 @@
     </row>
     <row r="305" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A305" s="26">
-        <v>10150020</v>
+        <v>10150019</v>
       </c>
       <c r="B305" s="26">
         <v>101500</v>
       </c>
       <c r="C305" s="26" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D305" s="26" t="s">
         <v>21</v>
@@ -12473,10 +12482,10 @@
         <v>133</v>
       </c>
       <c r="G305" s="26" t="s">
-        <v>525</v>
+        <v>427</v>
       </c>
       <c r="H305" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I305" s="26" t="s">
         <v>89</v>
@@ -12485,13 +12494,13 @@
     </row>
     <row r="306" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A306" s="26">
-        <v>10150021</v>
+        <v>10150020</v>
       </c>
       <c r="B306" s="26">
         <v>101500</v>
       </c>
       <c r="C306" s="26" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D306" s="26" t="s">
         <v>21</v>
@@ -12503,10 +12512,10 @@
         <v>133</v>
       </c>
       <c r="G306" s="26" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H306" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I306" s="26" t="s">
         <v>89</v>
@@ -12515,13 +12524,13 @@
     </row>
     <row r="307" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A307" s="26">
-        <v>10150022</v>
+        <v>10150021</v>
       </c>
       <c r="B307" s="26">
         <v>101500</v>
       </c>
       <c r="C307" s="26" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D307" s="26" t="s">
         <v>21</v>
@@ -12533,10 +12542,10 @@
         <v>133</v>
       </c>
       <c r="G307" s="26" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H307" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I307" s="26" t="s">
         <v>89</v>
@@ -12545,13 +12554,13 @@
     </row>
     <row r="308" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A308" s="26">
-        <v>10150023</v>
+        <v>10150022</v>
       </c>
       <c r="B308" s="26">
         <v>101500</v>
       </c>
       <c r="C308" s="26" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D308" s="26" t="s">
         <v>21</v>
@@ -12563,10 +12572,10 @@
         <v>133</v>
       </c>
       <c r="G308" s="26" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H308" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I308" s="26" t="s">
         <v>89</v>
@@ -12575,13 +12584,13 @@
     </row>
     <row r="309" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A309" s="26">
-        <v>10150024</v>
+        <v>10150023</v>
       </c>
       <c r="B309" s="26">
         <v>101500</v>
       </c>
       <c r="C309" s="26" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D309" s="26" t="s">
         <v>21</v>
@@ -12593,25 +12602,25 @@
         <v>133</v>
       </c>
       <c r="G309" s="26" t="s">
-        <v>297</v>
+        <v>535</v>
       </c>
       <c r="H309" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I309" s="26" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="K309" s="110"/>
     </row>
     <row r="310" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A310" s="26">
-        <v>10150025</v>
+        <v>10150024</v>
       </c>
       <c r="B310" s="26">
         <v>101500</v>
       </c>
       <c r="C310" s="26" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D310" s="26" t="s">
         <v>21</v>
@@ -12623,10 +12632,10 @@
         <v>133</v>
       </c>
       <c r="G310" s="26" t="s">
-        <v>534</v>
+        <v>297</v>
       </c>
       <c r="H310" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I310" s="26" t="s">
         <v>157</v>
@@ -12635,13 +12644,13 @@
     </row>
     <row r="311" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A311" s="26">
-        <v>10150026</v>
+        <v>10150025</v>
       </c>
       <c r="B311" s="26">
         <v>101500</v>
       </c>
       <c r="C311" s="26" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D311" s="26" t="s">
         <v>21</v>
@@ -12653,10 +12662,10 @@
         <v>133</v>
       </c>
       <c r="G311" s="26" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H311" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I311" s="26" t="s">
         <v>157</v>
@@ -12665,13 +12674,13 @@
     </row>
     <row r="312" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A312" s="26">
-        <v>10150027</v>
+        <v>10150026</v>
       </c>
       <c r="B312" s="26">
         <v>101500</v>
       </c>
       <c r="C312" s="26" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D312" s="26" t="s">
         <v>21</v>
@@ -12683,10 +12692,10 @@
         <v>133</v>
       </c>
       <c r="G312" s="26" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H312" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I312" s="26" t="s">
         <v>157</v>
@@ -12695,13 +12704,13 @@
     </row>
     <row r="313" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A313" s="26">
-        <v>10150028</v>
+        <v>10150027</v>
       </c>
       <c r="B313" s="26">
         <v>101500</v>
       </c>
       <c r="C313" s="26" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D313" s="26" t="s">
         <v>21</v>
@@ -12713,10 +12722,10 @@
         <v>133</v>
       </c>
       <c r="G313" s="26" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H313" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I313" s="26" t="s">
         <v>157</v>
@@ -12725,13 +12734,13 @@
     </row>
     <row r="314" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A314" s="26">
-        <v>10150029</v>
+        <v>10150028</v>
       </c>
       <c r="B314" s="26">
         <v>101500</v>
       </c>
       <c r="C314" s="26" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D314" s="26" t="s">
         <v>21</v>
@@ -12743,10 +12752,10 @@
         <v>133</v>
       </c>
       <c r="G314" s="26" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H314" s="26" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I314" s="26" t="s">
         <v>157</v>
@@ -12755,106 +12764,106 @@
     </row>
     <row r="315" s="26" customFormat="1" ht="16.5" spans="1:11">
       <c r="A315" s="26">
-        <v>10150030</v>
+        <v>10150029</v>
       </c>
       <c r="B315" s="26">
         <v>101500</v>
       </c>
       <c r="C315" s="26" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D315" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E315" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F315" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G315" s="26" t="s">
+        <v>546</v>
+      </c>
+      <c r="H315" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="I315" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="K315" s="110"/>
+    </row>
+    <row r="316" s="26" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A316" s="26">
+        <v>10150030</v>
+      </c>
+      <c r="B316" s="26">
+        <v>101500</v>
+      </c>
+      <c r="C316" s="26" t="s">
+        <v>547</v>
+      </c>
+      <c r="D316" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="E315" s="26" t="s">
+      <c r="E316" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="F315" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G315" s="26" t="s">
+      <c r="F316" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G316" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="H315" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="I315" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="K315" s="110"/>
-    </row>
-    <row r="316" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A316" s="27">
-        <v>10260001</v>
-      </c>
-      <c r="B316" s="27">
-        <v>102600</v>
-      </c>
-      <c r="C316" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="D316" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E316" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="F316" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G316" s="27" t="s">
-        <v>458</v>
-      </c>
-      <c r="H316" s="27" t="s">
-        <v>544</v>
-      </c>
-      <c r="I316" s="27" t="s">
-        <v>545</v>
-      </c>
-      <c r="K316" s="111"/>
+      <c r="H316" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="I316" s="26" t="s">
+        <v>470</v>
+      </c>
+      <c r="K316" s="110"/>
     </row>
     <row r="317" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A317" s="27">
-        <v>10260002</v>
+        <v>10260001</v>
       </c>
       <c r="B317" s="27">
         <v>102600</v>
       </c>
       <c r="C317" s="27" t="s">
-        <v>323</v>
+        <v>505</v>
       </c>
       <c r="D317" s="27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E317" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F317" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G317" s="27" t="s">
-        <v>546</v>
+        <v>461</v>
       </c>
       <c r="H317" s="27" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I317" s="27" t="s">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="K317" s="111"/>
     </row>
     <row r="318" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A318" s="27">
-        <v>10260003</v>
+        <v>10260002</v>
       </c>
       <c r="B318" s="27">
         <v>102600</v>
       </c>
       <c r="C318" s="27" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="D318" s="27" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E318" s="27" t="s">
         <v>143</v>
@@ -12863,28 +12872,28 @@
         <v>133</v>
       </c>
       <c r="G318" s="27" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H318" s="27" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I318" s="27" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="K318" s="111"/>
     </row>
     <row r="319" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A319" s="27">
-        <v>10260004</v>
+        <v>10260003</v>
       </c>
       <c r="B319" s="27">
         <v>102600</v>
       </c>
       <c r="C319" s="27" t="s">
-        <v>326</v>
+        <v>259</v>
       </c>
       <c r="D319" s="27" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E319" s="27" t="s">
         <v>143</v>
@@ -12893,70 +12902,70 @@
         <v>133</v>
       </c>
       <c r="G319" s="27" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H319" s="27" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I319" s="27" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="K319" s="111"/>
     </row>
     <row r="320" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A320" s="27">
-        <v>10260005</v>
+        <v>10260004</v>
       </c>
       <c r="B320" s="27">
         <v>102600</v>
       </c>
       <c r="C320" s="27" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D320" s="27" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="E320" s="27" t="s">
-        <v>331</v>
+        <v>143</v>
       </c>
       <c r="F320" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G320" s="27" t="s">
-        <v>464</v>
+        <v>550</v>
       </c>
       <c r="H320" s="27" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I320" s="27" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="K320" s="111"/>
     </row>
     <row r="321" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A321" s="27">
-        <v>10260006</v>
+        <v>10260005</v>
       </c>
       <c r="B321" s="27">
         <v>102600</v>
       </c>
       <c r="C321" s="27" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D321" s="27" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E321" s="27" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F321" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G321" s="27" t="s">
-        <v>547</v>
+        <v>468</v>
       </c>
       <c r="H321" s="27" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I321" s="27" t="s">
         <v>333</v>
@@ -12965,191 +12974,192 @@
     </row>
     <row r="322" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A322" s="27">
-        <v>10260007</v>
+        <v>10260006</v>
       </c>
       <c r="B322" s="27">
         <v>102600</v>
       </c>
       <c r="C322" s="27" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D322" s="27" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E322" s="27" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F322" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G322" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="H322" s="27" t="s">
         <v>548</v>
       </c>
-      <c r="H322" s="27" t="s">
-        <v>544</v>
-      </c>
       <c r="I322" s="27" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="K322" s="111"/>
     </row>
     <row r="323" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A323" s="27">
-        <v>10260008</v>
+        <v>10260007</v>
       </c>
       <c r="B323" s="27">
         <v>102600</v>
       </c>
       <c r="C323" s="27" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="D323" s="27" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E323" s="27" t="s">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="F323" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G323" s="27" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="H323" s="27" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I323" s="27" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K323" s="111"/>
     </row>
     <row r="324" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A324" s="27">
-        <v>10260009</v>
+        <v>10260008</v>
       </c>
       <c r="B324" s="27">
         <v>102600</v>
       </c>
       <c r="C324" s="27" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E324" s="27" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F324" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G324" s="27" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="H324" s="27" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="I324" s="27" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K324" s="111"/>
     </row>
     <row r="325" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A325" s="27">
-        <v>10260010</v>
+        <v>10260009</v>
       </c>
       <c r="B325" s="27">
         <v>102600</v>
       </c>
       <c r="C325" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="D325" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="E325" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="F325" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G325" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="H325" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="I325" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="K325" s="111"/>
+    </row>
+    <row r="326" s="27" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A326" s="27">
+        <v>10260010</v>
+      </c>
+      <c r="B326" s="27">
+        <v>102600</v>
+      </c>
+      <c r="C326" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="D325" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E325" s="27" t="s">
+      <c r="D326" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="E326" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="F325" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G325" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="I325" s="27" t="s">
+      <c r="F326" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G326" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="I326" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="K325" s="111"/>
-    </row>
-    <row r="326" s="20" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A326" s="20">
-        <v>10500001</v>
-      </c>
-      <c r="B326" s="20">
-        <v>105000</v>
-      </c>
-      <c r="C326" s="20" t="s">
-        <v>552</v>
-      </c>
-      <c r="D326" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="E326" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F326" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G326" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="H326" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="I326" s="20" t="s">
-        <v>545</v>
-      </c>
+      <c r="K326" s="111"/>
     </row>
     <row r="327" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A327" s="20">
-        <v>10500002</v>
+        <v>10500001</v>
       </c>
       <c r="B327" s="20">
         <v>105000</v>
       </c>
       <c r="C327" s="20" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D327" s="20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E327" s="20" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F327" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G327" s="20" t="s">
-        <v>555</v>
+        <v>461</v>
       </c>
       <c r="H327" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I327" s="20" t="s">
-        <v>325</v>
+        <v>549</v>
       </c>
     </row>
     <row r="328" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A328" s="20">
-        <v>10500003</v>
+        <v>10500002</v>
       </c>
       <c r="B328" s="20">
         <v>105000</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D328" s="20" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E328" s="20" t="s">
         <v>143</v>
@@ -13158,27 +13168,27 @@
         <v>133</v>
       </c>
       <c r="G328" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="H328" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="H328" s="20" t="s">
-        <v>553</v>
-      </c>
       <c r="I328" s="20" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
     </row>
     <row r="329" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A329" s="20">
-        <v>10500004</v>
+        <v>10500003</v>
       </c>
       <c r="B329" s="20">
         <v>105000</v>
       </c>
       <c r="C329" s="20" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D329" s="20" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E329" s="20" t="s">
         <v>143</v>
@@ -13187,68 +13197,68 @@
         <v>133</v>
       </c>
       <c r="G329" s="20" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="H329" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I329" s="20" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
     </row>
     <row r="330" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A330" s="20">
-        <v>10500005</v>
+        <v>10500004</v>
       </c>
       <c r="B330" s="20">
         <v>105000</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>330</v>
+        <v>562</v>
       </c>
       <c r="D330" s="20" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="E330" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F330" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G330" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="F330" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G330" s="20" t="s">
-        <v>560</v>
-      </c>
       <c r="H330" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I330" s="20" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="331" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A331" s="20">
-        <v>10500006</v>
+        <v>10500005</v>
       </c>
       <c r="B331" s="20">
         <v>105000</v>
       </c>
       <c r="C331" s="20" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D331" s="20" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E331" s="20" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F331" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G331" s="20" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H331" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I331" s="20" t="s">
         <v>333</v>
@@ -13256,159 +13266,158 @@
     </row>
     <row r="332" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A332" s="20">
-        <v>10500007</v>
+        <v>10500006</v>
       </c>
       <c r="B332" s="20">
         <v>105000</v>
       </c>
       <c r="C332" s="20" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D332" s="20" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E332" s="20" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F332" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G332" s="20" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H332" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I332" s="20" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="333" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A333" s="20">
-        <v>10500008</v>
+        <v>10500007</v>
       </c>
       <c r="B333" s="20">
         <v>105000</v>
       </c>
       <c r="C333" s="20" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="D333" s="20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E333" s="20" t="s">
-        <v>275</v>
+        <v>567</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G333" s="20" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H333" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I333" s="20" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
     </row>
     <row r="334" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A334" s="20">
-        <v>10500009</v>
+        <v>10500008</v>
       </c>
       <c r="B334" s="20">
         <v>105000</v>
       </c>
       <c r="C334" s="20" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D334" s="20" t="s">
-        <v>566</v>
+        <v>429</v>
       </c>
       <c r="E334" s="20" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F334" s="20" t="s">
         <v>133</v>
       </c>
       <c r="G334" s="20" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="H334" s="20" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I334" s="20" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
     </row>
     <row r="335" s="20" customFormat="1" ht="16.5" spans="1:11">
       <c r="A335" s="20">
-        <v>10500010</v>
+        <v>10500009</v>
       </c>
       <c r="B335" s="20">
         <v>105000</v>
       </c>
       <c r="C335" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="D335" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="E335" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F335" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G335" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="H335" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="I335" s="20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="336" s="20" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A336" s="20">
+        <v>10500010</v>
+      </c>
+      <c r="B336" s="20">
+        <v>105000</v>
+      </c>
+      <c r="C336" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="D335" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="E335" s="20" t="s">
+      <c r="D336" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="E336" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="F335" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G335" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="I335" s="20" t="s">
+      <c r="F336" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G336" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="I336" s="20" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="336" s="2" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A336" s="33">
-        <v>10510001</v>
-      </c>
-      <c r="B336" s="33">
-        <v>105100</v>
-      </c>
-      <c r="C336" s="33" t="s">
-        <v>567</v>
-      </c>
-      <c r="D336" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="E336" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="F336" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G336" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="H336" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="I336" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="K336" s="82"/>
     </row>
     <row r="337" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A337" s="33">
-        <v>10510002</v>
+        <v>10510001</v>
       </c>
       <c r="B337" s="33">
         <v>105100</v>
       </c>
       <c r="C337" s="33" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E337" s="33" t="s">
         <v>41</v>
@@ -13417,10 +13426,10 @@
         <v>133</v>
       </c>
       <c r="G337" s="33" t="s">
-        <v>344</v>
+        <v>25</v>
       </c>
       <c r="H337" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I337" s="33" t="s">
         <v>39</v>
@@ -13429,16 +13438,16 @@
     </row>
     <row r="338" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A338" s="33">
-        <v>10510003</v>
+        <v>10510002</v>
       </c>
       <c r="B338" s="33">
         <v>105100</v>
       </c>
       <c r="C338" s="33" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E338" s="33" t="s">
         <v>41</v>
@@ -13447,10 +13456,10 @@
         <v>133</v>
       </c>
       <c r="G338" s="33" t="s">
-        <v>460</v>
+        <v>344</v>
       </c>
       <c r="H338" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I338" s="33" t="s">
         <v>39</v>
@@ -13459,28 +13468,28 @@
     </row>
     <row r="339" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A339" s="33">
-        <v>10510004</v>
+        <v>10510003</v>
       </c>
       <c r="B339" s="33">
         <v>105100</v>
       </c>
       <c r="C339" s="33" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D339" s="33" t="s">
+        <v>575</v>
+      </c>
+      <c r="E339" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F339" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G339" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="H339" s="33" t="s">
         <v>573</v>
-      </c>
-      <c r="E339" s="33" t="s">
-        <v>574</v>
-      </c>
-      <c r="F339" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G339" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="H339" s="33" t="s">
-        <v>569</v>
       </c>
       <c r="I339" s="33" t="s">
         <v>39</v>
@@ -13489,28 +13498,28 @@
     </row>
     <row r="340" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A340" s="33">
-        <v>10510005</v>
+        <v>10510004</v>
       </c>
       <c r="B340" s="33">
         <v>105100</v>
       </c>
       <c r="C340" s="33" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E340" s="33" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="F340" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G340" s="33" t="s">
-        <v>344</v>
+        <v>25</v>
       </c>
       <c r="H340" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I340" s="33" t="s">
         <v>39</v>
@@ -13519,28 +13528,28 @@
     </row>
     <row r="341" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A341" s="33">
-        <v>10510006</v>
+        <v>10510005</v>
       </c>
       <c r="B341" s="33">
         <v>105100</v>
       </c>
       <c r="C341" s="33" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D341" s="33" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E341" s="33" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="F341" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G341" s="33" t="s">
-        <v>460</v>
+        <v>344</v>
       </c>
       <c r="H341" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I341" s="33" t="s">
         <v>39</v>
@@ -13549,135 +13558,136 @@
     </row>
     <row r="342" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A342" s="33">
-        <v>10510007</v>
+        <v>10510006</v>
       </c>
       <c r="B342" s="33">
         <v>105100</v>
       </c>
       <c r="C342" s="33" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="E342" s="33" t="s">
-        <v>36</v>
+        <v>578</v>
       </c>
       <c r="F342" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G342" s="33" t="s">
-        <v>25</v>
+        <v>463</v>
       </c>
       <c r="H342" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I342" s="33" t="s">
-        <v>578</v>
+        <v>39</v>
       </c>
       <c r="K342" s="82"/>
     </row>
     <row r="343" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A343" s="33">
-        <v>10510008</v>
+        <v>10510007</v>
       </c>
       <c r="B343" s="33">
         <v>105100</v>
       </c>
       <c r="C343" s="33" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D343" s="33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E343" s="33" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F343" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G343" s="33" t="s">
-        <v>344</v>
+        <v>25</v>
       </c>
       <c r="H343" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I343" s="33" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K343" s="82"/>
     </row>
     <row r="344" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A344" s="33">
-        <v>10510009</v>
+        <v>10510008</v>
       </c>
       <c r="B344" s="33">
         <v>105100</v>
       </c>
       <c r="C344" s="33" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D344" s="33" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E344" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F344" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G344" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="H344" s="33" t="s">
+        <v>573</v>
+      </c>
+      <c r="I344" s="33" t="s">
+        <v>582</v>
+      </c>
+      <c r="K344" s="82"/>
+    </row>
+    <row r="345" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A345" s="33">
+        <v>10510009</v>
+      </c>
+      <c r="B345" s="33">
+        <v>105100</v>
+      </c>
+      <c r="C345" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="D345" s="33" t="s">
+        <v>575</v>
+      </c>
+      <c r="E345" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F344" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G344" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="H344" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="I344" s="33" t="s">
-        <v>578</v>
-      </c>
-      <c r="K344" s="82"/>
-    </row>
-    <row r="345" s="27" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A345" s="27">
-        <v>10540001</v>
-      </c>
-      <c r="B345" s="27">
-        <v>105400</v>
-      </c>
-      <c r="C345" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="D345" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="E345" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="F345" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G345" s="27" t="s">
-        <v>555</v>
-      </c>
-      <c r="H345" s="27" t="s">
-        <v>581</v>
-      </c>
-      <c r="I345" s="27" t="s">
-        <v>325</v>
-      </c>
+      <c r="F345" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G345" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="H345" s="33" t="s">
+        <v>573</v>
+      </c>
+      <c r="I345" s="33" t="s">
+        <v>582</v>
+      </c>
+      <c r="K345" s="82"/>
     </row>
     <row r="346" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A346" s="27">
-        <v>10540002</v>
+        <v>10540001</v>
       </c>
       <c r="B346" s="27">
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E346" s="27" t="s">
         <v>140</v>
@@ -13686,27 +13696,27 @@
         <v>133</v>
       </c>
       <c r="G346" s="27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H346" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I346" s="27" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
     </row>
     <row r="347" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A347" s="27">
-        <v>10540003</v>
+        <v>10540002</v>
       </c>
       <c r="B347" s="27">
         <v>105400</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>326</v>
+        <v>259</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E347" s="27" t="s">
         <v>140</v>
@@ -13715,68 +13725,68 @@
         <v>133</v>
       </c>
       <c r="G347" s="27" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="H347" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I347" s="27" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A348" s="27">
-        <v>10540004</v>
+        <v>10540003</v>
       </c>
       <c r="B348" s="27">
         <v>105400</v>
       </c>
       <c r="C348" s="27" t="s">
-        <v>582</v>
+        <v>326</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="E348" s="27" t="s">
-        <v>583</v>
+        <v>140</v>
       </c>
       <c r="F348" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G348" s="27" t="s">
-        <v>584</v>
+        <v>559</v>
       </c>
       <c r="H348" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I348" s="27" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="349" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A349" s="27">
-        <v>10540005</v>
+        <v>10540004</v>
       </c>
       <c r="B349" s="27">
         <v>105400</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>330</v>
+        <v>586</v>
       </c>
       <c r="D349" s="27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E349" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="F349" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G349" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="H349" s="27" t="s">
         <v>585</v>
-      </c>
-      <c r="F349" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G349" s="27" t="s">
-        <v>584</v>
-      </c>
-      <c r="H349" s="27" t="s">
-        <v>581</v>
       </c>
       <c r="I349" s="27" t="s">
         <v>333</v>
@@ -13784,28 +13794,28 @@
     </row>
     <row r="350" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A350" s="27">
-        <v>10540006</v>
+        <v>10540005</v>
       </c>
       <c r="B350" s="27">
         <v>105400</v>
       </c>
       <c r="C350" s="27" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D350" s="27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E350" s="27" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F350" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G350" s="27" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="H350" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I350" s="27" t="s">
         <v>333</v>
@@ -13813,186 +13823,188 @@
     </row>
     <row r="351" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A351" s="27">
-        <v>10540007</v>
+        <v>10540006</v>
       </c>
       <c r="B351" s="27">
         <v>105400</v>
       </c>
       <c r="C351" s="27" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E351" s="27" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F351" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G351" s="27" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="H351" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I351" s="27" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="352" s="27" customFormat="1" ht="16.5" spans="1:11">
       <c r="A352" s="27">
-        <v>10540008</v>
+        <v>10540007</v>
       </c>
       <c r="B352" s="27">
         <v>105400</v>
       </c>
       <c r="C352" s="27" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E352" s="27" t="s">
-        <v>264</v>
+        <v>591</v>
       </c>
       <c r="F352" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G352" s="27" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="H352" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I352" s="27" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
     </row>
     <row r="353" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A353" s="27">
-        <v>10540009</v>
+        <v>10540008</v>
       </c>
       <c r="B353" s="27">
         <v>105400</v>
       </c>
       <c r="C353" s="27" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D353" s="27" t="s">
-        <v>566</v>
+        <v>429</v>
       </c>
       <c r="E353" s="27" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="F353" s="27" t="s">
         <v>133</v>
       </c>
       <c r="G353" s="27" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="H353" s="27" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I353" s="27" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
     </row>
     <row r="354" s="27" customFormat="1" ht="16.5" spans="1:12">
       <c r="A354" s="27">
-        <v>10540010</v>
+        <v>10540009</v>
       </c>
       <c r="B354" s="27">
         <v>105400</v>
       </c>
       <c r="C354" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="D354" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="E354" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F354" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G354" s="27" t="s">
+        <v>592</v>
+      </c>
+      <c r="H354" s="27" t="s">
+        <v>585</v>
+      </c>
+      <c r="I354" s="27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="355" s="27" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A355" s="27">
+        <v>10540010</v>
+      </c>
+      <c r="B355" s="27">
+        <v>105400</v>
+      </c>
+      <c r="C355" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="D354" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E354" s="27" t="s">
+      <c r="D355" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="E355" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="F354" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G354" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="I354" s="27" t="s">
+      <c r="F355" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G355" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="I355" s="27" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="355" s="28" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A355" s="28">
-        <v>10080001</v>
-      </c>
-      <c r="B355" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C355" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="D355" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E355" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="F355" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G355" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="H355" s="28" t="s">
-        <v>589</v>
-      </c>
-      <c r="I355" s="28" t="s">
-        <v>545</v>
-      </c>
-      <c r="K355" s="112"/>
     </row>
     <row r="356" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A356" s="28">
-        <v>10080002</v>
+        <v>10080001</v>
       </c>
       <c r="B356" s="28">
         <v>100800</v>
       </c>
       <c r="C356" s="28" t="s">
-        <v>323</v>
+        <v>505</v>
       </c>
       <c r="D356" s="28" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E356" s="28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F356" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G356" s="28" t="s">
-        <v>546</v>
+        <v>461</v>
+      </c>
+      <c r="H356" s="28" t="s">
+        <v>593</v>
       </c>
       <c r="I356" s="28" t="s">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="K356" s="112"/>
     </row>
     <row r="357" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A357" s="28">
-        <v>10080003</v>
+        <v>10080002</v>
       </c>
       <c r="B357" s="28">
         <v>100800</v>
       </c>
       <c r="C357" s="28" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="D357" s="28" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E357" s="28" t="s">
         <v>143</v>
@@ -14001,28 +14013,25 @@
         <v>133</v>
       </c>
       <c r="G357" s="28" t="s">
-        <v>546</v>
-      </c>
-      <c r="H357" s="28" t="s">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="I357" s="28" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="K357" s="112"/>
     </row>
     <row r="358" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A358" s="28">
-        <v>10080004</v>
+        <v>10080003</v>
       </c>
       <c r="B358" s="28">
         <v>100800</v>
       </c>
       <c r="C358" s="28" t="s">
-        <v>326</v>
+        <v>259</v>
       </c>
       <c r="D358" s="28" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E358" s="28" t="s">
         <v>143</v>
@@ -14031,70 +14040,70 @@
         <v>133</v>
       </c>
       <c r="G358" s="28" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H358" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I358" s="28" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="K358" s="112"/>
     </row>
     <row r="359" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A359" s="28">
-        <v>10080005</v>
+        <v>10080004</v>
       </c>
       <c r="B359" s="28">
         <v>100800</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D359" s="28" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="E359" s="28" t="s">
-        <v>590</v>
+        <v>143</v>
       </c>
       <c r="F359" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G359" s="28" t="s">
-        <v>464</v>
+        <v>550</v>
       </c>
       <c r="H359" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I359" s="28" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="K359" s="112"/>
     </row>
     <row r="360" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A360" s="28">
-        <v>10080006</v>
+        <v>10080005</v>
       </c>
       <c r="B360" s="28">
         <v>100800</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D360" s="28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E360" s="28" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F360" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G360" s="28" t="s">
-        <v>547</v>
+        <v>468</v>
       </c>
       <c r="H360" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I360" s="28" t="s">
         <v>333</v>
@@ -14103,163 +14112,163 @@
     </row>
     <row r="361" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A361" s="28">
-        <v>10080007</v>
+        <v>10080006</v>
       </c>
       <c r="B361" s="28">
         <v>100800</v>
       </c>
       <c r="C361" s="28" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D361" s="28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E361" s="28" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F361" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G361" s="28" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="H361" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I361" s="28" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="K361" s="112"/>
     </row>
     <row r="362" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A362" s="28">
-        <v>10080008</v>
+        <v>10080007</v>
       </c>
       <c r="B362" s="28">
         <v>100800</v>
       </c>
       <c r="C362" s="28" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="D362" s="28" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E362" s="28" t="s">
+        <v>596</v>
+      </c>
+      <c r="F362" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G362" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H362" s="28" t="s">
         <v>593</v>
       </c>
-      <c r="F362" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G362" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="H362" s="28" t="s">
-        <v>594</v>
-      </c>
       <c r="I362" s="28" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K362" s="112"/>
     </row>
     <row r="363" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A363" s="28">
-        <v>10080009</v>
+        <v>10080008</v>
       </c>
       <c r="B363" s="28">
         <v>100800</v>
       </c>
       <c r="C363" s="28" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D363" s="28" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E363" s="28" t="s">
-        <v>143</v>
+        <v>597</v>
       </c>
       <c r="F363" s="28" t="s">
         <v>133</v>
       </c>
       <c r="G363" s="28" t="s">
-        <v>546</v>
+        <v>341</v>
       </c>
       <c r="H363" s="28" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="I363" s="28" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K363" s="112"/>
     </row>
-    <row r="364" s="27" customFormat="1" ht="16.5" spans="1:12">
+    <row r="364" s="28" customFormat="1" ht="16.5" spans="1:12">
       <c r="A364" s="28">
-        <v>10080010</v>
+        <v>10080009</v>
       </c>
       <c r="B364" s="28">
         <v>100800</v>
       </c>
       <c r="C364" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="D364" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="E364" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F364" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G364" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="H364" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="I364" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="K364" s="112"/>
+    </row>
+    <row r="365" s="27" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A365" s="28">
+        <v>10080010</v>
+      </c>
+      <c r="B365" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C365" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="D364" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E364" s="28" t="s">
+      <c r="D365" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="E365" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="F364" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G364" s="28" t="s">
-        <v>551</v>
-      </c>
-      <c r="H364" s="28"/>
-      <c r="I364" s="28" t="s">
+      <c r="F365" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G365" s="28" t="s">
+        <v>555</v>
+      </c>
+      <c r="H365" s="28"/>
+      <c r="I365" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="J364" s="28"/>
-      <c r="K364" s="28"/>
-      <c r="L364" s="28"/>
-    </row>
-    <row r="365" s="29" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A365" s="29">
-        <v>10530001</v>
-      </c>
-      <c r="B365" s="29">
-        <v>105300</v>
-      </c>
-      <c r="C365" s="29" t="s">
-        <v>595</v>
-      </c>
-      <c r="D365" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E365" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="F365" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="G365" s="29" t="s">
-        <v>596</v>
-      </c>
-      <c r="H365" s="29" t="s">
-        <v>597</v>
-      </c>
-      <c r="I365" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="K365" s="113"/>
+      <c r="J365" s="28"/>
+      <c r="K365" s="28"/>
+      <c r="L365" s="28"/>
     </row>
     <row r="366" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A366" s="29">
-        <v>10530002</v>
+        <v>10530001</v>
       </c>
       <c r="B366" s="29">
         <v>105300</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D366" s="29" t="s">
         <v>21</v>
@@ -14271,28 +14280,28 @@
         <v>133</v>
       </c>
       <c r="G366" s="29" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="H366" s="29" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I366" s="29" t="s">
-        <v>599</v>
+        <v>340</v>
       </c>
       <c r="K366" s="113"/>
     </row>
     <row r="367" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A367" s="29">
-        <v>10530003</v>
+        <v>10530002</v>
       </c>
       <c r="B367" s="29">
         <v>105300</v>
       </c>
       <c r="C367" s="29" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D367" s="29" t="s">
-        <v>566</v>
+        <v>21</v>
       </c>
       <c r="E367" s="29" t="s">
         <v>136</v>
@@ -14301,118 +14310,118 @@
         <v>133</v>
       </c>
       <c r="G367" s="29" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="H367" s="29" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I367" s="29" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K367" s="113"/>
     </row>
     <row r="368" s="29" customFormat="1" ht="16.5" spans="1:12">
       <c r="A368" s="29">
-        <v>10530004</v>
+        <v>10530003</v>
       </c>
       <c r="B368" s="29">
         <v>105300</v>
       </c>
       <c r="C368" s="29" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D368" s="29" t="s">
-        <v>328</v>
+        <v>570</v>
       </c>
       <c r="E368" s="29" t="s">
-        <v>603</v>
+        <v>136</v>
       </c>
       <c r="F368" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G368" s="29" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H368" s="29" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I368" s="29" t="s">
-        <v>294</v>
+        <v>605</v>
       </c>
       <c r="K368" s="113"/>
     </row>
     <row r="369" s="29" customFormat="1" ht="16.5" spans="1:11">
       <c r="A369" s="29">
-        <v>10530006</v>
+        <v>10530004</v>
       </c>
       <c r="B369" s="29">
         <v>105300</v>
       </c>
       <c r="C369" s="29" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D369" s="29" t="s">
         <v>328</v>
       </c>
       <c r="E369" s="29" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="F369" s="29" t="s">
         <v>133</v>
       </c>
       <c r="G369" s="29" t="s">
+        <v>608</v>
+      </c>
+      <c r="H369" s="29" t="s">
+        <v>601</v>
+      </c>
+      <c r="I369" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="K369" s="113"/>
+    </row>
+    <row r="370" s="29" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A370" s="29">
+        <v>10530006</v>
+      </c>
+      <c r="B370" s="29">
+        <v>105300</v>
+      </c>
+      <c r="C370" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="D370" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="E370" s="29" t="s">
+        <v>607</v>
+      </c>
+      <c r="F370" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G370" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="H369" s="29" t="s">
-        <v>606</v>
-      </c>
-      <c r="I369" s="29" t="s">
+      <c r="H370" s="29" t="s">
+        <v>610</v>
+      </c>
+      <c r="I370" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="K369" s="113"/>
-    </row>
-    <row r="370" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A370" s="30">
-        <v>10570001</v>
-      </c>
-      <c r="B370" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C370" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="D370" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E370" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F370" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G370" s="30" t="s">
-        <v>607</v>
-      </c>
-      <c r="H370" s="30" t="s">
-        <v>608</v>
-      </c>
-      <c r="I370" s="30" t="s">
-        <v>601</v>
-      </c>
-      <c r="K370" s="114"/>
+      <c r="K370" s="113"/>
     </row>
     <row r="371" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A371" s="30">
-        <v>10570002</v>
+        <v>10570001</v>
       </c>
       <c r="B371" s="30">
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D371" s="30" t="s">
-        <v>328</v>
+        <v>442</v>
       </c>
       <c r="E371" s="30" t="s">
         <v>114</v>
@@ -14421,25 +14430,25 @@
         <v>133</v>
       </c>
       <c r="G371" s="30" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="H371" s="30" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="I371" s="30" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K371" s="114"/>
     </row>
     <row r="372" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A372" s="30">
-        <v>10570003</v>
+        <v>10570002</v>
       </c>
       <c r="B372" s="30">
         <v>105700</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>609</v>
+        <v>417</v>
       </c>
       <c r="D372" s="30" t="s">
         <v>328</v>
@@ -14451,145 +14460,145 @@
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="H372" s="30" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="I372" s="30" t="s">
-        <v>340</v>
+        <v>603</v>
       </c>
       <c r="K372" s="114"/>
     </row>
     <row r="373" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A373" s="30">
-        <v>10570004</v>
+        <v>10570003</v>
       </c>
       <c r="B373" s="30">
         <v>105700</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D373" s="30" t="s">
         <v>328</v>
       </c>
       <c r="E373" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F373" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G373" s="30" t="s">
         <v>611</v>
       </c>
-      <c r="F373" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G373" s="30" t="s">
+      <c r="H373" s="30" t="s">
         <v>612</v>
       </c>
-      <c r="H373" s="30" t="s">
-        <v>608</v>
-      </c>
       <c r="I373" s="30" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="K373" s="114"/>
     </row>
     <row r="374" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A374" s="30">
-        <v>10570005</v>
+        <v>10570004</v>
       </c>
       <c r="B374" s="30">
         <v>105700</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>253</v>
+        <v>614</v>
       </c>
       <c r="D374" s="30" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E374" s="30" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F374" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G374" s="30" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H374" s="30" t="s">
-        <v>455</v>
+        <v>612</v>
       </c>
       <c r="I374" s="30" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K374" s="114"/>
     </row>
     <row r="375" s="30" customFormat="1" ht="16.5" spans="1:11">
       <c r="A375" s="30">
-        <v>10570006</v>
+        <v>10570005</v>
       </c>
       <c r="B375" s="30">
         <v>105700</v>
       </c>
       <c r="C375" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D375" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E375" s="30" t="s">
+        <v>617</v>
+      </c>
+      <c r="F375" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G375" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="H375" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="I375" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="K375" s="114"/>
+    </row>
+    <row r="376" s="30" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A376" s="30">
+        <v>10570006</v>
+      </c>
+      <c r="B376" s="30">
+        <v>105700</v>
+      </c>
+      <c r="C376" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="D375" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E375" s="30" t="s">
+      <c r="D376" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="E376" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="F375" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G375" s="30" t="s">
-        <v>615</v>
-      </c>
-      <c r="I375" s="30" t="s">
+      <c r="F376" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G376" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="I376" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="K375" s="114"/>
-    </row>
-    <row r="376" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A376" s="31">
-        <v>10580001</v>
-      </c>
-      <c r="B376" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C376" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="D376" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E376" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F376" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G376" s="31" t="s">
-        <v>616</v>
-      </c>
-      <c r="H376" s="31" t="s">
-        <v>617</v>
-      </c>
-      <c r="I376" s="31" t="s">
-        <v>601</v>
-      </c>
-      <c r="K376" s="115"/>
+      <c r="K376" s="114"/>
     </row>
     <row r="377" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A377" s="31">
-        <v>10580002</v>
+        <v>10580001</v>
       </c>
       <c r="B377" s="31">
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D377" s="31" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="E377" s="31" t="s">
         <v>299</v>
@@ -14598,25 +14607,25 @@
         <v>133</v>
       </c>
       <c r="G377" s="31" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H377" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I377" s="31" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K377" s="115"/>
     </row>
     <row r="378" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A378" s="31">
-        <v>10580003</v>
+        <v>10580002</v>
       </c>
       <c r="B378" s="31">
         <v>105800</v>
       </c>
       <c r="C378" s="31" t="s">
-        <v>609</v>
+        <v>259</v>
       </c>
       <c r="D378" s="31" t="s">
         <v>328</v>
@@ -14628,169 +14637,169 @@
         <v>133</v>
       </c>
       <c r="G378" s="31" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H378" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I378" s="31" t="s">
-        <v>340</v>
+        <v>603</v>
       </c>
       <c r="K378" s="115"/>
     </row>
     <row r="379" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A379" s="31">
-        <v>10580004</v>
+        <v>10580003</v>
       </c>
       <c r="B379" s="31">
         <v>105800</v>
       </c>
       <c r="C379" s="31" t="s">
+        <v>613</v>
+      </c>
+      <c r="D379" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="E379" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F379" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G379" s="31" t="s">
+        <v>620</v>
+      </c>
+      <c r="H379" s="31" t="s">
+        <v>621</v>
+      </c>
+      <c r="I379" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="K379" s="115"/>
+    </row>
+    <row r="380" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A380" s="31">
+        <v>10580004</v>
+      </c>
+      <c r="B380" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C380" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="D379" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E379" s="31" t="s">
+      <c r="D380" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="E380" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="F379" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G379" s="31" t="s">
-        <v>618</v>
-      </c>
-      <c r="H379" s="31" t="s">
-        <v>617</v>
-      </c>
-      <c r="I379" s="31" t="s">
+      <c r="F380" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G380" s="31" t="s">
+        <v>622</v>
+      </c>
+      <c r="H380" s="31" t="s">
+        <v>621</v>
+      </c>
+      <c r="I380" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="K379" s="115"/>
-    </row>
-    <row r="380" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A380" s="32">
-        <v>10550001</v>
-      </c>
-      <c r="B380" s="32">
-        <v>105500</v>
-      </c>
-      <c r="C380" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="D380" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E380" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="F380" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G380" s="32" t="s">
-        <v>619</v>
-      </c>
-      <c r="I380" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="K380" s="116"/>
+      <c r="K380" s="115"/>
     </row>
     <row r="381" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A381" s="32">
-        <v>10550002</v>
+        <v>10550001</v>
       </c>
       <c r="B381" s="32">
         <v>105500</v>
       </c>
       <c r="C381" s="32" t="s">
-        <v>620</v>
+        <v>253</v>
       </c>
       <c r="D381" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E381" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F381" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G381" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="I381" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K381" s="116"/>
+    </row>
+    <row r="382" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A382" s="32">
+        <v>10550002</v>
+      </c>
+      <c r="B382" s="32">
+        <v>105500</v>
+      </c>
+      <c r="C382" s="32" t="s">
+        <v>624</v>
+      </c>
+      <c r="D382" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E382" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="F381" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G381" s="32" t="s">
+      <c r="F382" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G382" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="I381" s="32" t="s">
+      <c r="I382" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="K381" s="116"/>
-    </row>
-    <row r="382" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A382" s="33">
-        <v>10480001</v>
-      </c>
-      <c r="B382" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C382" s="33" t="s">
-        <v>501</v>
-      </c>
-      <c r="D382" s="33" t="s">
-        <v>422</v>
-      </c>
-      <c r="E382" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="F382" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G382" s="33" t="s">
-        <v>621</v>
-      </c>
-      <c r="H382" s="33" t="s">
-        <v>622</v>
-      </c>
-      <c r="I382" s="33" t="s">
-        <v>545</v>
-      </c>
-      <c r="K382" s="82"/>
+      <c r="K382" s="116"/>
     </row>
     <row r="383" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A383" s="33">
-        <v>10480002</v>
+        <v>10480001</v>
       </c>
       <c r="B383" s="33">
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>623</v>
+        <v>505</v>
       </c>
       <c r="D383" s="33" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="E383" s="33" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F383" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G383" s="33" t="s">
-        <v>460</v>
+        <v>625</v>
       </c>
       <c r="H383" s="33" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I383" s="33" t="s">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="K383" s="82"/>
     </row>
     <row r="384" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A384" s="33">
-        <v>10480003</v>
+        <v>10480002</v>
       </c>
       <c r="B384" s="33">
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D384" s="33" t="s">
         <v>328</v>
@@ -14802,28 +14811,28 @@
         <v>133</v>
       </c>
       <c r="G384" s="33" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H384" s="33" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K384" s="82"/>
     </row>
     <row r="385" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A385" s="33">
-        <v>10480004</v>
+        <v>10480003</v>
       </c>
       <c r="B385" s="33">
         <v>104800</v>
       </c>
       <c r="C385" s="33" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D385" s="33" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E385" s="33" t="s">
         <v>143</v>
@@ -14832,28 +14841,28 @@
         <v>133</v>
       </c>
       <c r="G385" s="33" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H385" s="33" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I385" s="33" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="K385" s="82"/>
     </row>
     <row r="386" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A386" s="33">
-        <v>10480005</v>
+        <v>10480004</v>
       </c>
       <c r="B386" s="33">
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>289</v>
+        <v>629</v>
       </c>
       <c r="D386" s="33" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
       <c r="E386" s="33" t="s">
         <v>143</v>
@@ -14862,70 +14871,70 @@
         <v>133</v>
       </c>
       <c r="G386" s="33" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H386" s="33" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I386" s="33" t="s">
-        <v>291</v>
+        <v>107</v>
       </c>
       <c r="K386" s="82"/>
     </row>
     <row r="387" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A387" s="33">
-        <v>10480006</v>
+        <v>10480005</v>
       </c>
       <c r="B387" s="33">
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="D387" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E387" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F387" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G387" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="H387" s="33" t="s">
         <v>626</v>
       </c>
-      <c r="F387" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G387" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="H387" s="33" t="s">
-        <v>622</v>
-      </c>
       <c r="I387" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K387" s="117"/>
+        <v>291</v>
+      </c>
+      <c r="K387" s="82"/>
     </row>
     <row r="388" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A388" s="33">
-        <v>10480007</v>
+        <v>10480006</v>
       </c>
       <c r="B388" s="33">
         <v>104800</v>
       </c>
       <c r="C388" s="33" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D388" s="33" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E388" s="33" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="F388" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G388" s="33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H388" s="33" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I388" s="33" t="s">
         <v>333</v>
@@ -14934,136 +14943,139 @@
     </row>
     <row r="389" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A389" s="33">
-        <v>10480008</v>
+        <v>10480007</v>
       </c>
       <c r="B389" s="33">
         <v>104800</v>
       </c>
       <c r="C389" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="D389" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="E389" s="33" t="s">
+        <v>631</v>
+      </c>
+      <c r="F389" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G389" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="H389" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I389" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="K389" s="117"/>
+    </row>
+    <row r="390" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A390" s="33">
+        <v>10480008</v>
+      </c>
+      <c r="B390" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C390" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="D389" s="33" t="s">
+      <c r="D390" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E389" s="33" t="s">
+      <c r="E390" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="F389" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G389" s="33" t="s">
-        <v>467</v>
-      </c>
-      <c r="H389" s="33" t="s">
+      <c r="F390" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G390" s="33" t="s">
+        <v>471</v>
+      </c>
+      <c r="H390" s="33" t="s">
         <v>408</v>
       </c>
-      <c r="I389" s="33" t="s">
+      <c r="I390" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="K389" s="82"/>
-    </row>
-    <row r="390" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A390" s="32">
-        <v>10550101</v>
-      </c>
-      <c r="B390" s="32">
-        <v>105501</v>
-      </c>
-      <c r="C390" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="D390" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E390" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="F390" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G390" s="32" t="s">
-        <v>619</v>
-      </c>
-      <c r="I390" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="K390" s="116"/>
+      <c r="K390" s="82"/>
     </row>
     <row r="391" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A391" s="32">
-        <v>10550102</v>
+        <v>10550101</v>
       </c>
       <c r="B391" s="32">
         <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>620</v>
+        <v>253</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="F391" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>297</v>
+        <v>623</v>
       </c>
       <c r="I391" s="32" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K391" s="116"/>
     </row>
     <row r="392" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A392" s="32">
-        <v>10550103</v>
+        <v>10550102</v>
       </c>
       <c r="B392" s="32">
         <v>105501</v>
       </c>
       <c r="C392" s="32" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D392" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>36</v>
+        <v>299</v>
       </c>
       <c r="F392" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>619</v>
+        <v>297</v>
       </c>
       <c r="I392" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K392" s="116"/>
     </row>
     <row r="393" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A393" s="32">
-        <v>10550201</v>
+        <v>10550103</v>
       </c>
       <c r="B393" s="32">
-        <v>105502</v>
+        <v>105501</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>253</v>
+        <v>632</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="F393" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G393" s="32" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I393" s="32" t="s">
         <v>39</v>
@@ -15072,46 +15084,46 @@
     </row>
     <row r="394" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A394" s="32">
-        <v>10550202</v>
+        <v>10550201</v>
       </c>
       <c r="B394" s="32">
         <v>105502</v>
       </c>
       <c r="C394" s="32" t="s">
-        <v>620</v>
+        <v>253</v>
       </c>
       <c r="D394" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="F394" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G394" s="32" t="s">
-        <v>297</v>
+        <v>623</v>
       </c>
       <c r="I394" s="32" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K394" s="116"/>
     </row>
-    <row r="395" ht="16.5" spans="1:11">
+    <row r="395" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A395" s="32">
-        <v>10550203</v>
+        <v>10550202</v>
       </c>
       <c r="B395" s="32">
         <v>105502</v>
       </c>
       <c r="C395" s="32" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D395" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="F395" s="32" t="s">
         <v>133</v>
@@ -15120,81 +15132,78 @@
         <v>297</v>
       </c>
       <c r="I395" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="K395" s="116"/>
+    </row>
+    <row r="396" ht="16.5" spans="1:11">
+      <c r="A396" s="32">
+        <v>10550203</v>
+      </c>
+      <c r="B396" s="32">
+        <v>105502</v>
+      </c>
+      <c r="C396" s="32" t="s">
+        <v>633</v>
+      </c>
+      <c r="D396" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E396" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F396" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G396" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="I396" s="32" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="396" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A396" s="34">
-        <v>10410001</v>
-      </c>
-      <c r="B396" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C396" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="D396" s="34" t="s">
-        <v>422</v>
-      </c>
-      <c r="E396" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="F396" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G396" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="H396" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I396" s="34" t="s">
-        <v>545</v>
-      </c>
-      <c r="K396" s="118"/>
     </row>
     <row r="397" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A397" s="34">
-        <v>10410002</v>
+        <v>10410001</v>
       </c>
       <c r="B397" s="34">
         <v>104100</v>
       </c>
       <c r="C397" s="34" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="E397" s="34" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="F397" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="H397" s="34" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="I397" s="34" t="s">
-        <v>107</v>
+        <v>549</v>
       </c>
       <c r="K397" s="118"/>
     </row>
     <row r="398" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A398" s="34">
-        <v>10410003</v>
+        <v>10410002</v>
       </c>
       <c r="B398" s="34">
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>412</v>
+        <v>560</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E398" s="34" t="s">
         <v>114</v>
@@ -15206,118 +15215,118 @@
         <v>234</v>
       </c>
       <c r="H398" s="34" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="I398" s="34" t="s">
-        <v>291</v>
+        <v>107</v>
       </c>
       <c r="K398" s="118"/>
     </row>
     <row r="399" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A399" s="34">
-        <v>10410004</v>
+        <v>10410003</v>
       </c>
       <c r="B399" s="34">
         <v>104100</v>
       </c>
       <c r="C399" s="34" t="s">
-        <v>253</v>
+        <v>414</v>
       </c>
       <c r="D399" s="34" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E399" s="34" t="s">
-        <v>416</v>
+        <v>114</v>
       </c>
       <c r="F399" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G399" s="34" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H399" s="34" t="s">
-        <v>630</v>
+        <v>415</v>
       </c>
       <c r="I399" s="34" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="K399" s="118"/>
     </row>
     <row r="400" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A400" s="34">
-        <v>10410005</v>
+        <v>10410004</v>
       </c>
       <c r="B400" s="34">
         <v>104100</v>
       </c>
       <c r="C400" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="D400" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E400" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="F400" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G400" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="H400" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="I400" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="K400" s="118"/>
+    </row>
+    <row r="401" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A401" s="34">
+        <v>10410005</v>
+      </c>
+      <c r="B401" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C401" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D400" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E400" s="34" t="s">
+      <c r="D401" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E401" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="F400" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G400" s="34" t="s">
+      <c r="F401" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G401" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="H400" s="34" t="s">
-        <v>455</v>
-      </c>
-      <c r="I400" s="34" t="s">
+      <c r="H401" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="I401" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="K400" s="118"/>
-    </row>
-    <row r="401" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A401" s="35">
-        <v>10420001</v>
-      </c>
-      <c r="B401" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C401" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="D401" s="35" t="s">
-        <v>422</v>
-      </c>
-      <c r="E401" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="F401" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G401" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H401" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I401" s="35" t="s">
-        <v>545</v>
-      </c>
-      <c r="K401" s="119"/>
+      <c r="K401" s="118"/>
     </row>
     <row r="402" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A402" s="35">
-        <v>10420002</v>
+        <v>10420001</v>
       </c>
       <c r="B402" s="35">
         <v>104200</v>
       </c>
       <c r="C402" s="35" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="E402" s="35" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F402" s="35" t="s">
         <v>133</v>
@@ -15326,25 +15335,25 @@
         <v>234</v>
       </c>
       <c r="H402" s="35" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="I402" s="35" t="s">
-        <v>107</v>
+        <v>549</v>
       </c>
       <c r="K402" s="119"/>
     </row>
     <row r="403" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A403" s="35">
-        <v>10420003</v>
+        <v>10420002</v>
       </c>
       <c r="B403" s="35">
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>412</v>
+        <v>560</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="E403" s="35" t="s">
         <v>143</v>
@@ -15356,143 +15365,144 @@
         <v>234</v>
       </c>
       <c r="H403" s="35" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="I403" s="35" t="s">
-        <v>291</v>
+        <v>107</v>
       </c>
       <c r="K403" s="119"/>
     </row>
     <row r="404" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A404" s="35">
-        <v>10420004</v>
+        <v>10420003</v>
       </c>
       <c r="B404" s="35">
         <v>104200</v>
       </c>
       <c r="C404" s="35" t="s">
-        <v>253</v>
+        <v>414</v>
       </c>
       <c r="D404" s="35" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E404" s="35" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F404" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G404" s="35" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H404" s="35" t="s">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="I404" s="35" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="K404" s="119"/>
     </row>
     <row r="405" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A405" s="35">
-        <v>10420005</v>
+        <v>10420004</v>
       </c>
       <c r="B405" s="35">
         <v>104200</v>
       </c>
       <c r="C405" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="D405" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E405" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="F405" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G405" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="H405" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="I405" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="K405" s="119"/>
+    </row>
+    <row r="406" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A406" s="35">
+        <v>10420005</v>
+      </c>
+      <c r="B406" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C406" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="D405" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="E405" s="35" t="s">
+      <c r="D406" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="E406" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="F405" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G405" s="35" t="s">
+      <c r="F406" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G406" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="H405" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I405" s="35" t="s">
+      <c r="H406" s="35" t="s">
+        <v>554</v>
+      </c>
+      <c r="I406" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="K405" s="119"/>
-    </row>
-    <row r="406" ht="16.5" spans="1:11">
-      <c r="A406" s="32">
-        <v>10190001</v>
-      </c>
-      <c r="B406" s="32">
-        <v>101900</v>
-      </c>
-      <c r="C406" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="D406" s="32" t="s">
-        <v>422</v>
-      </c>
-      <c r="E406" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="F406" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G406" s="32" t="s">
-        <v>458</v>
-      </c>
-      <c r="H406" s="32" t="s">
-        <v>631</v>
-      </c>
-      <c r="I406" s="32" t="s">
-        <v>294</v>
-      </c>
+      <c r="K406" s="119"/>
     </row>
     <row r="407" ht="16.5" spans="1:11">
       <c r="A407" s="32">
-        <v>10190002</v>
+        <v>10190001</v>
       </c>
       <c r="B407" s="32">
         <v>101900</v>
       </c>
       <c r="C407" s="32" t="s">
-        <v>623</v>
+        <v>313</v>
       </c>
       <c r="D407" s="32" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E407" s="32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F407" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G407" s="32" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H407" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I407" s="32" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
     </row>
     <row r="408" ht="16.5" spans="1:11">
       <c r="A408" s="32">
-        <v>10190003</v>
+        <v>10190002</v>
       </c>
       <c r="B408" s="32">
         <v>101900</v>
       </c>
       <c r="C408" s="32" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D408" s="32" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E408" s="32" t="s">
         <v>143</v>
@@ -15501,27 +15511,27 @@
         <v>133</v>
       </c>
       <c r="G408" s="32" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H408" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I408" s="32" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="409" ht="16.5" spans="1:11">
       <c r="A409" s="32">
-        <v>10190004</v>
+        <v>10190003</v>
       </c>
       <c r="B409" s="32">
         <v>101900</v>
       </c>
       <c r="C409" s="32" t="s">
-        <v>556</v>
+        <v>635</v>
       </c>
       <c r="D409" s="32" t="s">
-        <v>633</v>
+        <v>429</v>
       </c>
       <c r="E409" s="32" t="s">
         <v>143</v>
@@ -15530,27 +15540,27 @@
         <v>133</v>
       </c>
       <c r="G409" s="32" t="s">
-        <v>324</v>
+        <v>463</v>
       </c>
       <c r="H409" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I409" s="32" t="s">
-        <v>107</v>
+        <v>327</v>
       </c>
     </row>
     <row r="410" ht="16.5" spans="1:11">
       <c r="A410" s="32">
-        <v>10190005</v>
+        <v>10190004</v>
       </c>
       <c r="B410" s="32">
         <v>101900</v>
       </c>
       <c r="C410" s="32" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="D410" s="32" t="s">
-        <v>566</v>
+        <v>636</v>
       </c>
       <c r="E410" s="32" t="s">
         <v>143</v>
@@ -15559,68 +15569,68 @@
         <v>133</v>
       </c>
       <c r="G410" s="32" t="s">
-        <v>460</v>
+        <v>324</v>
       </c>
       <c r="H410" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I410" s="32" t="s">
-        <v>291</v>
+        <v>107</v>
       </c>
     </row>
     <row r="411" ht="16.5" spans="1:11">
       <c r="A411" s="32">
-        <v>10190006</v>
+        <v>10190005</v>
       </c>
       <c r="B411" s="32">
         <v>101900</v>
       </c>
       <c r="C411" s="32" t="s">
-        <v>330</v>
+        <v>604</v>
       </c>
       <c r="D411" s="32" t="s">
-        <v>422</v>
+        <v>570</v>
       </c>
       <c r="E411" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="F411" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G411" s="32" t="s">
+        <v>463</v>
+      </c>
+      <c r="H411" s="32" t="s">
         <v>634</v>
       </c>
-      <c r="F411" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G411" s="32" t="s">
-        <v>635</v>
-      </c>
-      <c r="H411" s="32" t="s">
-        <v>631</v>
-      </c>
       <c r="I411" s="32" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
     </row>
     <row r="412" ht="16.5" spans="1:11">
       <c r="A412" s="32">
-        <v>10190007</v>
+        <v>10190006</v>
       </c>
       <c r="B412" s="32">
         <v>101900</v>
       </c>
       <c r="C412" s="32" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D412" s="32" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E412" s="32" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F412" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G412" s="32" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H412" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I412" s="32" t="s">
         <v>333</v>
@@ -15628,45 +15638,45 @@
     </row>
     <row r="413" ht="16.5" spans="1:11">
       <c r="A413" s="32">
-        <v>10190008</v>
+        <v>10190007</v>
       </c>
       <c r="B413" s="32">
         <v>101900</v>
       </c>
       <c r="C413" s="32" t="s">
-        <v>638</v>
+        <v>334</v>
       </c>
       <c r="D413" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="E413" s="32" t="s">
         <v>639</v>
       </c>
-      <c r="E413" s="32" t="s">
+      <c r="F413" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G413" s="32" t="s">
         <v>640</v>
       </c>
-      <c r="F413" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G413" s="32" t="s">
-        <v>635</v>
-      </c>
       <c r="H413" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I413" s="32" t="s">
-        <v>641</v>
+        <v>333</v>
       </c>
     </row>
     <row r="414" ht="16.5" spans="1:11">
       <c r="A414" s="32">
-        <v>10190009</v>
+        <v>10190008</v>
       </c>
       <c r="B414" s="32">
         <v>101900</v>
       </c>
       <c r="C414" s="32" t="s">
+        <v>641</v>
+      </c>
+      <c r="D414" s="32" t="s">
         <v>642</v>
-      </c>
-      <c r="D414" s="32" t="s">
-        <v>639</v>
       </c>
       <c r="E414" s="32" t="s">
         <v>643</v>
@@ -15675,10 +15685,10 @@
         <v>133</v>
       </c>
       <c r="G414" s="32" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H414" s="32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="I414" s="32" t="s">
         <v>644</v>
@@ -15686,43 +15696,61 @@
     </row>
     <row r="415" ht="16.5" spans="1:11">
       <c r="A415" s="32">
-        <v>10190010</v>
+        <v>10190009</v>
       </c>
       <c r="B415" s="32">
         <v>101900</v>
       </c>
       <c r="C415" s="32" t="s">
+        <v>645</v>
+      </c>
+      <c r="D415" s="32" t="s">
+        <v>642</v>
+      </c>
+      <c r="E415" s="32" t="s">
+        <v>646</v>
+      </c>
+      <c r="F415" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G415" s="32" t="s">
+        <v>640</v>
+      </c>
+      <c r="H415" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="I415" s="32" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="416" ht="16.5" spans="1:11">
+      <c r="A416" s="32">
+        <v>10190010</v>
+      </c>
+      <c r="B416" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C416" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D415" s="32" t="s">
-        <v>645</v>
-      </c>
-      <c r="E415" s="32" t="s">
+      <c r="D416" s="32" t="s">
+        <v>648</v>
+      </c>
+      <c r="E416" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="F415" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G415" s="32" t="s">
-        <v>646</v>
-      </c>
-      <c r="H415" s="32" t="s">
-        <v>631</v>
-      </c>
-      <c r="I415" s="32" t="s">
+      <c r="F416" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G416" s="32" t="s">
+        <v>649</v>
+      </c>
+      <c r="H416" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="I416" s="32" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="416" ht="16.5" spans="1:11">
-      <c r="A416" s="32"/>
-      <c r="B416" s="32"/>
-      <c r="C416" s="32"/>
-      <c r="D416" s="32"/>
-      <c r="E416" s="32"/>
-      <c r="F416" s="32"/>
-      <c r="G416" s="32"/>
-      <c r="H416" s="32"/>
-      <c r="I416" s="32"/>
     </row>
     <row r="417" ht="16.5" spans="1:9">
       <c r="A417" s="32"/>
@@ -15756,6 +15784,17 @@
       <c r="G419" s="32"/>
       <c r="H419" s="32"/>
       <c r="I419" s="32"/>
+    </row>
+    <row r="420" ht="16.5" spans="1:9">
+      <c r="A420" s="32"/>
+      <c r="B420" s="32"/>
+      <c r="C420" s="32"/>
+      <c r="D420" s="32"/>
+      <c r="E420" s="32"/>
+      <c r="F420" s="32"/>
+      <c r="G420" s="32"/>
+      <c r="H420" s="32"/>
+      <c r="I420" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15775,24 +15814,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15800,16 +15839,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F3" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15817,16 +15856,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F4" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15834,16 +15873,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15851,7 +15890,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15859,7 +15898,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15867,7 +15906,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15875,7 +15914,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15883,7 +15922,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15891,7 +15930,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15899,7 +15938,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15907,7 +15946,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15915,7 +15954,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15923,7 +15962,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15931,7 +15970,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -15939,7 +15978,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -15947,7 +15986,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -15955,7 +15994,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -15963,7 +16002,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -15971,7 +16010,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -15979,7 +16018,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -15987,7 +16026,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -15995,7 +16034,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -16003,7 +16042,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -16011,7 +16050,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -16019,7 +16058,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -16027,7 +16066,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -16035,7 +16074,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -16043,7 +16082,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -16051,7 +16090,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -16059,7 +16098,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -16067,7 +16106,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -16075,7 +16114,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -16083,7 +16122,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -16091,7 +16130,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -16099,7 +16138,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -16107,7 +16146,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -16115,7 +16154,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -16123,7 +16162,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -16131,7 +16170,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -16139,7 +16178,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -16147,7 +16186,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -16155,7 +16194,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -16163,7 +16202,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -16171,7 +16210,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -16179,7 +16218,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -16187,7 +16226,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="705">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1990,6 +1990,9 @@
     <t>第3轴必然出现金色符号</t>
   </si>
   <si>
+    <t>12_100|13_90|14_80|15_60|16_40|17_20|18_10|19_5|20_1</t>
+  </si>
+  <si>
     <t>12_13_14_15_16_17_18_19_20</t>
   </si>
   <si>
@@ -2015,9 +2018,6 @@
   </si>
   <si>
     <t>28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|6_1_1|21_1_1|26_1_1|27_1_1</t>
   </si>
   <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1|37_1_1|38_1_1|39_1_1|40_1_1|41_1_1|42_1_1|43_1_1|44_1_1|45_1_1|46_1_1|47_1_1|48_1_1|49_1_1|</t>
@@ -2472,12 +2472,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3565,7 +3565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N420"/>
+  <dimension ref="A1:N419"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -14394,7 +14394,7 @@
         <v>328</v>
       </c>
       <c r="E370" s="29" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F370" s="29" t="s">
         <v>133</v>
@@ -14403,7 +14403,7 @@
         <v>353</v>
       </c>
       <c r="H370" s="29" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I370" s="29" t="s">
         <v>109</v>
@@ -14430,10 +14430,10 @@
         <v>133</v>
       </c>
       <c r="G371" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H371" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I371" s="30" t="s">
         <v>605</v>
@@ -14460,10 +14460,10 @@
         <v>133</v>
       </c>
       <c r="G372" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H372" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I372" s="30" t="s">
         <v>603</v>
@@ -14478,7 +14478,7 @@
         <v>105700</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D373" s="30" t="s">
         <v>328</v>
@@ -14490,10 +14490,10 @@
         <v>133</v>
       </c>
       <c r="G373" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H373" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I373" s="30" t="s">
         <v>340</v>
@@ -14508,22 +14508,22 @@
         <v>105700</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D374" s="30" t="s">
         <v>328</v>
       </c>
       <c r="E374" s="30" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F374" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G374" s="30" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H374" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I374" s="30" t="s">
         <v>294</v>
@@ -14544,13 +14544,13 @@
         <v>21</v>
       </c>
       <c r="E375" s="30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F375" s="30" t="s">
         <v>133</v>
       </c>
       <c r="G375" s="30" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H375" s="30" t="s">
         <v>415</v>
@@ -14560,45 +14560,48 @@
       </c>
       <c r="K375" s="114"/>
     </row>
-    <row r="376" s="30" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A376" s="30">
-        <v>10570006</v>
-      </c>
-      <c r="B376" s="30">
-        <v>105700</v>
-      </c>
-      <c r="C376" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="D376" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="E376" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="F376" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G376" s="30" t="s">
-        <v>619</v>
-      </c>
-      <c r="I376" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="K376" s="114"/>
+    <row r="376" s="31" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A376" s="31">
+        <v>10580001</v>
+      </c>
+      <c r="B376" s="31">
+        <v>105800</v>
+      </c>
+      <c r="C376" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D376" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="E376" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F376" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G376" s="31" t="s">
+        <v>620</v>
+      </c>
+      <c r="H376" s="31" t="s">
+        <v>621</v>
+      </c>
+      <c r="I376" s="31" t="s">
+        <v>605</v>
+      </c>
+      <c r="K376" s="115"/>
     </row>
     <row r="377" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A377" s="31">
-        <v>10580001</v>
+        <v>10580002</v>
       </c>
       <c r="B377" s="31">
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="D377" s="31" t="s">
-        <v>426</v>
+        <v>328</v>
       </c>
       <c r="E377" s="31" t="s">
         <v>299</v>
@@ -14613,19 +14616,19 @@
         <v>621</v>
       </c>
       <c r="I377" s="31" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K377" s="115"/>
     </row>
     <row r="378" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A378" s="31">
-        <v>10580002</v>
+        <v>10580003</v>
       </c>
       <c r="B378" s="31">
         <v>105800</v>
       </c>
       <c r="C378" s="31" t="s">
-        <v>259</v>
+        <v>614</v>
       </c>
       <c r="D378" s="31" t="s">
         <v>328</v>
@@ -14643,163 +14646,166 @@
         <v>621</v>
       </c>
       <c r="I378" s="31" t="s">
-        <v>603</v>
+        <v>340</v>
       </c>
       <c r="K378" s="115"/>
     </row>
     <row r="379" s="31" customFormat="1" ht="16.5" spans="1:11">
       <c r="A379" s="31">
-        <v>10580003</v>
+        <v>10580004</v>
       </c>
       <c r="B379" s="31">
         <v>105800</v>
       </c>
       <c r="C379" s="31" t="s">
-        <v>613</v>
+        <v>253</v>
       </c>
       <c r="D379" s="31" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="E379" s="31" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="F379" s="31" t="s">
         <v>133</v>
       </c>
       <c r="G379" s="31" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H379" s="31" t="s">
         <v>621</v>
       </c>
       <c r="I379" s="31" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="K379" s="115"/>
     </row>
-    <row r="380" s="31" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A380" s="31">
-        <v>10580004</v>
-      </c>
-      <c r="B380" s="31">
-        <v>105800</v>
-      </c>
-      <c r="C380" s="31" t="s">
+    <row r="380" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A380" s="32">
+        <v>10550001</v>
+      </c>
+      <c r="B380" s="32">
+        <v>105500</v>
+      </c>
+      <c r="C380" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D380" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="E380" s="31" t="s">
+      <c r="D380" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E380" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F380" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G380" s="31" t="s">
-        <v>622</v>
-      </c>
-      <c r="H380" s="31" t="s">
-        <v>621</v>
-      </c>
-      <c r="I380" s="31" t="s">
+      <c r="F380" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G380" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="I380" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K380" s="115"/>
+      <c r="K380" s="116"/>
     </row>
     <row r="381" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A381" s="32">
-        <v>10550001</v>
+        <v>10550002</v>
       </c>
       <c r="B381" s="32">
         <v>105500</v>
       </c>
       <c r="C381" s="32" t="s">
-        <v>253</v>
+        <v>624</v>
       </c>
       <c r="D381" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E381" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F381" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G381" s="32" t="s">
-        <v>623</v>
+        <v>297</v>
+      </c>
+      <c r="H381" s="32">
+        <v>8</v>
       </c>
       <c r="I381" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K381" s="116"/>
     </row>
-    <row r="382" s="32" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A382" s="32">
-        <v>10550002</v>
-      </c>
-      <c r="B382" s="32">
-        <v>105500</v>
-      </c>
-      <c r="C382" s="32" t="s">
-        <v>624</v>
-      </c>
-      <c r="D382" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E382" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="F382" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G382" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I382" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K382" s="116"/>
+    <row r="382" s="33" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A382" s="33">
+        <v>10480001</v>
+      </c>
+      <c r="B382" s="33">
+        <v>104800</v>
+      </c>
+      <c r="C382" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="D382" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="E382" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F382" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G382" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H382" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I382" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="K382" s="82"/>
     </row>
     <row r="383" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A383" s="33">
-        <v>10480001</v>
+        <v>10480002</v>
       </c>
       <c r="B383" s="33">
         <v>104800</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>505</v>
+        <v>627</v>
       </c>
       <c r="D383" s="33" t="s">
-        <v>426</v>
+        <v>328</v>
       </c>
       <c r="E383" s="33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F383" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G383" s="33" t="s">
-        <v>625</v>
+        <v>463</v>
       </c>
       <c r="H383" s="33" t="s">
         <v>626</v>
       </c>
       <c r="I383" s="33" t="s">
-        <v>549</v>
+        <v>325</v>
       </c>
       <c r="K383" s="82"/>
     </row>
     <row r="384" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A384" s="33">
-        <v>10480002</v>
+        <v>10480003</v>
       </c>
       <c r="B384" s="33">
         <v>104800</v>
       </c>
       <c r="C384" s="33" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D384" s="33" t="s">
         <v>328</v>
@@ -14817,22 +14823,22 @@
         <v>626</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K384" s="82"/>
     </row>
     <row r="385" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A385" s="33">
-        <v>10480003</v>
+        <v>10480004</v>
       </c>
       <c r="B385" s="33">
         <v>104800</v>
       </c>
       <c r="C385" s="33" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D385" s="33" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E385" s="33" t="s">
         <v>143</v>
@@ -14847,22 +14853,22 @@
         <v>626</v>
       </c>
       <c r="I385" s="33" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="K385" s="82"/>
     </row>
     <row r="386" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A386" s="33">
-        <v>10480004</v>
+        <v>10480005</v>
       </c>
       <c r="B386" s="33">
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>629</v>
+        <v>289</v>
       </c>
       <c r="D386" s="33" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E386" s="33" t="s">
         <v>143</v>
@@ -14877,61 +14883,61 @@
         <v>626</v>
       </c>
       <c r="I386" s="33" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K386" s="82"/>
     </row>
     <row r="387" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A387" s="33">
-        <v>10480005</v>
+        <v>10480006</v>
       </c>
       <c r="B387" s="33">
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="D387" s="33" t="s">
         <v>426</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>143</v>
+        <v>630</v>
       </c>
       <c r="F387" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G387" s="33" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H387" s="33" t="s">
         <v>626</v>
       </c>
       <c r="I387" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="K387" s="82"/>
+        <v>333</v>
+      </c>
+      <c r="K387" s="117"/>
     </row>
     <row r="388" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A388" s="33">
-        <v>10480006</v>
+        <v>10480007</v>
       </c>
       <c r="B388" s="33">
         <v>104800</v>
       </c>
       <c r="C388" s="33" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D388" s="33" t="s">
         <v>426</v>
       </c>
       <c r="E388" s="33" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F388" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G388" s="33" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="H388" s="33" t="s">
         <v>626</v>
@@ -14943,133 +14949,130 @@
     </row>
     <row r="389" s="33" customFormat="1" ht="16.5" spans="1:11">
       <c r="A389" s="33">
-        <v>10480007</v>
+        <v>10480008</v>
       </c>
       <c r="B389" s="33">
         <v>104800</v>
       </c>
       <c r="C389" s="33" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="D389" s="33" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="E389" s="33" t="s">
-        <v>631</v>
+        <v>254</v>
       </c>
       <c r="F389" s="33" t="s">
         <v>133</v>
       </c>
       <c r="G389" s="33" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H389" s="33" t="s">
-        <v>626</v>
+        <v>408</v>
       </c>
       <c r="I389" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="K389" s="117"/>
-    </row>
-    <row r="390" s="33" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A390" s="33">
-        <v>10480008</v>
-      </c>
-      <c r="B390" s="33">
-        <v>104800</v>
-      </c>
-      <c r="C390" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K389" s="82"/>
+    </row>
+    <row r="390" s="32" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A390" s="32">
+        <v>10550101</v>
+      </c>
+      <c r="B390" s="32">
+        <v>105501</v>
+      </c>
+      <c r="C390" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D390" s="33" t="s">
+      <c r="D390" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E390" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F390" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G390" s="33" t="s">
-        <v>471</v>
-      </c>
-      <c r="H390" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="I390" s="33" t="s">
+      <c r="E390" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F390" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G390" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="I390" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K390" s="82"/>
+      <c r="K390" s="116"/>
     </row>
     <row r="391" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A391" s="32">
-        <v>10550101</v>
+        <v>10550102</v>
       </c>
       <c r="B391" s="32">
         <v>105501</v>
       </c>
       <c r="C391" s="32" t="s">
-        <v>253</v>
+        <v>624</v>
       </c>
       <c r="D391" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F391" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>623</v>
+        <v>297</v>
       </c>
       <c r="I391" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K391" s="116"/>
     </row>
     <row r="392" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A392" s="32">
-        <v>10550102</v>
+        <v>10550103</v>
       </c>
       <c r="B392" s="32">
         <v>105501</v>
       </c>
       <c r="C392" s="32" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="D392" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="F392" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G392" s="32" t="s">
-        <v>297</v>
+        <v>623</v>
       </c>
       <c r="I392" s="32" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="K392" s="116"/>
     </row>
     <row r="393" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A393" s="32">
-        <v>10550103</v>
+        <v>10550201</v>
       </c>
       <c r="B393" s="32">
-        <v>105501</v>
+        <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>632</v>
+        <v>253</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="F393" s="32" t="s">
         <v>133</v>
@@ -15084,46 +15087,46 @@
     </row>
     <row r="394" s="32" customFormat="1" ht="16.5" spans="1:11">
       <c r="A394" s="32">
-        <v>10550201</v>
+        <v>10550202</v>
       </c>
       <c r="B394" s="32">
         <v>105502</v>
       </c>
       <c r="C394" s="32" t="s">
-        <v>253</v>
+        <v>624</v>
       </c>
       <c r="D394" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="F394" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G394" s="32" t="s">
-        <v>623</v>
+        <v>297</v>
       </c>
       <c r="I394" s="32" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="K394" s="116"/>
     </row>
-    <row r="395" s="32" customFormat="1" ht="16.5" spans="1:11">
+    <row r="395" ht="16.5" spans="1:11">
       <c r="A395" s="32">
-        <v>10550202</v>
+        <v>10550203</v>
       </c>
       <c r="B395" s="32">
         <v>105502</v>
       </c>
       <c r="C395" s="32" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D395" s="32" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="F395" s="32" t="s">
         <v>133</v>
@@ -15132,78 +15135,81 @@
         <v>297</v>
       </c>
       <c r="I395" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="K395" s="116"/>
-    </row>
-    <row r="396" ht="16.5" spans="1:11">
-      <c r="A396" s="32">
-        <v>10550203</v>
-      </c>
-      <c r="B396" s="32">
-        <v>105502</v>
-      </c>
-      <c r="C396" s="32" t="s">
-        <v>633</v>
-      </c>
-      <c r="D396" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E396" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="F396" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G396" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="I396" s="32" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="396" s="34" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A396" s="34">
+        <v>10410001</v>
+      </c>
+      <c r="B396" s="34">
+        <v>104100</v>
+      </c>
+      <c r="C396" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="D396" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="E396" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="F396" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G396" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H396" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="I396" s="34" t="s">
+        <v>549</v>
+      </c>
+      <c r="K396" s="118"/>
     </row>
     <row r="397" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A397" s="34">
-        <v>10410001</v>
+        <v>10410002</v>
       </c>
       <c r="B397" s="34">
         <v>104100</v>
       </c>
       <c r="C397" s="34" t="s">
-        <v>313</v>
+        <v>560</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>426</v>
+        <v>328</v>
       </c>
       <c r="E397" s="34" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="F397" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="H397" s="34" t="s">
         <v>415</v>
       </c>
       <c r="I397" s="34" t="s">
-        <v>549</v>
+        <v>107</v>
       </c>
       <c r="K397" s="118"/>
     </row>
     <row r="398" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A398" s="34">
-        <v>10410002</v>
+        <v>10410003</v>
       </c>
       <c r="B398" s="34">
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>560</v>
+        <v>414</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>328</v>
+        <v>442</v>
       </c>
       <c r="E398" s="34" t="s">
         <v>114</v>
@@ -15218,115 +15224,115 @@
         <v>415</v>
       </c>
       <c r="I398" s="34" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K398" s="118"/>
     </row>
     <row r="399" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A399" s="34">
-        <v>10410003</v>
+        <v>10410004</v>
       </c>
       <c r="B399" s="34">
         <v>104100</v>
       </c>
       <c r="C399" s="34" t="s">
-        <v>414</v>
+        <v>253</v>
       </c>
       <c r="D399" s="34" t="s">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="E399" s="34" t="s">
-        <v>114</v>
+        <v>418</v>
       </c>
       <c r="F399" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G399" s="34" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H399" s="34" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="I399" s="34" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K399" s="118"/>
     </row>
     <row r="400" s="34" customFormat="1" ht="16.5" spans="1:11">
       <c r="A400" s="34">
-        <v>10410004</v>
+        <v>10410005</v>
       </c>
       <c r="B400" s="34">
         <v>104100</v>
       </c>
       <c r="C400" s="34" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D400" s="34" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E400" s="34" t="s">
-        <v>418</v>
+        <v>114</v>
       </c>
       <c r="F400" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G400" s="34" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H400" s="34" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I400" s="34" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K400" s="118"/>
     </row>
-    <row r="401" s="34" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A401" s="34">
-        <v>10410005</v>
-      </c>
-      <c r="B401" s="34">
-        <v>104100</v>
-      </c>
-      <c r="C401" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="D401" s="34" t="s">
-        <v>442</v>
-      </c>
-      <c r="E401" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F401" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G401" s="34" t="s">
+    <row r="401" s="35" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A401" s="35">
+        <v>10420001</v>
+      </c>
+      <c r="B401" s="35">
+        <v>104200</v>
+      </c>
+      <c r="C401" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="D401" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="E401" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F401" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G401" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="H401" s="34" t="s">
-        <v>415</v>
-      </c>
-      <c r="I401" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="K401" s="118"/>
+      <c r="H401" s="35" t="s">
+        <v>554</v>
+      </c>
+      <c r="I401" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="K401" s="119"/>
     </row>
     <row r="402" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A402" s="35">
-        <v>10420001</v>
+        <v>10420002</v>
       </c>
       <c r="B402" s="35">
         <v>104200</v>
       </c>
       <c r="C402" s="35" t="s">
-        <v>313</v>
+        <v>560</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>426</v>
+        <v>328</v>
       </c>
       <c r="E402" s="35" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F402" s="35" t="s">
         <v>133</v>
@@ -15338,22 +15344,22 @@
         <v>554</v>
       </c>
       <c r="I402" s="35" t="s">
-        <v>549</v>
+        <v>107</v>
       </c>
       <c r="K402" s="119"/>
     </row>
     <row r="403" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A403" s="35">
-        <v>10420002</v>
+        <v>10420003</v>
       </c>
       <c r="B403" s="35">
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>560</v>
+        <v>414</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>328</v>
+        <v>442</v>
       </c>
       <c r="E403" s="35" t="s">
         <v>143</v>
@@ -15368,141 +15374,140 @@
         <v>554</v>
       </c>
       <c r="I403" s="35" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="K403" s="119"/>
     </row>
     <row r="404" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A404" s="35">
-        <v>10420003</v>
+        <v>10420004</v>
       </c>
       <c r="B404" s="35">
         <v>104200</v>
       </c>
       <c r="C404" s="35" t="s">
-        <v>414</v>
+        <v>253</v>
       </c>
       <c r="D404" s="35" t="s">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="E404" s="35" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="F404" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G404" s="35" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H404" s="35" t="s">
-        <v>554</v>
+        <v>598</v>
       </c>
       <c r="I404" s="35" t="s">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="K404" s="119"/>
     </row>
     <row r="405" s="35" customFormat="1" ht="16.5" spans="1:11">
       <c r="A405" s="35">
-        <v>10420004</v>
+        <v>10420005</v>
       </c>
       <c r="B405" s="35">
         <v>104200</v>
       </c>
       <c r="C405" s="35" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D405" s="35" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="E405" s="35" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="F405" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G405" s="35" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="H405" s="35" t="s">
-        <v>598</v>
+        <v>554</v>
       </c>
       <c r="I405" s="35" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="K405" s="119"/>
     </row>
-    <row r="406" s="35" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A406" s="35">
-        <v>10420005</v>
-      </c>
-      <c r="B406" s="35">
-        <v>104200</v>
-      </c>
-      <c r="C406" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="D406" s="35" t="s">
-        <v>442</v>
-      </c>
-      <c r="E406" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F406" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="G406" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H406" s="35" t="s">
-        <v>554</v>
-      </c>
-      <c r="I406" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="K406" s="119"/>
+    <row r="406" ht="16.5" spans="1:11">
+      <c r="A406" s="32">
+        <v>10190001</v>
+      </c>
+      <c r="B406" s="32">
+        <v>101900</v>
+      </c>
+      <c r="C406" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D406" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="E406" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F406" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G406" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="H406" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="I406" s="32" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="407" ht="16.5" spans="1:11">
       <c r="A407" s="32">
-        <v>10190001</v>
+        <v>10190002</v>
       </c>
       <c r="B407" s="32">
         <v>101900</v>
       </c>
       <c r="C407" s="32" t="s">
-        <v>313</v>
+        <v>627</v>
       </c>
       <c r="D407" s="32" t="s">
         <v>426</v>
       </c>
       <c r="E407" s="32" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F407" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G407" s="32" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H407" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I407" s="32" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="408" ht="16.5" spans="1:11">
       <c r="A408" s="32">
-        <v>10190002</v>
+        <v>10190003</v>
       </c>
       <c r="B408" s="32">
         <v>101900</v>
       </c>
       <c r="C408" s="32" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="D408" s="32" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E408" s="32" t="s">
         <v>143</v>
@@ -15517,21 +15522,21 @@
         <v>634</v>
       </c>
       <c r="I408" s="32" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="409" ht="16.5" spans="1:11">
       <c r="A409" s="32">
-        <v>10190003</v>
+        <v>10190004</v>
       </c>
       <c r="B409" s="32">
         <v>101900</v>
       </c>
       <c r="C409" s="32" t="s">
-        <v>635</v>
+        <v>560</v>
       </c>
       <c r="D409" s="32" t="s">
-        <v>429</v>
+        <v>636</v>
       </c>
       <c r="E409" s="32" t="s">
         <v>143</v>
@@ -15540,27 +15545,27 @@
         <v>133</v>
       </c>
       <c r="G409" s="32" t="s">
-        <v>463</v>
+        <v>324</v>
       </c>
       <c r="H409" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I409" s="32" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
     </row>
     <row r="410" ht="16.5" spans="1:11">
       <c r="A410" s="32">
-        <v>10190004</v>
+        <v>10190005</v>
       </c>
       <c r="B410" s="32">
         <v>101900</v>
       </c>
       <c r="C410" s="32" t="s">
-        <v>560</v>
+        <v>604</v>
       </c>
       <c r="D410" s="32" t="s">
-        <v>636</v>
+        <v>570</v>
       </c>
       <c r="E410" s="32" t="s">
         <v>143</v>
@@ -15569,65 +15574,65 @@
         <v>133</v>
       </c>
       <c r="G410" s="32" t="s">
-        <v>324</v>
+        <v>463</v>
       </c>
       <c r="H410" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I410" s="32" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
     </row>
     <row r="411" ht="16.5" spans="1:11">
       <c r="A411" s="32">
-        <v>10190005</v>
+        <v>10190006</v>
       </c>
       <c r="B411" s="32">
         <v>101900</v>
       </c>
       <c r="C411" s="32" t="s">
-        <v>604</v>
+        <v>330</v>
       </c>
       <c r="D411" s="32" t="s">
-        <v>570</v>
+        <v>426</v>
       </c>
       <c r="E411" s="32" t="s">
-        <v>143</v>
+        <v>637</v>
       </c>
       <c r="F411" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G411" s="32" t="s">
-        <v>463</v>
+        <v>638</v>
       </c>
       <c r="H411" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I411" s="32" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
     </row>
     <row r="412" ht="16.5" spans="1:11">
       <c r="A412" s="32">
-        <v>10190006</v>
+        <v>10190007</v>
       </c>
       <c r="B412" s="32">
         <v>101900</v>
       </c>
       <c r="C412" s="32" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D412" s="32" t="s">
         <v>426</v>
       </c>
       <c r="E412" s="32" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F412" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G412" s="32" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H412" s="32" t="s">
         <v>634</v>
@@ -15638,119 +15643,101 @@
     </row>
     <row r="413" ht="16.5" spans="1:11">
       <c r="A413" s="32">
-        <v>10190007</v>
+        <v>10190008</v>
       </c>
       <c r="B413" s="32">
         <v>101900</v>
       </c>
       <c r="C413" s="32" t="s">
-        <v>334</v>
+        <v>641</v>
       </c>
       <c r="D413" s="32" t="s">
-        <v>426</v>
+        <v>642</v>
       </c>
       <c r="E413" s="32" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F413" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G413" s="32" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H413" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I413" s="32" t="s">
-        <v>333</v>
+        <v>644</v>
       </c>
     </row>
     <row r="414" ht="16.5" spans="1:11">
       <c r="A414" s="32">
-        <v>10190008</v>
+        <v>10190009</v>
       </c>
       <c r="B414" s="32">
         <v>101900</v>
       </c>
       <c r="C414" s="32" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D414" s="32" t="s">
         <v>642</v>
       </c>
       <c r="E414" s="32" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F414" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G414" s="32" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H414" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I414" s="32" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="415" ht="16.5" spans="1:11">
       <c r="A415" s="32">
-        <v>10190009</v>
+        <v>10190010</v>
       </c>
       <c r="B415" s="32">
         <v>101900</v>
       </c>
       <c r="C415" s="32" t="s">
-        <v>645</v>
+        <v>253</v>
       </c>
       <c r="D415" s="32" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E415" s="32" t="s">
-        <v>646</v>
+        <v>275</v>
       </c>
       <c r="F415" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G415" s="32" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="H415" s="32" t="s">
         <v>634</v>
       </c>
       <c r="I415" s="32" t="s">
-        <v>647</v>
+        <v>39</v>
       </c>
     </row>
     <row r="416" ht="16.5" spans="1:11">
-      <c r="A416" s="32">
-        <v>10190010</v>
-      </c>
-      <c r="B416" s="32">
-        <v>101900</v>
-      </c>
-      <c r="C416" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="D416" s="32" t="s">
-        <v>648</v>
-      </c>
-      <c r="E416" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="F416" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="G416" s="32" t="s">
-        <v>649</v>
-      </c>
-      <c r="H416" s="32" t="s">
-        <v>634</v>
-      </c>
-      <c r="I416" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="A416" s="32"/>
+      <c r="B416" s="32"/>
+      <c r="C416" s="32"/>
+      <c r="D416" s="32"/>
+      <c r="E416" s="32"/>
+      <c r="F416" s="32"/>
+      <c r="G416" s="32"/>
+      <c r="H416" s="32"/>
+      <c r="I416" s="32"/>
     </row>
     <row r="417" ht="16.5" spans="1:9">
       <c r="A417" s="32"/>
@@ -15784,17 +15771,6 @@
       <c r="G419" s="32"/>
       <c r="H419" s="32"/>
       <c r="I419" s="32"/>
-    </row>
-    <row r="420" ht="16.5" spans="1:9">
-      <c r="A420" s="32"/>
-      <c r="B420" s="32"/>
-      <c r="C420" s="32"/>
-      <c r="D420" s="32"/>
-      <c r="E420" s="32"/>
-      <c r="F420" s="32"/>
-      <c r="G420" s="32"/>
-      <c r="H420" s="32"/>
-      <c r="I420" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -520,1002 +525,999 @@
     <t>概率出现1个免费图案</t>
   </si>
   <si>
+    <t>0_80|1_20</t>
+  </si>
+  <si>
+    <t>3列概率出现3个以下免费图案</t>
+  </si>
+  <si>
+    <t>2列必然出1个免费图案</t>
+  </si>
+  <si>
+    <t>12次&amp;14次免费</t>
+  </si>
+  <si>
+    <t>3列必然出1个免费图案</t>
+  </si>
+  <si>
+    <t>4列必然出1个免费图案</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1</t>
+  </si>
+  <si>
+    <t>4列必然额外出1个免费图案</t>
+  </si>
+  <si>
+    <t>14次免费</t>
+  </si>
+  <si>
+    <t>16_1_1</t>
+  </si>
+  <si>
+    <t>0_10|1_1</t>
+  </si>
+  <si>
+    <t>概率出现金色图标</t>
+  </si>
+  <si>
+    <t>11_1|12_1|13_1|14_1|15_1|16_1|17_1|18_1</t>
+  </si>
+  <si>
+    <t>修改对应图标</t>
+  </si>
+  <si>
+    <t>0_80|1_15|2_10|3_2</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-2条</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>0_95|1_5</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-2筒</t>
+  </si>
+  <si>
+    <t>12_1</t>
+  </si>
+  <si>
+    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-5条</t>
+  </si>
+  <si>
+    <t>13_1</t>
+  </si>
+  <si>
+    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-5筒</t>
+  </si>
+  <si>
+    <t>14_1</t>
+  </si>
+  <si>
+    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-八万</t>
+  </si>
+  <si>
+    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-白板</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-红中</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-发财</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>随机出大财神-不足5个</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>概率出现5个以下大财神</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>0_200|1_15|2_10|3_5|4_1</t>
+  </si>
+  <si>
+    <t>必出大财神-5个</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>横财神</t>
+  </si>
+  <si>
+    <t>第1行改为横财神</t>
+  </si>
+  <si>
+    <t>必然出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>4_1_1|7_1_1|10_1_1</t>
+  </si>
+  <si>
+    <t>第2行改为横财神</t>
+  </si>
+  <si>
+    <t>5_1_1|8_1_1|11_1_1</t>
+  </si>
+  <si>
+    <t>第3行改为横财神</t>
+  </si>
+  <si>
+    <t>6_1_1|9_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>正财神</t>
+  </si>
+  <si>
+    <t>第2列改为正财神</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1</t>
+  </si>
+  <si>
+    <t>第3列改为正财神</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第4列改为正财神</t>
+  </si>
+  <si>
+    <t>10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>中央第1行改为wild</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>中央第2行改为wild</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
+    <t>中央第3行改为wild</t>
+  </si>
+  <si>
+    <t>正财神第2列</t>
+  </si>
+  <si>
+    <t>中央第2列改为wild</t>
+  </si>
+  <si>
+    <t>中央第3列改为wild</t>
+  </si>
+  <si>
+    <t>中央第4列改为wild</t>
+  </si>
+  <si>
+    <t>横财神2次出现</t>
+  </si>
+  <si>
+    <t>概率出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16_21_22_23_24_25_26</t>
+  </si>
+  <si>
+    <t>0_60|1_40</t>
+  </si>
+  <si>
+    <t>23_1</t>
+  </si>
+  <si>
+    <t>正财神2次出现</t>
+  </si>
+  <si>
+    <t>24_1</t>
+  </si>
+  <si>
+    <t>25_1</t>
+  </si>
+  <si>
+    <t>26_1</t>
+  </si>
+  <si>
+    <t>横财神3次出现</t>
+  </si>
+  <si>
+    <t>31_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16_21_22_23_24_25_26_31_32_33_34_35_36</t>
+  </si>
+  <si>
+    <t>32_1</t>
+  </si>
+  <si>
+    <t>33_1</t>
+  </si>
+  <si>
+    <t>正财神3次出现</t>
+  </si>
+  <si>
+    <t>34_1</t>
+  </si>
+  <si>
+    <t>35_1</t>
+  </si>
+  <si>
+    <t>36_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭图案</t>
+  </si>
+  <si>
+    <t>概率出现百搭</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>12_13_1</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_20</t>
+  </si>
+  <si>
+    <t>1_60|2_25|3_15</t>
+  </si>
+  <si>
+    <t>必出出现jackpot图案</t>
+  </si>
+  <si>
+    <t>概率出现jackpot</t>
+  </si>
+  <si>
+    <t>第2列概率出现jackpot图案，最多1个</t>
+  </si>
+  <si>
+    <t>0_75|1_25</t>
+  </si>
+  <si>
+    <t>第3列概率出现jackpot图案，最多1个</t>
+  </si>
+  <si>
+    <t>0_85|1_15</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-铃铛</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-鞋子</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-杯子</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-饮品</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕1</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕2</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕3</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕4</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>9_10_11_12_13_14_15_16_17_18_19_20_21_22</t>
+  </si>
+  <si>
+    <t>改出1个奖池符号</t>
+  </si>
+  <si>
+    <t>19_10|20_5|21_2|22_1</t>
+  </si>
+  <si>
+    <t>概率改出百搭</t>
+  </si>
+  <si>
+    <t>百搭出现</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>0_50|1_35|2_10|3_5</t>
+  </si>
+  <si>
+    <t>冰冻玩法改出百搭</t>
+  </si>
+  <si>
+    <t>改出百搭</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>12_14</t>
+  </si>
+  <si>
+    <t>火焰玩法改出百搭</t>
+  </si>
+  <si>
+    <t>13_14</t>
+  </si>
+  <si>
+    <t>中央两个洛基</t>
+  </si>
+  <si>
+    <t>结束特殊玩法</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>概率改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>常规模式出现</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|4_1_1|6_1_1|7_1_1|8_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>0_62|1_35|2_3</t>
+  </si>
+  <si>
+    <t>用于触发奖池</t>
+  </si>
+  <si>
+    <t>11_14</t>
+  </si>
+  <si>
+    <t>改出1个大奖</t>
+  </si>
+  <si>
+    <t>改出奖池符号</t>
+  </si>
+  <si>
+    <t>15_10|16_5|17_2|18_1</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>99999_1</t>
+  </si>
+  <si>
+    <t>3_1_1|9_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>改出1个19符号</t>
+  </si>
+  <si>
+    <t>改出1个20符号</t>
+  </si>
+  <si>
+    <t>10_11_12</t>
+  </si>
+  <si>
+    <t>13_10|14_5|15_2|16_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>12_10</t>
+  </si>
+  <si>
+    <t>免费游戏概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>改出3个bonus</t>
+  </si>
+  <si>
+    <t>概率出现3个bonus</t>
+  </si>
+  <si>
+    <t>0_70|1_29|3_1</t>
+  </si>
+  <si>
+    <t>概率出现3个SCATTER</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17</t>
+  </si>
+  <si>
+    <t>14_10|15_5|16_2|17_1</t>
+  </si>
+  <si>
+    <t>21_1_1|22_1_1|23_1_1|24_1_1</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_15|3_10|4_7|5_3</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
+  </si>
+  <si>
+    <t>免费游戏</t>
+  </si>
+  <si>
+    <t>概率改出+1免费符号</t>
+  </si>
+  <si>
+    <t>11_12_13</t>
+  </si>
+  <si>
+    <t>0_90|1_10</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15</t>
+  </si>
+  <si>
+    <t>12_10|13_5|14_2|15_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10次&amp;15次&amp;20次免费</t>
+  </si>
+  <si>
+    <t>3_70|4_25|5_5</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号</t>
+  </si>
+  <si>
+    <t>免费游戏中概率出现</t>
+  </si>
+  <si>
+    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
+  </si>
+  <si>
+    <t>普通模式概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>免费模式概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_15|3_5</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号</t>
+  </si>
+  <si>
+    <t>7_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>改出奖金符号</t>
+  </si>
+  <si>
+    <t>8_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1</t>
+  </si>
+  <si>
+    <t>7_8_9_10_11_12</t>
+  </si>
+  <si>
+    <t>0_500|1_200|2_200|3_50|4_30|5_15|6_5</t>
+  </si>
+  <si>
+    <t>10_5000|20_3000|30_1000|40_500|50_400|80_50|100_40|200_10</t>
+  </si>
+  <si>
+    <t>金钱兔模式</t>
+  </si>
+  <si>
+    <t>0_50|1_150|2_150|3_250|4_200|5_150|6_45|7_5</t>
+  </si>
+  <si>
+    <t>改出wild</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_15|3_10</t>
+  </si>
+  <si>
+    <t>9_10|10_5|11_2|12_1</t>
+  </si>
+  <si>
+    <t>7_9</t>
+  </si>
+  <si>
+    <t>改出隐藏符号</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖符号</t>
+  </si>
+  <si>
+    <t>4_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>概率改出wild符号</t>
+  </si>
+  <si>
+    <t>必出现3个Jackpot符号</t>
+  </si>
+  <si>
+    <t>概率出现Jackpot符号</t>
+  </si>
+  <si>
+    <t>0_70|1_15|2_5</t>
+  </si>
+  <si>
+    <t>福鼠模式</t>
+  </si>
+  <si>
+    <t>第二轴改出三个9符号</t>
+  </si>
+  <si>
+    <t>第二轴改出三个wild符号</t>
+  </si>
+  <si>
+    <t>6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86</t>
+  </si>
+  <si>
+    <t>0_55|1_30|2_15</t>
+  </si>
+  <si>
+    <t>改出4个以上SCATTER</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>4_70|5_25|6_5</t>
+  </si>
+  <si>
+    <t>概率改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>0_55|1_25|2_15|3_5</t>
+  </si>
+  <si>
+    <t>免费模式</t>
+  </si>
+  <si>
+    <t>0_1000|1_400|2_190|3_120|4_20|5_5|6_1</t>
+  </si>
+  <si>
+    <t>概率改出占据2个格子符号</t>
+  </si>
+  <si>
+    <t>18_1|19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1|10_1_1|12_1_1|13_1_1|14_1_1|15_1_1|17_1_1|18_1_1|19_1_1|20_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
+  </si>
+  <si>
+    <t>0_50|1_40|2_8|3_2</t>
+  </si>
+  <si>
+    <t>概率改出占据3个格子符号</t>
+  </si>
+  <si>
+    <t>30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|65_1|66_1|67_1|68_1|69_1|70_1|71_1|72_1|73_1|74_1|75_1</t>
+  </si>
+  <si>
+    <t>8_1_1|9_1_1|10_1_1|13_1_1|14_1_1|15_1_1|18_1_1|19_1_1|20_1_1|23_1_1|24_1_1|25_1_1</t>
+  </si>
+  <si>
+    <t>概率改出占据4个格子符号</t>
+  </si>
+  <si>
+    <t>42_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|76_1|77_1|78_1|79_1|80_1|81_1|82_1|83_1|84_1|85_1|86_1</t>
+  </si>
+  <si>
+    <t>9_1_1|10_1_1|14_1_1|15_1_1|19_1_1|20_1_1|24_1_1|25_1_1</t>
+  </si>
+  <si>
+    <t>0_50|1_40|2_10</t>
+  </si>
+  <si>
+    <t>26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
+  </si>
+  <si>
+    <t>概率改成wild符号</t>
+  </si>
+  <si>
+    <t>普通&amp;免费概率改出wild符号</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
+  </si>
+  <si>
+    <t>21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42</t>
+  </si>
+  <si>
+    <t>0_60|1_30|2_10</t>
+  </si>
+  <si>
+    <t>概率在第1轴改出vs1符号</t>
+  </si>
+  <si>
+    <t>普通模式</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1</t>
+  </si>
+  <si>
+    <t>概率在第2轴改出vs2符号</t>
+  </si>
+  <si>
+    <t>6_1_1|7_1_1|8_1_1|9_1_1|10_1_1</t>
+  </si>
+  <si>
+    <t>概率在第3轴改出vs3符号</t>
+  </si>
+  <si>
+    <t>11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>概率在第4轴改出vs4符号</t>
+  </si>
+  <si>
+    <t>16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
+    <t>概率第1轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率第3轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>第3轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>第5轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>21_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
+  </si>
+  <si>
+    <t>第1轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>41_50|42_50</t>
+  </si>
+  <si>
+    <t>5_1_1</t>
+  </si>
+  <si>
+    <t>第2轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>10_1_1</t>
+  </si>
+  <si>
+    <t>第3轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>15_1_1</t>
+  </si>
+  <si>
+    <t>第4轴改出宙斯、哈迪斯大图标</t>
+  </si>
+  <si>
+    <t>20_1_1</t>
+  </si>
+  <si>
+    <t>第5轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>27_10|28_5|29_2|30_1</t>
+  </si>
+  <si>
+    <t>改出39符号</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏宙斯</t>
+  </si>
+  <si>
+    <t>39_1</t>
+  </si>
+  <si>
+    <t>免费模式-概率在第1轴改出vs1符号</t>
+  </si>
+  <si>
+    <t>免费模式 - 宙斯</t>
+  </si>
+  <si>
+    <t>免费模式-概率在第1轴改出vs2符号</t>
+  </si>
+  <si>
+    <t>27_1</t>
+  </si>
+  <si>
+    <t>免费模式-概率在第1轴改出vs3符号</t>
+  </si>
+  <si>
+    <t>免费模式-概率在第1轴改出vs4符号</t>
+  </si>
+  <si>
+    <t>29_1</t>
+  </si>
+  <si>
+    <t>第1轴改出宙斯</t>
+  </si>
+  <si>
+    <t>41_1</t>
+  </si>
+  <si>
+    <t>第2轴改出宙斯</t>
+  </si>
+  <si>
+    <t>第3轴改出宙斯</t>
+  </si>
+  <si>
+    <t>第4轴改出宙斯</t>
+  </si>
+  <si>
+    <t>改出40符号</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏哈迪斯</t>
+  </si>
+  <si>
+    <t>40_1</t>
+  </si>
+  <si>
+    <t>免费模式 - 哈迪斯</t>
+  </si>
+  <si>
+    <t>第1轴改出哈迪斯</t>
+  </si>
+  <si>
+    <t>42_1</t>
+  </si>
+  <si>
+    <t>第2轴改出哈迪斯</t>
+  </si>
+  <si>
+    <t>第3轴改出哈迪斯</t>
+  </si>
+  <si>
+    <t>第4轴改出哈迪斯</t>
+  </si>
+  <si>
+    <t>11_17_18</t>
+  </si>
+  <si>
+    <t>0_50|1_50</t>
+  </si>
+  <si>
+    <t>改出17图标</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏</t>
+  </si>
+  <si>
+    <t>改出18图标</t>
+  </si>
+  <si>
+    <t>用于收集金币</t>
+  </si>
+  <si>
+    <t>概率改出金币符号</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>0_300|1_200|2_200|3_50|4_30|5_15|6_5</t>
+  </si>
+  <si>
+    <t>40_40|80_30|160_20|200_10</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>改出金币符号</t>
+  </si>
+  <si>
+    <t>1_200|2_200|3_50|4_30|5_15|6_5</t>
+  </si>
+  <si>
+    <t>0_47|1_30|2_15|3_10|4_3</t>
+  </si>
+  <si>
+    <t>概率改出scatter符号</t>
+  </si>
+  <si>
+    <t>9_11_12_13_14</t>
+  </si>
+  <si>
+    <t>0_57|1_40|2_3</t>
+  </si>
+  <si>
+    <t>改出3个以上scatter符号</t>
+  </si>
+  <si>
+    <t>11_10|12_5|13_2|14_1</t>
+  </si>
+  <si>
+    <t>9_10</t>
+  </si>
+  <si>
+    <t>7_8</t>
+  </si>
+  <si>
+    <t>福牛模式</t>
+  </si>
+  <si>
+    <t>0_70|2_25|3_5</t>
+  </si>
+  <si>
+    <t>概率在第二轴或第四轴改出百搭wild</t>
+  </si>
+  <si>
+    <t>常规&amp;免费</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>在第二轴改出18符号</t>
+  </si>
+  <si>
+    <t>常规</t>
+  </si>
+  <si>
+    <t>11_12</t>
+  </si>
+  <si>
+    <t>在第三轴改出18符号</t>
+  </si>
+  <si>
+    <t>在第四轴改出18符号</t>
+  </si>
+  <si>
+    <t>在第三轴改出三个百搭wild</t>
+  </si>
+  <si>
+    <t>在二三四轴改出9个wild</t>
+  </si>
+  <si>
+    <t>11_12_18_14_15_16_17_13</t>
+  </si>
+  <si>
+    <t>概率改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>3_90|4_10</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_15|3_4|4_1</t>
+  </si>
+  <si>
+    <t>前四轴改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>概率在第一轴上改出bonus</t>
+  </si>
+  <si>
+    <t>常规&amp;免费模式</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1</t>
+  </si>
+  <si>
+    <t>在第一轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>在第五轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>第五轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>概率在第五轴上改出bonus</t>
+  </si>
+  <si>
+    <t>概率在第二三四轴改出18符号</t>
+  </si>
+  <si>
+    <t>11_12_18</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>1_20|2_20|3_20|4_20|5_10|6_6|7_4</t>
+  </si>
+  <si>
+    <t>在第二轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>在第三轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>在第四轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>概率在第二轴改出1个scatter</t>
+  </si>
+  <si>
     <t>0_70|1_30</t>
   </si>
   <si>
-    <t>3列概率出现3个以下免费图案</t>
-  </si>
-  <si>
-    <t>2列必然出1个免费图案</t>
-  </si>
-  <si>
-    <t>12次&amp;14次免费</t>
-  </si>
-  <si>
-    <t>3列必然出1个免费图案</t>
-  </si>
-  <si>
-    <t>4列必然出1个免费图案</t>
-  </si>
-  <si>
-    <t>13_1_1|14_1_1</t>
-  </si>
-  <si>
-    <t>4列必然额外出1个免费图案</t>
-  </si>
-  <si>
-    <t>14次免费</t>
-  </si>
-  <si>
-    <t>16_1_1</t>
-  </si>
-  <si>
-    <t>0_10|1_1</t>
-  </si>
-  <si>
-    <t>概率出现金色图标</t>
-  </si>
-  <si>
-    <t>11_1|12_1|13_1|14_1|15_1|16_1|17_1|18_1</t>
-  </si>
-  <si>
-    <t>修改对应图标</t>
-  </si>
-  <si>
-    <t>0_80|1_15|2_10|3_2</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-2条</t>
-  </si>
-  <si>
-    <t>11_1</t>
-  </si>
-  <si>
-    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>0_95|1_5</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-2筒</t>
-  </si>
-  <si>
-    <t>12_1</t>
-  </si>
-  <si>
-    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-5条</t>
-  </si>
-  <si>
-    <t>13_1</t>
-  </si>
-  <si>
-    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-5筒</t>
-  </si>
-  <si>
-    <t>14_1</t>
-  </si>
-  <si>
-    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-八万</t>
-  </si>
-  <si>
-    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-白板</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-红中</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-发财</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>随机出大财神-不足5个</t>
-  </si>
-  <si>
-    <t>9_1</t>
-  </si>
-  <si>
-    <t>概率出现5个以下大财神</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>0_200|1_15|2_10|3_5|4_1</t>
-  </si>
-  <si>
-    <t>必出大财神-5个</t>
-  </si>
-  <si>
-    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>横财神</t>
-  </si>
-  <si>
-    <t>第1行改为横财神</t>
-  </si>
-  <si>
-    <t>必然出1个正&amp;横财神</t>
-  </si>
-  <si>
-    <t>4_1_1|7_1_1|10_1_1</t>
-  </si>
-  <si>
-    <t>第2行改为横财神</t>
-  </si>
-  <si>
-    <t>5_1_1|8_1_1|11_1_1</t>
-  </si>
-  <si>
-    <t>第3行改为横财神</t>
-  </si>
-  <si>
-    <t>6_1_1|9_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>正财神</t>
-  </si>
-  <si>
-    <t>第2列改为正财神</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1</t>
-  </si>
-  <si>
-    <t>第3列改为正财神</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>第4列改为正财神</t>
-  </si>
-  <si>
-    <t>10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>横财神第1行</t>
-  </si>
-  <si>
-    <t>中央第1行改为wild</t>
-  </si>
-  <si>
-    <t>横财神第2行</t>
-  </si>
-  <si>
-    <t>中央第2行改为wild</t>
-  </si>
-  <si>
-    <t>横财神第3行</t>
-  </si>
-  <si>
-    <t>中央第3行改为wild</t>
-  </si>
-  <si>
-    <t>正财神第2列</t>
-  </si>
-  <si>
-    <t>中央第2列改为wild</t>
-  </si>
-  <si>
-    <t>中央第3列改为wild</t>
-  </si>
-  <si>
-    <t>中央第4列改为wild</t>
-  </si>
-  <si>
-    <t>横财神2次出现</t>
-  </si>
-  <si>
-    <t>概率出1个正&amp;横财神</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16_21_22_23_24_25_26</t>
-  </si>
-  <si>
-    <t>0_60|1_40</t>
-  </si>
-  <si>
-    <t>23_1</t>
-  </si>
-  <si>
-    <t>正财神2次出现</t>
-  </si>
-  <si>
-    <t>24_1</t>
-  </si>
-  <si>
-    <t>25_1</t>
-  </si>
-  <si>
-    <t>26_1</t>
-  </si>
-  <si>
-    <t>横财神3次出现</t>
-  </si>
-  <si>
-    <t>31_1</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16_21_22_23_24_25_26_31_32_33_34_35_36</t>
-  </si>
-  <si>
-    <t>0_80|1_20</t>
-  </si>
-  <si>
-    <t>32_1</t>
-  </si>
-  <si>
-    <t>33_1</t>
-  </si>
-  <si>
-    <t>正财神3次出现</t>
-  </si>
-  <si>
-    <t>34_1</t>
-  </si>
-  <si>
-    <t>35_1</t>
-  </si>
-  <si>
-    <t>36_1</t>
-  </si>
-  <si>
-    <t>概率出现百搭图案</t>
-  </si>
-  <si>
-    <t>概率出现百搭</t>
-  </si>
-  <si>
-    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>12_13_1</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_20</t>
-  </si>
-  <si>
-    <t>1_60|2_25|3_15</t>
-  </si>
-  <si>
-    <t>必出出现jackpot图案</t>
-  </si>
-  <si>
-    <t>概率出现jackpot</t>
-  </si>
-  <si>
-    <t>第2列概率出现jackpot图案，最多1个</t>
-  </si>
-  <si>
-    <t>0_75|1_25</t>
-  </si>
-  <si>
-    <t>第3列概率出现jackpot图案，最多1个</t>
-  </si>
-  <si>
-    <t>0_85|1_15</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-铃铛</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-鞋子</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-杯子</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-饮品</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-蛋糕1</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-蛋糕2</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-蛋糕3</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-蛋糕4</t>
-  </si>
-  <si>
-    <t>改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>9_10_11_12_13_14_15_16_17_18_19_20_21_22</t>
-  </si>
-  <si>
-    <t>改出1个奖池符号</t>
-  </si>
-  <si>
-    <t>19_10|20_5|21_2|22_1</t>
-  </si>
-  <si>
-    <t>概率改出百搭</t>
-  </si>
-  <si>
-    <t>百搭出现</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>0_50|1_35|2_10|3_5</t>
-  </si>
-  <si>
-    <t>冰冻玩法改出百搭</t>
-  </si>
-  <si>
-    <t>改出百搭</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>12_14</t>
-  </si>
-  <si>
-    <t>火焰玩法改出百搭</t>
-  </si>
-  <si>
-    <t>13_14</t>
-  </si>
-  <si>
-    <t>中央两个洛基</t>
-  </si>
-  <si>
-    <t>结束特殊玩法</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1</t>
-  </si>
-  <si>
-    <t>概率改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>常规模式出现</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|4_1_1|6_1_1|7_1_1|8_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>0_50|1_35|2_15</t>
-  </si>
-  <si>
-    <t>用于触发奖池</t>
-  </si>
-  <si>
-    <t>11_14</t>
-  </si>
-  <si>
-    <t>改出1个大奖</t>
-  </si>
-  <si>
-    <t>改出奖池符号</t>
-  </si>
-  <si>
-    <t>15_10|16_5|17_2|18_1</t>
-  </si>
-  <si>
-    <t>13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>99999_1</t>
-  </si>
-  <si>
-    <t>3_1_1|9_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出3个SCATTER</t>
-  </si>
-  <si>
-    <t>11_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>改出1个19符号</t>
-  </si>
-  <si>
-    <t>改出1个20符号</t>
-  </si>
-  <si>
-    <t>10_11_12</t>
-  </si>
-  <si>
-    <t>13_10|14_5|15_2|16_1</t>
-  </si>
-  <si>
-    <t>概率出现百搭符号</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>12_10</t>
-  </si>
-  <si>
-    <t>免费游戏概率出现百搭符号</t>
-  </si>
-  <si>
-    <t>改出3个bonus</t>
-  </si>
-  <si>
-    <t>概率出现3个bonus</t>
-  </si>
-  <si>
-    <t>0_70|1_29|3_1</t>
-  </si>
-  <si>
-    <t>概率出现3个SCATTER</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16_17</t>
-  </si>
-  <si>
-    <t>14_10|15_5|16_2|17_1</t>
-  </si>
-  <si>
-    <t>21_1_1|22_1_1|23_1_1|24_1_1</t>
-  </si>
-  <si>
-    <t>0_40|1_30|2_15|3_10|4_7|5_3</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
-  </si>
-  <si>
-    <t>免费游戏</t>
-  </si>
-  <si>
-    <t>概率改出+1免费符号</t>
-  </si>
-  <si>
-    <t>11_12_13</t>
-  </si>
-  <si>
-    <t>0_90|1_10</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15</t>
-  </si>
-  <si>
-    <t>12_10|13_5|14_2|15_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出3个以上SCATTER</t>
-  </si>
-  <si>
-    <t>10次&amp;15次&amp;20次免费</t>
-  </si>
-  <si>
-    <t>3_70|4_25|5_5</t>
-  </si>
-  <si>
-    <t>概率改出SCATTER符号</t>
-  </si>
-  <si>
-    <t>免费游戏中概率出现</t>
-  </si>
-  <si>
-    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
-  </si>
-  <si>
-    <t>普通模式概率出现百搭符号</t>
-  </si>
-  <si>
-    <t>免费模式概率出现百搭符号</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_15|3_5</t>
-  </si>
-  <si>
-    <t>概率改出百搭符号</t>
-  </si>
-  <si>
-    <t>7_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>改出奖金符号</t>
-  </si>
-  <si>
-    <t>8_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1</t>
-  </si>
-  <si>
-    <t>7_8_9_10_11_12</t>
-  </si>
-  <si>
-    <t>0_500|1_200|2_200|3_50|4_30|5_15|6_5</t>
-  </si>
-  <si>
-    <t>10_5000|20_3000|30_1000|40_500|50_400|80_50|100_40|200_10</t>
-  </si>
-  <si>
-    <t>金钱兔模式</t>
-  </si>
-  <si>
-    <t>0_50|1_150|2_150|3_250|4_200|5_150|6_45|7_5</t>
-  </si>
-  <si>
-    <t>改出wild</t>
-  </si>
-  <si>
-    <t>0_40|1_30|2_15|3_10</t>
-  </si>
-  <si>
-    <t>9_10|10_5|11_2|12_1</t>
-  </si>
-  <si>
-    <t>7_9</t>
-  </si>
-  <si>
-    <t>改出隐藏符号</t>
-  </si>
-  <si>
-    <t>异形位置改为不中奖符号</t>
-  </si>
-  <si>
-    <t>4_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>概率改出wild符号</t>
-  </si>
-  <si>
-    <t>必出现3个Jackpot符号</t>
-  </si>
-  <si>
-    <t>概率出现Jackpot符号</t>
-  </si>
-  <si>
-    <t>0_70|1_15|2_5</t>
-  </si>
-  <si>
-    <t>福鼠模式</t>
-  </si>
-  <si>
-    <t>第二轴改出三个9符号</t>
-  </si>
-  <si>
-    <t>第二轴改出三个wild符号</t>
-  </si>
-  <si>
-    <t>6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16_17_18_19_20_21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42_43_44_45_46_47_48_49_50_51_52_53_54_55_56_57_58_59_60_61_62_63_64_65_66_67_68_69_70_71_72_73_74_75_76_77_78_79_80_81_82_83_84_85_86</t>
-  </si>
-  <si>
-    <t>0_55|1_30|2_15</t>
-  </si>
-  <si>
-    <t>改出4个以上SCATTER</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>4_70|5_25|6_5</t>
-  </si>
-  <si>
-    <t>概率改出3个SCATTER</t>
-  </si>
-  <si>
-    <t>0_55|1_25|2_15|3_5</t>
-  </si>
-  <si>
-    <t>免费模式</t>
-  </si>
-  <si>
-    <t>0_1000|1_400|2_190|3_120|4_20|5_5|6_1</t>
-  </si>
-  <si>
-    <t>概率改出占据2个格子符号</t>
-  </si>
-  <si>
-    <t>18_1|19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|54_1|55_1|56_1|57_1|58_1|59_1|60_1|61_1|62_1|63_1|64_1</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1|10_1_1|12_1_1|13_1_1|14_1_1|15_1_1|17_1_1|18_1_1|19_1_1|20_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
-  </si>
-  <si>
-    <t>0_50|1_40|2_8|3_2</t>
-  </si>
-  <si>
-    <t>概率改出占据3个格子符号</t>
-  </si>
-  <si>
-    <t>30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1|65_1|66_1|67_1|68_1|69_1|70_1|71_1|72_1|73_1|74_1|75_1</t>
-  </si>
-  <si>
-    <t>8_1_1|9_1_1|10_1_1|13_1_1|14_1_1|15_1_1|18_1_1|19_1_1|20_1_1|23_1_1|24_1_1|25_1_1</t>
-  </si>
-  <si>
-    <t>概率改出占据4个格子符号</t>
-  </si>
-  <si>
-    <t>42_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|76_1|77_1|78_1|79_1|80_1|81_1|82_1|83_1|84_1|85_1|86_1</t>
-  </si>
-  <si>
-    <t>9_1_1|10_1_1|14_1_1|15_1_1|19_1_1|20_1_1|24_1_1|25_1_1</t>
-  </si>
-  <si>
-    <t>0_50|1_40|2_10</t>
-  </si>
-  <si>
-    <t>26_1_1|27_1_1|28_1_1|29_1_1|30_1_1</t>
-  </si>
-  <si>
-    <t>概率改成wild符号</t>
-  </si>
-  <si>
-    <t>普通&amp;免费概率改出wild符号</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
-  </si>
-  <si>
-    <t>21_22_23_24_25_26_27_28_29_30_31_32_33_34_35_36_37_38_39_40_41_42</t>
-  </si>
-  <si>
-    <t>0_60|1_30|2_10</t>
-  </si>
-  <si>
-    <t>概率在第1轴改出vs1符号</t>
-  </si>
-  <si>
-    <t>普通模式</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1</t>
-  </si>
-  <si>
-    <t>概率在第2轴改出vs2符号</t>
-  </si>
-  <si>
-    <t>6_1_1|7_1_1|8_1_1|9_1_1|10_1_1</t>
-  </si>
-  <si>
-    <t>概率在第3轴改出vs3符号</t>
-  </si>
-  <si>
-    <t>11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>概率在第4轴改出vs4符号</t>
-  </si>
-  <si>
-    <t>16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
-  </si>
-  <si>
-    <t>概率第1轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率第3轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>第1轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>第3轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>第5轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>21_1_1|22_1_1|23_1_1|24_1_1|25_1_1</t>
-  </si>
-  <si>
-    <t>第1轴改出宙斯、哈迪斯大图标</t>
-  </si>
-  <si>
-    <t>41_50|42_50</t>
-  </si>
-  <si>
-    <t>5_1_1</t>
-  </si>
-  <si>
-    <t>第2轴改出宙斯、哈迪斯大图标</t>
-  </si>
-  <si>
-    <t>10_1_1</t>
-  </si>
-  <si>
-    <t>第3轴改出宙斯、哈迪斯大图标</t>
-  </si>
-  <si>
-    <t>15_1_1</t>
-  </si>
-  <si>
-    <t>第4轴改出宙斯、哈迪斯大图标</t>
-  </si>
-  <si>
-    <t>20_1_1</t>
-  </si>
-  <si>
-    <t>第5轴改出奖池符号</t>
-  </si>
-  <si>
-    <t>27_10|28_5|29_2|30_1</t>
-  </si>
-  <si>
-    <t>改出39符号</t>
-  </si>
-  <si>
-    <t>用于触发免费游戏宙斯</t>
-  </si>
-  <si>
-    <t>39_1</t>
-  </si>
-  <si>
-    <t>免费模式-概率在第1轴改出vs1符号</t>
-  </si>
-  <si>
-    <t>免费模式 - 宙斯</t>
-  </si>
-  <si>
-    <t>免费模式-概率在第1轴改出vs2符号</t>
-  </si>
-  <si>
-    <t>27_1</t>
-  </si>
-  <si>
-    <t>免费模式-概率在第1轴改出vs3符号</t>
-  </si>
-  <si>
-    <t>免费模式-概率在第1轴改出vs4符号</t>
-  </si>
-  <si>
-    <t>29_1</t>
-  </si>
-  <si>
-    <t>第1轴改出宙斯</t>
-  </si>
-  <si>
-    <t>41_1</t>
-  </si>
-  <si>
-    <t>第2轴改出宙斯</t>
-  </si>
-  <si>
-    <t>第3轴改出宙斯</t>
-  </si>
-  <si>
-    <t>第4轴改出宙斯</t>
-  </si>
-  <si>
-    <t>改出40符号</t>
-  </si>
-  <si>
-    <t>用于触发免费游戏哈迪斯</t>
-  </si>
-  <si>
-    <t>40_1</t>
-  </si>
-  <si>
-    <t>免费模式 - 哈迪斯</t>
-  </si>
-  <si>
-    <t>第1轴改出哈迪斯</t>
-  </si>
-  <si>
-    <t>42_1</t>
-  </si>
-  <si>
-    <t>第2轴改出哈迪斯</t>
-  </si>
-  <si>
-    <t>第3轴改出哈迪斯</t>
-  </si>
-  <si>
-    <t>第4轴改出哈迪斯</t>
-  </si>
-  <si>
-    <t>11_17_18</t>
-  </si>
-  <si>
-    <t>0_50|1_50</t>
-  </si>
-  <si>
-    <t>改出17图标</t>
-  </si>
-  <si>
-    <t>用于触发免费游戏</t>
-  </si>
-  <si>
-    <t>改出18图标</t>
-  </si>
-  <si>
-    <t>用于收集金币</t>
-  </si>
-  <si>
-    <t>概率改出金币符号</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>0_300|1_200|2_200|3_50|4_30|5_15|6_5</t>
-  </si>
-  <si>
-    <t>40_40|80_30|160_20|200_10</t>
-  </si>
-  <si>
-    <t>12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>改出金币符号</t>
-  </si>
-  <si>
-    <t>1_200|2_200|3_50|4_30|5_15|6_5</t>
-  </si>
-  <si>
-    <t>0_47|1_30|2_15|3_10|4_3</t>
-  </si>
-  <si>
-    <t>概率改出scatter符号</t>
-  </si>
-  <si>
-    <t>9_11_12_13_14</t>
-  </si>
-  <si>
-    <t>0_55|1_40|2_5</t>
-  </si>
-  <si>
-    <t>改出3个以上scatter符号</t>
-  </si>
-  <si>
-    <t>11_10|12_5|13_2|14_1</t>
-  </si>
-  <si>
-    <t>9_10</t>
-  </si>
-  <si>
-    <t>7_8</t>
-  </si>
-  <si>
-    <t>福牛模式</t>
-  </si>
-  <si>
-    <t>0_70|2_25|3_5</t>
-  </si>
-  <si>
-    <t>概率在第二轴或第四轴改出百搭wild</t>
-  </si>
-  <si>
-    <t>常规&amp;免费</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>在第二轴改出18符号</t>
-  </si>
-  <si>
-    <t>常规</t>
-  </si>
-  <si>
-    <t>11_12</t>
-  </si>
-  <si>
-    <t>在第三轴改出18符号</t>
-  </si>
-  <si>
-    <t>在第四轴改出18符号</t>
-  </si>
-  <si>
-    <t>在第三轴改出三个百搭wild</t>
-  </si>
-  <si>
-    <t>在二三四轴改出9个wild</t>
-  </si>
-  <si>
-    <t>11_12_18_14_15_16_17_13</t>
-  </si>
-  <si>
-    <t>0_60|1_35|2_5</t>
-  </si>
-  <si>
-    <t>概率改出3个以上SCATTER</t>
-  </si>
-  <si>
-    <t>3_90|4_10</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_15|3_4|4_1</t>
-  </si>
-  <si>
-    <t>前四轴改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>概率在第一轴上改出bonus</t>
-  </si>
-  <si>
-    <t>常规&amp;免费模式</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1</t>
-  </si>
-  <si>
-    <t>在第一轴改出1个bonus</t>
-  </si>
-  <si>
-    <t>在第五轴改出1个bonus</t>
-  </si>
-  <si>
-    <t>第五轴改出奖池符号</t>
-  </si>
-  <si>
-    <t>概率在第五轴上改出bonus</t>
-  </si>
-  <si>
-    <t>概率在第二三四轴改出18符号</t>
-  </si>
-  <si>
-    <t>11_12_18</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>1_20|2_20|3_20|4_20|5_10|6_6|7_4</t>
-  </si>
-  <si>
-    <t>在第二轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>在第三轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>在第四轴改出1个scatter</t>
-  </si>
-  <si>
-    <t>概率在第二轴改出1个scatter</t>
-  </si>
-  <si>
     <t>概率第三轴改出1个scatter</t>
   </si>
   <si>
@@ -1541,6 +1543,9 @@
   </si>
   <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1|25_1_1|26_1_1|27_1_1|28_1_1|29_1_1|30_1_1|31_1_1|32_1_1|33_1_1|34_1_1|35_1_1|36_1_1</t>
+  </si>
+  <si>
+    <t>0_57|1_25|2_15|3_3</t>
   </si>
   <si>
     <t>19_1|20_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|43_1|44_1|45_1|46_1|47_1|48_1|49_1|50_1|51_1|52_1|53_1</t>
@@ -2412,12 +2417,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5591,7 +5596,7 @@
         <v>200</v>
       </c>
       <c r="I71" s="121" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="K71" s="54"/>
     </row>
@@ -5609,7 +5614,7 @@
         <v>168</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>190</v>
@@ -5621,7 +5626,7 @@
         <v>200</v>
       </c>
       <c r="I72" s="121" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="K72" s="54"/>
     </row>
@@ -5639,7 +5644,7 @@
         <v>170</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>190</v>
@@ -5651,7 +5656,7 @@
         <v>200</v>
       </c>
       <c r="I73" s="121" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="K73" s="54"/>
     </row>
@@ -5663,13 +5668,13 @@
         <v>101200</v>
       </c>
       <c r="C74" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>173</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>190</v>
@@ -5681,7 +5686,7 @@
         <v>200</v>
       </c>
       <c r="I74" s="121" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="K74" s="54"/>
     </row>
@@ -5693,13 +5698,13 @@
         <v>101200</v>
       </c>
       <c r="C75" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>175</v>
       </c>
       <c r="E75" s="53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>190</v>
@@ -5711,7 +5716,7 @@
         <v>200</v>
       </c>
       <c r="I75" s="121" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="K75" s="54"/>
     </row>
@@ -5723,13 +5728,13 @@
         <v>101200</v>
       </c>
       <c r="C76" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>177</v>
       </c>
       <c r="E76" s="53" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>190</v>
@@ -5741,7 +5746,7 @@
         <v>200</v>
       </c>
       <c r="I76" s="121" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="K76" s="54"/>
     </row>
@@ -5753,10 +5758,10 @@
         <v>101400</v>
       </c>
       <c r="C77" s="81" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="E77" s="81" t="s">
         <v>140</v>
@@ -5765,13 +5770,13 @@
         <v>133</v>
       </c>
       <c r="G77" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H77" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="H77" s="48" t="s">
+      <c r="I77" s="125" t="s">
         <v>211</v>
-      </c>
-      <c r="I77" s="125" t="s">
-        <v>212</v>
       </c>
       <c r="K77" s="82"/>
     </row>
@@ -5783,10 +5788,10 @@
         <v>101400</v>
       </c>
       <c r="C78" s="81" t="s">
+        <v>207</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="E78" s="81" t="s">
         <v>140</v>
@@ -5795,13 +5800,13 @@
         <v>133</v>
       </c>
       <c r="G78" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H78" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="48" t="s">
-        <v>211</v>
-      </c>
       <c r="I78" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K78" s="82"/>
     </row>
@@ -5813,10 +5818,10 @@
         <v>101400</v>
       </c>
       <c r="C79" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="D79" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="E79" s="48" t="s">
         <v>143</v>
@@ -5825,7 +5830,7 @@
         <v>133</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H79" s="48" t="s">
         <v>143</v>
@@ -5843,10 +5848,10 @@
         <v>101400</v>
       </c>
       <c r="C80" s="48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E80" s="48" t="s">
         <v>143</v>
@@ -5861,7 +5866,7 @@
         <v>143</v>
       </c>
       <c r="I80" s="125" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K80" s="49"/>
     </row>
@@ -5873,10 +5878,10 @@
         <v>101400</v>
       </c>
       <c r="C81" s="48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E81" s="48" t="s">
         <v>143</v>
@@ -5891,7 +5896,7 @@
         <v>143</v>
       </c>
       <c r="I81" s="125" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K81" s="49"/>
     </row>
@@ -6731,7 +6736,7 @@
         <v>101700</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>136</v>
@@ -6758,7 +6763,7 @@
         <v>101700</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>140</v>
@@ -6785,7 +6790,7 @@
         <v>101700</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>143</v>
@@ -6812,7 +6817,7 @@
         <v>101700</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>146</v>
@@ -6839,7 +6844,7 @@
         <v>101700</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>67</v>
@@ -6866,7 +6871,7 @@
         <v>101700</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>36</v>
@@ -6893,7 +6898,7 @@
         <v>101700</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>31</v>
@@ -6920,7 +6925,7 @@
         <v>101700</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>23</v>
@@ -6950,7 +6955,7 @@
         <v>21</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>114</v>
@@ -6962,7 +6967,7 @@
         <v>25</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>106</v>
@@ -6980,10 +6985,10 @@
         <v>21</v>
       </c>
       <c r="D120" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E120" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>231</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>133</v>
@@ -6992,7 +6997,7 @@
         <v>38</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>39</v>
@@ -7010,22 +7015,22 @@
         <v>21</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E121" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F121" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G121" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G121" s="8" t="s">
+      <c r="H121" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="I121" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="I121" s="8" t="s">
-        <v>236</v>
       </c>
       <c r="K121" s="86"/>
     </row>
@@ -7037,25 +7042,25 @@
         <v>102200</v>
       </c>
       <c r="C122" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D122" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>238</v>
       </c>
       <c r="E122" s="8" t="s">
         <v>140</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G122" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H122" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="H122" s="8" t="s">
-        <v>240</v>
-      </c>
       <c r="I122" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K122" s="86"/>
     </row>
@@ -7067,25 +7072,25 @@
         <v>102200</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E123" s="8" t="s">
         <v>143</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K123" s="86"/>
     </row>
@@ -7097,19 +7102,19 @@
         <v>102200</v>
       </c>
       <c r="C124" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D124" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>244</v>
       </c>
       <c r="E124" s="8" t="s">
         <v>157</v>
       </c>
       <c r="F124" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="G124" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>245</v>
       </c>
       <c r="I124" s="8" t="s">
         <v>106</v>
@@ -7124,22 +7129,22 @@
         <v>102200</v>
       </c>
       <c r="C125" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D125" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G125" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="I125" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="H125" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>249</v>
       </c>
       <c r="K125" s="86"/>
     </row>
@@ -7151,19 +7156,19 @@
         <v>102200</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I126" s="8" t="s">
         <v>106</v>
@@ -7178,19 +7183,19 @@
         <v>102200</v>
       </c>
       <c r="C127" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D127" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="E127" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E127" s="8" t="s">
+      <c r="G127" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="G127" s="8" t="s">
-        <v>255</v>
-      </c>
       <c r="H127" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I127" s="8" t="s">
         <v>39</v>
@@ -7205,13 +7210,13 @@
         <v>102200</v>
       </c>
       <c r="C128" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E128" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="E128" s="8" t="s">
+      <c r="G128" s="8" t="s">
         <v>257</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>258</v>
       </c>
       <c r="I128" s="8" t="s">
         <v>107</v>
@@ -7226,16 +7231,16 @@
         <v>102200</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E129" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I129" s="8" t="s">
         <v>107</v>
@@ -7250,13 +7255,13 @@
         <v>102200</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E130" s="8" t="s">
         <v>41</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I130" s="8" t="s">
         <v>39</v>
@@ -7271,13 +7276,13 @@
         <v>102200</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E131" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I131" s="8" t="s">
         <v>39</v>
@@ -7295,7 +7300,7 @@
         <v>21</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>140</v>
@@ -7304,10 +7309,10 @@
         <v>133</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I132" s="9" t="s">
         <v>106</v>
@@ -7325,19 +7330,19 @@
         <v>21</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>133</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I133" s="9" t="s">
         <v>39</v>
@@ -7352,10 +7357,10 @@
         <v>102100</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>136</v>
@@ -7364,13 +7369,13 @@
         <v>133</v>
       </c>
       <c r="G134" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H134" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="H134" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="I134" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K134" s="87"/>
     </row>
@@ -7382,7 +7387,7 @@
         <v>102100</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>136</v>
@@ -7391,13 +7396,13 @@
         <v>133</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="H135" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="I135" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K135" s="87"/>
     </row>
@@ -7409,7 +7414,7 @@
         <v>102100</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>140</v>
@@ -7418,10 +7423,10 @@
         <v>133</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I136" s="9" t="s">
         <v>107</v>
@@ -7436,7 +7441,7 @@
         <v>102100</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>114</v>
@@ -7445,10 +7450,10 @@
         <v>133</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I137" s="9" t="s">
         <v>107</v>
@@ -7463,7 +7468,7 @@
         <v>102100</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>114</v>
@@ -7472,13 +7477,13 @@
         <v>133</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I138" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K138" s="87"/>
     </row>
@@ -7490,7 +7495,7 @@
         <v>102100</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>140</v>
@@ -7499,13 +7504,13 @@
         <v>133</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I139" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K139" s="87"/>
     </row>
@@ -7520,7 +7525,7 @@
         <v>21</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>140</v>
@@ -7529,13 +7534,13 @@
         <v>133</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I140" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K140" s="87"/>
     </row>
@@ -7550,7 +7555,7 @@
         <v>21</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>140</v>
@@ -7559,10 +7564,10 @@
         <v>133</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="I141" s="10" t="s">
         <v>106</v>
@@ -7580,7 +7585,7 @@
         <v>21</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>140</v>
@@ -7589,13 +7594,13 @@
         <v>133</v>
       </c>
       <c r="G142" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H142" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H142" s="10" t="s">
-        <v>274</v>
-      </c>
       <c r="I142" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K142" s="88"/>
     </row>
@@ -7610,19 +7615,19 @@
         <v>21</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E143" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G143" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>276</v>
-      </c>
       <c r="H143" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I143" s="10" t="s">
         <v>39</v>
@@ -7637,10 +7642,10 @@
         <v>101800</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E144" s="10" t="s">
         <v>136</v>
@@ -7652,10 +7657,10 @@
         <v>71</v>
       </c>
       <c r="H144" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K144" s="88"/>
     </row>
@@ -7667,10 +7672,10 @@
         <v>101800</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>140</v>
@@ -7679,10 +7684,10 @@
         <v>133</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I145" s="10" t="s">
         <v>107</v>
@@ -7697,10 +7702,10 @@
         <v>101800</v>
       </c>
       <c r="C146" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D146" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>143</v>
@@ -7709,13 +7714,13 @@
         <v>133</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H146" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I146" s="10" t="s">
         <v>281</v>
-      </c>
-      <c r="I146" s="10" t="s">
-        <v>282</v>
       </c>
       <c r="K146" s="88"/>
     </row>
@@ -7730,7 +7735,7 @@
         <v>21</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E147" s="11" t="s">
         <v>136</v>
@@ -7739,13 +7744,13 @@
         <v>133</v>
       </c>
       <c r="G147" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K147" s="89"/>
     </row>
@@ -7760,7 +7765,7 @@
         <v>21</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E148" s="11" t="s">
         <v>136</v>
@@ -7769,10 +7774,10 @@
         <v>133</v>
       </c>
       <c r="G148" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H148" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>106</v>
@@ -7790,19 +7795,19 @@
         <v>21</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G149" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I149" s="11" t="s">
         <v>39</v>
@@ -7817,10 +7822,10 @@
         <v>102500</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E150" s="11" t="s">
         <v>114</v>
@@ -7829,13 +7834,13 @@
         <v>133</v>
       </c>
       <c r="G150" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I150" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K150" s="89"/>
     </row>
@@ -7850,22 +7855,22 @@
         <v>21</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E151" s="11" t="s">
         <v>136</v>
       </c>
       <c r="F151" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="I151" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="G151" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="H151" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="I151" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="K151" s="89"/>
     </row>
@@ -7877,22 +7882,22 @@
         <v>102500</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E152" s="11" t="s">
         <v>136</v>
       </c>
       <c r="F152" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="G152" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="H152" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="I152" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="I152" s="11" t="s">
-        <v>291</v>
       </c>
       <c r="K152" s="89"/>
     </row>
@@ -7907,7 +7912,7 @@
         <v>21</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E153" s="12" t="s">
         <v>136</v>
@@ -7916,13 +7921,13 @@
         <v>133</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H153" s="12" t="s">
         <v>160</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K153" s="90"/>
     </row>
@@ -7937,7 +7942,7 @@
         <v>21</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E154" s="12" t="s">
         <v>136</v>
@@ -7946,7 +7951,7 @@
         <v>133</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H154" s="12" t="s">
         <v>160</v>
@@ -7967,7 +7972,7 @@
         <v>21</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E155" s="12" t="s">
         <v>136</v>
@@ -7976,13 +7981,13 @@
         <v>133</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H155" s="12" t="s">
         <v>160</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K155" s="90"/>
     </row>
@@ -7997,10 +8002,10 @@
         <v>21</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F156" s="12" t="s">
         <v>133</v>
@@ -8024,10 +8029,10 @@
         <v>102300</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E157" s="12" t="s">
         <v>114</v>
@@ -8036,13 +8041,13 @@
         <v>133</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H157" s="12" t="s">
         <v>160</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K157" s="90"/>
     </row>
@@ -8054,10 +8059,10 @@
         <v>102300</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E158" s="12" t="s">
         <v>114</v>
@@ -8066,13 +8071,13 @@
         <v>133</v>
       </c>
       <c r="G158" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H158" s="12" t="s">
         <v>160</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K158" s="90"/>
     </row>
@@ -8084,10 +8089,10 @@
         <v>102300</v>
       </c>
       <c r="C159" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D159" s="12" t="s">
         <v>279</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>280</v>
       </c>
       <c r="E159" s="12" t="s">
         <v>140</v>
@@ -8096,13 +8101,13 @@
         <v>133</v>
       </c>
       <c r="G159" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H159" s="12" t="s">
         <v>160</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K159" s="90"/>
     </row>
@@ -8114,22 +8119,22 @@
         <v>103400</v>
       </c>
       <c r="C160" s="91" t="s">
+        <v>294</v>
+      </c>
+      <c r="D160" s="91" t="s">
+        <v>294</v>
+      </c>
+      <c r="E160" s="91" t="s">
         <v>295</v>
       </c>
-      <c r="D160" s="91" t="s">
-        <v>295</v>
-      </c>
-      <c r="E160" s="91" t="s">
+      <c r="F160" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="G160" s="91" t="s">
         <v>296</v>
       </c>
-      <c r="F160" s="91" t="s">
-        <v>133</v>
-      </c>
-      <c r="G160" s="91" t="s">
-        <v>297</v>
-      </c>
       <c r="I160" s="91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K160" s="92"/>
     </row>
@@ -8144,25 +8149,25 @@
         <v>21</v>
       </c>
       <c r="D161" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E161" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E161" s="14" t="s">
+      <c r="F161" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G161" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F161" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G161" s="14" t="s">
+      <c r="H161" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="H161" s="14" t="s">
+      <c r="I161" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="I161" s="14" t="s">
+      <c r="J161" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="J161" s="14" t="s">
-        <v>303</v>
       </c>
       <c r="K161" s="93" t="s">
         <v>29</v>
@@ -8176,28 +8181,28 @@
         <v>103500</v>
       </c>
       <c r="C162" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D162" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E162" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F162" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G162" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H162" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="I162" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="D162" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E162" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="F162" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G162" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="H162" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="I162" s="14" t="s">
-        <v>305</v>
-      </c>
       <c r="J162" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K162" s="93" t="s">
         <v>29</v>
@@ -8214,22 +8219,22 @@
         <v>21</v>
       </c>
       <c r="D163" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E163" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="F163" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G163" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H163" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="I163" s="15" t="s">
         <v>306</v>
-      </c>
-      <c r="E163" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="F163" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G163" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="H163" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="I163" s="15" t="s">
-        <v>307</v>
       </c>
       <c r="K163" s="94"/>
     </row>
@@ -8244,19 +8249,19 @@
         <v>21</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E164" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="F164" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G164" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H164" s="14" t="s">
         <v>308</v>
-      </c>
-      <c r="F164" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G164" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="H164" s="14" t="s">
-        <v>309</v>
       </c>
       <c r="I164" s="14" t="s">
         <v>39</v>
@@ -8274,7 +8279,7 @@
         <v>21</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E165" s="14" t="s">
         <v>146</v>
@@ -8283,10 +8288,10 @@
         <v>133</v>
       </c>
       <c r="G165" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H165" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I165" s="14" t="s">
         <v>39</v>
@@ -8301,16 +8306,16 @@
         <v>103500</v>
       </c>
       <c r="D166" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="E166" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F166" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G166" s="14" t="s">
         <v>311</v>
-      </c>
-      <c r="E166" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="F166" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G166" s="14" t="s">
-        <v>312</v>
       </c>
       <c r="I166" s="14" t="s">
         <v>106</v>
@@ -8328,25 +8333,25 @@
         <v>21</v>
       </c>
       <c r="D167" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E167" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E167" s="14" t="s">
+      <c r="F167" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G167" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F167" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G167" s="14" t="s">
+      <c r="H167" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="H167" s="14" t="s">
+      <c r="I167" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="I167" s="14" t="s">
+      <c r="J167" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="J167" s="14" t="s">
-        <v>303</v>
       </c>
       <c r="K167" s="93" t="s">
         <v>29</v>
@@ -8360,28 +8365,28 @@
         <v>103501</v>
       </c>
       <c r="C168" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D168" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E168" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F168" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G168" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H168" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="I168" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="D168" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E168" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="F168" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G168" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="H168" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="I168" s="14" t="s">
-        <v>305</v>
-      </c>
       <c r="J168" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K168" s="93" t="s">
         <v>29</v>
@@ -8398,22 +8403,22 @@
         <v>21</v>
       </c>
       <c r="D169" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E169" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="F169" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G169" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H169" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="I169" s="15" t="s">
         <v>306</v>
-      </c>
-      <c r="E169" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="F169" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G169" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="H169" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="I169" s="15" t="s">
-        <v>307</v>
       </c>
       <c r="K169" s="94"/>
     </row>
@@ -8428,19 +8433,19 @@
         <v>21</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E170" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="F170" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G170" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H170" s="14" t="s">
         <v>308</v>
-      </c>
-      <c r="F170" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G170" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="H170" s="14" t="s">
-        <v>309</v>
       </c>
       <c r="I170" s="14" t="s">
         <v>39</v>
@@ -8458,7 +8463,7 @@
         <v>21</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E171" s="14" t="s">
         <v>146</v>
@@ -8467,10 +8472,10 @@
         <v>133</v>
       </c>
       <c r="G171" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H171" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I171" s="14" t="s">
         <v>39</v>
@@ -8485,16 +8490,16 @@
         <v>103501</v>
       </c>
       <c r="D172" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="E172" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F172" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G172" s="14" t="s">
         <v>311</v>
-      </c>
-      <c r="E172" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="F172" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G172" s="14" t="s">
-        <v>312</v>
       </c>
       <c r="I172" s="14" t="s">
         <v>106</v>
@@ -8512,19 +8517,19 @@
         <v>21</v>
       </c>
       <c r="D173" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E173" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="F173" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G173" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="F173" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G173" s="16" t="s">
-        <v>297</v>
-      </c>
       <c r="I173" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K173" s="95"/>
     </row>
@@ -8539,16 +8544,16 @@
         <v>21</v>
       </c>
       <c r="D174" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F174" s="16" t="s">
         <v>133</v>
       </c>
       <c r="G174" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I174" s="16" t="s">
         <v>107</v>
@@ -8566,19 +8571,19 @@
         <v>21</v>
       </c>
       <c r="D175" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="E175" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F175" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G175" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="I175" s="16" t="s">
         <v>315</v>
-      </c>
-      <c r="E175" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="F175" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G175" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="I175" s="16" t="s">
-        <v>316</v>
       </c>
       <c r="K175" s="95"/>
     </row>
@@ -8590,10 +8595,10 @@
         <v>103600</v>
       </c>
       <c r="C176" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D176" s="16" t="s">
         <v>317</v>
-      </c>
-      <c r="D176" s="16" t="s">
-        <v>318</v>
       </c>
       <c r="E176" s="16" t="s">
         <v>157</v>
@@ -8617,13 +8622,13 @@
         <v>103600</v>
       </c>
       <c r="C177" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D177" s="16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E177" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F177" s="16" t="s">
         <v>133</v>
@@ -8644,10 +8649,10 @@
         <v>102800</v>
       </c>
       <c r="C178" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E178" s="17" t="s">
         <v>140</v>
@@ -8656,13 +8661,13 @@
         <v>133</v>
       </c>
       <c r="G178" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="H178" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="H178" s="17" t="s">
+      <c r="I178" s="17" t="s">
         <v>321</v>
-      </c>
-      <c r="I178" s="17" t="s">
-        <v>322</v>
       </c>
       <c r="K178" s="96"/>
     </row>
@@ -8677,7 +8682,7 @@
         <v>21</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E179" s="17" t="s">
         <v>143</v>
@@ -8686,13 +8691,13 @@
         <v>133</v>
       </c>
       <c r="G179" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="H179" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="I179" s="17" t="s">
         <v>324</v>
-      </c>
-      <c r="H179" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="I179" s="17" t="s">
-        <v>325</v>
       </c>
       <c r="K179" s="96"/>
     </row>
@@ -8707,7 +8712,7 @@
         <v>21</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E180" s="17" t="s">
         <v>143</v>
@@ -8716,13 +8721,13 @@
         <v>133</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H180" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I180" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K180" s="96"/>
     </row>
@@ -8737,7 +8742,7 @@
         <v>21</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E181" s="17" t="s">
         <v>143</v>
@@ -8746,10 +8751,10 @@
         <v>133</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H181" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I181" s="17" t="s">
         <v>107</v>
@@ -8764,10 +8769,10 @@
         <v>102800</v>
       </c>
       <c r="C182" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E182" s="17" t="s">
         <v>143</v>
@@ -8776,13 +8781,13 @@
         <v>133</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H182" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I182" s="17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K182" s="96"/>
     </row>
@@ -8794,22 +8799,22 @@
         <v>102800</v>
       </c>
       <c r="D183" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E183" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="E183" s="17" t="s">
+      <c r="F183" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G183" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="F183" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="G183" s="17" t="s">
+      <c r="H183" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="I183" s="17" t="s">
         <v>332</v>
-      </c>
-      <c r="H183" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="I183" s="17" t="s">
-        <v>333</v>
       </c>
       <c r="K183" s="96"/>
     </row>
@@ -8821,22 +8826,22 @@
         <v>102800</v>
       </c>
       <c r="D184" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="E184" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="E184" s="17" t="s">
+      <c r="F184" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G184" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="F184" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="G184" s="17" t="s">
-        <v>336</v>
-      </c>
       <c r="H184" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I184" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K184" s="96"/>
     </row>
@@ -8848,22 +8853,22 @@
         <v>102800</v>
       </c>
       <c r="D185" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="E185" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="E185" s="17" t="s">
+      <c r="F185" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G185" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="F185" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="G185" s="17" t="s">
+      <c r="H185" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="I185" s="17" t="s">
         <v>339</v>
-      </c>
-      <c r="H185" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="I185" s="17" t="s">
-        <v>340</v>
       </c>
       <c r="K185" s="96"/>
     </row>
@@ -8878,19 +8883,19 @@
         <v>21</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E186" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F186" s="17" t="s">
         <v>133</v>
       </c>
       <c r="G186" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H186" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I186" s="17" t="s">
         <v>39</v>
@@ -8905,22 +8910,22 @@
         <v>103401</v>
       </c>
       <c r="C187" s="97" t="s">
+        <v>294</v>
+      </c>
+      <c r="D187" s="97" t="s">
+        <v>294</v>
+      </c>
+      <c r="E187" s="97" t="s">
         <v>295</v>
       </c>
-      <c r="D187" s="97" t="s">
-        <v>295</v>
-      </c>
-      <c r="E187" s="97" t="s">
+      <c r="F187" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="G187" s="97" t="s">
         <v>296</v>
       </c>
-      <c r="F187" s="97" t="s">
-        <v>133</v>
-      </c>
-      <c r="G187" s="97" t="s">
-        <v>297</v>
-      </c>
       <c r="I187" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K187" s="98"/>
     </row>
@@ -8932,10 +8937,10 @@
         <v>102000</v>
       </c>
       <c r="C188" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="D188" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="D188" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="E188" s="13" t="s">
         <v>51</v>
@@ -8944,13 +8949,13 @@
         <v>133</v>
       </c>
       <c r="G188" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="H188" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="H188" s="1" t="s">
+      <c r="I188" s="13" t="s">
         <v>345</v>
-      </c>
-      <c r="I188" s="13" t="s">
-        <v>346</v>
       </c>
       <c r="K188" s="92"/>
     </row>
@@ -8962,10 +8967,10 @@
         <v>102000</v>
       </c>
       <c r="C189" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>56</v>
@@ -8974,13 +8979,13 @@
         <v>133</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K189" s="70"/>
     </row>
@@ -8992,10 +8997,10 @@
         <v>102000</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>193</v>
@@ -9004,13 +9009,13 @@
         <v>133</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K190" s="70"/>
     </row>
@@ -9022,10 +9027,10 @@
         <v>102000</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>195</v>
@@ -9034,13 +9039,13 @@
         <v>133</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K191" s="70"/>
     </row>
@@ -9052,10 +9057,10 @@
         <v>102000</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>196</v>
@@ -9064,13 +9069,13 @@
         <v>133</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K192" s="70"/>
     </row>
@@ -9082,22 +9087,22 @@
         <v>102000</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D193" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F193" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G193" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E193" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F193" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="H193" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>120</v>
@@ -9112,22 +9117,22 @@
         <v>102000</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F194" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>120</v>
@@ -9142,22 +9147,22 @@
         <v>102000</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D195" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F195" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G195" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E195" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F195" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="H195" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>39</v>
@@ -9172,22 +9177,22 @@
         <v>102000</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F196" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>39</v>
@@ -9202,22 +9207,22 @@
         <v>102000</v>
       </c>
       <c r="C197" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F197" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G197" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D197" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F197" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="H197" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>39</v>
@@ -9232,19 +9237,19 @@
         <v>102000</v>
       </c>
       <c r="C198" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E198" s="1" t="s">
+      <c r="F198" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G198" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="F198" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>39</v>
@@ -9259,19 +9264,19 @@
         <v>102000</v>
       </c>
       <c r="C199" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F199" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G199" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F199" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>39</v>
@@ -9286,19 +9291,19 @@
         <v>102000</v>
       </c>
       <c r="C200" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F200" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G200" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F200" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>39</v>
@@ -9313,19 +9318,19 @@
         <v>102000</v>
       </c>
       <c r="C201" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F201" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G201" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F201" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>39</v>
@@ -9340,22 +9345,22 @@
         <v>102000</v>
       </c>
       <c r="C202" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D202" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="F202" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>39</v>
@@ -9370,22 +9375,22 @@
         <v>102000</v>
       </c>
       <c r="C203" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D203" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D203" s="6" t="s">
+      <c r="E203" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E203" s="6" t="s">
-        <v>375</v>
-      </c>
       <c r="F203" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G203" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="H203" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="H203" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="I203" s="6" t="s">
         <v>39</v>
@@ -9400,10 +9405,10 @@
         <v>102000</v>
       </c>
       <c r="C204" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D204" s="6" t="s">
         <v>376</v>
-      </c>
-      <c r="D204" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>197</v>
@@ -9412,13 +9417,13 @@
         <v>133</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K204" s="49"/>
     </row>
@@ -9430,25 +9435,25 @@
         <v>102000</v>
       </c>
       <c r="C205" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E205" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="D205" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E205" s="6" t="s">
-        <v>379</v>
-      </c>
       <c r="F205" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G205" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H205" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K205" s="49"/>
     </row>
@@ -9460,10 +9465,10 @@
         <v>102000</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>61</v>
@@ -9472,13 +9477,13 @@
         <v>133</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K206" s="49"/>
     </row>
@@ -9490,25 +9495,25 @@
         <v>102000</v>
       </c>
       <c r="C207" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E207" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="D207" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E207" s="6" t="s">
-        <v>382</v>
-      </c>
       <c r="F207" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H207" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K207" s="49"/>
     </row>
@@ -9520,19 +9525,19 @@
         <v>102000</v>
       </c>
       <c r="C208" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E208" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="D208" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E208" s="6" t="s">
-        <v>384</v>
-      </c>
       <c r="F208" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I208" s="6" t="s">
         <v>39</v>
@@ -9547,19 +9552,19 @@
         <v>102000</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E209" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F209" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G209" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I209" s="6" t="s">
         <v>39</v>
@@ -9574,19 +9579,19 @@
         <v>102000</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F210" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I210" s="6" t="s">
         <v>39</v>
@@ -9601,19 +9606,19 @@
         <v>102000</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F211" s="99" t="s">
         <v>133</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I211" s="6" t="s">
         <v>39</v>
@@ -9628,22 +9633,22 @@
         <v>102000</v>
       </c>
       <c r="C212" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="D212" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="D212" s="19" t="s">
+      <c r="E212" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="E212" s="19" t="s">
-        <v>390</v>
-      </c>
       <c r="F212" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G212" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="H212" s="19" t="s">
         <v>344</v>
-      </c>
-      <c r="H212" s="19" t="s">
-        <v>345</v>
       </c>
       <c r="I212" s="19" t="s">
         <v>39</v>
@@ -9658,10 +9663,10 @@
         <v>102000</v>
       </c>
       <c r="C213" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D213" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E213" s="20" t="s">
         <v>77</v>
@@ -9670,13 +9675,13 @@
         <v>133</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H213" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I213" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K213" s="102"/>
     </row>
@@ -9688,10 +9693,10 @@
         <v>102000</v>
       </c>
       <c r="C214" s="20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D214" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E214" s="20" t="s">
         <v>199</v>
@@ -9700,13 +9705,13 @@
         <v>133</v>
       </c>
       <c r="G214" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H214" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I214" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K214" s="102"/>
     </row>
@@ -9718,25 +9723,25 @@
         <v>102000</v>
       </c>
       <c r="C215" s="20" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D215" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E215" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F215" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H215" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I215" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K215" s="102"/>
     </row>
@@ -9748,25 +9753,25 @@
         <v>102000</v>
       </c>
       <c r="C216" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D216" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E216" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F216" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G216" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H216" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I216" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K216" s="102"/>
     </row>
@@ -9778,19 +9783,19 @@
         <v>102000</v>
       </c>
       <c r="C217" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="D217" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="E217" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="D217" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="E217" s="20" t="s">
-        <v>393</v>
-      </c>
       <c r="F217" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I217" s="20" t="s">
         <v>39</v>
@@ -9805,19 +9810,19 @@
         <v>102000</v>
       </c>
       <c r="C218" s="20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D218" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E218" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F218" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G218" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I218" s="20" t="s">
         <v>39</v>
@@ -9832,19 +9837,19 @@
         <v>102000</v>
       </c>
       <c r="C219" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D219" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E219" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F219" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I219" s="20" t="s">
         <v>39</v>
@@ -9859,19 +9864,19 @@
         <v>102000</v>
       </c>
       <c r="C220" s="20" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D220" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E220" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F220" s="100" t="s">
         <v>133</v>
       </c>
       <c r="G220" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I220" s="20" t="s">
         <v>39</v>
@@ -9886,10 +9891,10 @@
         <v>103800</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D221" s="21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E221" s="21" t="s">
         <v>136</v>
@@ -9901,10 +9906,10 @@
         <v>103</v>
       </c>
       <c r="H221" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="I221" s="21" t="s">
         <v>397</v>
-      </c>
-      <c r="I221" s="21" t="s">
-        <v>398</v>
       </c>
       <c r="K221" s="104"/>
     </row>
@@ -9916,10 +9921,10 @@
         <v>103800</v>
       </c>
       <c r="C222" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="D222" s="21" t="s">
         <v>399</v>
-      </c>
-      <c r="D222" s="21" t="s">
-        <v>400</v>
       </c>
       <c r="E222" s="21" t="s">
         <v>31</v>
@@ -9931,7 +9936,7 @@
         <v>103</v>
       </c>
       <c r="H222" s="21" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I222" s="21" t="s">
         <v>39</v>
@@ -9946,10 +9951,10 @@
         <v>103800</v>
       </c>
       <c r="C223" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="D223" s="21" t="s">
         <v>401</v>
-      </c>
-      <c r="D223" s="21" t="s">
-        <v>402</v>
       </c>
       <c r="E223" s="21" t="s">
         <v>23</v>
@@ -9961,7 +9966,7 @@
         <v>103</v>
       </c>
       <c r="H223" s="21" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I223" s="21" t="s">
         <v>39</v>
@@ -9976,10 +9981,10 @@
         <v>103800</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D224" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E224" s="21" t="s">
         <v>140</v>
@@ -9988,16 +9993,16 @@
         <v>133</v>
       </c>
       <c r="G224" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="H224" s="21" t="s">
         <v>404</v>
       </c>
-      <c r="H224" s="21" t="s">
+      <c r="I224" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="I224" s="21" t="s">
+      <c r="J224" s="21" t="s">
         <v>406</v>
-      </c>
-      <c r="J224" s="21" t="s">
-        <v>407</v>
       </c>
       <c r="K224" s="104" t="s">
         <v>29</v>
@@ -10011,22 +10016,22 @@
         <v>103800</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D225" s="21" t="s">
         <v>21</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F225" s="103" t="s">
         <v>133</v>
       </c>
       <c r="G225" s="21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H225" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I225" s="21" t="s">
         <v>39</v>
@@ -10041,10 +10046,10 @@
         <v>103800</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D226" s="21" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E226" s="21" t="s">
         <v>140</v>
@@ -10053,16 +10058,16 @@
         <v>133</v>
       </c>
       <c r="G226" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="H226" s="21" t="s">
         <v>404</v>
       </c>
-      <c r="H226" s="21" t="s">
-        <v>405</v>
-      </c>
       <c r="I226" s="21" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J226" s="21" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K226" s="104" t="s">
         <v>29</v>
@@ -10076,10 +10081,10 @@
         <v>102700</v>
       </c>
       <c r="C227" s="22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E227" s="22" t="s">
         <v>157</v>
@@ -10088,13 +10093,13 @@
         <v>133</v>
       </c>
       <c r="G227" s="22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H227" s="22">
         <v>10</v>
       </c>
       <c r="I227" s="22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K227" s="105"/>
     </row>
@@ -10106,10 +10111,10 @@
         <v>102700</v>
       </c>
       <c r="C228" s="22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E228" s="22" t="s">
         <v>114</v>
@@ -10118,13 +10123,13 @@
         <v>133</v>
       </c>
       <c r="G228" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H228" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="I228" s="22" t="s">
         <v>413</v>
-      </c>
-      <c r="I228" s="22" t="s">
-        <v>414</v>
       </c>
       <c r="K228" s="105"/>
     </row>
@@ -10136,10 +10141,10 @@
         <v>102700</v>
       </c>
       <c r="C229" s="22" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E229" s="22" t="s">
         <v>114</v>
@@ -10148,10 +10153,10 @@
         <v>133</v>
       </c>
       <c r="G229" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H229" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I229" s="22" t="s">
         <v>72</v>
@@ -10166,10 +10171,10 @@
         <v>102700</v>
       </c>
       <c r="C230" s="22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E230" s="22" t="s">
         <v>114</v>
@@ -10178,13 +10183,13 @@
         <v>133</v>
       </c>
       <c r="G230" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H230" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I230" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K230" s="105"/>
     </row>
@@ -10196,22 +10201,22 @@
         <v>102700</v>
       </c>
       <c r="C231" s="22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E231" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="F231" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G231" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="H231" s="22" t="s">
         <v>416</v>
-      </c>
-      <c r="F231" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G231" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="H231" s="22" t="s">
-        <v>417</v>
       </c>
       <c r="I231" s="22" t="s">
         <v>39</v>
@@ -10226,10 +10231,10 @@
         <v>102700</v>
       </c>
       <c r="C232" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E232" s="22" t="s">
         <v>114</v>
@@ -10238,7 +10243,7 @@
         <v>133</v>
       </c>
       <c r="G232" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H232" s="22">
         <v>9</v>
@@ -10256,25 +10261,25 @@
         <v>103700</v>
       </c>
       <c r="C233" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D233" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="E233" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="D233" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="E233" s="23" t="s">
-        <v>296</v>
-      </c>
       <c r="F233" s="106" t="s">
         <v>133</v>
       </c>
       <c r="G233" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H233" s="23" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I233" s="23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K233" s="107"/>
     </row>
@@ -10286,13 +10291,13 @@
         <v>103700</v>
       </c>
       <c r="C234" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D234" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="E234" s="23" t="s">
         <v>295</v>
-      </c>
-      <c r="D234" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="E234" s="23" t="s">
-        <v>296</v>
       </c>
       <c r="F234" s="106" t="s">
         <v>133</v>
@@ -10301,10 +10306,10 @@
         <v>48</v>
       </c>
       <c r="H234" s="23" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I234" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K234" s="107"/>
     </row>
@@ -10316,16 +10321,16 @@
         <v>103700</v>
       </c>
       <c r="C235" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="E235" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="E235" s="23" t="s">
-        <v>257</v>
-      </c>
       <c r="F235" s="106" t="s">
         <v>133</v>
       </c>
       <c r="G235" s="23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I235" s="23" t="s">
         <v>106</v>
@@ -10340,10 +10345,10 @@
         <v>103100</v>
       </c>
       <c r="C236" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="D236" s="24" t="s">
         <v>421</v>
-      </c>
-      <c r="D236" s="24" t="s">
-        <v>422</v>
       </c>
       <c r="E236" s="24" t="s">
         <v>136</v>
@@ -10352,13 +10357,13 @@
         <v>133</v>
       </c>
       <c r="G236" s="24" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H236" s="24">
         <v>12</v>
       </c>
       <c r="I236" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K236" s="108"/>
     </row>
@@ -10370,10 +10375,10 @@
         <v>103100</v>
       </c>
       <c r="C237" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="D237" s="24" t="s">
         <v>424</v>
-      </c>
-      <c r="D237" s="24" t="s">
-        <v>425</v>
       </c>
       <c r="E237" s="24" t="s">
         <v>23</v>
@@ -10385,7 +10390,7 @@
         <v>174</v>
       </c>
       <c r="H237" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I237" s="24" t="s">
         <v>39</v>
@@ -10400,10 +10405,10 @@
         <v>103100</v>
       </c>
       <c r="C238" s="24" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D238" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E238" s="24" t="s">
         <v>23</v>
@@ -10415,7 +10420,7 @@
         <v>176</v>
       </c>
       <c r="H238" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I238" s="24" t="s">
         <v>39</v>
@@ -10430,10 +10435,10 @@
         <v>103100</v>
       </c>
       <c r="C239" s="24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D239" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E239" s="24" t="s">
         <v>23</v>
@@ -10445,7 +10450,7 @@
         <v>178</v>
       </c>
       <c r="H239" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I239" s="24" t="s">
         <v>39</v>
@@ -10460,10 +10465,10 @@
         <v>103100</v>
       </c>
       <c r="C240" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D240" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E240" s="24" t="s">
         <v>136</v>
@@ -10475,7 +10480,7 @@
         <v>176</v>
       </c>
       <c r="H240" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I240" s="24" t="s">
         <v>107</v>
@@ -10490,10 +10495,10 @@
         <v>103100</v>
       </c>
       <c r="C241" s="24" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D241" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E241" s="24" t="s">
         <v>136</v>
@@ -10502,10 +10507,10 @@
         <v>133</v>
       </c>
       <c r="G241" s="24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H241" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I241" s="24" t="s">
         <v>157</v>
@@ -10520,10 +10525,10 @@
         <v>103100</v>
       </c>
       <c r="C242" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D242" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E242" s="24" t="s">
         <v>140</v>
@@ -10532,13 +10537,13 @@
         <v>133</v>
       </c>
       <c r="G242" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H242" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I242" s="24" t="s">
-        <v>432</v>
+        <v>248</v>
       </c>
       <c r="K242" s="108"/>
     </row>
@@ -10550,7 +10555,7 @@
         <v>103100</v>
       </c>
       <c r="C243" s="24" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D243" s="24" t="s">
         <v>21</v>
@@ -10562,13 +10567,13 @@
         <v>133</v>
       </c>
       <c r="G243" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H243" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I243" s="24" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K243" s="108"/>
     </row>
@@ -10580,10 +10585,10 @@
         <v>103100</v>
       </c>
       <c r="C244" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D244" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E244" s="24" t="s">
         <v>140</v>
@@ -10592,13 +10597,13 @@
         <v>133</v>
       </c>
       <c r="G244" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H244" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I244" s="24" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K244" s="108"/>
     </row>
@@ -10610,7 +10615,7 @@
         <v>103100</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D245" s="24" t="s">
         <v>21</v>
@@ -10622,10 +10627,10 @@
         <v>133</v>
       </c>
       <c r="G245" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H245" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I245" s="24" t="s">
         <v>106</v>
@@ -10640,10 +10645,10 @@
         <v>103100</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D246" s="24" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E246" s="24" t="s">
         <v>143</v>
@@ -10652,13 +10657,13 @@
         <v>133</v>
       </c>
       <c r="G246" s="24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H246" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I246" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K246" s="108"/>
     </row>
@@ -10670,7 +10675,7 @@
         <v>103100</v>
       </c>
       <c r="C247" s="24" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D247" s="24" t="s">
         <v>21</v>
@@ -10682,10 +10687,10 @@
         <v>133</v>
       </c>
       <c r="G247" s="24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H247" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I247" s="24" t="s">
         <v>39</v>
@@ -10700,7 +10705,7 @@
         <v>103100</v>
       </c>
       <c r="C248" s="24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D248" s="24" t="s">
         <v>21</v>
@@ -10712,10 +10717,10 @@
         <v>133</v>
       </c>
       <c r="G248" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H248" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I248" s="24" t="s">
         <v>39</v>
@@ -10730,22 +10735,22 @@
         <v>103100</v>
       </c>
       <c r="C249" s="24" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D249" s="24" t="s">
         <v>21</v>
       </c>
       <c r="E249" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F249" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G249" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H249" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I249" s="24" t="s">
         <v>39</v>
@@ -10760,10 +10765,10 @@
         <v>103100</v>
       </c>
       <c r="C250" s="24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D250" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E250" s="24" t="s">
         <v>143</v>
@@ -10772,10 +10777,10 @@
         <v>133</v>
       </c>
       <c r="G250" s="24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H250" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I250" s="24" t="s">
         <v>138</v>
@@ -10790,10 +10795,10 @@
         <v>103100</v>
       </c>
       <c r="C251" s="24" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D251" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E251" s="24" t="s">
         <v>23</v>
@@ -10802,13 +10807,13 @@
         <v>133</v>
       </c>
       <c r="G251" s="24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H251" s="24" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I251" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K251" s="108"/>
     </row>
@@ -10820,7 +10825,7 @@
         <v>104000</v>
       </c>
       <c r="C252" s="25" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D252" s="25" t="s">
         <v>21</v>
@@ -10832,13 +10837,13 @@
         <v>133</v>
       </c>
       <c r="G252" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H252" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I252" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J252" s="109"/>
     </row>
@@ -10850,10 +10855,10 @@
         <v>104000</v>
       </c>
       <c r="C253" s="25" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D253" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E253" s="25" t="s">
         <v>136</v>
@@ -10862,13 +10867,13 @@
         <v>133</v>
       </c>
       <c r="G253" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H253" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I253" s="25" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K253" s="109"/>
     </row>
@@ -10880,7 +10885,7 @@
         <v>104000</v>
       </c>
       <c r="C254" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D254" s="25" t="s">
         <v>21</v>
@@ -10895,7 +10900,7 @@
         <v>174</v>
       </c>
       <c r="H254" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I254" s="25" t="s">
         <v>39</v>
@@ -10910,7 +10915,7 @@
         <v>104000</v>
       </c>
       <c r="C255" s="25" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D255" s="25" t="s">
         <v>21</v>
@@ -10925,7 +10930,7 @@
         <v>176</v>
       </c>
       <c r="H255" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I255" s="25" t="s">
         <v>39</v>
@@ -10940,7 +10945,7 @@
         <v>104000</v>
       </c>
       <c r="C256" s="25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D256" s="25" t="s">
         <v>21</v>
@@ -10955,7 +10960,7 @@
         <v>178</v>
       </c>
       <c r="H256" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I256" s="25" t="s">
         <v>39</v>
@@ -10970,10 +10975,10 @@
         <v>104000</v>
       </c>
       <c r="C257" s="25" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D257" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E257" s="25" t="s">
         <v>140</v>
@@ -10985,10 +10990,10 @@
         <v>174</v>
       </c>
       <c r="H257" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I257" s="25" t="s">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="K257" s="109"/>
     </row>
@@ -11000,10 +11005,10 @@
         <v>104000</v>
       </c>
       <c r="C258" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D258" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E258" s="25" t="s">
         <v>140</v>
@@ -11015,10 +11020,10 @@
         <v>176</v>
       </c>
       <c r="H258" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I258" s="25" t="s">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="K258" s="109"/>
     </row>
@@ -11030,10 +11035,10 @@
         <v>104000</v>
       </c>
       <c r="C259" s="25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E259" s="25" t="s">
         <v>140</v>
@@ -11045,10 +11050,10 @@
         <v>178</v>
       </c>
       <c r="H259" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I259" s="25" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K259" s="109"/>
     </row>
@@ -11060,22 +11065,22 @@
         <v>104000</v>
       </c>
       <c r="C260" s="25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D260" s="25" t="s">
         <v>21</v>
       </c>
       <c r="E260" s="25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F260" s="25" t="s">
         <v>133</v>
       </c>
       <c r="G260" s="25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H260" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I260" s="25" t="s">
         <v>39</v>
@@ -11090,10 +11095,10 @@
         <v>103900</v>
       </c>
       <c r="C261" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D261" s="26" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E261" s="26" t="s">
         <v>157</v>
@@ -11105,10 +11110,10 @@
         <v>159</v>
       </c>
       <c r="H261" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I261" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K261" s="110"/>
     </row>
@@ -11120,10 +11125,10 @@
         <v>103900</v>
       </c>
       <c r="C262" s="26" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D262" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E262" s="26" t="s">
         <v>157</v>
@@ -11135,7 +11140,7 @@
         <v>159</v>
       </c>
       <c r="H262" s="26" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I262" s="26" t="s">
         <v>39</v>
@@ -11150,7 +11155,7 @@
         <v>103900</v>
       </c>
       <c r="C263" s="26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D263" s="26" t="s">
         <v>21</v>
@@ -11162,13 +11167,13 @@
         <v>133</v>
       </c>
       <c r="G263" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H263" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I263" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K263" s="110"/>
     </row>
@@ -11180,7 +11185,7 @@
         <v>103900</v>
       </c>
       <c r="C264" s="26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D264" s="26" t="s">
         <v>21</v>
@@ -11192,13 +11197,13 @@
         <v>133</v>
       </c>
       <c r="G264" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H264" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I264" s="26" t="s">
-        <v>340</v>
+        <v>413</v>
       </c>
       <c r="K264" s="110"/>
     </row>
@@ -11210,7 +11215,7 @@
         <v>103900</v>
       </c>
       <c r="C265" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D265" s="26" t="s">
         <v>21</v>
@@ -11222,10 +11227,10 @@
         <v>133</v>
       </c>
       <c r="G265" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H265" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I265" s="26" t="s">
         <v>106</v>
@@ -11240,22 +11245,22 @@
         <v>103900</v>
       </c>
       <c r="C266" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D266" s="26" t="s">
         <v>21</v>
       </c>
       <c r="E266" s="26" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F266" s="26" t="s">
         <v>133</v>
       </c>
       <c r="G266" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H266" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I266" s="26" t="s">
         <v>39</v>
@@ -11270,10 +11275,10 @@
         <v>101600</v>
       </c>
       <c r="C267" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D267" s="24" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E267" s="24" t="s">
         <v>140</v>
@@ -11282,13 +11287,13 @@
         <v>133</v>
       </c>
       <c r="G267" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="H267" s="24" t="s">
         <v>458</v>
       </c>
-      <c r="H267" s="24" t="s">
-        <v>459</v>
-      </c>
       <c r="I267" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K267" s="108"/>
     </row>
@@ -11300,7 +11305,7 @@
         <v>101600</v>
       </c>
       <c r="C268" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D268" s="24" t="s">
         <v>21</v>
@@ -11312,13 +11317,13 @@
         <v>133</v>
       </c>
       <c r="G268" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H268" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I268" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K268" s="108"/>
     </row>
@@ -11330,7 +11335,7 @@
         <v>101600</v>
       </c>
       <c r="C269" s="24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D269" s="24" t="s">
         <v>21</v>
@@ -11342,13 +11347,13 @@
         <v>133</v>
       </c>
       <c r="G269" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="H269" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="I269" s="24" t="s">
         <v>460</v>
-      </c>
-      <c r="H269" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="I269" s="24" t="s">
-        <v>327</v>
       </c>
       <c r="K269" s="108"/>
     </row>
@@ -11360,7 +11365,7 @@
         <v>101600</v>
       </c>
       <c r="C270" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D270" s="24" t="s">
         <v>21</v>
@@ -11372,10 +11377,10 @@
         <v>133</v>
       </c>
       <c r="G270" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H270" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I270" s="24" t="s">
         <v>107</v>
@@ -11390,10 +11395,10 @@
         <v>101600</v>
       </c>
       <c r="C271" s="24" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D271" s="24" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E271" s="24" t="s">
         <v>461</v>
@@ -11405,10 +11410,10 @@
         <v>462</v>
       </c>
       <c r="H271" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I271" s="24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K271" s="108"/>
     </row>
@@ -11420,10 +11425,10 @@
         <v>101600</v>
       </c>
       <c r="C272" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D272" s="24" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E272" s="24" t="s">
         <v>463</v>
@@ -11435,10 +11440,10 @@
         <v>464</v>
       </c>
       <c r="H272" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I272" s="24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K272" s="108"/>
     </row>
@@ -11453,7 +11458,7 @@
         <v>465</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E273" s="24" t="s">
         <v>146</v>
@@ -11462,10 +11467,10 @@
         <v>133</v>
       </c>
       <c r="G273" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H273" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I273" s="24" t="s">
         <v>466</v>
@@ -11480,13 +11485,13 @@
         <v>101600</v>
       </c>
       <c r="C274" s="24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D274" s="24" t="s">
         <v>21</v>
       </c>
       <c r="E274" s="24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F274" s="24" t="s">
         <v>133</v>
@@ -11495,7 +11500,7 @@
         <v>467</v>
       </c>
       <c r="H274" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I274" s="24" t="s">
         <v>39</v>
@@ -11513,7 +11518,7 @@
         <v>468</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E275" s="24" t="s">
         <v>469</v>
@@ -11522,7 +11527,7 @@
         <v>133</v>
       </c>
       <c r="G275" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H275" s="24" t="s">
         <v>470</v>
@@ -11543,7 +11548,7 @@
         <v>471</v>
       </c>
       <c r="D276" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E276" s="24" t="s">
         <v>472</v>
@@ -11552,7 +11557,7 @@
         <v>133</v>
       </c>
       <c r="G276" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H276" s="24" t="s">
         <v>473</v>
@@ -11573,7 +11578,7 @@
         <v>474</v>
       </c>
       <c r="D277" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E277" s="24" t="s">
         <v>475</v>
@@ -11582,7 +11587,7 @@
         <v>133</v>
       </c>
       <c r="G277" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H277" s="24" t="s">
         <v>476</v>
@@ -11603,7 +11608,7 @@
         <v>477</v>
       </c>
       <c r="D278" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E278" s="24" t="s">
         <v>478</v>
@@ -11612,7 +11617,7 @@
         <v>133</v>
       </c>
       <c r="G278" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H278" s="24" t="s">
         <v>479</v>
@@ -11633,7 +11638,7 @@
         <v>480</v>
       </c>
       <c r="D279" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E279" s="24" t="s">
         <v>481</v>
@@ -11642,7 +11647,7 @@
         <v>133</v>
       </c>
       <c r="G279" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H279" s="24" t="s">
         <v>482</v>
@@ -11663,7 +11668,7 @@
         <v>483</v>
       </c>
       <c r="D280" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E280" s="24" t="s">
         <v>484</v>
@@ -11672,7 +11677,7 @@
         <v>133</v>
       </c>
       <c r="G280" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H280" s="24" t="s">
         <v>485</v>
@@ -11693,7 +11698,7 @@
         <v>486</v>
       </c>
       <c r="D281" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E281" s="24" t="s">
         <v>487</v>
@@ -11702,7 +11707,7 @@
         <v>133</v>
       </c>
       <c r="G281" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H281" s="24" t="s">
         <v>488</v>
@@ -11723,7 +11728,7 @@
         <v>489</v>
       </c>
       <c r="D282" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E282" s="24" t="s">
         <v>490</v>
@@ -11732,7 +11737,7 @@
         <v>133</v>
       </c>
       <c r="G282" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H282" s="24" t="s">
         <v>491</v>
@@ -11753,7 +11758,7 @@
         <v>492</v>
       </c>
       <c r="D283" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E283" s="24" t="s">
         <v>493</v>
@@ -11762,7 +11767,7 @@
         <v>133</v>
       </c>
       <c r="G283" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H283" s="24" t="s">
         <v>494</v>
@@ -11783,7 +11788,7 @@
         <v>495</v>
       </c>
       <c r="D284" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E284" s="24" t="s">
         <v>496</v>
@@ -11792,7 +11797,7 @@
         <v>133</v>
       </c>
       <c r="G284" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H284" s="24" t="s">
         <v>497</v>
@@ -11813,7 +11818,7 @@
         <v>498</v>
       </c>
       <c r="D285" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E285" s="24" t="s">
         <v>499</v>
@@ -11822,7 +11827,7 @@
         <v>133</v>
       </c>
       <c r="G285" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H285" s="24" t="s">
         <v>500</v>
@@ -11843,7 +11848,7 @@
         <v>501</v>
       </c>
       <c r="D286" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E286" s="26" t="s">
         <v>143</v>
@@ -11852,13 +11857,13 @@
         <v>133</v>
       </c>
       <c r="G286" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H286" s="26" t="s">
         <v>502</v>
       </c>
       <c r="I286" s="26" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K286" s="110"/>
     </row>
@@ -11870,7 +11875,7 @@
         <v>101500</v>
       </c>
       <c r="C287" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D287" s="26" t="s">
         <v>21</v>
@@ -11882,7 +11887,7 @@
         <v>133</v>
       </c>
       <c r="G287" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H287" s="26" t="s">
         <v>502</v>
@@ -11900,7 +11905,7 @@
         <v>101500</v>
       </c>
       <c r="C288" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D288" s="26" t="s">
         <v>21</v>
@@ -11912,7 +11917,7 @@
         <v>133</v>
       </c>
       <c r="G288" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H288" s="26" t="s">
         <v>502</v>
@@ -11930,7 +11935,7 @@
         <v>101500</v>
       </c>
       <c r="C289" s="26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D289" s="26" t="s">
         <v>21</v>
@@ -11942,13 +11947,13 @@
         <v>133</v>
       </c>
       <c r="G289" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H289" s="26" t="s">
         <v>502</v>
       </c>
       <c r="I289" s="26" t="s">
-        <v>432</v>
+        <v>248</v>
       </c>
       <c r="K289" s="110"/>
     </row>
@@ -11963,7 +11968,7 @@
         <v>503</v>
       </c>
       <c r="D290" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E290" s="26" t="s">
         <v>46</v>
@@ -11972,7 +11977,7 @@
         <v>133</v>
       </c>
       <c r="G290" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H290" s="26" t="s">
         <v>502</v>
@@ -11993,7 +11998,7 @@
         <v>504</v>
       </c>
       <c r="D291" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E291" s="26" t="s">
         <v>51</v>
@@ -12002,7 +12007,7 @@
         <v>133</v>
       </c>
       <c r="G291" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H291" s="26" t="s">
         <v>502</v>
@@ -12023,7 +12028,7 @@
         <v>505</v>
       </c>
       <c r="D292" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E292" s="26" t="s">
         <v>56</v>
@@ -12032,7 +12037,7 @@
         <v>133</v>
       </c>
       <c r="G292" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H292" s="26" t="s">
         <v>502</v>
@@ -12050,10 +12055,10 @@
         <v>101500</v>
       </c>
       <c r="C293" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D293" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E293" s="26" t="s">
         <v>506</v>
@@ -12062,7 +12067,7 @@
         <v>133</v>
       </c>
       <c r="G293" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H293" s="26" t="s">
         <v>502</v>
@@ -12083,7 +12088,7 @@
         <v>507</v>
       </c>
       <c r="D294" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E294" s="26" t="s">
         <v>143</v>
@@ -12092,7 +12097,7 @@
         <v>133</v>
       </c>
       <c r="G294" s="26" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H294" s="26" t="s">
         <v>502</v>
@@ -12113,7 +12118,7 @@
         <v>508</v>
       </c>
       <c r="D295" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E295" s="26" t="s">
         <v>143</v>
@@ -12143,7 +12148,7 @@
         <v>509</v>
       </c>
       <c r="D296" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E296" s="26" t="s">
         <v>143</v>
@@ -12173,7 +12178,7 @@
         <v>510</v>
       </c>
       <c r="D297" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E297" s="26" t="s">
         <v>143</v>
@@ -12203,7 +12208,7 @@
         <v>511</v>
       </c>
       <c r="D298" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E298" s="26" t="s">
         <v>143</v>
@@ -12212,7 +12217,7 @@
         <v>133</v>
       </c>
       <c r="G298" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H298" s="26" t="s">
         <v>502</v>
@@ -12392,7 +12397,7 @@
         <v>133</v>
       </c>
       <c r="G304" s="26" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H304" s="26" t="s">
         <v>502</v>
@@ -12542,7 +12547,7 @@
         <v>133</v>
       </c>
       <c r="G309" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H309" s="26" t="s">
         <v>502</v>
@@ -12713,7 +12718,7 @@
         <v>542</v>
       </c>
       <c r="D315" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E315" s="26" t="s">
         <v>67</v>
@@ -12722,7 +12727,7 @@
         <v>133</v>
       </c>
       <c r="G315" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H315" s="26" t="s">
         <v>502</v>
@@ -12743,7 +12748,7 @@
         <v>501</v>
       </c>
       <c r="D316" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E316" s="27" t="s">
         <v>140</v>
@@ -12752,7 +12757,7 @@
         <v>133</v>
       </c>
       <c r="G316" s="27" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H316" s="27" t="s">
         <v>543</v>
@@ -12770,10 +12775,10 @@
         <v>102600</v>
       </c>
       <c r="C317" s="27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D317" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E317" s="27" t="s">
         <v>143</v>
@@ -12788,7 +12793,7 @@
         <v>543</v>
       </c>
       <c r="I317" s="27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K317" s="111"/>
     </row>
@@ -12800,7 +12805,7 @@
         <v>102600</v>
       </c>
       <c r="C318" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D318" s="27" t="s">
         <v>21</v>
@@ -12830,10 +12835,10 @@
         <v>102600</v>
       </c>
       <c r="C319" s="27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D319" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E319" s="27" t="s">
         <v>143</v>
@@ -12848,7 +12853,7 @@
         <v>543</v>
       </c>
       <c r="I319" s="27" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K319" s="111"/>
     </row>
@@ -12860,13 +12865,13 @@
         <v>102600</v>
       </c>
       <c r="C320" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="D320" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="E320" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="D320" s="27" t="s">
-        <v>438</v>
-      </c>
-      <c r="E320" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="F320" s="27" t="s">
         <v>133</v>
@@ -12878,7 +12883,7 @@
         <v>543</v>
       </c>
       <c r="I320" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K320" s="111"/>
     </row>
@@ -12890,13 +12895,13 @@
         <v>102600</v>
       </c>
       <c r="C321" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="D321" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="E321" s="27" t="s">
         <v>334</v>
-      </c>
-      <c r="D321" s="27" t="s">
-        <v>438</v>
-      </c>
-      <c r="E321" s="27" t="s">
-        <v>335</v>
       </c>
       <c r="F321" s="27" t="s">
         <v>133</v>
@@ -12908,7 +12913,7 @@
         <v>543</v>
       </c>
       <c r="I321" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K321" s="111"/>
     </row>
@@ -12920,13 +12925,13 @@
         <v>102600</v>
       </c>
       <c r="C322" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="D322" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="E322" s="27" t="s">
         <v>337</v>
-      </c>
-      <c r="D322" s="27" t="s">
-        <v>438</v>
-      </c>
-      <c r="E322" s="27" t="s">
-        <v>338</v>
       </c>
       <c r="F322" s="27" t="s">
         <v>133</v>
@@ -12938,7 +12943,7 @@
         <v>543</v>
       </c>
       <c r="I322" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K322" s="111"/>
     </row>
@@ -12950,13 +12955,13 @@
         <v>102600</v>
       </c>
       <c r="C323" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D323" s="27" t="s">
         <v>21</v>
       </c>
       <c r="E323" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F323" s="27" t="s">
         <v>133</v>
@@ -12980,10 +12985,10 @@
         <v>102600</v>
       </c>
       <c r="C324" s="27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E324" s="27" t="s">
         <v>143</v>
@@ -12998,7 +13003,7 @@
         <v>543</v>
       </c>
       <c r="I324" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K324" s="111"/>
     </row>
@@ -13010,13 +13015,13 @@
         <v>102600</v>
       </c>
       <c r="C325" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="D325" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E325" s="27" t="s">
         <v>256</v>
-      </c>
-      <c r="D325" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E325" s="27" t="s">
-        <v>257</v>
       </c>
       <c r="F325" s="27" t="s">
         <v>133</v>
@@ -13040,7 +13045,7 @@
         <v>551</v>
       </c>
       <c r="D326" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E326" s="20" t="s">
         <v>140</v>
@@ -13049,7 +13054,7 @@
         <v>133</v>
       </c>
       <c r="G326" s="20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H326" s="20" t="s">
         <v>552</v>
@@ -13069,7 +13074,7 @@
         <v>553</v>
       </c>
       <c r="D327" s="20" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E327" s="20" t="s">
         <v>143</v>
@@ -13084,7 +13089,7 @@
         <v>552</v>
       </c>
       <c r="I327" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="328" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13098,7 +13103,7 @@
         <v>555</v>
       </c>
       <c r="D328" s="20" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E328" s="20" t="s">
         <v>143</v>
@@ -13127,7 +13132,7 @@
         <v>557</v>
       </c>
       <c r="D329" s="20" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E329" s="20" t="s">
         <v>143</v>
@@ -13142,7 +13147,7 @@
         <v>552</v>
       </c>
       <c r="I329" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="330" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13153,10 +13158,10 @@
         <v>105000</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D330" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E330" s="20" t="s">
         <v>558</v>
@@ -13171,7 +13176,7 @@
         <v>552</v>
       </c>
       <c r="I330" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="331" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13182,10 +13187,10 @@
         <v>105000</v>
       </c>
       <c r="C331" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D331" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E331" s="20" t="s">
         <v>560</v>
@@ -13200,7 +13205,7 @@
         <v>552</v>
       </c>
       <c r="I331" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="332" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13211,10 +13216,10 @@
         <v>105000</v>
       </c>
       <c r="C332" s="20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D332" s="20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E332" s="20" t="s">
         <v>562</v>
@@ -13229,7 +13234,7 @@
         <v>552</v>
       </c>
       <c r="I332" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="333" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13240,13 +13245,13 @@
         <v>105000</v>
       </c>
       <c r="C333" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D333" s="20" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E333" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F333" s="20" t="s">
         <v>133</v>
@@ -13269,7 +13274,7 @@
         <v>105000</v>
       </c>
       <c r="C334" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D334" s="20" t="s">
         <v>565</v>
@@ -13287,7 +13292,7 @@
         <v>552</v>
       </c>
       <c r="I334" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="335" s="20" customFormat="1" ht="16.5" spans="1:11">
@@ -13298,13 +13303,13 @@
         <v>105000</v>
       </c>
       <c r="C335" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D335" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="E335" s="20" t="s">
         <v>256</v>
-      </c>
-      <c r="D335" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="E335" s="20" t="s">
-        <v>257</v>
       </c>
       <c r="F335" s="20" t="s">
         <v>133</v>
@@ -13366,7 +13371,7 @@
         <v>133</v>
       </c>
       <c r="G337" s="33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H337" s="33" t="s">
         <v>568</v>
@@ -13396,7 +13401,7 @@
         <v>133</v>
       </c>
       <c r="G338" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H338" s="33" t="s">
         <v>568</v>
@@ -13456,7 +13461,7 @@
         <v>133</v>
       </c>
       <c r="G340" s="33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H340" s="33" t="s">
         <v>568</v>
@@ -13486,7 +13491,7 @@
         <v>133</v>
       </c>
       <c r="G341" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H341" s="33" t="s">
         <v>568</v>
@@ -13546,7 +13551,7 @@
         <v>133</v>
       </c>
       <c r="G343" s="33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H343" s="33" t="s">
         <v>568</v>
@@ -13576,7 +13581,7 @@
         <v>133</v>
       </c>
       <c r="G344" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H344" s="33" t="s">
         <v>568</v>
@@ -13594,10 +13599,10 @@
         <v>105400</v>
       </c>
       <c r="C345" s="27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D345" s="27" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E345" s="27" t="s">
         <v>140</v>
@@ -13612,7 +13617,7 @@
         <v>580</v>
       </c>
       <c r="I345" s="27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="346" s="27" customFormat="1" ht="16.5" spans="1:11">
@@ -13623,10 +13628,10 @@
         <v>105400</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E346" s="27" t="s">
         <v>140</v>
@@ -13652,10 +13657,10 @@
         <v>105400</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E347" s="27" t="s">
         <v>140</v>
@@ -13670,7 +13675,7 @@
         <v>580</v>
       </c>
       <c r="I347" s="27" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="348" s="27" customFormat="1" ht="16.5" spans="1:11">
@@ -13684,7 +13689,7 @@
         <v>581</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E348" s="27" t="s">
         <v>582</v>
@@ -13699,7 +13704,7 @@
         <v>580</v>
       </c>
       <c r="I348" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="349" s="27" customFormat="1" ht="16.5" spans="1:11">
@@ -13710,10 +13715,10 @@
         <v>105400</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D349" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E349" s="27" t="s">
         <v>584</v>
@@ -13728,7 +13733,7 @@
         <v>580</v>
       </c>
       <c r="I349" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="350" s="27" customFormat="1" ht="16.5" spans="1:11">
@@ -13739,10 +13744,10 @@
         <v>105400</v>
       </c>
       <c r="C350" s="27" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D350" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E350" s="27" t="s">
         <v>585</v>
@@ -13757,7 +13762,7 @@
         <v>580</v>
       </c>
       <c r="I350" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="351" s="27" customFormat="1" ht="16.5" spans="1:11">
@@ -13768,10 +13773,10 @@
         <v>105400</v>
       </c>
       <c r="C351" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E351" s="27" t="s">
         <v>586</v>
@@ -13786,7 +13791,7 @@
         <v>580</v>
       </c>
       <c r="I351" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="352" s="27" customFormat="1" ht="16.5" spans="1:11">
@@ -13797,13 +13802,13 @@
         <v>105400</v>
       </c>
       <c r="C352" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E352" s="27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F352" s="27" t="s">
         <v>133</v>
@@ -13826,7 +13831,7 @@
         <v>105400</v>
       </c>
       <c r="C353" s="27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D353" s="27" t="s">
         <v>565</v>
@@ -13844,7 +13849,7 @@
         <v>580</v>
       </c>
       <c r="I353" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="354" s="27" customFormat="1" ht="16.5" spans="1:12">
@@ -13855,13 +13860,13 @@
         <v>105400</v>
       </c>
       <c r="C354" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="D354" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E354" s="27" t="s">
         <v>256</v>
-      </c>
-      <c r="D354" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="E354" s="27" t="s">
-        <v>257</v>
       </c>
       <c r="F354" s="27" t="s">
         <v>133</v>
@@ -13884,7 +13889,7 @@
         <v>501</v>
       </c>
       <c r="D355" s="28" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E355" s="28" t="s">
         <v>140</v>
@@ -13893,7 +13898,7 @@
         <v>133</v>
       </c>
       <c r="G355" s="28" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H355" s="28" t="s">
         <v>588</v>
@@ -13911,10 +13916,10 @@
         <v>100800</v>
       </c>
       <c r="C356" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D356" s="28" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E356" s="28" t="s">
         <v>143</v>
@@ -13926,7 +13931,7 @@
         <v>545</v>
       </c>
       <c r="I356" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K356" s="112"/>
     </row>
@@ -13938,7 +13943,7 @@
         <v>100800</v>
       </c>
       <c r="C357" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D357" s="28" t="s">
         <v>21</v>
@@ -13968,10 +13973,10 @@
         <v>100800</v>
       </c>
       <c r="C358" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D358" s="28" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E358" s="28" t="s">
         <v>143</v>
@@ -13986,7 +13991,7 @@
         <v>588</v>
       </c>
       <c r="I358" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K358" s="112"/>
     </row>
@@ -13998,10 +14003,10 @@
         <v>100800</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D359" s="28" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E359" s="28" t="s">
         <v>589</v>
@@ -14016,7 +14021,7 @@
         <v>588</v>
       </c>
       <c r="I359" s="28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K359" s="112"/>
     </row>
@@ -14028,10 +14033,10 @@
         <v>100800</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D360" s="28" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E360" s="28" t="s">
         <v>590</v>
@@ -14046,7 +14051,7 @@
         <v>588</v>
       </c>
       <c r="I360" s="28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K360" s="112"/>
     </row>
@@ -14058,10 +14063,10 @@
         <v>100800</v>
       </c>
       <c r="C361" s="28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D361" s="28" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E361" s="28" t="s">
         <v>591</v>
@@ -14076,7 +14081,7 @@
         <v>588</v>
       </c>
       <c r="I361" s="28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K361" s="112"/>
     </row>
@@ -14088,7 +14093,7 @@
         <v>100800</v>
       </c>
       <c r="C362" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D362" s="28" t="s">
         <v>21</v>
@@ -14100,7 +14105,7 @@
         <v>133</v>
       </c>
       <c r="G362" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H362" s="28" t="s">
         <v>593</v>
@@ -14118,10 +14123,10 @@
         <v>100800</v>
       </c>
       <c r="C363" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D363" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E363" s="28" t="s">
         <v>143</v>
@@ -14136,7 +14141,7 @@
         <v>588</v>
       </c>
       <c r="I363" s="28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K363" s="112"/>
     </row>
@@ -14148,13 +14153,13 @@
         <v>100800</v>
       </c>
       <c r="C364" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="D364" s="28" t="s">
+        <v>421</v>
+      </c>
+      <c r="E364" s="28" t="s">
         <v>256</v>
-      </c>
-      <c r="D364" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="E364" s="28" t="s">
-        <v>257</v>
       </c>
       <c r="F364" s="28" t="s">
         <v>133</v>
@@ -14196,7 +14201,7 @@
         <v>596</v>
       </c>
       <c r="I365" s="29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K365" s="113"/>
     </row>
@@ -14271,7 +14276,7 @@
         <v>601</v>
       </c>
       <c r="D368" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E368" s="29" t="s">
         <v>602</v>
@@ -14286,7 +14291,7 @@
         <v>596</v>
       </c>
       <c r="I368" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K368" s="113"/>
     </row>
@@ -14301,7 +14306,7 @@
         <v>604</v>
       </c>
       <c r="D369" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E369" s="29" t="s">
         <v>602</v>
@@ -14310,7 +14315,7 @@
         <v>133</v>
       </c>
       <c r="G369" s="29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H369" s="29" t="s">
         <v>605</v>
@@ -14328,10 +14333,10 @@
         <v>105700</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D370" s="30" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E370" s="30" t="s">
         <v>114</v>
@@ -14358,10 +14363,10 @@
         <v>105700</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D371" s="30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E371" s="30" t="s">
         <v>114</v>
@@ -14391,7 +14396,7 @@
         <v>608</v>
       </c>
       <c r="D372" s="30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E372" s="30" t="s">
         <v>114</v>
@@ -14406,7 +14411,7 @@
         <v>607</v>
       </c>
       <c r="I372" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K372" s="114"/>
     </row>
@@ -14421,7 +14426,7 @@
         <v>609</v>
       </c>
       <c r="D373" s="30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E373" s="30" t="s">
         <v>610</v>
@@ -14436,7 +14441,7 @@
         <v>607</v>
       </c>
       <c r="I373" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K373" s="114"/>
     </row>
@@ -14448,7 +14453,7 @@
         <v>105700</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D374" s="30" t="s">
         <v>21</v>
@@ -14463,7 +14468,7 @@
         <v>613</v>
       </c>
       <c r="H374" s="30" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I374" s="30" t="s">
         <v>39</v>
@@ -14478,13 +14483,13 @@
         <v>105700</v>
       </c>
       <c r="C375" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="D375" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="E375" s="30" t="s">
         <v>256</v>
-      </c>
-      <c r="D375" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="E375" s="30" t="s">
-        <v>257</v>
       </c>
       <c r="F375" s="30" t="s">
         <v>133</v>
@@ -14505,13 +14510,13 @@
         <v>105800</v>
       </c>
       <c r="C376" s="31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D376" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E376" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F376" s="31" t="s">
         <v>133</v>
@@ -14535,13 +14540,13 @@
         <v>105800</v>
       </c>
       <c r="C377" s="31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D377" s="31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E377" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F377" s="31" t="s">
         <v>133</v>
@@ -14568,10 +14573,10 @@
         <v>608</v>
       </c>
       <c r="D378" s="31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E378" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F378" s="31" t="s">
         <v>133</v>
@@ -14583,7 +14588,7 @@
         <v>616</v>
       </c>
       <c r="I378" s="31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K378" s="115"/>
     </row>
@@ -14595,10 +14600,10 @@
         <v>105800</v>
       </c>
       <c r="C379" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D379" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E379" s="31" t="s">
         <v>157</v>
@@ -14625,7 +14630,7 @@
         <v>105500</v>
       </c>
       <c r="C380" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D380" s="32" t="s">
         <v>21</v>
@@ -14658,16 +14663,16 @@
         <v>21</v>
       </c>
       <c r="E381" s="32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F381" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G381" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I381" s="32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K381" s="116"/>
     </row>
@@ -14682,7 +14687,7 @@
         <v>501</v>
       </c>
       <c r="D382" s="33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E382" s="33" t="s">
         <v>140</v>
@@ -14712,7 +14717,7 @@
         <v>622</v>
       </c>
       <c r="D383" s="33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E383" s="33" t="s">
         <v>143</v>
@@ -14721,13 +14726,13 @@
         <v>133</v>
       </c>
       <c r="G383" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H383" s="33" t="s">
         <v>621</v>
       </c>
       <c r="I383" s="33" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K383" s="82"/>
     </row>
@@ -14742,7 +14747,7 @@
         <v>623</v>
       </c>
       <c r="D384" s="33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E384" s="33" t="s">
         <v>143</v>
@@ -14751,13 +14756,13 @@
         <v>133</v>
       </c>
       <c r="G384" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H384" s="33" t="s">
         <v>621</v>
       </c>
       <c r="I384" s="33" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K384" s="82"/>
     </row>
@@ -14781,7 +14786,7 @@
         <v>133</v>
       </c>
       <c r="G385" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H385" s="33" t="s">
         <v>621</v>
@@ -14799,10 +14804,10 @@
         <v>104800</v>
       </c>
       <c r="C386" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D386" s="33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E386" s="33" t="s">
         <v>143</v>
@@ -14811,13 +14816,13 @@
         <v>133</v>
       </c>
       <c r="G386" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H386" s="33" t="s">
         <v>621</v>
       </c>
       <c r="I386" s="33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K386" s="82"/>
     </row>
@@ -14829,10 +14834,10 @@
         <v>104800</v>
       </c>
       <c r="C387" s="33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D387" s="33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E387" s="33" t="s">
         <v>625</v>
@@ -14847,7 +14852,7 @@
         <v>621</v>
       </c>
       <c r="I387" s="33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K387" s="117"/>
     </row>
@@ -14859,10 +14864,10 @@
         <v>104800</v>
       </c>
       <c r="C388" s="33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D388" s="33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E388" s="33" t="s">
         <v>626</v>
@@ -14877,7 +14882,7 @@
         <v>621</v>
       </c>
       <c r="I388" s="33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K388" s="117"/>
     </row>
@@ -14889,13 +14894,13 @@
         <v>104800</v>
       </c>
       <c r="C389" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D389" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E389" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F389" s="33" t="s">
         <v>133</v>
@@ -14904,7 +14909,7 @@
         <v>467</v>
       </c>
       <c r="H389" s="33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I389" s="33" t="s">
         <v>39</v>
@@ -14919,7 +14924,7 @@
         <v>105501</v>
       </c>
       <c r="C390" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D390" s="32" t="s">
         <v>21</v>
@@ -14952,16 +14957,16 @@
         <v>21</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F391" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G391" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I391" s="32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K391" s="116"/>
     </row>
@@ -15000,7 +15005,7 @@
         <v>105502</v>
       </c>
       <c r="C393" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D393" s="32" t="s">
         <v>21</v>
@@ -15033,16 +15038,16 @@
         <v>21</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F394" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G394" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I394" s="32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K394" s="116"/>
     </row>
@@ -15060,13 +15065,13 @@
         <v>21</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F395" s="32" t="s">
         <v>133</v>
       </c>
       <c r="G395" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I395" s="32" t="s">
         <v>39</v>
@@ -15080,10 +15085,10 @@
         <v>104100</v>
       </c>
       <c r="C396" s="34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D396" s="34" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E396" s="34" t="s">
         <v>157</v>
@@ -15095,7 +15100,7 @@
         <v>159</v>
       </c>
       <c r="H396" s="34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I396" s="34" t="s">
         <v>544</v>
@@ -15113,7 +15118,7 @@
         <v>555</v>
       </c>
       <c r="D397" s="34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E397" s="34" t="s">
         <v>114</v>
@@ -15122,10 +15127,10 @@
         <v>133</v>
       </c>
       <c r="G397" s="34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H397" s="34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I397" s="34" t="s">
         <v>107</v>
@@ -15140,10 +15145,10 @@
         <v>104100</v>
       </c>
       <c r="C398" s="34" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D398" s="34" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E398" s="34" t="s">
         <v>114</v>
@@ -15152,13 +15157,13 @@
         <v>133</v>
       </c>
       <c r="G398" s="34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H398" s="34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I398" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K398" s="118"/>
     </row>
@@ -15170,19 +15175,19 @@
         <v>104100</v>
       </c>
       <c r="C399" s="34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D399" s="34" t="s">
         <v>21</v>
       </c>
       <c r="E399" s="34" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F399" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G399" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H399" s="34" t="s">
         <v>629</v>
@@ -15200,10 +15205,10 @@
         <v>104100</v>
       </c>
       <c r="C400" s="34" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D400" s="34" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E400" s="34" t="s">
         <v>114</v>
@@ -15212,13 +15217,13 @@
         <v>133</v>
       </c>
       <c r="G400" s="34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H400" s="34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I400" s="34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K400" s="118"/>
     </row>
@@ -15230,10 +15235,10 @@
         <v>104200</v>
       </c>
       <c r="C401" s="35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D401" s="35" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E401" s="35" t="s">
         <v>140</v>
@@ -15242,7 +15247,7 @@
         <v>133</v>
       </c>
       <c r="G401" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H401" s="35" t="s">
         <v>549</v>
@@ -15263,7 +15268,7 @@
         <v>555</v>
       </c>
       <c r="D402" s="35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E402" s="35" t="s">
         <v>143</v>
@@ -15272,7 +15277,7 @@
         <v>133</v>
       </c>
       <c r="G402" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H402" s="35" t="s">
         <v>549</v>
@@ -15290,10 +15295,10 @@
         <v>104200</v>
       </c>
       <c r="C403" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D403" s="35" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E403" s="35" t="s">
         <v>143</v>
@@ -15302,13 +15307,13 @@
         <v>133</v>
       </c>
       <c r="G403" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H403" s="35" t="s">
         <v>549</v>
       </c>
       <c r="I403" s="35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K403" s="119"/>
     </row>
@@ -15320,19 +15325,19 @@
         <v>104200</v>
       </c>
       <c r="C404" s="35" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D404" s="35" t="s">
         <v>21</v>
       </c>
       <c r="E404" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F404" s="35" t="s">
         <v>133</v>
       </c>
       <c r="G404" s="35" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H404" s="35" t="s">
         <v>593</v>
@@ -15350,10 +15355,10 @@
         <v>104200</v>
       </c>
       <c r="C405" s="35" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D405" s="35" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E405" s="35" t="s">
         <v>143</v>
@@ -15362,13 +15367,13 @@
         <v>133</v>
       </c>
       <c r="G405" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H405" s="35" t="s">
         <v>549</v>
       </c>
       <c r="I405" s="35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K405" s="119"/>
     </row>
